--- a/inputs/template_en.xlsx
+++ b/inputs/template_en.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="5100" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Economic instruments" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Instruments overview" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Regulatory instruments" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Government I&amp;C" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Information instruments" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Voluntary approaches" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Summary" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Cover" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Classification framework" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Categories and groups" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Attributes definitions" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Ended" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Economic instruments" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instruments overview" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory instruments" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Government I&amp;C" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information instruments" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voluntary approaches" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification framework" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories and groups" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attributes definitions" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ended" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="162913" fullCalcOnLoad="1"/>
@@ -639,7 +639,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="74">
+  <borders count="79">
     <border>
       <left/>
       <right/>
@@ -1466,16 +1466,16 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1483,46 +1483,95 @@
       <left/>
       <right/>
       <top style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </right>
       <top style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </top>
       <bottom style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </left>
       <right style="thin">
-        <color auto="Values must be of type &lt;class 'bool'&gt;"/>
+        <color auto="1"/>
       </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top/>
       <bottom/>
       <diagonal/>
@@ -11019,7 +11068,7 @@
       </c>
       <c r="N39" s="225" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Total number of approaches</t>
         </is>
       </c>
     </row>
@@ -16913,8 +16962,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A3:B3"/>
     <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/inputs/template_en.xlsx
+++ b/inputs/template_en.xlsx
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="73">
+  <fonts count="89">
     <font>
       <name val="等线"/>
       <family val="2"/>
@@ -513,6 +513,113 @@
       <color rgb="FFFFFFFF"/>
       <sz val="12"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <color rgb="FF0E5C46"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <family val="2"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <family val="3"/>
+      <color rgb="FF1F2329"/>
+      <sz val="12"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <color rgb="FF0E5C46"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <family val="2"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <b val="1"/>
+      <color rgb="FF0E5C46"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <family val="2"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="46">
     <fill>
@@ -774,7 +881,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="82">
+  <borders count="90">
     <border>
       <left/>
       <right/>
@@ -1746,11 +1853,103 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FFDEE0E3"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDEE0E3"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="463">
+  <cellXfs count="530">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3018,6 +3217,163 @@
     <xf numFmtId="0" fontId="72" fillId="29" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="60" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="44" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="73" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="74" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="19" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="75" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="66" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="28" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="28" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="72" fillId="29" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="30" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="31" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="32" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="33" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="34" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="38" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="78" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="76" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="77" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="79" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="70" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="19" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="80" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="41" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="19" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="82" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="81" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="19" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="86" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="83" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="85" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="86" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="87" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -3372,60 +3728,60 @@
   </cols>
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
-      <c r="A1" s="203" t="inlineStr">
+      <c r="A1" s="463" t="inlineStr">
         <is>
           <t>Summary statistics</t>
         </is>
       </c>
-      <c r="B1" s="204" t="n"/>
-      <c r="C1" s="205" t="n"/>
-      <c r="D1" s="205" t="n"/>
-      <c r="E1" s="205" t="n"/>
-      <c r="F1" s="205" t="n"/>
-      <c r="G1" s="205" t="n"/>
-      <c r="H1" s="205" t="n"/>
-      <c r="I1" s="205" t="n"/>
-      <c r="J1" s="205" t="n"/>
-      <c r="K1" s="205" t="n"/>
-      <c r="L1" s="205" t="n"/>
-      <c r="M1" s="205" t="n"/>
-      <c r="N1" s="205" t="n"/>
+      <c r="B1" s="208" t="n"/>
+      <c r="C1" s="464" t="n"/>
+      <c r="D1" s="464" t="n"/>
+      <c r="E1" s="464" t="n"/>
+      <c r="F1" s="464" t="n"/>
+      <c r="G1" s="464" t="n"/>
+      <c r="H1" s="464" t="n"/>
+      <c r="I1" s="464" t="n"/>
+      <c r="J1" s="464" t="n"/>
+      <c r="K1" s="464" t="n"/>
+      <c r="L1" s="464" t="n"/>
+      <c r="M1" s="464" t="n"/>
+      <c r="N1" s="464" t="n"/>
     </row>
     <row r="2" ht="14.25" customHeight="1">
-      <c r="A2" s="204" t="n"/>
-      <c r="B2" s="204" t="n"/>
-      <c r="C2" s="205" t="n"/>
-      <c r="D2" s="205" t="n"/>
-      <c r="E2" s="205" t="n"/>
-      <c r="F2" s="205" t="n"/>
-      <c r="G2" s="205" t="n"/>
-      <c r="H2" s="205" t="n"/>
-      <c r="I2" s="205" t="n"/>
-      <c r="J2" s="205" t="n"/>
-      <c r="K2" s="205" t="n"/>
-      <c r="L2" s="205" t="n"/>
-      <c r="M2" s="205" t="n"/>
-      <c r="N2" s="205" t="n"/>
+      <c r="A2" s="208" t="n"/>
+      <c r="B2" s="208" t="n"/>
+      <c r="C2" s="464" t="n"/>
+      <c r="D2" s="464" t="n"/>
+      <c r="E2" s="464" t="n"/>
+      <c r="F2" s="464" t="n"/>
+      <c r="G2" s="464" t="n"/>
+      <c r="H2" s="464" t="n"/>
+      <c r="I2" s="464" t="n"/>
+      <c r="J2" s="464" t="n"/>
+      <c r="K2" s="464" t="n"/>
+      <c r="L2" s="464" t="n"/>
+      <c r="M2" s="464" t="n"/>
+      <c r="N2" s="464" t="n"/>
     </row>
     <row r="3" ht="16.5" customHeight="1">
-      <c r="A3" s="206" t="inlineStr">
+      <c r="A3" s="463" t="inlineStr">
         <is>
           <t>Scope of this dataset</t>
         </is>
       </c>
-      <c r="B3" s="204" t="n"/>
-      <c r="C3" s="205" t="n"/>
-      <c r="D3" s="205" t="n"/>
-      <c r="E3" s="205" t="n"/>
-      <c r="F3" s="205" t="n"/>
-      <c r="G3" s="205" t="n"/>
-      <c r="H3" s="205" t="n"/>
-      <c r="I3" s="205" t="n"/>
-      <c r="J3" s="205" t="n"/>
-      <c r="K3" s="205" t="n"/>
-      <c r="L3" s="205" t="n"/>
-      <c r="M3" s="205" t="n"/>
-      <c r="N3" s="205" t="n"/>
+      <c r="B3" s="208" t="n"/>
+      <c r="C3" s="464" t="n"/>
+      <c r="D3" s="464" t="n"/>
+      <c r="E3" s="464" t="n"/>
+      <c r="F3" s="464" t="n"/>
+      <c r="G3" s="464" t="n"/>
+      <c r="H3" s="464" t="n"/>
+      <c r="I3" s="464" t="n"/>
+      <c r="J3" s="464" t="n"/>
+      <c r="K3" s="464" t="n"/>
+      <c r="L3" s="464" t="n"/>
+      <c r="M3" s="464" t="n"/>
+      <c r="N3" s="464" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="207" t="inlineStr">
@@ -3437,18 +3793,18 @@
         <f>COUNTA(Approaches!C:C)-1</f>
         <v/>
       </c>
-      <c r="C4" s="205" t="n"/>
-      <c r="D4" s="205" t="n"/>
-      <c r="E4" s="205" t="n"/>
-      <c r="F4" s="205" t="n"/>
-      <c r="G4" s="205" t="n"/>
-      <c r="H4" s="205" t="n"/>
-      <c r="I4" s="205" t="n"/>
-      <c r="J4" s="205" t="n"/>
-      <c r="K4" s="205" t="n"/>
-      <c r="L4" s="205" t="n"/>
-      <c r="M4" s="205" t="n"/>
-      <c r="N4" s="205" t="n"/>
+      <c r="C4" s="464" t="n"/>
+      <c r="D4" s="464" t="n"/>
+      <c r="E4" s="464" t="n"/>
+      <c r="F4" s="464" t="n"/>
+      <c r="G4" s="464" t="n"/>
+      <c r="H4" s="464" t="n"/>
+      <c r="I4" s="464" t="n"/>
+      <c r="J4" s="464" t="n"/>
+      <c r="K4" s="464" t="n"/>
+      <c r="L4" s="464" t="n"/>
+      <c r="M4" s="464" t="n"/>
+      <c r="N4" s="464" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="207" t="inlineStr">
@@ -3460,18 +3816,18 @@
         <f>COUNTA('Instruments overview'!A:A)-2</f>
         <v/>
       </c>
-      <c r="C5" s="205" t="n"/>
-      <c r="D5" s="205" t="n"/>
-      <c r="E5" s="205" t="n"/>
-      <c r="F5" s="205" t="n"/>
-      <c r="G5" s="205" t="n"/>
-      <c r="H5" s="205" t="n"/>
-      <c r="I5" s="205" t="n"/>
-      <c r="J5" s="205" t="n"/>
-      <c r="K5" s="205" t="n"/>
-      <c r="L5" s="205" t="n"/>
-      <c r="M5" s="205" t="n"/>
-      <c r="N5" s="205" t="n"/>
+      <c r="C5" s="464" t="n"/>
+      <c r="D5" s="464" t="n"/>
+      <c r="E5" s="464" t="n"/>
+      <c r="F5" s="464" t="n"/>
+      <c r="G5" s="464" t="n"/>
+      <c r="H5" s="464" t="n"/>
+      <c r="I5" s="464" t="n"/>
+      <c r="J5" s="464" t="n"/>
+      <c r="K5" s="464" t="n"/>
+      <c r="L5" s="464" t="n"/>
+      <c r="M5" s="464" t="n"/>
+      <c r="N5" s="464" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="207" t="inlineStr">
@@ -3484,50 +3840,50 @@
           <t>Energy, transport, buildings, industry, AFOLU, waste</t>
         </is>
       </c>
-      <c r="C6" s="205" t="n"/>
-      <c r="D6" s="205" t="n"/>
-      <c r="E6" s="205" t="n"/>
-      <c r="F6" s="205" t="n"/>
-      <c r="G6" s="205" t="n"/>
-      <c r="H6" s="205" t="n"/>
-      <c r="I6" s="205" t="n"/>
-      <c r="J6" s="205" t="n"/>
-      <c r="K6" s="205" t="n"/>
-      <c r="L6" s="205" t="n"/>
-      <c r="M6" s="205" t="n"/>
-      <c r="N6" s="205" t="n"/>
+      <c r="C6" s="464" t="n"/>
+      <c r="D6" s="464" t="n"/>
+      <c r="E6" s="464" t="n"/>
+      <c r="F6" s="464" t="n"/>
+      <c r="G6" s="464" t="n"/>
+      <c r="H6" s="464" t="n"/>
+      <c r="I6" s="464" t="n"/>
+      <c r="J6" s="464" t="n"/>
+      <c r="K6" s="464" t="n"/>
+      <c r="L6" s="464" t="n"/>
+      <c r="M6" s="464" t="n"/>
+      <c r="N6" s="464" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
-      <c r="A7" s="205" t="n"/>
-      <c r="B7" s="205" t="n"/>
-      <c r="C7" s="205" t="n"/>
-      <c r="D7" s="205" t="n"/>
-      <c r="E7" s="205" t="n"/>
-      <c r="F7" s="205" t="n"/>
-      <c r="G7" s="205" t="n"/>
-      <c r="H7" s="205" t="n"/>
-      <c r="I7" s="205" t="n"/>
-      <c r="J7" s="205" t="n"/>
-      <c r="K7" s="205" t="n"/>
-      <c r="L7" s="205" t="n"/>
-      <c r="M7" s="205" t="n"/>
-      <c r="N7" s="205" t="n"/>
+      <c r="A7" s="464" t="n"/>
+      <c r="B7" s="464" t="n"/>
+      <c r="C7" s="464" t="n"/>
+      <c r="D7" s="464" t="n"/>
+      <c r="E7" s="464" t="n"/>
+      <c r="F7" s="464" t="n"/>
+      <c r="G7" s="464" t="n"/>
+      <c r="H7" s="464" t="n"/>
+      <c r="I7" s="464" t="n"/>
+      <c r="J7" s="464" t="n"/>
+      <c r="K7" s="464" t="n"/>
+      <c r="L7" s="464" t="n"/>
+      <c r="M7" s="464" t="n"/>
+      <c r="N7" s="464" t="n"/>
     </row>
     <row r="8" ht="14.25" customHeight="1">
-      <c r="A8" s="205" t="n"/>
-      <c r="B8" s="205" t="n"/>
-      <c r="C8" s="205" t="n"/>
-      <c r="D8" s="205" t="n"/>
-      <c r="E8" s="205" t="n"/>
-      <c r="F8" s="205" t="n"/>
-      <c r="G8" s="205" t="n"/>
-      <c r="H8" s="205" t="n"/>
-      <c r="I8" s="205" t="n"/>
-      <c r="J8" s="205" t="n"/>
-      <c r="K8" s="205" t="n"/>
-      <c r="L8" s="205" t="n"/>
-      <c r="M8" s="205" t="n"/>
-      <c r="N8" s="205" t="n"/>
+      <c r="A8" s="464" t="n"/>
+      <c r="B8" s="464" t="n"/>
+      <c r="C8" s="464" t="n"/>
+      <c r="D8" s="464" t="n"/>
+      <c r="E8" s="464" t="n"/>
+      <c r="F8" s="464" t="n"/>
+      <c r="G8" s="464" t="n"/>
+      <c r="H8" s="464" t="n"/>
+      <c r="I8" s="464" t="n"/>
+      <c r="J8" s="464" t="n"/>
+      <c r="K8" s="464" t="n"/>
+      <c r="L8" s="464" t="n"/>
+      <c r="M8" s="464" t="n"/>
+      <c r="N8" s="464" t="n"/>
     </row>
     <row r="9" ht="16.9" customHeight="1">
       <c r="A9" s="460" t="inlineStr">
@@ -3550,9 +3906,9 @@
           <t>Number of Instruments</t>
         </is>
       </c>
-      <c r="E9" s="205" t="n"/>
-      <c r="F9" s="205" t="n"/>
-      <c r="G9" s="205" t="n"/>
+      <c r="E9" s="464" t="n"/>
+      <c r="F9" s="464" t="n"/>
+      <c r="G9" s="464" t="n"/>
       <c r="H9" s="226" t="inlineStr">
         <is>
           <t>Category</t>
@@ -3568,10 +3924,10 @@
           <t>Number of Instruments</t>
         </is>
       </c>
-      <c r="K9" s="205" t="n"/>
-      <c r="L9" s="205" t="n"/>
-      <c r="M9" s="205" t="n"/>
-      <c r="N9" s="205" t="n"/>
+      <c r="K9" s="464" t="n"/>
+      <c r="L9" s="464" t="n"/>
+      <c r="M9" s="464" t="n"/>
+      <c r="N9" s="464" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
       <c r="A10" s="378" t="inlineStr">
@@ -3579,147 +3935,147 @@
           <t>Economic instruments</t>
         </is>
       </c>
-      <c r="B10" s="212" t="inlineStr">
+      <c r="B10" s="465" t="inlineStr">
         <is>
           <t>Trading scheme</t>
         </is>
       </c>
-      <c r="C10" s="212">
+      <c r="C10" s="465">
         <f>COUNTIF(Approaches!B:B, "Trading scheme")</f>
         <v/>
       </c>
-      <c r="D10" s="212">
+      <c r="D10" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Trading scheme")</f>
         <v/>
       </c>
-      <c r="E10" s="205" t="n"/>
-      <c r="F10" s="205" t="n"/>
-      <c r="G10" s="205" t="n"/>
+      <c r="E10" s="464" t="n"/>
+      <c r="F10" s="464" t="n"/>
+      <c r="G10" s="464" t="n"/>
       <c r="H10" s="379" t="inlineStr">
         <is>
           <t>Economic instruments</t>
         </is>
       </c>
-      <c r="I10" s="214">
+      <c r="I10" s="466">
         <f>COUNTIF(Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J10" s="214">
+      <c r="J10" s="466">
         <f>COUNTIF('Instruments overview'!I:I, "Economic instruments")</f>
         <v/>
       </c>
-      <c r="K10" s="205" t="n"/>
-      <c r="L10" s="205" t="n"/>
-      <c r="M10" s="205" t="n"/>
-      <c r="N10" s="205" t="n"/>
+      <c r="K10" s="464" t="n"/>
+      <c r="L10" s="464" t="n"/>
+      <c r="M10" s="464" t="n"/>
+      <c r="N10" s="464" t="n"/>
     </row>
     <row r="11" ht="14.25" customHeight="1">
       <c r="A11" s="153" t="n"/>
-      <c r="B11" s="212" t="inlineStr">
+      <c r="B11" s="465" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="C11" s="212">
+      <c r="C11" s="465">
         <f>COUNTIF(Approaches!B:B, "Subsidy")</f>
         <v/>
       </c>
-      <c r="D11" s="212">
+      <c r="D11" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Subsidy")</f>
         <v/>
       </c>
-      <c r="E11" s="205" t="n"/>
-      <c r="F11" s="205" t="n"/>
-      <c r="G11" s="205" t="n"/>
+      <c r="E11" s="464" t="n"/>
+      <c r="F11" s="464" t="n"/>
+      <c r="G11" s="464" t="n"/>
       <c r="H11" s="379" t="inlineStr">
         <is>
           <t>Regulatory instruments</t>
         </is>
       </c>
-      <c r="I11" s="214">
+      <c r="I11" s="466">
         <f>COUNTIF(Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="J11" s="214">
+      <c r="J11" s="466">
         <f>COUNTIF('Instruments overview'!I:I, "Regulatory instruments")</f>
         <v/>
       </c>
-      <c r="K11" s="205" t="n"/>
-      <c r="L11" s="205" t="n"/>
-      <c r="M11" s="205" t="n"/>
-      <c r="N11" s="205" t="n"/>
+      <c r="K11" s="464" t="n"/>
+      <c r="L11" s="464" t="n"/>
+      <c r="M11" s="464" t="n"/>
+      <c r="N11" s="464" t="n"/>
     </row>
     <row r="12" ht="14.25" customHeight="1">
       <c r="A12" s="153" t="n"/>
-      <c r="B12" s="212" t="inlineStr">
+      <c r="B12" s="465" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="C12" s="212">
+      <c r="C12" s="465">
         <f>COUNTIF(Approaches!B:B, "Tax")</f>
         <v/>
       </c>
-      <c r="D12" s="212">
+      <c r="D12" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Tax")</f>
         <v/>
       </c>
-      <c r="E12" s="205" t="n"/>
-      <c r="F12" s="205" t="n"/>
-      <c r="G12" s="205" t="n"/>
+      <c r="E12" s="464" t="n"/>
+      <c r="F12" s="464" t="n"/>
+      <c r="G12" s="464" t="n"/>
       <c r="H12" s="379" t="inlineStr">
         <is>
           <t>Government I&amp;C</t>
         </is>
       </c>
-      <c r="I12" s="214">
+      <c r="I12" s="466">
         <f>COUNTIF(Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="J12" s="214">
+      <c r="J12" s="466">
         <f>COUNTIF('Instruments overview'!I:I, "Government I&amp;C")</f>
         <v/>
       </c>
-      <c r="K12" s="205" t="n"/>
-      <c r="L12" s="205" t="n"/>
-      <c r="M12" s="205" t="n"/>
-      <c r="N12" s="205" t="n"/>
+      <c r="K12" s="464" t="n"/>
+      <c r="L12" s="464" t="n"/>
+      <c r="M12" s="464" t="n"/>
+      <c r="N12" s="464" t="n"/>
     </row>
     <row r="13" ht="14.25" customHeight="1">
       <c r="A13" s="154" t="n"/>
-      <c r="B13" s="212" t="inlineStr">
+      <c r="B13" s="465" t="inlineStr">
         <is>
           <t>Administered price</t>
         </is>
       </c>
-      <c r="C13" s="212">
+      <c r="C13" s="465">
         <f>COUNTIF(Approaches!B:B, "Administered price")</f>
         <v/>
       </c>
-      <c r="D13" s="212">
+      <c r="D13" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Administered price")</f>
         <v/>
       </c>
-      <c r="E13" s="205" t="n"/>
-      <c r="F13" s="205" t="n"/>
-      <c r="G13" s="205" t="n"/>
+      <c r="E13" s="464" t="n"/>
+      <c r="F13" s="464" t="n"/>
+      <c r="G13" s="464" t="n"/>
       <c r="H13" s="379" t="inlineStr">
         <is>
           <t>Information instruments</t>
         </is>
       </c>
-      <c r="I13" s="214">
+      <c r="I13" s="466">
         <f>COUNTIF(Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="J13" s="214">
+      <c r="J13" s="466">
         <f>COUNTIF('Instruments overview'!I:I, "Information instruments")</f>
         <v/>
       </c>
-      <c r="K13" s="205" t="n"/>
-      <c r="L13" s="205" t="n"/>
-      <c r="M13" s="205" t="n"/>
-      <c r="N13" s="205" t="n"/>
+      <c r="K13" s="464" t="n"/>
+      <c r="L13" s="464" t="n"/>
+      <c r="M13" s="464" t="n"/>
+      <c r="N13" s="464" t="n"/>
     </row>
     <row r="14" ht="14.25" customHeight="1">
       <c r="A14" s="380" t="inlineStr">
@@ -3727,89 +4083,89 @@
           <t>Regulatory instruments</t>
         </is>
       </c>
-      <c r="B14" s="212" t="inlineStr">
+      <c r="B14" s="465" t="inlineStr">
         <is>
           <t>Technology standard</t>
         </is>
       </c>
-      <c r="C14" s="212">
+      <c r="C14" s="465">
         <f>COUNTIF(Approaches!B:B, "Technology standard")</f>
         <v/>
       </c>
-      <c r="D14" s="212">
+      <c r="D14" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Technology standard")</f>
         <v/>
       </c>
-      <c r="E14" s="205" t="n"/>
-      <c r="F14" s="205" t="n"/>
-      <c r="G14" s="205" t="n"/>
+      <c r="E14" s="464" t="n"/>
+      <c r="F14" s="464" t="n"/>
+      <c r="G14" s="464" t="n"/>
       <c r="H14" s="379" t="inlineStr">
         <is>
           <t>Voluntary approaches</t>
         </is>
       </c>
-      <c r="I14" s="214">
+      <c r="I14" s="466">
         <f>COUNTIF(Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="J14" s="214">
+      <c r="J14" s="466">
         <f>COUNTIF('Instruments overview'!I:I, "Voluntary approaches")</f>
         <v/>
       </c>
-      <c r="K14" s="205" t="n"/>
-      <c r="L14" s="205" t="n"/>
-      <c r="M14" s="205" t="n"/>
-      <c r="N14" s="205" t="n"/>
+      <c r="K14" s="464" t="n"/>
+      <c r="L14" s="464" t="n"/>
+      <c r="M14" s="464" t="n"/>
+      <c r="N14" s="464" t="n"/>
     </row>
     <row r="15" ht="14.25" customHeight="1">
-      <c r="B15" s="212" t="inlineStr">
+      <c r="B15" s="465" t="inlineStr">
         <is>
           <t>Performance standard</t>
         </is>
       </c>
-      <c r="C15" s="212">
+      <c r="C15" s="465">
         <f>COUNTIF(Approaches!B:B, "Performance standard")</f>
         <v/>
       </c>
-      <c r="D15" s="212">
+      <c r="D15" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Performance standard")</f>
         <v/>
       </c>
-      <c r="E15" s="205" t="n"/>
-      <c r="F15" s="205" t="n"/>
-      <c r="G15" s="205" t="n"/>
-      <c r="H15" s="205" t="n"/>
-      <c r="I15" s="205" t="n"/>
-      <c r="J15" s="205" t="n"/>
-      <c r="K15" s="205" t="n"/>
-      <c r="L15" s="205" t="n"/>
-      <c r="M15" s="205" t="n"/>
-      <c r="N15" s="205" t="n"/>
+      <c r="E15" s="464" t="n"/>
+      <c r="F15" s="464" t="n"/>
+      <c r="G15" s="464" t="n"/>
+      <c r="H15" s="464" t="n"/>
+      <c r="I15" s="464" t="n"/>
+      <c r="J15" s="464" t="n"/>
+      <c r="K15" s="464" t="n"/>
+      <c r="L15" s="464" t="n"/>
+      <c r="M15" s="464" t="n"/>
+      <c r="N15" s="464" t="n"/>
     </row>
     <row r="16" ht="14.25" customHeight="1">
-      <c r="B16" s="212" t="inlineStr">
+      <c r="B16" s="465" t="inlineStr">
         <is>
           <t>Framework regulation</t>
         </is>
       </c>
-      <c r="C16" s="212">
+      <c r="C16" s="465">
         <f>COUNTIF(Approaches!B:B, "Framework regulation")</f>
         <v/>
       </c>
-      <c r="D16" s="212">
+      <c r="D16" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Framework regulation")</f>
         <v/>
       </c>
-      <c r="E16" s="205" t="n"/>
-      <c r="F16" s="205" t="n"/>
-      <c r="G16" s="205" t="n"/>
-      <c r="H16" s="205" t="n"/>
-      <c r="I16" s="205" t="n"/>
-      <c r="J16" s="205" t="n"/>
-      <c r="K16" s="205" t="n"/>
-      <c r="L16" s="205" t="n"/>
-      <c r="M16" s="205" t="n"/>
-      <c r="N16" s="205" t="n"/>
+      <c r="E16" s="464" t="n"/>
+      <c r="F16" s="464" t="n"/>
+      <c r="G16" s="464" t="n"/>
+      <c r="H16" s="464" t="n"/>
+      <c r="I16" s="464" t="n"/>
+      <c r="J16" s="464" t="n"/>
+      <c r="K16" s="464" t="n"/>
+      <c r="L16" s="464" t="n"/>
+      <c r="M16" s="464" t="n"/>
+      <c r="N16" s="464" t="n"/>
     </row>
     <row r="17" ht="16.9" customHeight="1">
       <c r="A17" s="380" t="inlineStr">
@@ -3817,28 +4173,28 @@
           <t>Government I&amp;C</t>
         </is>
       </c>
-      <c r="B17" s="212" t="inlineStr">
+      <c r="B17" s="465" t="inlineStr">
         <is>
           <t>Public procurement</t>
         </is>
       </c>
-      <c r="C17" s="212">
+      <c r="C17" s="465">
         <f>COUNTIF(Approaches!B:B, "Public procurement")</f>
         <v/>
       </c>
-      <c r="D17" s="212">
+      <c r="D17" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Public procurement")</f>
         <v/>
       </c>
-      <c r="E17" s="205" t="n"/>
-      <c r="F17" s="205" t="n"/>
-      <c r="G17" s="205" t="n"/>
+      <c r="E17" s="464" t="n"/>
+      <c r="F17" s="464" t="n"/>
+      <c r="G17" s="464" t="n"/>
       <c r="H17" s="226" t="inlineStr">
         <is>
           <t>Emission Sector</t>
         </is>
       </c>
-      <c r="I17" s="225" t="inlineStr">
+      <c r="I17" s="226" t="inlineStr">
         <is>
           <t>Number of Approaches</t>
         </is>
@@ -3848,80 +4204,80 @@
           <t>Number of Instruments</t>
         </is>
       </c>
-      <c r="K17" s="205" t="n"/>
-      <c r="L17" s="205" t="n"/>
-      <c r="M17" s="205" t="n"/>
-      <c r="N17" s="205" t="n"/>
+      <c r="K17" s="464" t="n"/>
+      <c r="L17" s="464" t="n"/>
+      <c r="M17" s="464" t="n"/>
+      <c r="N17" s="464" t="n"/>
     </row>
     <row r="18" ht="16.5" customHeight="1">
-      <c r="B18" s="212" t="inlineStr">
+      <c r="B18" s="465" t="inlineStr">
         <is>
           <t>Public investment</t>
         </is>
       </c>
-      <c r="C18" s="212">
+      <c r="C18" s="465">
         <f>COUNTIF(Approaches!B:B, "Public investment")</f>
         <v/>
       </c>
-      <c r="D18" s="212">
+      <c r="D18" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Public investment")</f>
         <v/>
       </c>
-      <c r="E18" s="205" t="n"/>
-      <c r="F18" s="205" t="n"/>
-      <c r="G18" s="205" t="n"/>
+      <c r="E18" s="464" t="n"/>
+      <c r="F18" s="464" t="n"/>
+      <c r="G18" s="464" t="n"/>
       <c r="H18" s="379" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I18" s="214">
+      <c r="I18" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Energy",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J18" s="214">
+      <c r="J18" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Energy*")</f>
         <v/>
       </c>
-      <c r="K18" s="205" t="n"/>
-      <c r="L18" s="205" t="n"/>
-      <c r="M18" s="205" t="n"/>
-      <c r="N18" s="205" t="n"/>
+      <c r="K18" s="464" t="n"/>
+      <c r="L18" s="464" t="n"/>
+      <c r="M18" s="464" t="n"/>
+      <c r="N18" s="464" t="n"/>
     </row>
     <row r="19" ht="14.25" customHeight="1">
-      <c r="B19" s="212" t="inlineStr">
+      <c r="B19" s="465" t="inlineStr">
         <is>
           <t>Public appraisal rule</t>
         </is>
       </c>
-      <c r="C19" s="212">
+      <c r="C19" s="465">
         <f>COUNTIF(Approaches!B:B, "Public appraisal rules")</f>
         <v/>
       </c>
-      <c r="D19" s="212">
+      <c r="D19" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Public appraisal rules")</f>
         <v/>
       </c>
-      <c r="E19" s="205" t="n"/>
-      <c r="F19" s="205" t="n"/>
-      <c r="G19" s="205" t="n"/>
+      <c r="E19" s="464" t="n"/>
+      <c r="F19" s="464" t="n"/>
+      <c r="G19" s="464" t="n"/>
       <c r="H19" s="379" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="I19" s="214">
+      <c r="I19" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Industry",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J19" s="214">
+      <c r="J19" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Industry*")</f>
         <v/>
       </c>
-      <c r="K19" s="205" t="n"/>
-      <c r="L19" s="205" t="n"/>
-      <c r="M19" s="205" t="n"/>
-      <c r="N19" s="205" t="n"/>
+      <c r="K19" s="464" t="n"/>
+      <c r="L19" s="464" t="n"/>
+      <c r="M19" s="464" t="n"/>
+      <c r="N19" s="464" t="n"/>
     </row>
     <row r="20" ht="14.25" customHeight="1">
       <c r="A20" s="380" t="inlineStr">
@@ -3929,109 +4285,109 @@
           <t>Information instruments</t>
         </is>
       </c>
-      <c r="B20" s="212" t="inlineStr">
+      <c r="B20" s="465" t="inlineStr">
         <is>
           <t>Label</t>
         </is>
       </c>
-      <c r="C20" s="212">
+      <c r="C20" s="465">
         <f>COUNTIF(Approaches!B:B, "Comparative energy efficiency label")</f>
         <v/>
       </c>
-      <c r="D20" s="212">
+      <c r="D20" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Comparative energy efficiency label")</f>
         <v/>
       </c>
-      <c r="E20" s="205" t="n"/>
-      <c r="F20" s="205" t="n"/>
-      <c r="G20" s="205" t="n"/>
+      <c r="E20" s="464" t="n"/>
+      <c r="F20" s="464" t="n"/>
+      <c r="G20" s="464" t="n"/>
       <c r="H20" s="379" t="inlineStr">
         <is>
           <t>Buildings</t>
         </is>
       </c>
-      <c r="I20" s="214">
+      <c r="I20" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Buildings",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J20" s="214">
+      <c r="J20" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Buildings*")</f>
         <v/>
       </c>
-      <c r="K20" s="205" t="n"/>
-      <c r="L20" s="205" t="n"/>
-      <c r="M20" s="205" t="n"/>
-      <c r="N20" s="205" t="n"/>
+      <c r="K20" s="464" t="n"/>
+      <c r="L20" s="464" t="n"/>
+      <c r="M20" s="464" t="n"/>
+      <c r="N20" s="464" t="n"/>
     </row>
     <row r="21" ht="14.25" customHeight="1">
-      <c r="B21" s="212" t="inlineStr">
+      <c r="B21" s="465" t="inlineStr">
         <is>
           <t>Reporting requirement</t>
         </is>
       </c>
-      <c r="C21" s="212">
+      <c r="C21" s="465">
         <f>COUNTIF(Approaches!B:B, "Reporting requirements")</f>
         <v/>
       </c>
-      <c r="D21" s="212">
+      <c r="D21" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Reporting requirements")</f>
         <v/>
       </c>
-      <c r="E21" s="205" t="n"/>
-      <c r="F21" s="205" t="n"/>
-      <c r="G21" s="205" t="n"/>
+      <c r="E21" s="464" t="n"/>
+      <c r="F21" s="464" t="n"/>
+      <c r="G21" s="464" t="n"/>
       <c r="H21" s="379" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I21" s="214">
+      <c r="I21" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Transport",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J21" s="214">
+      <c r="J21" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Transport*")</f>
         <v/>
       </c>
-      <c r="K21" s="205" t="n"/>
-      <c r="L21" s="205" t="n"/>
-      <c r="M21" s="205" t="n"/>
-      <c r="N21" s="205" t="n"/>
+      <c r="K21" s="464" t="n"/>
+      <c r="L21" s="464" t="n"/>
+      <c r="M21" s="464" t="n"/>
+      <c r="N21" s="464" t="n"/>
     </row>
     <row r="22" ht="14.25" customHeight="1">
-      <c r="B22" s="212" t="inlineStr">
+      <c r="B22" s="465" t="inlineStr">
         <is>
           <t>Capacity building and public awareness</t>
         </is>
       </c>
-      <c r="C22" s="212">
+      <c r="C22" s="465">
         <f>COUNTIF(Approaches!B:B, "Capacity building and public awareness")</f>
         <v/>
       </c>
-      <c r="D22" s="212">
+      <c r="D22" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Capacity building and public awareness")</f>
         <v/>
       </c>
-      <c r="E22" s="205" t="n"/>
-      <c r="F22" s="205" t="n"/>
-      <c r="G22" s="205" t="n"/>
+      <c r="E22" s="464" t="n"/>
+      <c r="F22" s="464" t="n"/>
+      <c r="G22" s="464" t="n"/>
       <c r="H22" s="379" t="inlineStr">
         <is>
           <t>AFOLU</t>
         </is>
       </c>
-      <c r="I22" s="214">
+      <c r="I22" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("AFOLU",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J22" s="214">
+      <c r="J22" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*AFOLU*")</f>
         <v/>
       </c>
-      <c r="K22" s="205" t="n"/>
-      <c r="L22" s="205" t="n"/>
-      <c r="M22" s="205" t="n"/>
-      <c r="N22" s="205" t="n"/>
+      <c r="K22" s="464" t="n"/>
+      <c r="L22" s="464" t="n"/>
+      <c r="M22" s="464" t="n"/>
+      <c r="N22" s="464" t="n"/>
     </row>
     <row r="23" ht="14.25" customHeight="1">
       <c r="A23" s="380" t="inlineStr">
@@ -4039,601 +4395,601 @@
           <t>Voluntary approaches</t>
         </is>
       </c>
-      <c r="B23" s="212" t="inlineStr">
+      <c r="B23" s="465" t="inlineStr">
         <is>
           <t>Voluntary information instrument</t>
         </is>
       </c>
-      <c r="C23" s="212">
+      <c r="C23" s="465">
         <f>COUNTIF(Approaches!B:B, "Voluntary information instrument")</f>
         <v/>
       </c>
-      <c r="D23" s="212">
+      <c r="D23" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Voluntary information instrument")</f>
         <v/>
       </c>
-      <c r="E23" s="205" t="n"/>
-      <c r="F23" s="205" t="n"/>
-      <c r="G23" s="205" t="n"/>
+      <c r="E23" s="464" t="n"/>
+      <c r="F23" s="464" t="n"/>
+      <c r="G23" s="464" t="n"/>
       <c r="H23" s="379" t="inlineStr">
         <is>
           <t>Waste</t>
         </is>
       </c>
-      <c r="I23" s="214">
+      <c r="I23" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Waste",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J23" s="214">
+      <c r="J23" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Waste*")</f>
         <v/>
       </c>
-      <c r="K23" s="205" t="n"/>
-      <c r="L23" s="205" t="n"/>
-      <c r="M23" s="205" t="n"/>
-      <c r="N23" s="205" t="n"/>
+      <c r="K23" s="464" t="n"/>
+      <c r="L23" s="464" t="n"/>
+      <c r="M23" s="464" t="n"/>
+      <c r="N23" s="464" t="n"/>
     </row>
     <row r="24" ht="14.25" customHeight="1">
-      <c r="B24" s="212" t="inlineStr">
+      <c r="B24" s="465" t="inlineStr">
         <is>
           <t>Voluntary target</t>
         </is>
       </c>
-      <c r="C24" s="212">
+      <c r="C24" s="465">
         <f>COUNTIF(Approaches!B:B, "Voluntary target")</f>
         <v/>
       </c>
-      <c r="D24" s="212">
+      <c r="D24" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Voluntary target")</f>
         <v/>
       </c>
-      <c r="E24" s="205" t="n"/>
-      <c r="F24" s="205" t="n"/>
-      <c r="G24" s="205" t="n"/>
+      <c r="E24" s="464" t="n"/>
+      <c r="F24" s="464" t="n"/>
+      <c r="G24" s="464" t="n"/>
       <c r="H24" s="379" t="inlineStr">
         <is>
           <t>Cross-sectoral</t>
         </is>
       </c>
-      <c r="I24" s="214">
+      <c r="I24" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Cross-sectoral",Approaches!F:F)))*1)</f>
         <v/>
       </c>
-      <c r="J24" s="214">
+      <c r="J24" s="466">
         <f>COUNTIF('Instruments overview'!K:K, "*Cross-sectoral*")</f>
         <v/>
       </c>
-      <c r="K24" s="205" t="n"/>
-      <c r="L24" s="205" t="n"/>
-      <c r="M24" s="205" t="n"/>
-      <c r="N24" s="205" t="n"/>
+      <c r="K24" s="464" t="n"/>
+      <c r="L24" s="464" t="n"/>
+      <c r="M24" s="464" t="n"/>
+      <c r="N24" s="464" t="n"/>
     </row>
     <row r="25" ht="14.25" customHeight="1">
-      <c r="B25" s="212" t="inlineStr">
+      <c r="B25" s="465" t="inlineStr">
         <is>
           <t>Voluntary trading system</t>
         </is>
       </c>
-      <c r="C25" s="212">
+      <c r="C25" s="465">
         <f>COUNTIF(Approaches!B:B, "Voluntary trading system")</f>
         <v/>
       </c>
-      <c r="D25" s="212">
+      <c r="D25" s="465">
         <f>COUNTIF('Instruments overview'!J:J, "Voluntary trading system")</f>
         <v/>
       </c>
-      <c r="E25" s="205" t="n"/>
-      <c r="F25" s="205" t="n"/>
-      <c r="G25" s="205" t="n"/>
+      <c r="E25" s="464" t="n"/>
+      <c r="F25" s="464" t="n"/>
+      <c r="G25" s="464" t="n"/>
       <c r="H25" s="381" t="n"/>
-      <c r="I25" s="205" t="n"/>
-      <c r="J25" s="205" t="n"/>
-      <c r="K25" s="205" t="n"/>
-      <c r="L25" s="205" t="n"/>
-      <c r="M25" s="205" t="n"/>
-      <c r="N25" s="205" t="n"/>
+      <c r="I25" s="464" t="n"/>
+      <c r="J25" s="464" t="n"/>
+      <c r="K25" s="464" t="n"/>
+      <c r="L25" s="464" t="n"/>
+      <c r="M25" s="464" t="n"/>
+      <c r="N25" s="464" t="n"/>
     </row>
     <row r="26" ht="14.25" customHeight="1">
-      <c r="A26" s="205" t="n"/>
-      <c r="B26" s="205" t="n"/>
-      <c r="C26" s="205" t="n"/>
-      <c r="D26" s="205" t="n"/>
-      <c r="E26" s="205" t="n"/>
-      <c r="F26" s="205" t="n"/>
-      <c r="G26" s="205" t="n"/>
-      <c r="H26" s="205" t="n"/>
-      <c r="I26" s="205" t="n"/>
-      <c r="J26" s="205" t="n"/>
-      <c r="K26" s="205" t="n"/>
-      <c r="L26" s="205" t="n"/>
-      <c r="M26" s="205" t="n"/>
-      <c r="N26" s="205" t="n"/>
+      <c r="A26" s="464" t="n"/>
+      <c r="B26" s="464" t="n"/>
+      <c r="C26" s="464" t="n"/>
+      <c r="D26" s="464" t="n"/>
+      <c r="E26" s="464" t="n"/>
+      <c r="F26" s="464" t="n"/>
+      <c r="G26" s="464" t="n"/>
+      <c r="H26" s="464" t="n"/>
+      <c r="I26" s="464" t="n"/>
+      <c r="J26" s="464" t="n"/>
+      <c r="K26" s="464" t="n"/>
+      <c r="L26" s="464" t="n"/>
+      <c r="M26" s="464" t="n"/>
+      <c r="N26" s="464" t="n"/>
     </row>
     <row r="27" ht="14.25" customHeight="1">
-      <c r="A27" s="218" t="inlineStr">
+      <c r="A27" s="467" t="inlineStr">
         <is>
           <t>Note: The sum of numbers for "category" and "group" equals the total number of approaches/instruments, since each approach/instrument only belongs to one category/group. The sum of numbers in the other tables are larger than the total number of approaches/instruments since some approaches/instruments belong to more than one classification.</t>
         </is>
       </c>
-      <c r="B27" s="205" t="n"/>
-      <c r="C27" s="205" t="n"/>
-      <c r="D27" s="205" t="n"/>
-      <c r="E27" s="205" t="n"/>
-      <c r="F27" s="205" t="n"/>
-      <c r="G27" s="205" t="n"/>
-      <c r="H27" s="205" t="n"/>
-      <c r="I27" s="205" t="n"/>
-      <c r="J27" s="205" t="n"/>
-      <c r="K27" s="205" t="n"/>
-      <c r="L27" s="205" t="n"/>
-      <c r="M27" s="205" t="n"/>
-      <c r="N27" s="205" t="n"/>
+      <c r="B27" s="464" t="n"/>
+      <c r="C27" s="464" t="n"/>
+      <c r="D27" s="464" t="n"/>
+      <c r="E27" s="464" t="n"/>
+      <c r="F27" s="464" t="n"/>
+      <c r="G27" s="464" t="n"/>
+      <c r="H27" s="464" t="n"/>
+      <c r="I27" s="464" t="n"/>
+      <c r="J27" s="464" t="n"/>
+      <c r="K27" s="464" t="n"/>
+      <c r="L27" s="464" t="n"/>
+      <c r="M27" s="464" t="n"/>
+      <c r="N27" s="464" t="n"/>
     </row>
     <row r="28" ht="14.25" customHeight="1">
-      <c r="A28" s="205" t="n"/>
-      <c r="B28" s="205" t="n"/>
-      <c r="C28" s="205" t="n"/>
-      <c r="D28" s="205" t="n"/>
-      <c r="E28" s="205" t="n"/>
-      <c r="F28" s="205" t="n"/>
-      <c r="G28" s="205" t="n"/>
-      <c r="H28" s="205" t="n"/>
-      <c r="I28" s="205" t="n"/>
-      <c r="J28" s="205" t="n"/>
-      <c r="K28" s="205" t="n"/>
-      <c r="L28" s="205" t="n"/>
-      <c r="M28" s="205" t="n"/>
-      <c r="N28" s="205" t="n"/>
+      <c r="A28" s="464" t="n"/>
+      <c r="B28" s="464" t="n"/>
+      <c r="C28" s="464" t="n"/>
+      <c r="D28" s="464" t="n"/>
+      <c r="E28" s="464" t="n"/>
+      <c r="F28" s="464" t="n"/>
+      <c r="G28" s="464" t="n"/>
+      <c r="H28" s="464" t="n"/>
+      <c r="I28" s="464" t="n"/>
+      <c r="J28" s="464" t="n"/>
+      <c r="K28" s="464" t="n"/>
+      <c r="L28" s="464" t="n"/>
+      <c r="M28" s="464" t="n"/>
+      <c r="N28" s="464" t="n"/>
     </row>
     <row r="29" ht="14.25" customHeight="1">
-      <c r="A29" s="205" t="n"/>
-      <c r="B29" s="205" t="n"/>
-      <c r="C29" s="205" t="n"/>
-      <c r="D29" s="205" t="n"/>
-      <c r="E29" s="205" t="n"/>
-      <c r="F29" s="205" t="n"/>
-      <c r="G29" s="205" t="n"/>
-      <c r="H29" s="205" t="n"/>
-      <c r="I29" s="205" t="n"/>
-      <c r="J29" s="205" t="n"/>
-      <c r="K29" s="205" t="n"/>
-      <c r="L29" s="205" t="n"/>
-      <c r="M29" s="205" t="n"/>
-      <c r="N29" s="205" t="n"/>
+      <c r="A29" s="464" t="n"/>
+      <c r="B29" s="464" t="n"/>
+      <c r="C29" s="464" t="n"/>
+      <c r="D29" s="464" t="n"/>
+      <c r="E29" s="464" t="n"/>
+      <c r="F29" s="464" t="n"/>
+      <c r="G29" s="464" t="n"/>
+      <c r="H29" s="464" t="n"/>
+      <c r="I29" s="464" t="n"/>
+      <c r="J29" s="464" t="n"/>
+      <c r="K29" s="464" t="n"/>
+      <c r="L29" s="464" t="n"/>
+      <c r="M29" s="464" t="n"/>
+      <c r="N29" s="464" t="n"/>
     </row>
     <row r="30" ht="16.9" customHeight="1">
-      <c r="A30" s="205" t="n"/>
-      <c r="B30" s="205" t="n"/>
-      <c r="C30" s="205" t="n"/>
-      <c r="D30" s="205" t="n"/>
-      <c r="E30" s="205" t="n"/>
-      <c r="F30" s="205" t="n"/>
-      <c r="G30" s="205" t="n"/>
-      <c r="H30" s="225" t="inlineStr">
+      <c r="A30" s="464" t="n"/>
+      <c r="B30" s="464" t="n"/>
+      <c r="C30" s="464" t="n"/>
+      <c r="D30" s="464" t="n"/>
+      <c r="E30" s="464" t="n"/>
+      <c r="F30" s="464" t="n"/>
+      <c r="G30" s="464" t="n"/>
+      <c r="H30" s="226" t="inlineStr">
         <is>
           <t>Mitigation relevance</t>
         </is>
       </c>
-      <c r="I30" s="225" t="inlineStr">
+      <c r="I30" s="226" t="inlineStr">
         <is>
           <t>Number of Approaches</t>
         </is>
       </c>
-      <c r="J30" s="225" t="inlineStr">
+      <c r="J30" s="226" t="inlineStr">
         <is>
           <t>Number of Instruments</t>
         </is>
       </c>
-      <c r="K30" s="205" t="n"/>
-      <c r="L30" s="205" t="n"/>
-      <c r="M30" s="205" t="n"/>
-      <c r="N30" s="205" t="n"/>
+      <c r="K30" s="464" t="n"/>
+      <c r="L30" s="464" t="n"/>
+      <c r="M30" s="464" t="n"/>
+      <c r="N30" s="464" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="205" t="n"/>
-      <c r="B31" s="205" t="n"/>
-      <c r="C31" s="205" t="n"/>
-      <c r="D31" s="205" t="n"/>
-      <c r="E31" s="205" t="n"/>
-      <c r="F31" s="205" t="n"/>
-      <c r="G31" s="205" t="n"/>
+      <c r="A31" s="464" t="n"/>
+      <c r="B31" s="464" t="n"/>
+      <c r="C31" s="464" t="n"/>
+      <c r="D31" s="464" t="n"/>
+      <c r="E31" s="464" t="n"/>
+      <c r="F31" s="464" t="n"/>
+      <c r="G31" s="464" t="n"/>
       <c r="H31" s="379" t="inlineStr">
         <is>
           <t>Direct</t>
         </is>
       </c>
-      <c r="I31" s="214">
+      <c r="I31" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Direct",Approaches!G:G)))*1)</f>
         <v/>
       </c>
-      <c r="J31" s="214">
+      <c r="J31" s="466">
         <f>COUNTIF('Instruments overview'!H:H, "Direct")</f>
         <v/>
       </c>
-      <c r="K31" s="205" t="n"/>
-      <c r="L31" s="205" t="n"/>
-      <c r="M31" s="205" t="n"/>
-      <c r="N31" s="205" t="n"/>
+      <c r="K31" s="464" t="n"/>
+      <c r="L31" s="464" t="n"/>
+      <c r="M31" s="464" t="n"/>
+      <c r="N31" s="464" t="n"/>
     </row>
     <row r="32" ht="14.25" customHeight="1">
-      <c r="A32" s="205" t="n"/>
-      <c r="B32" s="205" t="n"/>
-      <c r="C32" s="205" t="n"/>
-      <c r="D32" s="205" t="n"/>
-      <c r="E32" s="205" t="n"/>
-      <c r="F32" s="205" t="n"/>
-      <c r="G32" s="205" t="n"/>
+      <c r="A32" s="464" t="n"/>
+      <c r="B32" s="464" t="n"/>
+      <c r="C32" s="464" t="n"/>
+      <c r="D32" s="464" t="n"/>
+      <c r="E32" s="464" t="n"/>
+      <c r="F32" s="464" t="n"/>
+      <c r="G32" s="464" t="n"/>
       <c r="H32" s="379" t="inlineStr">
         <is>
           <t>Indirect</t>
         </is>
       </c>
-      <c r="I32" s="214">
+      <c r="I32" s="466">
         <f>SUMPRODUCT((ISNUMBER(SEARCH("Indirect",Approaches!G:G)))*1)</f>
         <v/>
       </c>
-      <c r="J32" s="214">
+      <c r="J32" s="466">
         <f>COUNTIF('Instruments overview'!H:H, "Indirect")</f>
         <v/>
       </c>
-      <c r="K32" s="205" t="n"/>
-      <c r="L32" s="205" t="n"/>
-      <c r="M32" s="205" t="n"/>
-      <c r="N32" s="205" t="n"/>
+      <c r="K32" s="464" t="n"/>
+      <c r="L32" s="464" t="n"/>
+      <c r="M32" s="464" t="n"/>
+      <c r="N32" s="464" t="n"/>
     </row>
     <row r="33" ht="14.25" customHeight="1">
-      <c r="A33" s="205" t="n"/>
-      <c r="B33" s="205" t="n"/>
-      <c r="C33" s="205" t="n"/>
-      <c r="D33" s="205" t="n"/>
-      <c r="E33" s="205" t="n"/>
-      <c r="F33" s="205" t="n"/>
-      <c r="G33" s="205" t="n"/>
-      <c r="H33" s="205" t="n"/>
-      <c r="I33" s="205" t="n"/>
-      <c r="J33" s="205" t="n"/>
-      <c r="K33" s="205" t="n"/>
-      <c r="L33" s="205" t="n"/>
-      <c r="M33" s="205" t="n"/>
-      <c r="N33" s="205" t="n"/>
+      <c r="A33" s="464" t="n"/>
+      <c r="B33" s="464" t="n"/>
+      <c r="C33" s="464" t="n"/>
+      <c r="D33" s="464" t="n"/>
+      <c r="E33" s="464" t="n"/>
+      <c r="F33" s="464" t="n"/>
+      <c r="G33" s="464" t="n"/>
+      <c r="H33" s="464" t="n"/>
+      <c r="I33" s="464" t="n"/>
+      <c r="J33" s="464" t="n"/>
+      <c r="K33" s="464" t="n"/>
+      <c r="L33" s="464" t="n"/>
+      <c r="M33" s="464" t="n"/>
+      <c r="N33" s="464" t="n"/>
     </row>
     <row r="34" ht="14.25" customHeight="1">
-      <c r="A34" s="205" t="n"/>
-      <c r="B34" s="205" t="n"/>
-      <c r="C34" s="205" t="n"/>
-      <c r="D34" s="205" t="n"/>
-      <c r="E34" s="205" t="n"/>
-      <c r="F34" s="205" t="n"/>
-      <c r="G34" s="205" t="n"/>
-      <c r="H34" s="205" t="n"/>
-      <c r="I34" s="205" t="n"/>
-      <c r="J34" s="205" t="n"/>
-      <c r="K34" s="205" t="n"/>
-      <c r="L34" s="205" t="n"/>
-      <c r="M34" s="205" t="n"/>
-      <c r="N34" s="205" t="n"/>
+      <c r="A34" s="464" t="n"/>
+      <c r="B34" s="464" t="n"/>
+      <c r="C34" s="464" t="n"/>
+      <c r="D34" s="464" t="n"/>
+      <c r="E34" s="464" t="n"/>
+      <c r="F34" s="464" t="n"/>
+      <c r="G34" s="464" t="n"/>
+      <c r="H34" s="464" t="n"/>
+      <c r="I34" s="464" t="n"/>
+      <c r="J34" s="464" t="n"/>
+      <c r="K34" s="464" t="n"/>
+      <c r="L34" s="464" t="n"/>
+      <c r="M34" s="464" t="n"/>
+      <c r="N34" s="464" t="n"/>
     </row>
     <row r="35" ht="16.9" customHeight="1">
-      <c r="A35" s="205" t="n"/>
-      <c r="B35" s="205" t="n"/>
-      <c r="C35" s="205" t="n"/>
-      <c r="D35" s="205" t="n"/>
-      <c r="E35" s="205" t="n"/>
-      <c r="F35" s="205" t="n"/>
-      <c r="G35" s="205" t="n"/>
-      <c r="H35" s="214" t="n"/>
-      <c r="I35" s="225" t="inlineStr">
+      <c r="A35" s="464" t="n"/>
+      <c r="B35" s="464" t="n"/>
+      <c r="C35" s="464" t="n"/>
+      <c r="D35" s="464" t="n"/>
+      <c r="E35" s="464" t="n"/>
+      <c r="F35" s="464" t="n"/>
+      <c r="G35" s="464" t="n"/>
+      <c r="H35" s="466" t="n"/>
+      <c r="I35" s="226" t="inlineStr">
         <is>
           <t>Economic instruments</t>
         </is>
       </c>
-      <c r="J35" s="225" t="inlineStr">
+      <c r="J35" s="226" t="inlineStr">
         <is>
           <t>Regulatory instruments</t>
         </is>
       </c>
-      <c r="K35" s="225" t="inlineStr">
+      <c r="K35" s="226" t="inlineStr">
         <is>
           <t>Government I&amp;C</t>
         </is>
       </c>
-      <c r="L35" s="225" t="inlineStr">
+      <c r="L35" s="226" t="inlineStr">
         <is>
           <t>Information instruments</t>
         </is>
       </c>
-      <c r="M35" s="225" t="inlineStr">
+      <c r="M35" s="226" t="inlineStr">
         <is>
           <t>Voluntary approaches</t>
         </is>
       </c>
-      <c r="N35" s="225" t="inlineStr">
+      <c r="N35" s="226" t="inlineStr">
         <is>
           <t>Total number of approaches</t>
         </is>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1">
-      <c r="A36" s="205" t="n"/>
-      <c r="B36" s="205" t="n"/>
-      <c r="C36" s="205" t="n"/>
-      <c r="D36" s="205" t="n"/>
-      <c r="E36" s="205" t="n"/>
-      <c r="F36" s="205" t="n"/>
-      <c r="G36" s="205" t="n"/>
+      <c r="A36" s="464" t="n"/>
+      <c r="B36" s="464" t="n"/>
+      <c r="C36" s="464" t="n"/>
+      <c r="D36" s="464" t="n"/>
+      <c r="E36" s="464" t="n"/>
+      <c r="F36" s="464" t="n"/>
+      <c r="G36" s="464" t="n"/>
       <c r="H36" s="382" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I36" s="214">
+      <c r="I36" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Energy*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J36" s="214">
+      <c r="J36" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Energy*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K36" s="214">
+      <c r="K36" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Energy*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L36" s="214">
+      <c r="L36" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Energy*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M36" s="214">
+      <c r="M36" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Energy*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N36" s="214">
+      <c r="N36" s="466">
         <f>SUM(I36:M36)</f>
         <v/>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1">
-      <c r="A37" s="205" t="n"/>
-      <c r="B37" s="205" t="n"/>
-      <c r="C37" s="205" t="n"/>
-      <c r="D37" s="205" t="n"/>
-      <c r="E37" s="205" t="n"/>
-      <c r="F37" s="205" t="n"/>
-      <c r="G37" s="205" t="n"/>
+      <c r="A37" s="464" t="n"/>
+      <c r="B37" s="464" t="n"/>
+      <c r="C37" s="464" t="n"/>
+      <c r="D37" s="464" t="n"/>
+      <c r="E37" s="464" t="n"/>
+      <c r="F37" s="464" t="n"/>
+      <c r="G37" s="464" t="n"/>
       <c r="H37" s="382" t="inlineStr">
         <is>
           <t>Industry</t>
         </is>
       </c>
-      <c r="I37" s="214">
+      <c r="I37" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Industry*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J37" s="214">
+      <c r="J37" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Industry*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K37" s="214">
+      <c r="K37" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Industry*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L37" s="214">
+      <c r="L37" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Industry*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M37" s="214">
+      <c r="M37" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Industry*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N37" s="214">
+      <c r="N37" s="466">
         <f>SUM(I37:M37)</f>
         <v/>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1">
-      <c r="A38" s="205" t="n"/>
-      <c r="B38" s="205" t="n"/>
-      <c r="C38" s="205" t="n"/>
-      <c r="D38" s="205" t="n"/>
-      <c r="E38" s="205" t="n"/>
-      <c r="F38" s="205" t="n"/>
-      <c r="G38" s="205" t="n"/>
+      <c r="A38" s="464" t="n"/>
+      <c r="B38" s="464" t="n"/>
+      <c r="C38" s="464" t="n"/>
+      <c r="D38" s="464" t="n"/>
+      <c r="E38" s="464" t="n"/>
+      <c r="F38" s="464" t="n"/>
+      <c r="G38" s="464" t="n"/>
       <c r="H38" s="382" t="inlineStr">
         <is>
           <t>Buildings</t>
         </is>
       </c>
-      <c r="I38" s="214">
+      <c r="I38" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Buildings*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J38" s="214">
+      <c r="J38" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Buildings*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K38" s="214">
+      <c r="K38" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Buildings*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L38" s="214">
+      <c r="L38" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Buildings*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M38" s="214">
+      <c r="M38" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Buildings*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N38" s="214">
+      <c r="N38" s="466">
         <f>SUM(I38:M38)</f>
         <v/>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1">
-      <c r="A39" s="205" t="n"/>
-      <c r="B39" s="205" t="n"/>
-      <c r="C39" s="205" t="n"/>
-      <c r="D39" s="205" t="n"/>
-      <c r="E39" s="205" t="n"/>
-      <c r="F39" s="205" t="n"/>
-      <c r="G39" s="205" t="n"/>
+      <c r="A39" s="464" t="n"/>
+      <c r="B39" s="464" t="n"/>
+      <c r="C39" s="464" t="n"/>
+      <c r="D39" s="464" t="n"/>
+      <c r="E39" s="464" t="n"/>
+      <c r="F39" s="464" t="n"/>
+      <c r="G39" s="464" t="n"/>
       <c r="H39" s="382" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I39" s="214">
+      <c r="I39" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Transport*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J39" s="214">
+      <c r="J39" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Transport*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K39" s="214">
+      <c r="K39" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Transport*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L39" s="214">
+      <c r="L39" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Transport*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M39" s="214">
+      <c r="M39" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Transport*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N39" s="214">
+      <c r="N39" s="466">
         <f>SUM(I39:M39)</f>
         <v/>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1">
-      <c r="A40" s="205" t="n"/>
-      <c r="B40" s="205" t="n"/>
-      <c r="C40" s="205" t="n"/>
-      <c r="D40" s="205" t="n"/>
-      <c r="E40" s="205" t="n"/>
-      <c r="F40" s="205" t="n"/>
-      <c r="G40" s="205" t="n"/>
+      <c r="A40" s="464" t="n"/>
+      <c r="B40" s="464" t="n"/>
+      <c r="C40" s="464" t="n"/>
+      <c r="D40" s="464" t="n"/>
+      <c r="E40" s="464" t="n"/>
+      <c r="F40" s="464" t="n"/>
+      <c r="G40" s="464" t="n"/>
       <c r="H40" s="382" t="inlineStr">
         <is>
           <t>AFOLU</t>
         </is>
       </c>
-      <c r="I40" s="214">
+      <c r="I40" s="466">
         <f>COUNTIFS(Approaches!F:F, "*AFOLU*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J40" s="214">
+      <c r="J40" s="466">
         <f>COUNTIFS(Approaches!F:F, "*AFOLU*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K40" s="214">
+      <c r="K40" s="466">
         <f>COUNTIFS(Approaches!F:F, "*AFOLU*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L40" s="214">
+      <c r="L40" s="466">
         <f>COUNTIFS(Approaches!F:F, "*AFOLU*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M40" s="214">
+      <c r="M40" s="466">
         <f>COUNTIFS(Approaches!F:F, "*AFOLU*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N40" s="214">
+      <c r="N40" s="466">
         <f>SUM(I40:M40)</f>
         <v/>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1">
-      <c r="A41" s="205" t="n"/>
-      <c r="B41" s="205" t="n"/>
-      <c r="C41" s="205" t="n"/>
-      <c r="D41" s="205" t="n"/>
-      <c r="E41" s="205" t="n"/>
-      <c r="F41" s="205" t="n"/>
-      <c r="G41" s="205" t="n"/>
+      <c r="A41" s="464" t="n"/>
+      <c r="B41" s="464" t="n"/>
+      <c r="C41" s="464" t="n"/>
+      <c r="D41" s="464" t="n"/>
+      <c r="E41" s="464" t="n"/>
+      <c r="F41" s="464" t="n"/>
+      <c r="G41" s="464" t="n"/>
       <c r="H41" s="382" t="inlineStr">
         <is>
           <t>Waste</t>
         </is>
       </c>
-      <c r="I41" s="214">
+      <c r="I41" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Waste*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J41" s="214">
+      <c r="J41" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Waste*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K41" s="214">
+      <c r="K41" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Waste*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L41" s="214">
+      <c r="L41" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Waste*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M41" s="214">
+      <c r="M41" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Waste*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N41" s="214">
+      <c r="N41" s="466">
         <f>SUM(I41:M41)</f>
         <v/>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1">
-      <c r="A42" s="205" t="n"/>
-      <c r="B42" s="205" t="n"/>
-      <c r="C42" s="205" t="n"/>
-      <c r="D42" s="205" t="n"/>
-      <c r="E42" s="205" t="n"/>
-      <c r="F42" s="205" t="n"/>
-      <c r="G42" s="205" t="n"/>
+      <c r="A42" s="464" t="n"/>
+      <c r="B42" s="464" t="n"/>
+      <c r="C42" s="464" t="n"/>
+      <c r="D42" s="464" t="n"/>
+      <c r="E42" s="464" t="n"/>
+      <c r="F42" s="464" t="n"/>
+      <c r="G42" s="464" t="n"/>
       <c r="H42" s="382" t="inlineStr">
         <is>
           <t>Cross-sectoral</t>
         </is>
       </c>
-      <c r="I42" s="214">
+      <c r="I42" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Cross-sectoral*", Approaches!A:A, "Economic")</f>
         <v/>
       </c>
-      <c r="J42" s="214">
+      <c r="J42" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Cross-sectoral*", Approaches!A:A, "Regulatory")</f>
         <v/>
       </c>
-      <c r="K42" s="214">
+      <c r="K42" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Cross-sectoral*", Approaches!A:A, "Government investment and consumption")</f>
         <v/>
       </c>
-      <c r="L42" s="214">
+      <c r="L42" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Cross-sectoral*", Approaches!A:A, "Information")</f>
         <v/>
       </c>
-      <c r="M42" s="214">
+      <c r="M42" s="466">
         <f>COUNTIFS(Approaches!F:F, "*Cross-sectoral*", Approaches!A:A, "Voluntary")</f>
         <v/>
       </c>
-      <c r="N42" s="214">
+      <c r="N42" s="466">
         <f>SUM(I42:M42)</f>
         <v/>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1">
-      <c r="A43" s="205" t="n"/>
-      <c r="B43" s="205" t="n"/>
-      <c r="C43" s="205" t="n"/>
-      <c r="D43" s="205" t="n"/>
-      <c r="E43" s="205" t="n"/>
-      <c r="F43" s="205" t="n"/>
-      <c r="G43" s="205" t="n"/>
-      <c r="H43" s="227" t="n"/>
-      <c r="I43" s="205" t="n"/>
-      <c r="J43" s="205" t="n"/>
-      <c r="K43" s="205" t="n"/>
-      <c r="L43" s="205" t="n"/>
-      <c r="M43" s="205" t="n"/>
-      <c r="N43" s="205" t="n"/>
+      <c r="A43" s="464" t="n"/>
+      <c r="B43" s="464" t="n"/>
+      <c r="C43" s="464" t="n"/>
+      <c r="D43" s="464" t="n"/>
+      <c r="E43" s="464" t="n"/>
+      <c r="F43" s="464" t="n"/>
+      <c r="G43" s="464" t="n"/>
+      <c r="H43" s="468" t="n"/>
+      <c r="I43" s="464" t="n"/>
+      <c r="J43" s="464" t="n"/>
+      <c r="K43" s="464" t="n"/>
+      <c r="L43" s="464" t="n"/>
+      <c r="M43" s="464" t="n"/>
+      <c r="N43" s="464" t="n"/>
     </row>
     <row r="44" ht="16.5" customHeight="1"/>
   </sheetData>
@@ -4685,22 +5041,22 @@
           <t>Definition</t>
         </is>
       </c>
-      <c r="E1" s="263" t="n"/>
-      <c r="F1" s="264" t="n"/>
-      <c r="G1" s="264" t="n"/>
-      <c r="H1" s="264" t="n"/>
-      <c r="I1" s="264" t="n"/>
-      <c r="J1" s="264" t="n"/>
-      <c r="K1" s="264" t="n"/>
-      <c r="L1" s="264" t="n"/>
-      <c r="M1" s="264" t="n"/>
-      <c r="N1" s="264" t="n"/>
-      <c r="O1" s="264" t="n"/>
-      <c r="P1" s="264" t="n"/>
-      <c r="Q1" s="264" t="n"/>
-      <c r="R1" s="264" t="n"/>
-      <c r="S1" s="264" t="n"/>
-      <c r="T1" s="264" t="n"/>
+      <c r="E1" s="357" t="n"/>
+      <c r="F1" s="254" t="n"/>
+      <c r="G1" s="254" t="n"/>
+      <c r="H1" s="254" t="n"/>
+      <c r="I1" s="254" t="n"/>
+      <c r="J1" s="254" t="n"/>
+      <c r="K1" s="254" t="n"/>
+      <c r="L1" s="254" t="n"/>
+      <c r="M1" s="254" t="n"/>
+      <c r="N1" s="254" t="n"/>
+      <c r="O1" s="254" t="n"/>
+      <c r="P1" s="254" t="n"/>
+      <c r="Q1" s="254" t="n"/>
+      <c r="R1" s="254" t="n"/>
+      <c r="S1" s="254" t="n"/>
+      <c r="T1" s="254" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="367" t="inlineStr">
@@ -4723,22 +5079,22 @@
           <t>Unrequited payments from government to non-government units</t>
         </is>
       </c>
-      <c r="E2" s="263" t="n"/>
-      <c r="F2" s="264" t="n"/>
-      <c r="G2" s="264" t="n"/>
-      <c r="H2" s="264" t="n"/>
-      <c r="I2" s="264" t="n"/>
-      <c r="J2" s="264" t="n"/>
-      <c r="K2" s="264" t="n"/>
-      <c r="L2" s="264" t="n"/>
-      <c r="M2" s="264" t="n"/>
-      <c r="N2" s="264" t="n"/>
-      <c r="O2" s="264" t="n"/>
-      <c r="P2" s="264" t="n"/>
-      <c r="Q2" s="264" t="n"/>
-      <c r="R2" s="264" t="n"/>
-      <c r="S2" s="264" t="n"/>
-      <c r="T2" s="264" t="n"/>
+      <c r="E2" s="357" t="n"/>
+      <c r="F2" s="254" t="n"/>
+      <c r="G2" s="254" t="n"/>
+      <c r="H2" s="254" t="n"/>
+      <c r="I2" s="254" t="n"/>
+      <c r="J2" s="254" t="n"/>
+      <c r="K2" s="254" t="n"/>
+      <c r="L2" s="254" t="n"/>
+      <c r="M2" s="254" t="n"/>
+      <c r="N2" s="254" t="n"/>
+      <c r="O2" s="254" t="n"/>
+      <c r="P2" s="254" t="n"/>
+      <c r="Q2" s="254" t="n"/>
+      <c r="R2" s="254" t="n"/>
+      <c r="S2" s="254" t="n"/>
+      <c r="T2" s="254" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="369" t="n"/>
@@ -4753,22 +5109,22 @@
           <t>Compulsory unrequited payments to a government unit</t>
         </is>
       </c>
-      <c r="E3" s="263" t="n"/>
-      <c r="F3" s="264" t="n"/>
-      <c r="G3" s="264" t="n"/>
-      <c r="H3" s="264" t="n"/>
-      <c r="I3" s="264" t="n"/>
-      <c r="J3" s="264" t="n"/>
-      <c r="K3" s="264" t="n"/>
-      <c r="L3" s="264" t="n"/>
-      <c r="M3" s="264" t="n"/>
-      <c r="N3" s="264" t="n"/>
-      <c r="O3" s="264" t="n"/>
-      <c r="P3" s="264" t="n"/>
-      <c r="Q3" s="264" t="n"/>
-      <c r="R3" s="264" t="n"/>
-      <c r="S3" s="264" t="n"/>
-      <c r="T3" s="264" t="n"/>
+      <c r="E3" s="357" t="n"/>
+      <c r="F3" s="254" t="n"/>
+      <c r="G3" s="254" t="n"/>
+      <c r="H3" s="254" t="n"/>
+      <c r="I3" s="254" t="n"/>
+      <c r="J3" s="254" t="n"/>
+      <c r="K3" s="254" t="n"/>
+      <c r="L3" s="254" t="n"/>
+      <c r="M3" s="254" t="n"/>
+      <c r="N3" s="254" t="n"/>
+      <c r="O3" s="254" t="n"/>
+      <c r="P3" s="254" t="n"/>
+      <c r="Q3" s="254" t="n"/>
+      <c r="R3" s="254" t="n"/>
+      <c r="S3" s="254" t="n"/>
+      <c r="T3" s="254" t="n"/>
     </row>
     <row r="4" ht="45" customHeight="1">
       <c r="A4" s="369" t="n"/>
@@ -4783,22 +5139,22 @@
           <t>Trading schemes cause changes in the relative costs or prices faced by economic agents by regulating the trade of permits or certificates, which may cause a direct financial benefit (e.g. by providing the options of selling them) or set a price on the behaviour of the regulated agents (e.g. by providing the options of purchasing them).</t>
         </is>
       </c>
-      <c r="E4" s="263" t="n"/>
-      <c r="F4" s="264" t="n"/>
-      <c r="G4" s="264" t="n"/>
-      <c r="H4" s="264" t="n"/>
-      <c r="I4" s="264" t="n"/>
-      <c r="J4" s="264" t="n"/>
-      <c r="K4" s="264" t="n"/>
-      <c r="L4" s="264" t="n"/>
-      <c r="M4" s="264" t="n"/>
-      <c r="N4" s="264" t="n"/>
-      <c r="O4" s="264" t="n"/>
-      <c r="P4" s="264" t="n"/>
-      <c r="Q4" s="264" t="n"/>
-      <c r="R4" s="264" t="n"/>
-      <c r="S4" s="264" t="n"/>
-      <c r="T4" s="264" t="n"/>
+      <c r="E4" s="357" t="n"/>
+      <c r="F4" s="254" t="n"/>
+      <c r="G4" s="254" t="n"/>
+      <c r="H4" s="254" t="n"/>
+      <c r="I4" s="254" t="n"/>
+      <c r="J4" s="254" t="n"/>
+      <c r="K4" s="254" t="n"/>
+      <c r="L4" s="254" t="n"/>
+      <c r="M4" s="254" t="n"/>
+      <c r="N4" s="254" t="n"/>
+      <c r="O4" s="254" t="n"/>
+      <c r="P4" s="254" t="n"/>
+      <c r="Q4" s="254" t="n"/>
+      <c r="R4" s="254" t="n"/>
+      <c r="S4" s="254" t="n"/>
+      <c r="T4" s="254" t="n"/>
     </row>
     <row r="5" ht="30" customHeight="1">
       <c r="A5" s="361" t="n"/>
@@ -4813,22 +5169,22 @@
           <t>Government-administered pricing mechanisms that directly set, differentiate, or regulate prices of energy or emissions-intensive activities to influence behaviour, without operating through explicit fiscal transfers or tax instruments.</t>
         </is>
       </c>
-      <c r="E5" s="263" t="n"/>
-      <c r="F5" s="264" t="n"/>
-      <c r="G5" s="264" t="n"/>
-      <c r="H5" s="264" t="n"/>
-      <c r="I5" s="264" t="n"/>
-      <c r="J5" s="264" t="n"/>
-      <c r="K5" s="264" t="n"/>
-      <c r="L5" s="264" t="n"/>
-      <c r="M5" s="264" t="n"/>
-      <c r="N5" s="264" t="n"/>
-      <c r="O5" s="264" t="n"/>
-      <c r="P5" s="264" t="n"/>
-      <c r="Q5" s="264" t="n"/>
-      <c r="R5" s="264" t="n"/>
-      <c r="S5" s="264" t="n"/>
-      <c r="T5" s="264" t="n"/>
+      <c r="E5" s="357" t="n"/>
+      <c r="F5" s="254" t="n"/>
+      <c r="G5" s="254" t="n"/>
+      <c r="H5" s="254" t="n"/>
+      <c r="I5" s="254" t="n"/>
+      <c r="J5" s="254" t="n"/>
+      <c r="K5" s="254" t="n"/>
+      <c r="L5" s="254" t="n"/>
+      <c r="M5" s="254" t="n"/>
+      <c r="N5" s="254" t="n"/>
+      <c r="O5" s="254" t="n"/>
+      <c r="P5" s="254" t="n"/>
+      <c r="Q5" s="254" t="n"/>
+      <c r="R5" s="254" t="n"/>
+      <c r="S5" s="254" t="n"/>
+      <c r="T5" s="254" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="370" t="inlineStr">
@@ -4851,22 +5207,22 @@
           <t>Performance standards mandate a specific outcome, giving regulated agents the freedom to choose technologies and processes to achieve the specified performance level.</t>
         </is>
       </c>
-      <c r="E6" s="263" t="n"/>
-      <c r="F6" s="264" t="n"/>
-      <c r="G6" s="264" t="n"/>
-      <c r="H6" s="264" t="n"/>
-      <c r="I6" s="264" t="n"/>
-      <c r="J6" s="264" t="n"/>
-      <c r="K6" s="264" t="n"/>
-      <c r="L6" s="264" t="n"/>
-      <c r="M6" s="264" t="n"/>
-      <c r="N6" s="264" t="n"/>
-      <c r="O6" s="264" t="n"/>
-      <c r="P6" s="264" t="n"/>
-      <c r="Q6" s="264" t="n"/>
-      <c r="R6" s="264" t="n"/>
-      <c r="S6" s="264" t="n"/>
-      <c r="T6" s="264" t="n"/>
+      <c r="E6" s="357" t="n"/>
+      <c r="F6" s="254" t="n"/>
+      <c r="G6" s="254" t="n"/>
+      <c r="H6" s="254" t="n"/>
+      <c r="I6" s="254" t="n"/>
+      <c r="J6" s="254" t="n"/>
+      <c r="K6" s="254" t="n"/>
+      <c r="L6" s="254" t="n"/>
+      <c r="M6" s="254" t="n"/>
+      <c r="N6" s="254" t="n"/>
+      <c r="O6" s="254" t="n"/>
+      <c r="P6" s="254" t="n"/>
+      <c r="Q6" s="254" t="n"/>
+      <c r="R6" s="254" t="n"/>
+      <c r="S6" s="254" t="n"/>
+      <c r="T6" s="254" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="369" t="n"/>
@@ -4881,22 +5237,22 @@
           <t>Technology standards require or prohibit a specific input or technology, or design for production.</t>
         </is>
       </c>
-      <c r="E7" s="263" t="n"/>
-      <c r="F7" s="264" t="n"/>
-      <c r="G7" s="264" t="n"/>
-      <c r="H7" s="264" t="n"/>
-      <c r="I7" s="264" t="n"/>
-      <c r="J7" s="264" t="n"/>
-      <c r="K7" s="264" t="n"/>
-      <c r="L7" s="264" t="n"/>
-      <c r="M7" s="264" t="n"/>
-      <c r="N7" s="264" t="n"/>
-      <c r="O7" s="264" t="n"/>
-      <c r="P7" s="264" t="n"/>
-      <c r="Q7" s="264" t="n"/>
-      <c r="R7" s="264" t="n"/>
-      <c r="S7" s="264" t="n"/>
-      <c r="T7" s="264" t="n"/>
+      <c r="E7" s="357" t="n"/>
+      <c r="F7" s="254" t="n"/>
+      <c r="G7" s="254" t="n"/>
+      <c r="H7" s="254" t="n"/>
+      <c r="I7" s="254" t="n"/>
+      <c r="J7" s="254" t="n"/>
+      <c r="K7" s="254" t="n"/>
+      <c r="L7" s="254" t="n"/>
+      <c r="M7" s="254" t="n"/>
+      <c r="N7" s="254" t="n"/>
+      <c r="O7" s="254" t="n"/>
+      <c r="P7" s="254" t="n"/>
+      <c r="Q7" s="254" t="n"/>
+      <c r="R7" s="254" t="n"/>
+      <c r="S7" s="254" t="n"/>
+      <c r="T7" s="254" t="n"/>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="361" t="n"/>
@@ -4911,22 +5267,22 @@
           <t>Framework standards prescribe requirements on production processes without mandating the use of specific inputs or technologies or prescribing a specific outcome. Often, these requirements are of qualitative nature and they may require case-by-case interpretation and application. They may also regulate the functioning of markets.</t>
         </is>
       </c>
-      <c r="E8" s="263" t="n"/>
-      <c r="F8" s="264" t="n"/>
-      <c r="G8" s="264" t="n"/>
-      <c r="H8" s="264" t="n"/>
-      <c r="I8" s="264" t="n"/>
-      <c r="J8" s="264" t="n"/>
-      <c r="K8" s="264" t="n"/>
-      <c r="L8" s="264" t="n"/>
-      <c r="M8" s="264" t="n"/>
-      <c r="N8" s="264" t="n"/>
-      <c r="O8" s="264" t="n"/>
-      <c r="P8" s="264" t="n"/>
-      <c r="Q8" s="264" t="n"/>
-      <c r="R8" s="264" t="n"/>
-      <c r="S8" s="264" t="n"/>
-      <c r="T8" s="264" t="n"/>
+      <c r="E8" s="357" t="n"/>
+      <c r="F8" s="254" t="n"/>
+      <c r="G8" s="254" t="n"/>
+      <c r="H8" s="254" t="n"/>
+      <c r="I8" s="254" t="n"/>
+      <c r="J8" s="254" t="n"/>
+      <c r="K8" s="254" t="n"/>
+      <c r="L8" s="254" t="n"/>
+      <c r="M8" s="254" t="n"/>
+      <c r="N8" s="254" t="n"/>
+      <c r="O8" s="254" t="n"/>
+      <c r="P8" s="254" t="n"/>
+      <c r="Q8" s="254" t="n"/>
+      <c r="R8" s="254" t="n"/>
+      <c r="S8" s="254" t="n"/>
+      <c r="T8" s="254" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
       <c r="A9" s="372" t="inlineStr">
@@ -4949,22 +5305,22 @@
           <t>Spending by a government unit towards forming fixed capital such as transport and energy infrastructure, or nature-based infrastructure solutions, as well as intangible assets such as R&amp;D.</t>
         </is>
       </c>
-      <c r="E9" s="263" t="n"/>
-      <c r="F9" s="264" t="n"/>
-      <c r="G9" s="264" t="n"/>
-      <c r="H9" s="264" t="n"/>
-      <c r="I9" s="264" t="n"/>
-      <c r="J9" s="264" t="n"/>
-      <c r="K9" s="264" t="n"/>
-      <c r="L9" s="264" t="n"/>
-      <c r="M9" s="264" t="n"/>
-      <c r="N9" s="264" t="n"/>
-      <c r="O9" s="264" t="n"/>
-      <c r="P9" s="264" t="n"/>
-      <c r="Q9" s="264" t="n"/>
-      <c r="R9" s="264" t="n"/>
-      <c r="S9" s="264" t="n"/>
-      <c r="T9" s="264" t="n"/>
+      <c r="E9" s="357" t="n"/>
+      <c r="F9" s="254" t="n"/>
+      <c r="G9" s="254" t="n"/>
+      <c r="H9" s="254" t="n"/>
+      <c r="I9" s="254" t="n"/>
+      <c r="J9" s="254" t="n"/>
+      <c r="K9" s="254" t="n"/>
+      <c r="L9" s="254" t="n"/>
+      <c r="M9" s="254" t="n"/>
+      <c r="N9" s="254" t="n"/>
+      <c r="O9" s="254" t="n"/>
+      <c r="P9" s="254" t="n"/>
+      <c r="Q9" s="254" t="n"/>
+      <c r="R9" s="254" t="n"/>
+      <c r="S9" s="254" t="n"/>
+      <c r="T9" s="254" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="369" t="n"/>
@@ -4979,22 +5335,22 @@
           <t>Instruments that oblige or encourage public agents to consider climate change mitigation impacts when purchasing the goods, services and works from external suppliers or providers to fulfil public sector needs, deliver public services, and execute government projects and programmes.</t>
         </is>
       </c>
-      <c r="E10" s="263" t="n"/>
-      <c r="F10" s="264" t="n"/>
-      <c r="G10" s="264" t="n"/>
-      <c r="H10" s="264" t="n"/>
-      <c r="I10" s="264" t="n"/>
-      <c r="J10" s="264" t="n"/>
-      <c r="K10" s="264" t="n"/>
-      <c r="L10" s="264" t="n"/>
-      <c r="M10" s="264" t="n"/>
-      <c r="N10" s="264" t="n"/>
-      <c r="O10" s="264" t="n"/>
-      <c r="P10" s="264" t="n"/>
-      <c r="Q10" s="264" t="n"/>
-      <c r="R10" s="264" t="n"/>
-      <c r="S10" s="264" t="n"/>
-      <c r="T10" s="264" t="n"/>
+      <c r="E10" s="357" t="n"/>
+      <c r="F10" s="254" t="n"/>
+      <c r="G10" s="254" t="n"/>
+      <c r="H10" s="254" t="n"/>
+      <c r="I10" s="254" t="n"/>
+      <c r="J10" s="254" t="n"/>
+      <c r="K10" s="254" t="n"/>
+      <c r="L10" s="254" t="n"/>
+      <c r="M10" s="254" t="n"/>
+      <c r="N10" s="254" t="n"/>
+      <c r="O10" s="254" t="n"/>
+      <c r="P10" s="254" t="n"/>
+      <c r="Q10" s="254" t="n"/>
+      <c r="R10" s="254" t="n"/>
+      <c r="S10" s="254" t="n"/>
+      <c r="T10" s="254" t="n"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="361" t="n"/>
@@ -5009,22 +5365,22 @@
           <t>Public appraisal rules prescribe requirements on the decision-making processes and operations of the government without mandating the use of specific inputs or technologies or prescribing a specific outcome. Rather, they specify the process to be followed in decision-making processes and operations or define qualitative outcomes that may require case-by-case interpretation.</t>
         </is>
       </c>
-      <c r="E11" s="263" t="n"/>
-      <c r="F11" s="264" t="n"/>
-      <c r="G11" s="264" t="n"/>
-      <c r="H11" s="264" t="n"/>
-      <c r="I11" s="264" t="n"/>
-      <c r="J11" s="264" t="n"/>
-      <c r="K11" s="264" t="n"/>
-      <c r="L11" s="264" t="n"/>
-      <c r="M11" s="264" t="n"/>
-      <c r="N11" s="264" t="n"/>
-      <c r="O11" s="264" t="n"/>
-      <c r="P11" s="264" t="n"/>
-      <c r="Q11" s="264" t="n"/>
-      <c r="R11" s="264" t="n"/>
-      <c r="S11" s="264" t="n"/>
-      <c r="T11" s="264" t="n"/>
+      <c r="E11" s="357" t="n"/>
+      <c r="F11" s="254" t="n"/>
+      <c r="G11" s="254" t="n"/>
+      <c r="H11" s="254" t="n"/>
+      <c r="I11" s="254" t="n"/>
+      <c r="J11" s="254" t="n"/>
+      <c r="K11" s="254" t="n"/>
+      <c r="L11" s="254" t="n"/>
+      <c r="M11" s="254" t="n"/>
+      <c r="N11" s="254" t="n"/>
+      <c r="O11" s="254" t="n"/>
+      <c r="P11" s="254" t="n"/>
+      <c r="Q11" s="254" t="n"/>
+      <c r="R11" s="254" t="n"/>
+      <c r="S11" s="254" t="n"/>
+      <c r="T11" s="254" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="374" t="inlineStr">
@@ -5047,22 +5403,22 @@
           <t>A mandatory label that provides standardised, comparable information on the energy efficiency of products, buildings, or vehicles to guide consumer decision-making.</t>
         </is>
       </c>
-      <c r="E12" s="263" t="n"/>
-      <c r="F12" s="264" t="n"/>
-      <c r="G12" s="264" t="n"/>
-      <c r="H12" s="264" t="n"/>
-      <c r="I12" s="264" t="n"/>
-      <c r="J12" s="264" t="n"/>
-      <c r="K12" s="264" t="n"/>
-      <c r="L12" s="264" t="n"/>
-      <c r="M12" s="264" t="n"/>
-      <c r="N12" s="264" t="n"/>
-      <c r="O12" s="264" t="n"/>
-      <c r="P12" s="264" t="n"/>
-      <c r="Q12" s="264" t="n"/>
-      <c r="R12" s="264" t="n"/>
-      <c r="S12" s="264" t="n"/>
-      <c r="T12" s="264" t="n"/>
+      <c r="E12" s="357" t="n"/>
+      <c r="F12" s="254" t="n"/>
+      <c r="G12" s="254" t="n"/>
+      <c r="H12" s="254" t="n"/>
+      <c r="I12" s="254" t="n"/>
+      <c r="J12" s="254" t="n"/>
+      <c r="K12" s="254" t="n"/>
+      <c r="L12" s="254" t="n"/>
+      <c r="M12" s="254" t="n"/>
+      <c r="N12" s="254" t="n"/>
+      <c r="O12" s="254" t="n"/>
+      <c r="P12" s="254" t="n"/>
+      <c r="Q12" s="254" t="n"/>
+      <c r="R12" s="254" t="n"/>
+      <c r="S12" s="254" t="n"/>
+      <c r="T12" s="254" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="369" t="n"/>
@@ -5077,22 +5433,22 @@
           <t>Reporting requirements mandate agents to submit regular reports, disclosures, or documentation to the regulating agents, oversight bodies, or stakeholders.</t>
         </is>
       </c>
-      <c r="E13" s="263" t="n"/>
-      <c r="F13" s="264" t="n"/>
-      <c r="G13" s="264" t="n"/>
-      <c r="H13" s="264" t="n"/>
-      <c r="I13" s="264" t="n"/>
-      <c r="J13" s="264" t="n"/>
-      <c r="K13" s="264" t="n"/>
-      <c r="L13" s="264" t="n"/>
-      <c r="M13" s="264" t="n"/>
-      <c r="N13" s="264" t="n"/>
-      <c r="O13" s="264" t="n"/>
-      <c r="P13" s="264" t="n"/>
-      <c r="Q13" s="264" t="n"/>
-      <c r="R13" s="264" t="n"/>
-      <c r="S13" s="264" t="n"/>
-      <c r="T13" s="264" t="n"/>
+      <c r="E13" s="357" t="n"/>
+      <c r="F13" s="254" t="n"/>
+      <c r="G13" s="254" t="n"/>
+      <c r="H13" s="254" t="n"/>
+      <c r="I13" s="254" t="n"/>
+      <c r="J13" s="254" t="n"/>
+      <c r="K13" s="254" t="n"/>
+      <c r="L13" s="254" t="n"/>
+      <c r="M13" s="254" t="n"/>
+      <c r="N13" s="254" t="n"/>
+      <c r="O13" s="254" t="n"/>
+      <c r="P13" s="254" t="n"/>
+      <c r="Q13" s="254" t="n"/>
+      <c r="R13" s="254" t="n"/>
+      <c r="S13" s="254" t="n"/>
+      <c r="T13" s="254" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="361" t="n"/>
@@ -5107,22 +5463,22 @@
           <t>Government provides information to non-government units to disseminate information, raise awareness, and enhance understanding on specific issues, initiatives, or policies.</t>
         </is>
       </c>
-      <c r="E14" s="263" t="n"/>
-      <c r="F14" s="264" t="n"/>
-      <c r="G14" s="264" t="n"/>
-      <c r="H14" s="264" t="n"/>
-      <c r="I14" s="264" t="n"/>
-      <c r="J14" s="264" t="n"/>
-      <c r="K14" s="264" t="n"/>
-      <c r="L14" s="264" t="n"/>
-      <c r="M14" s="264" t="n"/>
-      <c r="N14" s="264" t="n"/>
-      <c r="O14" s="264" t="n"/>
-      <c r="P14" s="264" t="n"/>
-      <c r="Q14" s="264" t="n"/>
-      <c r="R14" s="264" t="n"/>
-      <c r="S14" s="264" t="n"/>
-      <c r="T14" s="264" t="n"/>
+      <c r="E14" s="357" t="n"/>
+      <c r="F14" s="254" t="n"/>
+      <c r="G14" s="254" t="n"/>
+      <c r="H14" s="254" t="n"/>
+      <c r="I14" s="254" t="n"/>
+      <c r="J14" s="254" t="n"/>
+      <c r="K14" s="254" t="n"/>
+      <c r="L14" s="254" t="n"/>
+      <c r="M14" s="254" t="n"/>
+      <c r="N14" s="254" t="n"/>
+      <c r="O14" s="254" t="n"/>
+      <c r="P14" s="254" t="n"/>
+      <c r="Q14" s="254" t="n"/>
+      <c r="R14" s="254" t="n"/>
+      <c r="S14" s="254" t="n"/>
+      <c r="T14" s="254" t="n"/>
     </row>
     <row r="15" ht="45" customHeight="1">
       <c r="A15" s="376" t="inlineStr">
@@ -5146,22 +5502,22 @@
 Examples: voluntary energy efficiency labels; voluntary financial labels, voluntary reporting standards; voluntary audits.</t>
         </is>
       </c>
-      <c r="E15" s="263" t="n"/>
-      <c r="F15" s="264" t="n"/>
-      <c r="G15" s="264" t="n"/>
-      <c r="H15" s="264" t="n"/>
-      <c r="I15" s="264" t="n"/>
-      <c r="J15" s="264" t="n"/>
-      <c r="K15" s="264" t="n"/>
-      <c r="L15" s="264" t="n"/>
-      <c r="M15" s="264" t="n"/>
-      <c r="N15" s="264" t="n"/>
-      <c r="O15" s="264" t="n"/>
-      <c r="P15" s="264" t="n"/>
-      <c r="Q15" s="264" t="n"/>
-      <c r="R15" s="264" t="n"/>
-      <c r="S15" s="264" t="n"/>
-      <c r="T15" s="264" t="n"/>
+      <c r="E15" s="357" t="n"/>
+      <c r="F15" s="254" t="n"/>
+      <c r="G15" s="254" t="n"/>
+      <c r="H15" s="254" t="n"/>
+      <c r="I15" s="254" t="n"/>
+      <c r="J15" s="254" t="n"/>
+      <c r="K15" s="254" t="n"/>
+      <c r="L15" s="254" t="n"/>
+      <c r="M15" s="254" t="n"/>
+      <c r="N15" s="254" t="n"/>
+      <c r="O15" s="254" t="n"/>
+      <c r="P15" s="254" t="n"/>
+      <c r="Q15" s="254" t="n"/>
+      <c r="R15" s="254" t="n"/>
+      <c r="S15" s="254" t="n"/>
+      <c r="T15" s="254" t="n"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="369" t="n"/>
@@ -5177,22 +5533,22 @@
 Examples: voluntary GHG emission trading systems.</t>
         </is>
       </c>
-      <c r="E16" s="263" t="n"/>
-      <c r="F16" s="264" t="n"/>
-      <c r="G16" s="264" t="n"/>
-      <c r="H16" s="264" t="n"/>
-      <c r="I16" s="264" t="n"/>
-      <c r="J16" s="264" t="n"/>
-      <c r="K16" s="264" t="n"/>
-      <c r="L16" s="264" t="n"/>
-      <c r="M16" s="264" t="n"/>
-      <c r="N16" s="264" t="n"/>
-      <c r="O16" s="264" t="n"/>
-      <c r="P16" s="264" t="n"/>
-      <c r="Q16" s="264" t="n"/>
-      <c r="R16" s="264" t="n"/>
-      <c r="S16" s="264" t="n"/>
-      <c r="T16" s="264" t="n"/>
+      <c r="E16" s="357" t="n"/>
+      <c r="F16" s="254" t="n"/>
+      <c r="G16" s="254" t="n"/>
+      <c r="H16" s="254" t="n"/>
+      <c r="I16" s="254" t="n"/>
+      <c r="J16" s="254" t="n"/>
+      <c r="K16" s="254" t="n"/>
+      <c r="L16" s="254" t="n"/>
+      <c r="M16" s="254" t="n"/>
+      <c r="N16" s="254" t="n"/>
+      <c r="O16" s="254" t="n"/>
+      <c r="P16" s="254" t="n"/>
+      <c r="Q16" s="254" t="n"/>
+      <c r="R16" s="254" t="n"/>
+      <c r="S16" s="254" t="n"/>
+      <c r="T16" s="254" t="n"/>
     </row>
     <row r="17" ht="45" customHeight="1">
       <c r="A17" s="361" t="n"/>
@@ -5208,70 +5564,70 @@
 Examples: voluntary GHG emission reduction targets, voluntary energy performance targets.</t>
         </is>
       </c>
-      <c r="E17" s="263" t="n"/>
-      <c r="F17" s="264" t="n"/>
-      <c r="G17" s="264" t="n"/>
-      <c r="H17" s="264" t="n"/>
-      <c r="I17" s="264" t="n"/>
-      <c r="J17" s="264" t="n"/>
-      <c r="K17" s="264" t="n"/>
-      <c r="L17" s="264" t="n"/>
-      <c r="M17" s="264" t="n"/>
-      <c r="N17" s="264" t="n"/>
-      <c r="O17" s="264" t="n"/>
-      <c r="P17" s="264" t="n"/>
-      <c r="Q17" s="264" t="n"/>
-      <c r="R17" s="264" t="n"/>
-      <c r="S17" s="264" t="n"/>
-      <c r="T17" s="264" t="n"/>
+      <c r="E17" s="357" t="n"/>
+      <c r="F17" s="254" t="n"/>
+      <c r="G17" s="254" t="n"/>
+      <c r="H17" s="254" t="n"/>
+      <c r="I17" s="254" t="n"/>
+      <c r="J17" s="254" t="n"/>
+      <c r="K17" s="254" t="n"/>
+      <c r="L17" s="254" t="n"/>
+      <c r="M17" s="254" t="n"/>
+      <c r="N17" s="254" t="n"/>
+      <c r="O17" s="254" t="n"/>
+      <c r="P17" s="254" t="n"/>
+      <c r="Q17" s="254" t="n"/>
+      <c r="R17" s="254" t="n"/>
+      <c r="S17" s="254" t="n"/>
+      <c r="T17" s="254" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="277" t="n"/>
-      <c r="B18" s="277" t="n"/>
-      <c r="C18" s="277" t="n"/>
-      <c r="D18" s="277" t="n"/>
-      <c r="E18" s="264" t="n"/>
-      <c r="F18" s="264" t="n"/>
-      <c r="G18" s="264" t="n"/>
-      <c r="H18" s="264" t="n"/>
-      <c r="I18" s="264" t="n"/>
-      <c r="J18" s="264" t="n"/>
-      <c r="K18" s="264" t="n"/>
-      <c r="L18" s="264" t="n"/>
-      <c r="M18" s="264" t="n"/>
-      <c r="N18" s="264" t="n"/>
-      <c r="O18" s="264" t="n"/>
-      <c r="P18" s="264" t="n"/>
-      <c r="Q18" s="264" t="n"/>
-      <c r="R18" s="264" t="n"/>
-      <c r="S18" s="264" t="n"/>
-      <c r="T18" s="264" t="n"/>
+      <c r="A18" s="365" t="n"/>
+      <c r="B18" s="365" t="n"/>
+      <c r="C18" s="365" t="n"/>
+      <c r="D18" s="365" t="n"/>
+      <c r="E18" s="254" t="n"/>
+      <c r="F18" s="254" t="n"/>
+      <c r="G18" s="254" t="n"/>
+      <c r="H18" s="254" t="n"/>
+      <c r="I18" s="254" t="n"/>
+      <c r="J18" s="254" t="n"/>
+      <c r="K18" s="254" t="n"/>
+      <c r="L18" s="254" t="n"/>
+      <c r="M18" s="254" t="n"/>
+      <c r="N18" s="254" t="n"/>
+      <c r="O18" s="254" t="n"/>
+      <c r="P18" s="254" t="n"/>
+      <c r="Q18" s="254" t="n"/>
+      <c r="R18" s="254" t="n"/>
+      <c r="S18" s="254" t="n"/>
+      <c r="T18" s="254" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="278" t="inlineStr">
+      <c r="A19" s="498" t="inlineStr">
         <is>
           <t>Source: IFCMA(2024), MGF Lab.</t>
         </is>
       </c>
-      <c r="B19" s="264" t="n"/>
-      <c r="C19" s="264" t="n"/>
-      <c r="D19" s="264" t="n"/>
-      <c r="E19" s="264" t="n"/>
-      <c r="F19" s="264" t="n"/>
-      <c r="G19" s="264" t="n"/>
-      <c r="H19" s="264" t="n"/>
-      <c r="I19" s="264" t="n"/>
-      <c r="J19" s="264" t="n"/>
-      <c r="K19" s="264" t="n"/>
-      <c r="L19" s="264" t="n"/>
-      <c r="M19" s="264" t="n"/>
-      <c r="N19" s="264" t="n"/>
-      <c r="O19" s="264" t="n"/>
-      <c r="P19" s="264" t="n"/>
-      <c r="Q19" s="264" t="n"/>
-      <c r="R19" s="264" t="n"/>
-      <c r="S19" s="264" t="n"/>
-      <c r="T19" s="264" t="n"/>
+      <c r="B19" s="254" t="n"/>
+      <c r="C19" s="254" t="n"/>
+      <c r="D19" s="254" t="n"/>
+      <c r="E19" s="254" t="n"/>
+      <c r="F19" s="254" t="n"/>
+      <c r="G19" s="254" t="n"/>
+      <c r="H19" s="254" t="n"/>
+      <c r="I19" s="254" t="n"/>
+      <c r="J19" s="254" t="n"/>
+      <c r="K19" s="254" t="n"/>
+      <c r="L19" s="254" t="n"/>
+      <c r="M19" s="254" t="n"/>
+      <c r="N19" s="254" t="n"/>
+      <c r="O19" s="254" t="n"/>
+      <c r="P19" s="254" t="n"/>
+      <c r="Q19" s="254" t="n"/>
+      <c r="R19" s="254" t="n"/>
+      <c r="S19" s="254" t="n"/>
+      <c r="T19" s="254" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -5331,21 +5687,21 @@
           <t>Details</t>
         </is>
       </c>
-      <c r="F1" s="444" t="n"/>
-      <c r="G1" s="445" t="n"/>
-      <c r="H1" s="445" t="n"/>
-      <c r="I1" s="445" t="n"/>
-      <c r="J1" s="445" t="n"/>
-      <c r="K1" s="445" t="n"/>
-      <c r="L1" s="445" t="n"/>
-      <c r="M1" s="445" t="n"/>
-      <c r="N1" s="445" t="n"/>
-      <c r="O1" s="445" t="n"/>
-      <c r="P1" s="445" t="n"/>
-      <c r="Q1" s="445" t="n"/>
-      <c r="R1" s="445" t="n"/>
-      <c r="S1" s="445" t="n"/>
-      <c r="T1" s="445" t="n"/>
+      <c r="F1" s="459" t="n"/>
+      <c r="G1" s="499" t="n"/>
+      <c r="H1" s="499" t="n"/>
+      <c r="I1" s="499" t="n"/>
+      <c r="J1" s="499" t="n"/>
+      <c r="K1" s="499" t="n"/>
+      <c r="L1" s="499" t="n"/>
+      <c r="M1" s="499" t="n"/>
+      <c r="N1" s="499" t="n"/>
+      <c r="O1" s="499" t="n"/>
+      <c r="P1" s="499" t="n"/>
+      <c r="Q1" s="499" t="n"/>
+      <c r="R1" s="499" t="n"/>
+      <c r="S1" s="499" t="n"/>
+      <c r="T1" s="499" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="446" t="inlineStr">
@@ -5357,21 +5713,21 @@
       <c r="C2" s="339" t="n"/>
       <c r="D2" s="339" t="n"/>
       <c r="E2" s="340" t="n"/>
-      <c r="F2" s="444" t="n"/>
-      <c r="G2" s="445" t="n"/>
-      <c r="H2" s="445" t="n"/>
-      <c r="I2" s="445" t="n"/>
-      <c r="J2" s="445" t="n"/>
-      <c r="K2" s="445" t="n"/>
-      <c r="L2" s="445" t="n"/>
-      <c r="M2" s="445" t="n"/>
-      <c r="N2" s="445" t="n"/>
-      <c r="O2" s="445" t="n"/>
-      <c r="P2" s="445" t="n"/>
-      <c r="Q2" s="445" t="n"/>
-      <c r="R2" s="445" t="n"/>
-      <c r="S2" s="445" t="n"/>
-      <c r="T2" s="445" t="n"/>
+      <c r="F2" s="459" t="n"/>
+      <c r="G2" s="499" t="n"/>
+      <c r="H2" s="499" t="n"/>
+      <c r="I2" s="499" t="n"/>
+      <c r="J2" s="499" t="n"/>
+      <c r="K2" s="499" t="n"/>
+      <c r="L2" s="499" t="n"/>
+      <c r="M2" s="499" t="n"/>
+      <c r="N2" s="499" t="n"/>
+      <c r="O2" s="499" t="n"/>
+      <c r="P2" s="499" t="n"/>
+      <c r="Q2" s="499" t="n"/>
+      <c r="R2" s="499" t="n"/>
+      <c r="S2" s="499" t="n"/>
+      <c r="T2" s="499" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
       <c r="A3" s="447" t="inlineStr">
@@ -5399,21 +5755,21 @@
           <t>Instrument; Subscheme</t>
         </is>
       </c>
-      <c r="F3" s="444" t="n"/>
-      <c r="G3" s="445" t="n"/>
-      <c r="H3" s="445" t="n"/>
-      <c r="I3" s="445" t="n"/>
-      <c r="J3" s="445" t="n"/>
-      <c r="K3" s="445" t="n"/>
-      <c r="L3" s="445" t="n"/>
-      <c r="M3" s="445" t="n"/>
-      <c r="N3" s="445" t="n"/>
-      <c r="O3" s="445" t="n"/>
-      <c r="P3" s="445" t="n"/>
-      <c r="Q3" s="445" t="n"/>
-      <c r="R3" s="445" t="n"/>
-      <c r="S3" s="445" t="n"/>
-      <c r="T3" s="445" t="n"/>
+      <c r="F3" s="459" t="n"/>
+      <c r="G3" s="499" t="n"/>
+      <c r="H3" s="499" t="n"/>
+      <c r="I3" s="499" t="n"/>
+      <c r="J3" s="499" t="n"/>
+      <c r="K3" s="499" t="n"/>
+      <c r="L3" s="499" t="n"/>
+      <c r="M3" s="499" t="n"/>
+      <c r="N3" s="499" t="n"/>
+      <c r="O3" s="499" t="n"/>
+      <c r="P3" s="499" t="n"/>
+      <c r="Q3" s="499" t="n"/>
+      <c r="R3" s="499" t="n"/>
+      <c r="S3" s="499" t="n"/>
+      <c r="T3" s="499" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
       <c r="A4" s="450" t="inlineStr">
@@ -5441,21 +5797,21 @@
           <t>E.g., Taxes, Subsidies; Technology standards; Performance standards, …</t>
         </is>
       </c>
-      <c r="F4" s="444" t="n"/>
-      <c r="G4" s="445" t="n"/>
-      <c r="H4" s="445" t="n"/>
-      <c r="I4" s="445" t="n"/>
-      <c r="J4" s="445" t="n"/>
-      <c r="K4" s="445" t="n"/>
-      <c r="L4" s="445" t="n"/>
-      <c r="M4" s="445" t="n"/>
-      <c r="N4" s="445" t="n"/>
-      <c r="O4" s="445" t="n"/>
-      <c r="P4" s="445" t="n"/>
-      <c r="Q4" s="445" t="n"/>
-      <c r="R4" s="445" t="n"/>
-      <c r="S4" s="445" t="n"/>
-      <c r="T4" s="445" t="n"/>
+      <c r="F4" s="459" t="n"/>
+      <c r="G4" s="499" t="n"/>
+      <c r="H4" s="499" t="n"/>
+      <c r="I4" s="499" t="n"/>
+      <c r="J4" s="499" t="n"/>
+      <c r="K4" s="499" t="n"/>
+      <c r="L4" s="499" t="n"/>
+      <c r="M4" s="499" t="n"/>
+      <c r="N4" s="499" t="n"/>
+      <c r="O4" s="499" t="n"/>
+      <c r="P4" s="499" t="n"/>
+      <c r="Q4" s="499" t="n"/>
+      <c r="R4" s="499" t="n"/>
+      <c r="S4" s="499" t="n"/>
+      <c r="T4" s="499" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="369" t="n"/>
@@ -5479,21 +5835,21 @@
           <t>E.g., Carbon tax, Renewable electricity feed-in tariff, Subsidy for CCS, Bans and phase outs of ICE vehicles, Fuel Economy Standards, …</t>
         </is>
       </c>
-      <c r="F5" s="444" t="n"/>
-      <c r="G5" s="445" t="n"/>
-      <c r="H5" s="445" t="n"/>
-      <c r="I5" s="445" t="n"/>
-      <c r="J5" s="445" t="n"/>
-      <c r="K5" s="445" t="n"/>
-      <c r="L5" s="445" t="n"/>
-      <c r="M5" s="445" t="n"/>
-      <c r="N5" s="445" t="n"/>
-      <c r="O5" s="445" t="n"/>
-      <c r="P5" s="445" t="n"/>
-      <c r="Q5" s="445" t="n"/>
-      <c r="R5" s="445" t="n"/>
-      <c r="S5" s="445" t="n"/>
-      <c r="T5" s="445" t="n"/>
+      <c r="F5" s="459" t="n"/>
+      <c r="G5" s="499" t="n"/>
+      <c r="H5" s="499" t="n"/>
+      <c r="I5" s="499" t="n"/>
+      <c r="J5" s="499" t="n"/>
+      <c r="K5" s="499" t="n"/>
+      <c r="L5" s="499" t="n"/>
+      <c r="M5" s="499" t="n"/>
+      <c r="N5" s="499" t="n"/>
+      <c r="O5" s="499" t="n"/>
+      <c r="P5" s="499" t="n"/>
+      <c r="Q5" s="499" t="n"/>
+      <c r="R5" s="499" t="n"/>
+      <c r="S5" s="499" t="n"/>
+      <c r="T5" s="499" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="369" t="n"/>
@@ -5517,21 +5873,21 @@
           <t>Energy, transport, buildings, industry, agriculture, waste, LULUCF</t>
         </is>
       </c>
-      <c r="F6" s="444" t="n"/>
-      <c r="G6" s="445" t="n"/>
-      <c r="H6" s="445" t="n"/>
-      <c r="I6" s="445" t="n"/>
-      <c r="J6" s="445" t="n"/>
-      <c r="K6" s="445" t="n"/>
-      <c r="L6" s="445" t="n"/>
-      <c r="M6" s="445" t="n"/>
-      <c r="N6" s="445" t="n"/>
-      <c r="O6" s="445" t="n"/>
-      <c r="P6" s="445" t="n"/>
-      <c r="Q6" s="445" t="n"/>
-      <c r="R6" s="445" t="n"/>
-      <c r="S6" s="445" t="n"/>
-      <c r="T6" s="445" t="n"/>
+      <c r="F6" s="459" t="n"/>
+      <c r="G6" s="499" t="n"/>
+      <c r="H6" s="499" t="n"/>
+      <c r="I6" s="499" t="n"/>
+      <c r="J6" s="499" t="n"/>
+      <c r="K6" s="499" t="n"/>
+      <c r="L6" s="499" t="n"/>
+      <c r="M6" s="499" t="n"/>
+      <c r="N6" s="499" t="n"/>
+      <c r="O6" s="499" t="n"/>
+      <c r="P6" s="499" t="n"/>
+      <c r="Q6" s="499" t="n"/>
+      <c r="R6" s="499" t="n"/>
+      <c r="S6" s="499" t="n"/>
+      <c r="T6" s="499" t="n"/>
     </row>
     <row r="7" ht="15" customHeight="1">
       <c r="A7" s="361" t="n"/>
@@ -5555,21 +5911,21 @@
           <t>Coal, solar power, wind power, hydrogen, nuclear power, steel, cement, automobile, battery, etc.</t>
         </is>
       </c>
-      <c r="F7" s="444" t="n"/>
-      <c r="G7" s="445" t="n"/>
-      <c r="H7" s="445" t="n"/>
-      <c r="I7" s="445" t="n"/>
-      <c r="J7" s="445" t="n"/>
-      <c r="K7" s="445" t="n"/>
-      <c r="L7" s="445" t="n"/>
-      <c r="M7" s="445" t="n"/>
-      <c r="N7" s="445" t="n"/>
-      <c r="O7" s="445" t="n"/>
-      <c r="P7" s="445" t="n"/>
-      <c r="Q7" s="445" t="n"/>
-      <c r="R7" s="445" t="n"/>
-      <c r="S7" s="445" t="n"/>
-      <c r="T7" s="445" t="n"/>
+      <c r="F7" s="459" t="n"/>
+      <c r="G7" s="499" t="n"/>
+      <c r="H7" s="499" t="n"/>
+      <c r="I7" s="499" t="n"/>
+      <c r="J7" s="499" t="n"/>
+      <c r="K7" s="499" t="n"/>
+      <c r="L7" s="499" t="n"/>
+      <c r="M7" s="499" t="n"/>
+      <c r="N7" s="499" t="n"/>
+      <c r="O7" s="499" t="n"/>
+      <c r="P7" s="499" t="n"/>
+      <c r="Q7" s="499" t="n"/>
+      <c r="R7" s="499" t="n"/>
+      <c r="S7" s="499" t="n"/>
+      <c r="T7" s="499" t="n"/>
     </row>
     <row r="8" ht="15" customHeight="1">
       <c r="A8" s="450" t="inlineStr">
@@ -5597,21 +5953,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F8" s="444" t="n"/>
-      <c r="G8" s="445" t="n"/>
-      <c r="H8" s="445" t="n"/>
-      <c r="I8" s="445" t="n"/>
-      <c r="J8" s="445" t="n"/>
-      <c r="K8" s="445" t="n"/>
-      <c r="L8" s="445" t="n"/>
-      <c r="M8" s="445" t="n"/>
-      <c r="N8" s="445" t="n"/>
-      <c r="O8" s="445" t="n"/>
-      <c r="P8" s="445" t="n"/>
-      <c r="Q8" s="445" t="n"/>
-      <c r="R8" s="445" t="n"/>
-      <c r="S8" s="445" t="n"/>
-      <c r="T8" s="445" t="n"/>
+      <c r="F8" s="459" t="n"/>
+      <c r="G8" s="499" t="n"/>
+      <c r="H8" s="499" t="n"/>
+      <c r="I8" s="499" t="n"/>
+      <c r="J8" s="499" t="n"/>
+      <c r="K8" s="499" t="n"/>
+      <c r="L8" s="499" t="n"/>
+      <c r="M8" s="499" t="n"/>
+      <c r="N8" s="499" t="n"/>
+      <c r="O8" s="499" t="n"/>
+      <c r="P8" s="499" t="n"/>
+      <c r="Q8" s="499" t="n"/>
+      <c r="R8" s="499" t="n"/>
+      <c r="S8" s="499" t="n"/>
+      <c r="T8" s="499" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1">
       <c r="A9" s="369" t="n"/>
@@ -5635,21 +5991,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F9" s="444" t="n"/>
-      <c r="G9" s="445" t="n"/>
-      <c r="H9" s="445" t="n"/>
-      <c r="I9" s="445" t="n"/>
-      <c r="J9" s="445" t="n"/>
-      <c r="K9" s="445" t="n"/>
-      <c r="L9" s="445" t="n"/>
-      <c r="M9" s="445" t="n"/>
-      <c r="N9" s="445" t="n"/>
-      <c r="O9" s="445" t="n"/>
-      <c r="P9" s="445" t="n"/>
-      <c r="Q9" s="445" t="n"/>
-      <c r="R9" s="445" t="n"/>
-      <c r="S9" s="445" t="n"/>
-      <c r="T9" s="445" t="n"/>
+      <c r="F9" s="459" t="n"/>
+      <c r="G9" s="499" t="n"/>
+      <c r="H9" s="499" t="n"/>
+      <c r="I9" s="499" t="n"/>
+      <c r="J9" s="499" t="n"/>
+      <c r="K9" s="499" t="n"/>
+      <c r="L9" s="499" t="n"/>
+      <c r="M9" s="499" t="n"/>
+      <c r="N9" s="499" t="n"/>
+      <c r="O9" s="499" t="n"/>
+      <c r="P9" s="499" t="n"/>
+      <c r="Q9" s="499" t="n"/>
+      <c r="R9" s="499" t="n"/>
+      <c r="S9" s="499" t="n"/>
+      <c r="T9" s="499" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1">
       <c r="A10" s="369" t="n"/>
@@ -5673,21 +6029,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F10" s="444" t="n"/>
-      <c r="G10" s="445" t="n"/>
-      <c r="H10" s="445" t="n"/>
-      <c r="I10" s="445" t="n"/>
-      <c r="J10" s="445" t="n"/>
-      <c r="K10" s="445" t="n"/>
-      <c r="L10" s="445" t="n"/>
-      <c r="M10" s="445" t="n"/>
-      <c r="N10" s="445" t="n"/>
-      <c r="O10" s="445" t="n"/>
-      <c r="P10" s="445" t="n"/>
-      <c r="Q10" s="445" t="n"/>
-      <c r="R10" s="445" t="n"/>
-      <c r="S10" s="445" t="n"/>
-      <c r="T10" s="445" t="n"/>
+      <c r="F10" s="459" t="n"/>
+      <c r="G10" s="499" t="n"/>
+      <c r="H10" s="499" t="n"/>
+      <c r="I10" s="499" t="n"/>
+      <c r="J10" s="499" t="n"/>
+      <c r="K10" s="499" t="n"/>
+      <c r="L10" s="499" t="n"/>
+      <c r="M10" s="499" t="n"/>
+      <c r="N10" s="499" t="n"/>
+      <c r="O10" s="499" t="n"/>
+      <c r="P10" s="499" t="n"/>
+      <c r="Q10" s="499" t="n"/>
+      <c r="R10" s="499" t="n"/>
+      <c r="S10" s="499" t="n"/>
+      <c r="T10" s="499" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1">
       <c r="A11" s="369" t="n"/>
@@ -5711,21 +6067,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F11" s="444" t="n"/>
-      <c r="G11" s="445" t="n"/>
-      <c r="H11" s="445" t="n"/>
-      <c r="I11" s="445" t="n"/>
-      <c r="J11" s="445" t="n"/>
-      <c r="K11" s="445" t="n"/>
-      <c r="L11" s="445" t="n"/>
-      <c r="M11" s="445" t="n"/>
-      <c r="N11" s="445" t="n"/>
-      <c r="O11" s="445" t="n"/>
-      <c r="P11" s="445" t="n"/>
-      <c r="Q11" s="445" t="n"/>
-      <c r="R11" s="445" t="n"/>
-      <c r="S11" s="445" t="n"/>
-      <c r="T11" s="445" t="n"/>
+      <c r="F11" s="459" t="n"/>
+      <c r="G11" s="499" t="n"/>
+      <c r="H11" s="499" t="n"/>
+      <c r="I11" s="499" t="n"/>
+      <c r="J11" s="499" t="n"/>
+      <c r="K11" s="499" t="n"/>
+      <c r="L11" s="499" t="n"/>
+      <c r="M11" s="499" t="n"/>
+      <c r="N11" s="499" t="n"/>
+      <c r="O11" s="499" t="n"/>
+      <c r="P11" s="499" t="n"/>
+      <c r="Q11" s="499" t="n"/>
+      <c r="R11" s="499" t="n"/>
+      <c r="S11" s="499" t="n"/>
+      <c r="T11" s="499" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1">
       <c r="A12" s="369" t="n"/>
@@ -5749,21 +6105,21 @@
           <t>Air pollution; Waste reduction/ circular economy; Climate change mitigation; Climate change adaptation; Economic growth; Energy efficiency; Energy security; Social security/poverty reduction; Other; Not specified</t>
         </is>
       </c>
-      <c r="F12" s="444" t="n"/>
-      <c r="G12" s="445" t="n"/>
-      <c r="H12" s="445" t="n"/>
-      <c r="I12" s="445" t="n"/>
-      <c r="J12" s="445" t="n"/>
-      <c r="K12" s="445" t="n"/>
-      <c r="L12" s="445" t="n"/>
-      <c r="M12" s="445" t="n"/>
-      <c r="N12" s="445" t="n"/>
-      <c r="O12" s="445" t="n"/>
-      <c r="P12" s="445" t="n"/>
-      <c r="Q12" s="445" t="n"/>
-      <c r="R12" s="445" t="n"/>
-      <c r="S12" s="445" t="n"/>
-      <c r="T12" s="445" t="n"/>
+      <c r="F12" s="459" t="n"/>
+      <c r="G12" s="499" t="n"/>
+      <c r="H12" s="499" t="n"/>
+      <c r="I12" s="499" t="n"/>
+      <c r="J12" s="499" t="n"/>
+      <c r="K12" s="499" t="n"/>
+      <c r="L12" s="499" t="n"/>
+      <c r="M12" s="499" t="n"/>
+      <c r="N12" s="499" t="n"/>
+      <c r="O12" s="499" t="n"/>
+      <c r="P12" s="499" t="n"/>
+      <c r="Q12" s="499" t="n"/>
+      <c r="R12" s="499" t="n"/>
+      <c r="S12" s="499" t="n"/>
+      <c r="T12" s="499" t="n"/>
     </row>
     <row r="13" ht="15" customHeight="1">
       <c r="A13" s="369" t="n"/>
@@ -5787,21 +6143,21 @@
           <t>Direct; Indirect</t>
         </is>
       </c>
-      <c r="F13" s="444" t="n"/>
-      <c r="G13" s="445" t="n"/>
-      <c r="H13" s="445" t="n"/>
-      <c r="I13" s="445" t="n"/>
-      <c r="J13" s="445" t="n"/>
-      <c r="K13" s="445" t="n"/>
-      <c r="L13" s="445" t="n"/>
-      <c r="M13" s="445" t="n"/>
-      <c r="N13" s="445" t="n"/>
-      <c r="O13" s="445" t="n"/>
-      <c r="P13" s="445" t="n"/>
-      <c r="Q13" s="445" t="n"/>
-      <c r="R13" s="445" t="n"/>
-      <c r="S13" s="445" t="n"/>
-      <c r="T13" s="445" t="n"/>
+      <c r="F13" s="459" t="n"/>
+      <c r="G13" s="499" t="n"/>
+      <c r="H13" s="499" t="n"/>
+      <c r="I13" s="499" t="n"/>
+      <c r="J13" s="499" t="n"/>
+      <c r="K13" s="499" t="n"/>
+      <c r="L13" s="499" t="n"/>
+      <c r="M13" s="499" t="n"/>
+      <c r="N13" s="499" t="n"/>
+      <c r="O13" s="499" t="n"/>
+      <c r="P13" s="499" t="n"/>
+      <c r="Q13" s="499" t="n"/>
+      <c r="R13" s="499" t="n"/>
+      <c r="S13" s="499" t="n"/>
+      <c r="T13" s="499" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1">
       <c r="A14" s="369" t="n"/>
@@ -5825,21 +6181,21 @@
           <t>IFCMA member country list</t>
         </is>
       </c>
-      <c r="F14" s="444" t="n"/>
-      <c r="G14" s="445" t="n"/>
-      <c r="H14" s="445" t="n"/>
-      <c r="I14" s="445" t="n"/>
-      <c r="J14" s="445" t="n"/>
-      <c r="K14" s="445" t="n"/>
-      <c r="L14" s="445" t="n"/>
-      <c r="M14" s="445" t="n"/>
-      <c r="N14" s="445" t="n"/>
-      <c r="O14" s="445" t="n"/>
-      <c r="P14" s="445" t="n"/>
-      <c r="Q14" s="445" t="n"/>
-      <c r="R14" s="445" t="n"/>
-      <c r="S14" s="445" t="n"/>
-      <c r="T14" s="445" t="n"/>
+      <c r="F14" s="459" t="n"/>
+      <c r="G14" s="499" t="n"/>
+      <c r="H14" s="499" t="n"/>
+      <c r="I14" s="499" t="n"/>
+      <c r="J14" s="499" t="n"/>
+      <c r="K14" s="499" t="n"/>
+      <c r="L14" s="499" t="n"/>
+      <c r="M14" s="499" t="n"/>
+      <c r="N14" s="499" t="n"/>
+      <c r="O14" s="499" t="n"/>
+      <c r="P14" s="499" t="n"/>
+      <c r="Q14" s="499" t="n"/>
+      <c r="R14" s="499" t="n"/>
+      <c r="S14" s="499" t="n"/>
+      <c r="T14" s="499" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1">
       <c r="A15" s="369" t="n"/>
@@ -5863,21 +6219,21 @@
           <t>National; Sub-national; Supra-national; Special economic zone</t>
         </is>
       </c>
-      <c r="F15" s="444" t="n"/>
-      <c r="G15" s="445" t="n"/>
-      <c r="H15" s="445" t="n"/>
-      <c r="I15" s="445" t="n"/>
-      <c r="J15" s="445" t="n"/>
-      <c r="K15" s="445" t="n"/>
-      <c r="L15" s="445" t="n"/>
-      <c r="M15" s="445" t="n"/>
-      <c r="N15" s="445" t="n"/>
-      <c r="O15" s="445" t="n"/>
-      <c r="P15" s="445" t="n"/>
-      <c r="Q15" s="445" t="n"/>
-      <c r="R15" s="445" t="n"/>
-      <c r="S15" s="445" t="n"/>
-      <c r="T15" s="445" t="n"/>
+      <c r="F15" s="459" t="n"/>
+      <c r="G15" s="499" t="n"/>
+      <c r="H15" s="499" t="n"/>
+      <c r="I15" s="499" t="n"/>
+      <c r="J15" s="499" t="n"/>
+      <c r="K15" s="499" t="n"/>
+      <c r="L15" s="499" t="n"/>
+      <c r="M15" s="499" t="n"/>
+      <c r="N15" s="499" t="n"/>
+      <c r="O15" s="499" t="n"/>
+      <c r="P15" s="499" t="n"/>
+      <c r="Q15" s="499" t="n"/>
+      <c r="R15" s="499" t="n"/>
+      <c r="S15" s="499" t="n"/>
+      <c r="T15" s="499" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1">
       <c r="A16" s="369" t="n"/>
@@ -5901,21 +6257,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F16" s="444" t="n"/>
-      <c r="G16" s="445" t="n"/>
-      <c r="H16" s="445" t="n"/>
-      <c r="I16" s="445" t="n"/>
-      <c r="J16" s="445" t="n"/>
-      <c r="K16" s="445" t="n"/>
-      <c r="L16" s="445" t="n"/>
-      <c r="M16" s="445" t="n"/>
-      <c r="N16" s="445" t="n"/>
-      <c r="O16" s="445" t="n"/>
-      <c r="P16" s="445" t="n"/>
-      <c r="Q16" s="445" t="n"/>
-      <c r="R16" s="445" t="n"/>
-      <c r="S16" s="445" t="n"/>
-      <c r="T16" s="445" t="n"/>
+      <c r="F16" s="459" t="n"/>
+      <c r="G16" s="499" t="n"/>
+      <c r="H16" s="499" t="n"/>
+      <c r="I16" s="499" t="n"/>
+      <c r="J16" s="499" t="n"/>
+      <c r="K16" s="499" t="n"/>
+      <c r="L16" s="499" t="n"/>
+      <c r="M16" s="499" t="n"/>
+      <c r="N16" s="499" t="n"/>
+      <c r="O16" s="499" t="n"/>
+      <c r="P16" s="499" t="n"/>
+      <c r="Q16" s="499" t="n"/>
+      <c r="R16" s="499" t="n"/>
+      <c r="S16" s="499" t="n"/>
+      <c r="T16" s="499" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1">
       <c r="A17" s="369" t="n"/>
@@ -5939,21 +6295,21 @@
           <t>In force; Scheduled; Ended; Non-existent</t>
         </is>
       </c>
-      <c r="F17" s="444" t="n"/>
-      <c r="G17" s="445" t="n"/>
-      <c r="H17" s="445" t="n"/>
-      <c r="I17" s="445" t="n"/>
-      <c r="J17" s="445" t="n"/>
-      <c r="K17" s="445" t="n"/>
-      <c r="L17" s="445" t="n"/>
-      <c r="M17" s="445" t="n"/>
-      <c r="N17" s="445" t="n"/>
-      <c r="O17" s="445" t="n"/>
-      <c r="P17" s="445" t="n"/>
-      <c r="Q17" s="445" t="n"/>
-      <c r="R17" s="445" t="n"/>
-      <c r="S17" s="445" t="n"/>
-      <c r="T17" s="445" t="n"/>
+      <c r="F17" s="459" t="n"/>
+      <c r="G17" s="499" t="n"/>
+      <c r="H17" s="499" t="n"/>
+      <c r="I17" s="499" t="n"/>
+      <c r="J17" s="499" t="n"/>
+      <c r="K17" s="499" t="n"/>
+      <c r="L17" s="499" t="n"/>
+      <c r="M17" s="499" t="n"/>
+      <c r="N17" s="499" t="n"/>
+      <c r="O17" s="499" t="n"/>
+      <c r="P17" s="499" t="n"/>
+      <c r="Q17" s="499" t="n"/>
+      <c r="R17" s="499" t="n"/>
+      <c r="S17" s="499" t="n"/>
+      <c r="T17" s="499" t="n"/>
     </row>
     <row r="18" ht="15" customHeight="1">
       <c r="A18" s="369" t="n"/>
@@ -5977,21 +6333,21 @@
           <t>Fixed structure [mm/yyyy] or [yyyy]</t>
         </is>
       </c>
-      <c r="F18" s="444" t="n"/>
-      <c r="G18" s="445" t="n"/>
-      <c r="H18" s="445" t="n"/>
-      <c r="I18" s="445" t="n"/>
-      <c r="J18" s="445" t="n"/>
-      <c r="K18" s="445" t="n"/>
-      <c r="L18" s="445" t="n"/>
-      <c r="M18" s="445" t="n"/>
-      <c r="N18" s="445" t="n"/>
-      <c r="O18" s="445" t="n"/>
-      <c r="P18" s="445" t="n"/>
-      <c r="Q18" s="445" t="n"/>
-      <c r="R18" s="445" t="n"/>
-      <c r="S18" s="445" t="n"/>
-      <c r="T18" s="445" t="n"/>
+      <c r="F18" s="459" t="n"/>
+      <c r="G18" s="499" t="n"/>
+      <c r="H18" s="499" t="n"/>
+      <c r="I18" s="499" t="n"/>
+      <c r="J18" s="499" t="n"/>
+      <c r="K18" s="499" t="n"/>
+      <c r="L18" s="499" t="n"/>
+      <c r="M18" s="499" t="n"/>
+      <c r="N18" s="499" t="n"/>
+      <c r="O18" s="499" t="n"/>
+      <c r="P18" s="499" t="n"/>
+      <c r="Q18" s="499" t="n"/>
+      <c r="R18" s="499" t="n"/>
+      <c r="S18" s="499" t="n"/>
+      <c r="T18" s="499" t="n"/>
     </row>
     <row r="19" ht="15" customHeight="1">
       <c r="A19" s="369" t="n"/>
@@ -6015,21 +6371,21 @@
           <t>Fixed structure [mm/yyyy] or [yyyy]</t>
         </is>
       </c>
-      <c r="F19" s="444" t="n"/>
-      <c r="G19" s="445" t="n"/>
-      <c r="H19" s="445" t="n"/>
-      <c r="I19" s="445" t="n"/>
-      <c r="J19" s="445" t="n"/>
-      <c r="K19" s="445" t="n"/>
-      <c r="L19" s="445" t="n"/>
-      <c r="M19" s="445" t="n"/>
-      <c r="N19" s="445" t="n"/>
-      <c r="O19" s="445" t="n"/>
-      <c r="P19" s="445" t="n"/>
-      <c r="Q19" s="445" t="n"/>
-      <c r="R19" s="445" t="n"/>
-      <c r="S19" s="445" t="n"/>
-      <c r="T19" s="445" t="n"/>
+      <c r="F19" s="459" t="n"/>
+      <c r="G19" s="499" t="n"/>
+      <c r="H19" s="499" t="n"/>
+      <c r="I19" s="499" t="n"/>
+      <c r="J19" s="499" t="n"/>
+      <c r="K19" s="499" t="n"/>
+      <c r="L19" s="499" t="n"/>
+      <c r="M19" s="499" t="n"/>
+      <c r="N19" s="499" t="n"/>
+      <c r="O19" s="499" t="n"/>
+      <c r="P19" s="499" t="n"/>
+      <c r="Q19" s="499" t="n"/>
+      <c r="R19" s="499" t="n"/>
+      <c r="S19" s="499" t="n"/>
+      <c r="T19" s="499" t="n"/>
     </row>
     <row r="20" ht="15" customHeight="1">
       <c r="A20" s="369" t="n"/>
@@ -6053,21 +6409,21 @@
           <t>Fixed structure [mm/yyyy] or [yyyy]</t>
         </is>
       </c>
-      <c r="F20" s="444" t="n"/>
-      <c r="G20" s="445" t="n"/>
-      <c r="H20" s="445" t="n"/>
-      <c r="I20" s="445" t="n"/>
-      <c r="J20" s="445" t="n"/>
-      <c r="K20" s="445" t="n"/>
-      <c r="L20" s="445" t="n"/>
-      <c r="M20" s="445" t="n"/>
-      <c r="N20" s="445" t="n"/>
-      <c r="O20" s="445" t="n"/>
-      <c r="P20" s="445" t="n"/>
-      <c r="Q20" s="445" t="n"/>
-      <c r="R20" s="445" t="n"/>
-      <c r="S20" s="445" t="n"/>
-      <c r="T20" s="445" t="n"/>
+      <c r="F20" s="459" t="n"/>
+      <c r="G20" s="499" t="n"/>
+      <c r="H20" s="499" t="n"/>
+      <c r="I20" s="499" t="n"/>
+      <c r="J20" s="499" t="n"/>
+      <c r="K20" s="499" t="n"/>
+      <c r="L20" s="499" t="n"/>
+      <c r="M20" s="499" t="n"/>
+      <c r="N20" s="499" t="n"/>
+      <c r="O20" s="499" t="n"/>
+      <c r="P20" s="499" t="n"/>
+      <c r="Q20" s="499" t="n"/>
+      <c r="R20" s="499" t="n"/>
+      <c r="S20" s="499" t="n"/>
+      <c r="T20" s="499" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="369" t="n"/>
@@ -6091,21 +6447,21 @@
           <t>Fixed structure [mm/yyyy] or [yyyy]</t>
         </is>
       </c>
-      <c r="F21" s="444" t="n"/>
-      <c r="G21" s="445" t="n"/>
-      <c r="H21" s="445" t="n"/>
-      <c r="I21" s="445" t="n"/>
-      <c r="J21" s="445" t="n"/>
-      <c r="K21" s="445" t="n"/>
-      <c r="L21" s="445" t="n"/>
-      <c r="M21" s="445" t="n"/>
-      <c r="N21" s="445" t="n"/>
-      <c r="O21" s="445" t="n"/>
-      <c r="P21" s="445" t="n"/>
-      <c r="Q21" s="445" t="n"/>
-      <c r="R21" s="445" t="n"/>
-      <c r="S21" s="445" t="n"/>
-      <c r="T21" s="445" t="n"/>
+      <c r="F21" s="459" t="n"/>
+      <c r="G21" s="499" t="n"/>
+      <c r="H21" s="499" t="n"/>
+      <c r="I21" s="499" t="n"/>
+      <c r="J21" s="499" t="n"/>
+      <c r="K21" s="499" t="n"/>
+      <c r="L21" s="499" t="n"/>
+      <c r="M21" s="499" t="n"/>
+      <c r="N21" s="499" t="n"/>
+      <c r="O21" s="499" t="n"/>
+      <c r="P21" s="499" t="n"/>
+      <c r="Q21" s="499" t="n"/>
+      <c r="R21" s="499" t="n"/>
+      <c r="S21" s="499" t="n"/>
+      <c r="T21" s="499" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
       <c r="A22" s="369" t="n"/>
@@ -6125,21 +6481,21 @@
         </is>
       </c>
       <c r="E22" s="449" t="n"/>
-      <c r="F22" s="444" t="n"/>
-      <c r="G22" s="445" t="n"/>
-      <c r="H22" s="445" t="n"/>
-      <c r="I22" s="445" t="n"/>
-      <c r="J22" s="445" t="n"/>
-      <c r="K22" s="445" t="n"/>
-      <c r="L22" s="445" t="n"/>
-      <c r="M22" s="445" t="n"/>
-      <c r="N22" s="445" t="n"/>
-      <c r="O22" s="445" t="n"/>
-      <c r="P22" s="445" t="n"/>
-      <c r="Q22" s="445" t="n"/>
-      <c r="R22" s="445" t="n"/>
-      <c r="S22" s="445" t="n"/>
-      <c r="T22" s="445" t="n"/>
+      <c r="F22" s="459" t="n"/>
+      <c r="G22" s="499" t="n"/>
+      <c r="H22" s="499" t="n"/>
+      <c r="I22" s="499" t="n"/>
+      <c r="J22" s="499" t="n"/>
+      <c r="K22" s="499" t="n"/>
+      <c r="L22" s="499" t="n"/>
+      <c r="M22" s="499" t="n"/>
+      <c r="N22" s="499" t="n"/>
+      <c r="O22" s="499" t="n"/>
+      <c r="P22" s="499" t="n"/>
+      <c r="Q22" s="499" t="n"/>
+      <c r="R22" s="499" t="n"/>
+      <c r="S22" s="499" t="n"/>
+      <c r="T22" s="499" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
       <c r="A23" s="361" t="n"/>
@@ -6163,21 +6519,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F23" s="444" t="n"/>
-      <c r="G23" s="445" t="n"/>
-      <c r="H23" s="445" t="n"/>
-      <c r="I23" s="445" t="n"/>
-      <c r="J23" s="445" t="n"/>
-      <c r="K23" s="445" t="n"/>
-      <c r="L23" s="445" t="n"/>
-      <c r="M23" s="445" t="n"/>
-      <c r="N23" s="445" t="n"/>
-      <c r="O23" s="445" t="n"/>
-      <c r="P23" s="445" t="n"/>
-      <c r="Q23" s="445" t="n"/>
-      <c r="R23" s="445" t="n"/>
-      <c r="S23" s="445" t="n"/>
-      <c r="T23" s="445" t="n"/>
+      <c r="F23" s="459" t="n"/>
+      <c r="G23" s="499" t="n"/>
+      <c r="H23" s="499" t="n"/>
+      <c r="I23" s="499" t="n"/>
+      <c r="J23" s="499" t="n"/>
+      <c r="K23" s="499" t="n"/>
+      <c r="L23" s="499" t="n"/>
+      <c r="M23" s="499" t="n"/>
+      <c r="N23" s="499" t="n"/>
+      <c r="O23" s="499" t="n"/>
+      <c r="P23" s="499" t="n"/>
+      <c r="Q23" s="499" t="n"/>
+      <c r="R23" s="499" t="n"/>
+      <c r="S23" s="499" t="n"/>
+      <c r="T23" s="499" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
       <c r="A24" s="452" t="inlineStr">
@@ -6205,21 +6561,21 @@
           <t>Non-exhaustive list</t>
         </is>
       </c>
-      <c r="F24" s="444" t="n"/>
-      <c r="G24" s="445" t="n"/>
-      <c r="H24" s="445" t="n"/>
-      <c r="I24" s="445" t="n"/>
-      <c r="J24" s="445" t="n"/>
-      <c r="K24" s="445" t="n"/>
-      <c r="L24" s="445" t="n"/>
-      <c r="M24" s="445" t="n"/>
-      <c r="N24" s="445" t="n"/>
-      <c r="O24" s="445" t="n"/>
-      <c r="P24" s="445" t="n"/>
-      <c r="Q24" s="445" t="n"/>
-      <c r="R24" s="445" t="n"/>
-      <c r="S24" s="445" t="n"/>
-      <c r="T24" s="445" t="n"/>
+      <c r="F24" s="459" t="n"/>
+      <c r="G24" s="499" t="n"/>
+      <c r="H24" s="499" t="n"/>
+      <c r="I24" s="499" t="n"/>
+      <c r="J24" s="499" t="n"/>
+      <c r="K24" s="499" t="n"/>
+      <c r="L24" s="499" t="n"/>
+      <c r="M24" s="499" t="n"/>
+      <c r="N24" s="499" t="n"/>
+      <c r="O24" s="499" t="n"/>
+      <c r="P24" s="499" t="n"/>
+      <c r="Q24" s="499" t="n"/>
+      <c r="R24" s="499" t="n"/>
+      <c r="S24" s="499" t="n"/>
+      <c r="T24" s="499" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1">
       <c r="A25" s="369" t="n"/>
@@ -6243,21 +6599,21 @@
           <t>New; existing</t>
         </is>
       </c>
-      <c r="F25" s="444" t="n"/>
-      <c r="G25" s="445" t="n"/>
-      <c r="H25" s="445" t="n"/>
-      <c r="I25" s="445" t="n"/>
-      <c r="J25" s="445" t="n"/>
-      <c r="K25" s="445" t="n"/>
-      <c r="L25" s="445" t="n"/>
-      <c r="M25" s="445" t="n"/>
-      <c r="N25" s="445" t="n"/>
-      <c r="O25" s="445" t="n"/>
-      <c r="P25" s="445" t="n"/>
-      <c r="Q25" s="445" t="n"/>
-      <c r="R25" s="445" t="n"/>
-      <c r="S25" s="445" t="n"/>
-      <c r="T25" s="445" t="n"/>
+      <c r="F25" s="459" t="n"/>
+      <c r="G25" s="499" t="n"/>
+      <c r="H25" s="499" t="n"/>
+      <c r="I25" s="499" t="n"/>
+      <c r="J25" s="499" t="n"/>
+      <c r="K25" s="499" t="n"/>
+      <c r="L25" s="499" t="n"/>
+      <c r="M25" s="499" t="n"/>
+      <c r="N25" s="499" t="n"/>
+      <c r="O25" s="499" t="n"/>
+      <c r="P25" s="499" t="n"/>
+      <c r="Q25" s="499" t="n"/>
+      <c r="R25" s="499" t="n"/>
+      <c r="S25" s="499" t="n"/>
+      <c r="T25" s="499" t="n"/>
     </row>
     <row r="26" ht="15" customHeight="1">
       <c r="A26" s="369" t="n"/>
@@ -6281,21 +6637,21 @@
           <t>Non-exhaustive list</t>
         </is>
       </c>
-      <c r="F26" s="444" t="n"/>
-      <c r="G26" s="445" t="n"/>
-      <c r="H26" s="445" t="n"/>
-      <c r="I26" s="445" t="n"/>
-      <c r="J26" s="445" t="n"/>
-      <c r="K26" s="445" t="n"/>
-      <c r="L26" s="445" t="n"/>
-      <c r="M26" s="445" t="n"/>
-      <c r="N26" s="445" t="n"/>
-      <c r="O26" s="445" t="n"/>
-      <c r="P26" s="445" t="n"/>
-      <c r="Q26" s="445" t="n"/>
-      <c r="R26" s="445" t="n"/>
-      <c r="S26" s="445" t="n"/>
-      <c r="T26" s="445" t="n"/>
+      <c r="F26" s="459" t="n"/>
+      <c r="G26" s="499" t="n"/>
+      <c r="H26" s="499" t="n"/>
+      <c r="I26" s="499" t="n"/>
+      <c r="J26" s="499" t="n"/>
+      <c r="K26" s="499" t="n"/>
+      <c r="L26" s="499" t="n"/>
+      <c r="M26" s="499" t="n"/>
+      <c r="N26" s="499" t="n"/>
+      <c r="O26" s="499" t="n"/>
+      <c r="P26" s="499" t="n"/>
+      <c r="Q26" s="499" t="n"/>
+      <c r="R26" s="499" t="n"/>
+      <c r="S26" s="499" t="n"/>
+      <c r="T26" s="499" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1">
       <c r="A27" s="369" t="n"/>
@@ -6319,21 +6675,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F27" s="444" t="n"/>
-      <c r="G27" s="445" t="n"/>
-      <c r="H27" s="445" t="n"/>
-      <c r="I27" s="445" t="n"/>
-      <c r="J27" s="445" t="n"/>
-      <c r="K27" s="445" t="n"/>
-      <c r="L27" s="445" t="n"/>
-      <c r="M27" s="445" t="n"/>
-      <c r="N27" s="445" t="n"/>
-      <c r="O27" s="445" t="n"/>
-      <c r="P27" s="445" t="n"/>
-      <c r="Q27" s="445" t="n"/>
-      <c r="R27" s="445" t="n"/>
-      <c r="S27" s="445" t="n"/>
-      <c r="T27" s="445" t="n"/>
+      <c r="F27" s="459" t="n"/>
+      <c r="G27" s="499" t="n"/>
+      <c r="H27" s="499" t="n"/>
+      <c r="I27" s="499" t="n"/>
+      <c r="J27" s="499" t="n"/>
+      <c r="K27" s="499" t="n"/>
+      <c r="L27" s="499" t="n"/>
+      <c r="M27" s="499" t="n"/>
+      <c r="N27" s="499" t="n"/>
+      <c r="O27" s="499" t="n"/>
+      <c r="P27" s="499" t="n"/>
+      <c r="Q27" s="499" t="n"/>
+      <c r="R27" s="499" t="n"/>
+      <c r="S27" s="499" t="n"/>
+      <c r="T27" s="499" t="n"/>
     </row>
     <row r="28" ht="15" customHeight="1">
       <c r="A28" s="369" t="n"/>
@@ -6357,21 +6713,21 @@
           <t>[XXXX ; YYYY] + unit</t>
         </is>
       </c>
-      <c r="F28" s="444" t="n"/>
-      <c r="G28" s="445" t="n"/>
-      <c r="H28" s="445" t="n"/>
-      <c r="I28" s="445" t="n"/>
-      <c r="J28" s="445" t="n"/>
-      <c r="K28" s="445" t="n"/>
-      <c r="L28" s="445" t="n"/>
-      <c r="M28" s="445" t="n"/>
-      <c r="N28" s="445" t="n"/>
-      <c r="O28" s="445" t="n"/>
-      <c r="P28" s="445" t="n"/>
-      <c r="Q28" s="445" t="n"/>
-      <c r="R28" s="445" t="n"/>
-      <c r="S28" s="445" t="n"/>
-      <c r="T28" s="445" t="n"/>
+      <c r="F28" s="459" t="n"/>
+      <c r="G28" s="499" t="n"/>
+      <c r="H28" s="499" t="n"/>
+      <c r="I28" s="499" t="n"/>
+      <c r="J28" s="499" t="n"/>
+      <c r="K28" s="499" t="n"/>
+      <c r="L28" s="499" t="n"/>
+      <c r="M28" s="499" t="n"/>
+      <c r="N28" s="499" t="n"/>
+      <c r="O28" s="499" t="n"/>
+      <c r="P28" s="499" t="n"/>
+      <c r="Q28" s="499" t="n"/>
+      <c r="R28" s="499" t="n"/>
+      <c r="S28" s="499" t="n"/>
+      <c r="T28" s="499" t="n"/>
     </row>
     <row r="29" ht="15" customHeight="1">
       <c r="A29" s="369" t="n"/>
@@ -6395,21 +6751,21 @@
           <t>Households; Firms; Governments; Non-governmental organisations</t>
         </is>
       </c>
-      <c r="F29" s="444" t="n"/>
-      <c r="G29" s="445" t="n"/>
-      <c r="H29" s="445" t="n"/>
-      <c r="I29" s="445" t="n"/>
-      <c r="J29" s="445" t="n"/>
-      <c r="K29" s="445" t="n"/>
-      <c r="L29" s="445" t="n"/>
-      <c r="M29" s="445" t="n"/>
-      <c r="N29" s="445" t="n"/>
-      <c r="O29" s="445" t="n"/>
-      <c r="P29" s="445" t="n"/>
-      <c r="Q29" s="445" t="n"/>
-      <c r="R29" s="445" t="n"/>
-      <c r="S29" s="445" t="n"/>
-      <c r="T29" s="445" t="n"/>
+      <c r="F29" s="459" t="n"/>
+      <c r="G29" s="499" t="n"/>
+      <c r="H29" s="499" t="n"/>
+      <c r="I29" s="499" t="n"/>
+      <c r="J29" s="499" t="n"/>
+      <c r="K29" s="499" t="n"/>
+      <c r="L29" s="499" t="n"/>
+      <c r="M29" s="499" t="n"/>
+      <c r="N29" s="499" t="n"/>
+      <c r="O29" s="499" t="n"/>
+      <c r="P29" s="499" t="n"/>
+      <c r="Q29" s="499" t="n"/>
+      <c r="R29" s="499" t="n"/>
+      <c r="S29" s="499" t="n"/>
+      <c r="T29" s="499" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1">
       <c r="A30" s="369" t="n"/>
@@ -6433,21 +6789,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F30" s="444" t="n"/>
-      <c r="G30" s="445" t="n"/>
-      <c r="H30" s="445" t="n"/>
-      <c r="I30" s="445" t="n"/>
-      <c r="J30" s="445" t="n"/>
-      <c r="K30" s="445" t="n"/>
-      <c r="L30" s="445" t="n"/>
-      <c r="M30" s="445" t="n"/>
-      <c r="N30" s="445" t="n"/>
-      <c r="O30" s="445" t="n"/>
-      <c r="P30" s="445" t="n"/>
-      <c r="Q30" s="445" t="n"/>
-      <c r="R30" s="445" t="n"/>
-      <c r="S30" s="445" t="n"/>
-      <c r="T30" s="445" t="n"/>
+      <c r="F30" s="459" t="n"/>
+      <c r="G30" s="499" t="n"/>
+      <c r="H30" s="499" t="n"/>
+      <c r="I30" s="499" t="n"/>
+      <c r="J30" s="499" t="n"/>
+      <c r="K30" s="499" t="n"/>
+      <c r="L30" s="499" t="n"/>
+      <c r="M30" s="499" t="n"/>
+      <c r="N30" s="499" t="n"/>
+      <c r="O30" s="499" t="n"/>
+      <c r="P30" s="499" t="n"/>
+      <c r="Q30" s="499" t="n"/>
+      <c r="R30" s="499" t="n"/>
+      <c r="S30" s="499" t="n"/>
+      <c r="T30" s="499" t="n"/>
     </row>
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="369" t="n"/>
@@ -6471,21 +6827,21 @@
           <t>Non-exhaustive list</t>
         </is>
       </c>
-      <c r="F31" s="444" t="n"/>
-      <c r="G31" s="445" t="n"/>
-      <c r="H31" s="445" t="n"/>
-      <c r="I31" s="445" t="n"/>
-      <c r="J31" s="445" t="n"/>
-      <c r="K31" s="445" t="n"/>
-      <c r="L31" s="445" t="n"/>
-      <c r="M31" s="445" t="n"/>
-      <c r="N31" s="445" t="n"/>
-      <c r="O31" s="445" t="n"/>
-      <c r="P31" s="445" t="n"/>
-      <c r="Q31" s="445" t="n"/>
-      <c r="R31" s="445" t="n"/>
-      <c r="S31" s="445" t="n"/>
-      <c r="T31" s="445" t="n"/>
+      <c r="F31" s="459" t="n"/>
+      <c r="G31" s="499" t="n"/>
+      <c r="H31" s="499" t="n"/>
+      <c r="I31" s="499" t="n"/>
+      <c r="J31" s="499" t="n"/>
+      <c r="K31" s="499" t="n"/>
+      <c r="L31" s="499" t="n"/>
+      <c r="M31" s="499" t="n"/>
+      <c r="N31" s="499" t="n"/>
+      <c r="O31" s="499" t="n"/>
+      <c r="P31" s="499" t="n"/>
+      <c r="Q31" s="499" t="n"/>
+      <c r="R31" s="499" t="n"/>
+      <c r="S31" s="499" t="n"/>
+      <c r="T31" s="499" t="n"/>
     </row>
     <row r="32" ht="15" customHeight="1">
       <c r="A32" s="369" t="n"/>
@@ -6509,21 +6865,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F32" s="444" t="n"/>
-      <c r="G32" s="445" t="n"/>
-      <c r="H32" s="445" t="n"/>
-      <c r="I32" s="445" t="n"/>
-      <c r="J32" s="445" t="n"/>
-      <c r="K32" s="445" t="n"/>
-      <c r="L32" s="445" t="n"/>
-      <c r="M32" s="445" t="n"/>
-      <c r="N32" s="445" t="n"/>
-      <c r="O32" s="445" t="n"/>
-      <c r="P32" s="445" t="n"/>
-      <c r="Q32" s="445" t="n"/>
-      <c r="R32" s="445" t="n"/>
-      <c r="S32" s="445" t="n"/>
-      <c r="T32" s="445" t="n"/>
+      <c r="F32" s="459" t="n"/>
+      <c r="G32" s="499" t="n"/>
+      <c r="H32" s="499" t="n"/>
+      <c r="I32" s="499" t="n"/>
+      <c r="J32" s="499" t="n"/>
+      <c r="K32" s="499" t="n"/>
+      <c r="L32" s="499" t="n"/>
+      <c r="M32" s="499" t="n"/>
+      <c r="N32" s="499" t="n"/>
+      <c r="O32" s="499" t="n"/>
+      <c r="P32" s="499" t="n"/>
+      <c r="Q32" s="499" t="n"/>
+      <c r="R32" s="499" t="n"/>
+      <c r="S32" s="499" t="n"/>
+      <c r="T32" s="499" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1">
       <c r="A33" s="369" t="n"/>
@@ -6547,21 +6903,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F33" s="444" t="n"/>
-      <c r="G33" s="445" t="n"/>
-      <c r="H33" s="445" t="n"/>
-      <c r="I33" s="445" t="n"/>
-      <c r="J33" s="445" t="n"/>
-      <c r="K33" s="445" t="n"/>
-      <c r="L33" s="445" t="n"/>
-      <c r="M33" s="445" t="n"/>
-      <c r="N33" s="445" t="n"/>
-      <c r="O33" s="445" t="n"/>
-      <c r="P33" s="445" t="n"/>
-      <c r="Q33" s="445" t="n"/>
-      <c r="R33" s="445" t="n"/>
-      <c r="S33" s="445" t="n"/>
-      <c r="T33" s="445" t="n"/>
+      <c r="F33" s="459" t="n"/>
+      <c r="G33" s="499" t="n"/>
+      <c r="H33" s="499" t="n"/>
+      <c r="I33" s="499" t="n"/>
+      <c r="J33" s="499" t="n"/>
+      <c r="K33" s="499" t="n"/>
+      <c r="L33" s="499" t="n"/>
+      <c r="M33" s="499" t="n"/>
+      <c r="N33" s="499" t="n"/>
+      <c r="O33" s="499" t="n"/>
+      <c r="P33" s="499" t="n"/>
+      <c r="Q33" s="499" t="n"/>
+      <c r="R33" s="499" t="n"/>
+      <c r="S33" s="499" t="n"/>
+      <c r="T33" s="499" t="n"/>
     </row>
     <row r="34" ht="15" customHeight="1">
       <c r="A34" s="369" t="n"/>
@@ -6585,21 +6941,21 @@
           <t>[unit as stated in the regulation]</t>
         </is>
       </c>
-      <c r="F34" s="444" t="n"/>
-      <c r="G34" s="445" t="n"/>
-      <c r="H34" s="445" t="n"/>
-      <c r="I34" s="445" t="n"/>
-      <c r="J34" s="445" t="n"/>
-      <c r="K34" s="445" t="n"/>
-      <c r="L34" s="445" t="n"/>
-      <c r="M34" s="445" t="n"/>
-      <c r="N34" s="445" t="n"/>
-      <c r="O34" s="445" t="n"/>
-      <c r="P34" s="445" t="n"/>
-      <c r="Q34" s="445" t="n"/>
-      <c r="R34" s="445" t="n"/>
-      <c r="S34" s="445" t="n"/>
-      <c r="T34" s="445" t="n"/>
+      <c r="F34" s="459" t="n"/>
+      <c r="G34" s="499" t="n"/>
+      <c r="H34" s="499" t="n"/>
+      <c r="I34" s="499" t="n"/>
+      <c r="J34" s="499" t="n"/>
+      <c r="K34" s="499" t="n"/>
+      <c r="L34" s="499" t="n"/>
+      <c r="M34" s="499" t="n"/>
+      <c r="N34" s="499" t="n"/>
+      <c r="O34" s="499" t="n"/>
+      <c r="P34" s="499" t="n"/>
+      <c r="Q34" s="499" t="n"/>
+      <c r="R34" s="499" t="n"/>
+      <c r="S34" s="499" t="n"/>
+      <c r="T34" s="499" t="n"/>
     </row>
     <row r="35" ht="15" customHeight="1">
       <c r="A35" s="369" t="n"/>
@@ -6623,21 +6979,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F35" s="444" t="n"/>
-      <c r="G35" s="445" t="n"/>
-      <c r="H35" s="445" t="n"/>
-      <c r="I35" s="445" t="n"/>
-      <c r="J35" s="445" t="n"/>
-      <c r="K35" s="445" t="n"/>
-      <c r="L35" s="445" t="n"/>
-      <c r="M35" s="445" t="n"/>
-      <c r="N35" s="445" t="n"/>
-      <c r="O35" s="445" t="n"/>
-      <c r="P35" s="445" t="n"/>
-      <c r="Q35" s="445" t="n"/>
-      <c r="R35" s="445" t="n"/>
-      <c r="S35" s="445" t="n"/>
-      <c r="T35" s="445" t="n"/>
+      <c r="F35" s="459" t="n"/>
+      <c r="G35" s="499" t="n"/>
+      <c r="H35" s="499" t="n"/>
+      <c r="I35" s="499" t="n"/>
+      <c r="J35" s="499" t="n"/>
+      <c r="K35" s="499" t="n"/>
+      <c r="L35" s="499" t="n"/>
+      <c r="M35" s="499" t="n"/>
+      <c r="N35" s="499" t="n"/>
+      <c r="O35" s="499" t="n"/>
+      <c r="P35" s="499" t="n"/>
+      <c r="Q35" s="499" t="n"/>
+      <c r="R35" s="499" t="n"/>
+      <c r="S35" s="499" t="n"/>
+      <c r="T35" s="499" t="n"/>
     </row>
     <row r="36" ht="15" customHeight="1">
       <c r="A36" s="369" t="n"/>
@@ -6661,21 +7017,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F36" s="444" t="n"/>
-      <c r="G36" s="445" t="n"/>
-      <c r="H36" s="445" t="n"/>
-      <c r="I36" s="445" t="n"/>
-      <c r="J36" s="445" t="n"/>
-      <c r="K36" s="445" t="n"/>
-      <c r="L36" s="445" t="n"/>
-      <c r="M36" s="445" t="n"/>
-      <c r="N36" s="445" t="n"/>
-      <c r="O36" s="445" t="n"/>
-      <c r="P36" s="445" t="n"/>
-      <c r="Q36" s="445" t="n"/>
-      <c r="R36" s="445" t="n"/>
-      <c r="S36" s="445" t="n"/>
-      <c r="T36" s="445" t="n"/>
+      <c r="F36" s="459" t="n"/>
+      <c r="G36" s="499" t="n"/>
+      <c r="H36" s="499" t="n"/>
+      <c r="I36" s="499" t="n"/>
+      <c r="J36" s="499" t="n"/>
+      <c r="K36" s="499" t="n"/>
+      <c r="L36" s="499" t="n"/>
+      <c r="M36" s="499" t="n"/>
+      <c r="N36" s="499" t="n"/>
+      <c r="O36" s="499" t="n"/>
+      <c r="P36" s="499" t="n"/>
+      <c r="Q36" s="499" t="n"/>
+      <c r="R36" s="499" t="n"/>
+      <c r="S36" s="499" t="n"/>
+      <c r="T36" s="499" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
       <c r="A37" s="369" t="n"/>
@@ -6699,21 +7055,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F37" s="444" t="n"/>
-      <c r="G37" s="445" t="n"/>
-      <c r="H37" s="445" t="n"/>
-      <c r="I37" s="445" t="n"/>
-      <c r="J37" s="445" t="n"/>
-      <c r="K37" s="445" t="n"/>
-      <c r="L37" s="445" t="n"/>
-      <c r="M37" s="445" t="n"/>
-      <c r="N37" s="445" t="n"/>
-      <c r="O37" s="445" t="n"/>
-      <c r="P37" s="445" t="n"/>
-      <c r="Q37" s="445" t="n"/>
-      <c r="R37" s="445" t="n"/>
-      <c r="S37" s="445" t="n"/>
-      <c r="T37" s="445" t="n"/>
+      <c r="F37" s="459" t="n"/>
+      <c r="G37" s="499" t="n"/>
+      <c r="H37" s="499" t="n"/>
+      <c r="I37" s="499" t="n"/>
+      <c r="J37" s="499" t="n"/>
+      <c r="K37" s="499" t="n"/>
+      <c r="L37" s="499" t="n"/>
+      <c r="M37" s="499" t="n"/>
+      <c r="N37" s="499" t="n"/>
+      <c r="O37" s="499" t="n"/>
+      <c r="P37" s="499" t="n"/>
+      <c r="Q37" s="499" t="n"/>
+      <c r="R37" s="499" t="n"/>
+      <c r="S37" s="499" t="n"/>
+      <c r="T37" s="499" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
       <c r="A38" s="361" t="n"/>
@@ -6737,21 +7093,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F38" s="444" t="n"/>
-      <c r="G38" s="445" t="n"/>
-      <c r="H38" s="445" t="n"/>
-      <c r="I38" s="445" t="n"/>
-      <c r="J38" s="445" t="n"/>
-      <c r="K38" s="445" t="n"/>
-      <c r="L38" s="445" t="n"/>
-      <c r="M38" s="445" t="n"/>
-      <c r="N38" s="445" t="n"/>
-      <c r="O38" s="445" t="n"/>
-      <c r="P38" s="445" t="n"/>
-      <c r="Q38" s="445" t="n"/>
-      <c r="R38" s="445" t="n"/>
-      <c r="S38" s="445" t="n"/>
-      <c r="T38" s="445" t="n"/>
+      <c r="F38" s="459" t="n"/>
+      <c r="G38" s="499" t="n"/>
+      <c r="H38" s="499" t="n"/>
+      <c r="I38" s="499" t="n"/>
+      <c r="J38" s="499" t="n"/>
+      <c r="K38" s="499" t="n"/>
+      <c r="L38" s="499" t="n"/>
+      <c r="M38" s="499" t="n"/>
+      <c r="N38" s="499" t="n"/>
+      <c r="O38" s="499" t="n"/>
+      <c r="P38" s="499" t="n"/>
+      <c r="Q38" s="499" t="n"/>
+      <c r="R38" s="499" t="n"/>
+      <c r="S38" s="499" t="n"/>
+      <c r="T38" s="499" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
       <c r="A39" s="452" t="inlineStr">
@@ -6779,21 +7135,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F39" s="444" t="n"/>
-      <c r="G39" s="445" t="n"/>
-      <c r="H39" s="445" t="n"/>
-      <c r="I39" s="445" t="n"/>
-      <c r="J39" s="445" t="n"/>
-      <c r="K39" s="445" t="n"/>
-      <c r="L39" s="445" t="n"/>
-      <c r="M39" s="445" t="n"/>
-      <c r="N39" s="445" t="n"/>
-      <c r="O39" s="445" t="n"/>
-      <c r="P39" s="445" t="n"/>
-      <c r="Q39" s="445" t="n"/>
-      <c r="R39" s="445" t="n"/>
-      <c r="S39" s="445" t="n"/>
-      <c r="T39" s="445" t="n"/>
+      <c r="F39" s="459" t="n"/>
+      <c r="G39" s="499" t="n"/>
+      <c r="H39" s="499" t="n"/>
+      <c r="I39" s="499" t="n"/>
+      <c r="J39" s="499" t="n"/>
+      <c r="K39" s="499" t="n"/>
+      <c r="L39" s="499" t="n"/>
+      <c r="M39" s="499" t="n"/>
+      <c r="N39" s="499" t="n"/>
+      <c r="O39" s="499" t="n"/>
+      <c r="P39" s="499" t="n"/>
+      <c r="Q39" s="499" t="n"/>
+      <c r="R39" s="499" t="n"/>
+      <c r="S39" s="499" t="n"/>
+      <c r="T39" s="499" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
       <c r="A40" s="369" t="n"/>
@@ -6817,21 +7173,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F40" s="444" t="n"/>
-      <c r="G40" s="445" t="n"/>
-      <c r="H40" s="445" t="n"/>
-      <c r="I40" s="445" t="n"/>
-      <c r="J40" s="445" t="n"/>
-      <c r="K40" s="445" t="n"/>
-      <c r="L40" s="445" t="n"/>
-      <c r="M40" s="445" t="n"/>
-      <c r="N40" s="445" t="n"/>
-      <c r="O40" s="445" t="n"/>
-      <c r="P40" s="445" t="n"/>
-      <c r="Q40" s="445" t="n"/>
-      <c r="R40" s="445" t="n"/>
-      <c r="S40" s="445" t="n"/>
-      <c r="T40" s="445" t="n"/>
+      <c r="F40" s="459" t="n"/>
+      <c r="G40" s="499" t="n"/>
+      <c r="H40" s="499" t="n"/>
+      <c r="I40" s="499" t="n"/>
+      <c r="J40" s="499" t="n"/>
+      <c r="K40" s="499" t="n"/>
+      <c r="L40" s="499" t="n"/>
+      <c r="M40" s="499" t="n"/>
+      <c r="N40" s="499" t="n"/>
+      <c r="O40" s="499" t="n"/>
+      <c r="P40" s="499" t="n"/>
+      <c r="Q40" s="499" t="n"/>
+      <c r="R40" s="499" t="n"/>
+      <c r="S40" s="499" t="n"/>
+      <c r="T40" s="499" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
       <c r="A41" s="361" t="n"/>
@@ -6855,21 +7211,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F41" s="444" t="n"/>
-      <c r="G41" s="445" t="n"/>
-      <c r="H41" s="445" t="n"/>
-      <c r="I41" s="445" t="n"/>
-      <c r="J41" s="445" t="n"/>
-      <c r="K41" s="445" t="n"/>
-      <c r="L41" s="445" t="n"/>
-      <c r="M41" s="445" t="n"/>
-      <c r="N41" s="445" t="n"/>
-      <c r="O41" s="445" t="n"/>
-      <c r="P41" s="445" t="n"/>
-      <c r="Q41" s="445" t="n"/>
-      <c r="R41" s="445" t="n"/>
-      <c r="S41" s="445" t="n"/>
-      <c r="T41" s="445" t="n"/>
+      <c r="F41" s="459" t="n"/>
+      <c r="G41" s="499" t="n"/>
+      <c r="H41" s="499" t="n"/>
+      <c r="I41" s="499" t="n"/>
+      <c r="J41" s="499" t="n"/>
+      <c r="K41" s="499" t="n"/>
+      <c r="L41" s="499" t="n"/>
+      <c r="M41" s="499" t="n"/>
+      <c r="N41" s="499" t="n"/>
+      <c r="O41" s="499" t="n"/>
+      <c r="P41" s="499" t="n"/>
+      <c r="Q41" s="499" t="n"/>
+      <c r="R41" s="499" t="n"/>
+      <c r="S41" s="499" t="n"/>
+      <c r="T41" s="499" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
       <c r="A42" s="452" t="inlineStr">
@@ -6897,21 +7253,21 @@
           <t>in KtCO2eq</t>
         </is>
       </c>
-      <c r="F42" s="453" t="n"/>
-      <c r="G42" s="454" t="n"/>
-      <c r="H42" s="454" t="n"/>
-      <c r="I42" s="455" t="n"/>
-      <c r="J42" s="445" t="n"/>
-      <c r="K42" s="445" t="n"/>
-      <c r="L42" s="445" t="n"/>
-      <c r="M42" s="445" t="n"/>
-      <c r="N42" s="445" t="n"/>
-      <c r="O42" s="445" t="n"/>
-      <c r="P42" s="445" t="n"/>
-      <c r="Q42" s="445" t="n"/>
-      <c r="R42" s="445" t="n"/>
-      <c r="S42" s="445" t="n"/>
-      <c r="T42" s="445" t="n"/>
+      <c r="F42" s="500" t="n"/>
+      <c r="G42" s="501" t="n"/>
+      <c r="H42" s="501" t="n"/>
+      <c r="I42" s="502" t="n"/>
+      <c r="J42" s="499" t="n"/>
+      <c r="K42" s="499" t="n"/>
+      <c r="L42" s="499" t="n"/>
+      <c r="M42" s="499" t="n"/>
+      <c r="N42" s="499" t="n"/>
+      <c r="O42" s="499" t="n"/>
+      <c r="P42" s="499" t="n"/>
+      <c r="Q42" s="499" t="n"/>
+      <c r="R42" s="499" t="n"/>
+      <c r="S42" s="499" t="n"/>
+      <c r="T42" s="499" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
       <c r="A43" s="361" t="n"/>
@@ -6935,21 +7291,21 @@
           <t>in % [over domestic emissions]</t>
         </is>
       </c>
-      <c r="F43" s="453" t="n"/>
-      <c r="G43" s="454" t="n"/>
-      <c r="H43" s="454" t="n"/>
-      <c r="I43" s="455" t="n"/>
-      <c r="J43" s="445" t="n"/>
-      <c r="K43" s="445" t="n"/>
-      <c r="L43" s="445" t="n"/>
-      <c r="M43" s="445" t="n"/>
-      <c r="N43" s="445" t="n"/>
-      <c r="O43" s="445" t="n"/>
-      <c r="P43" s="445" t="n"/>
-      <c r="Q43" s="445" t="n"/>
-      <c r="R43" s="445" t="n"/>
-      <c r="S43" s="445" t="n"/>
-      <c r="T43" s="445" t="n"/>
+      <c r="F43" s="500" t="n"/>
+      <c r="G43" s="501" t="n"/>
+      <c r="H43" s="501" t="n"/>
+      <c r="I43" s="502" t="n"/>
+      <c r="J43" s="499" t="n"/>
+      <c r="K43" s="499" t="n"/>
+      <c r="L43" s="499" t="n"/>
+      <c r="M43" s="499" t="n"/>
+      <c r="N43" s="499" t="n"/>
+      <c r="O43" s="499" t="n"/>
+      <c r="P43" s="499" t="n"/>
+      <c r="Q43" s="499" t="n"/>
+      <c r="R43" s="499" t="n"/>
+      <c r="S43" s="499" t="n"/>
+      <c r="T43" s="499" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
       <c r="A44" s="452" t="inlineStr">
@@ -6977,21 +7333,21 @@
           <t>2-digit ISIC classification</t>
         </is>
       </c>
-      <c r="F44" s="444" t="n"/>
-      <c r="G44" s="445" t="n"/>
-      <c r="H44" s="445" t="n"/>
-      <c r="I44" s="445" t="n"/>
-      <c r="J44" s="445" t="n"/>
-      <c r="K44" s="445" t="n"/>
-      <c r="L44" s="445" t="n"/>
-      <c r="M44" s="445" t="n"/>
-      <c r="N44" s="445" t="n"/>
-      <c r="O44" s="445" t="n"/>
-      <c r="P44" s="445" t="n"/>
-      <c r="Q44" s="445" t="n"/>
-      <c r="R44" s="445" t="n"/>
-      <c r="S44" s="445" t="n"/>
-      <c r="T44" s="445" t="n"/>
+      <c r="F44" s="459" t="n"/>
+      <c r="G44" s="499" t="n"/>
+      <c r="H44" s="499" t="n"/>
+      <c r="I44" s="499" t="n"/>
+      <c r="J44" s="499" t="n"/>
+      <c r="K44" s="499" t="n"/>
+      <c r="L44" s="499" t="n"/>
+      <c r="M44" s="499" t="n"/>
+      <c r="N44" s="499" t="n"/>
+      <c r="O44" s="499" t="n"/>
+      <c r="P44" s="499" t="n"/>
+      <c r="Q44" s="499" t="n"/>
+      <c r="R44" s="499" t="n"/>
+      <c r="S44" s="499" t="n"/>
+      <c r="T44" s="499" t="n"/>
     </row>
     <row r="45" ht="15" customHeight="1">
       <c r="A45" s="369" t="n"/>
@@ -7015,21 +7371,21 @@
           <t>CO2; CH4; N2O; SF6; HFCs; PFCs; NF3</t>
         </is>
       </c>
-      <c r="F45" s="444" t="n"/>
-      <c r="G45" s="445" t="n"/>
-      <c r="H45" s="445" t="n"/>
-      <c r="I45" s="445" t="n"/>
-      <c r="J45" s="445" t="n"/>
-      <c r="K45" s="445" t="n"/>
-      <c r="L45" s="445" t="n"/>
-      <c r="M45" s="445" t="n"/>
-      <c r="N45" s="445" t="n"/>
-      <c r="O45" s="445" t="n"/>
-      <c r="P45" s="445" t="n"/>
-      <c r="Q45" s="445" t="n"/>
-      <c r="R45" s="445" t="n"/>
-      <c r="S45" s="445" t="n"/>
-      <c r="T45" s="445" t="n"/>
+      <c r="F45" s="459" t="n"/>
+      <c r="G45" s="499" t="n"/>
+      <c r="H45" s="499" t="n"/>
+      <c r="I45" s="499" t="n"/>
+      <c r="J45" s="499" t="n"/>
+      <c r="K45" s="499" t="n"/>
+      <c r="L45" s="499" t="n"/>
+      <c r="M45" s="499" t="n"/>
+      <c r="N45" s="499" t="n"/>
+      <c r="O45" s="499" t="n"/>
+      <c r="P45" s="499" t="n"/>
+      <c r="Q45" s="499" t="n"/>
+      <c r="R45" s="499" t="n"/>
+      <c r="S45" s="499" t="n"/>
+      <c r="T45" s="499" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
       <c r="A46" s="369" t="n"/>
@@ -7053,21 +7409,21 @@
           <t>positive, negative, neutral, unknown</t>
         </is>
       </c>
-      <c r="F46" s="444" t="n"/>
-      <c r="G46" s="445" t="n"/>
-      <c r="H46" s="445" t="n"/>
-      <c r="I46" s="445" t="n"/>
-      <c r="J46" s="445" t="n"/>
-      <c r="K46" s="445" t="n"/>
-      <c r="L46" s="445" t="n"/>
-      <c r="M46" s="445" t="n"/>
-      <c r="N46" s="445" t="n"/>
-      <c r="O46" s="445" t="n"/>
-      <c r="P46" s="445" t="n"/>
-      <c r="Q46" s="445" t="n"/>
-      <c r="R46" s="445" t="n"/>
-      <c r="S46" s="445" t="n"/>
-      <c r="T46" s="445" t="n"/>
+      <c r="F46" s="459" t="n"/>
+      <c r="G46" s="499" t="n"/>
+      <c r="H46" s="499" t="n"/>
+      <c r="I46" s="499" t="n"/>
+      <c r="J46" s="499" t="n"/>
+      <c r="K46" s="499" t="n"/>
+      <c r="L46" s="499" t="n"/>
+      <c r="M46" s="499" t="n"/>
+      <c r="N46" s="499" t="n"/>
+      <c r="O46" s="499" t="n"/>
+      <c r="P46" s="499" t="n"/>
+      <c r="Q46" s="499" t="n"/>
+      <c r="R46" s="499" t="n"/>
+      <c r="S46" s="499" t="n"/>
+      <c r="T46" s="499" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
       <c r="A47" s="361" t="n"/>
@@ -7091,21 +7447,21 @@
           <t>Adaptation; Air pollution; Energy supply security; Technological innovation; Poverty reduction; Employment; Industrial development; Other (non-exhaustive list, current options here based on IPCC)</t>
         </is>
       </c>
-      <c r="F47" s="444" t="n"/>
-      <c r="G47" s="445" t="n"/>
-      <c r="H47" s="445" t="n"/>
-      <c r="I47" s="445" t="n"/>
-      <c r="J47" s="445" t="n"/>
-      <c r="K47" s="445" t="n"/>
-      <c r="L47" s="445" t="n"/>
-      <c r="M47" s="445" t="n"/>
-      <c r="N47" s="445" t="n"/>
-      <c r="O47" s="445" t="n"/>
-      <c r="P47" s="445" t="n"/>
-      <c r="Q47" s="445" t="n"/>
-      <c r="R47" s="445" t="n"/>
-      <c r="S47" s="445" t="n"/>
-      <c r="T47" s="445" t="n"/>
+      <c r="F47" s="459" t="n"/>
+      <c r="G47" s="499" t="n"/>
+      <c r="H47" s="499" t="n"/>
+      <c r="I47" s="499" t="n"/>
+      <c r="J47" s="499" t="n"/>
+      <c r="K47" s="499" t="n"/>
+      <c r="L47" s="499" t="n"/>
+      <c r="M47" s="499" t="n"/>
+      <c r="N47" s="499" t="n"/>
+      <c r="O47" s="499" t="n"/>
+      <c r="P47" s="499" t="n"/>
+      <c r="Q47" s="499" t="n"/>
+      <c r="R47" s="499" t="n"/>
+      <c r="S47" s="499" t="n"/>
+      <c r="T47" s="499" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
       <c r="A48" s="446" t="inlineStr">
@@ -7117,21 +7473,21 @@
       <c r="C48" s="339" t="n"/>
       <c r="D48" s="339" t="n"/>
       <c r="E48" s="340" t="n"/>
-      <c r="F48" s="444" t="n"/>
-      <c r="G48" s="445" t="n"/>
-      <c r="H48" s="445" t="n"/>
-      <c r="I48" s="445" t="n"/>
-      <c r="J48" s="445" t="n"/>
-      <c r="K48" s="445" t="n"/>
-      <c r="L48" s="445" t="n"/>
-      <c r="M48" s="445" t="n"/>
-      <c r="N48" s="445" t="n"/>
-      <c r="O48" s="445" t="n"/>
-      <c r="P48" s="445" t="n"/>
-      <c r="Q48" s="445" t="n"/>
-      <c r="R48" s="445" t="n"/>
-      <c r="S48" s="445" t="n"/>
-      <c r="T48" s="445" t="n"/>
+      <c r="F48" s="459" t="n"/>
+      <c r="G48" s="499" t="n"/>
+      <c r="H48" s="499" t="n"/>
+      <c r="I48" s="499" t="n"/>
+      <c r="J48" s="499" t="n"/>
+      <c r="K48" s="499" t="n"/>
+      <c r="L48" s="499" t="n"/>
+      <c r="M48" s="499" t="n"/>
+      <c r="N48" s="499" t="n"/>
+      <c r="O48" s="499" t="n"/>
+      <c r="P48" s="499" t="n"/>
+      <c r="Q48" s="499" t="n"/>
+      <c r="R48" s="499" t="n"/>
+      <c r="S48" s="499" t="n"/>
+      <c r="T48" s="499" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
       <c r="A49" s="452" t="inlineStr">
@@ -7159,21 +7515,21 @@
           <t>in millions of domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
-      <c r="F49" s="457" t="n"/>
-      <c r="G49" s="458" t="n"/>
-      <c r="H49" s="458" t="n"/>
-      <c r="I49" s="458" t="n"/>
-      <c r="J49" s="458" t="n"/>
-      <c r="K49" s="458" t="n"/>
-      <c r="L49" s="458" t="n"/>
-      <c r="M49" s="458" t="n"/>
-      <c r="N49" s="458" t="n"/>
-      <c r="O49" s="458" t="n"/>
-      <c r="P49" s="458" t="n"/>
-      <c r="Q49" s="458" t="n"/>
-      <c r="R49" s="458" t="n"/>
-      <c r="S49" s="458" t="n"/>
-      <c r="T49" s="458" t="n"/>
+      <c r="F49" s="503" t="n"/>
+      <c r="G49" s="504" t="n"/>
+      <c r="H49" s="504" t="n"/>
+      <c r="I49" s="504" t="n"/>
+      <c r="J49" s="504" t="n"/>
+      <c r="K49" s="504" t="n"/>
+      <c r="L49" s="504" t="n"/>
+      <c r="M49" s="504" t="n"/>
+      <c r="N49" s="504" t="n"/>
+      <c r="O49" s="504" t="n"/>
+      <c r="P49" s="504" t="n"/>
+      <c r="Q49" s="504" t="n"/>
+      <c r="R49" s="504" t="n"/>
+      <c r="S49" s="504" t="n"/>
+      <c r="T49" s="504" t="n"/>
     </row>
     <row r="50" ht="15" customHeight="1">
       <c r="A50" s="369" t="n"/>
@@ -7197,21 +7553,21 @@
           <t>ID of the financed policy instrument or “Earmarked” if financed policy is not included in the database</t>
         </is>
       </c>
-      <c r="F50" s="444" t="n"/>
-      <c r="G50" s="445" t="n"/>
-      <c r="H50" s="445" t="n"/>
-      <c r="I50" s="445" t="n"/>
-      <c r="J50" s="445" t="n"/>
-      <c r="K50" s="445" t="n"/>
-      <c r="L50" s="445" t="n"/>
-      <c r="M50" s="445" t="n"/>
-      <c r="N50" s="445" t="n"/>
-      <c r="O50" s="445" t="n"/>
-      <c r="P50" s="445" t="n"/>
-      <c r="Q50" s="445" t="n"/>
-      <c r="R50" s="445" t="n"/>
-      <c r="S50" s="445" t="n"/>
-      <c r="T50" s="445" t="n"/>
+      <c r="F50" s="459" t="n"/>
+      <c r="G50" s="499" t="n"/>
+      <c r="H50" s="499" t="n"/>
+      <c r="I50" s="499" t="n"/>
+      <c r="J50" s="499" t="n"/>
+      <c r="K50" s="499" t="n"/>
+      <c r="L50" s="499" t="n"/>
+      <c r="M50" s="499" t="n"/>
+      <c r="N50" s="499" t="n"/>
+      <c r="O50" s="499" t="n"/>
+      <c r="P50" s="499" t="n"/>
+      <c r="Q50" s="499" t="n"/>
+      <c r="R50" s="499" t="n"/>
+      <c r="S50" s="499" t="n"/>
+      <c r="T50" s="499" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
       <c r="A51" s="361" t="n"/>
@@ -7235,21 +7591,21 @@
           <t>in millions of domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
-      <c r="F51" s="444" t="n"/>
-      <c r="G51" s="445" t="n"/>
-      <c r="H51" s="445" t="n"/>
-      <c r="I51" s="445" t="n"/>
-      <c r="J51" s="445" t="n"/>
-      <c r="K51" s="445" t="n"/>
-      <c r="L51" s="445" t="n"/>
-      <c r="M51" s="445" t="n"/>
-      <c r="N51" s="445" t="n"/>
-      <c r="O51" s="445" t="n"/>
-      <c r="P51" s="445" t="n"/>
-      <c r="Q51" s="445" t="n"/>
-      <c r="R51" s="445" t="n"/>
-      <c r="S51" s="445" t="n"/>
-      <c r="T51" s="445" t="n"/>
+      <c r="F51" s="459" t="n"/>
+      <c r="G51" s="499" t="n"/>
+      <c r="H51" s="499" t="n"/>
+      <c r="I51" s="499" t="n"/>
+      <c r="J51" s="499" t="n"/>
+      <c r="K51" s="499" t="n"/>
+      <c r="L51" s="499" t="n"/>
+      <c r="M51" s="499" t="n"/>
+      <c r="N51" s="499" t="n"/>
+      <c r="O51" s="499" t="n"/>
+      <c r="P51" s="499" t="n"/>
+      <c r="Q51" s="499" t="n"/>
+      <c r="R51" s="499" t="n"/>
+      <c r="S51" s="499" t="n"/>
+      <c r="T51" s="499" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
       <c r="A52" s="447" t="inlineStr">
@@ -7277,21 +7633,21 @@
           <t>in millions of domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
-      <c r="F52" s="444" t="n"/>
-      <c r="G52" s="445" t="n"/>
-      <c r="H52" s="445" t="n"/>
-      <c r="I52" s="445" t="n"/>
-      <c r="J52" s="445" t="n"/>
-      <c r="K52" s="445" t="n"/>
-      <c r="L52" s="445" t="n"/>
-      <c r="M52" s="445" t="n"/>
-      <c r="N52" s="445" t="n"/>
-      <c r="O52" s="445" t="n"/>
-      <c r="P52" s="445" t="n"/>
-      <c r="Q52" s="445" t="n"/>
-      <c r="R52" s="445" t="n"/>
-      <c r="S52" s="445" t="n"/>
-      <c r="T52" s="445" t="n"/>
+      <c r="F52" s="459" t="n"/>
+      <c r="G52" s="499" t="n"/>
+      <c r="H52" s="499" t="n"/>
+      <c r="I52" s="499" t="n"/>
+      <c r="J52" s="499" t="n"/>
+      <c r="K52" s="499" t="n"/>
+      <c r="L52" s="499" t="n"/>
+      <c r="M52" s="499" t="n"/>
+      <c r="N52" s="499" t="n"/>
+      <c r="O52" s="499" t="n"/>
+      <c r="P52" s="499" t="n"/>
+      <c r="Q52" s="499" t="n"/>
+      <c r="R52" s="499" t="n"/>
+      <c r="S52" s="499" t="n"/>
+      <c r="T52" s="499" t="n"/>
     </row>
     <row r="53" ht="15" customHeight="1">
       <c r="A53" s="369" t="n"/>
@@ -7315,21 +7671,21 @@
           <t>in domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
-      <c r="F53" s="444" t="n"/>
-      <c r="G53" s="445" t="n"/>
-      <c r="H53" s="445" t="n"/>
-      <c r="I53" s="445" t="n"/>
-      <c r="J53" s="445" t="n"/>
-      <c r="K53" s="445" t="n"/>
-      <c r="L53" s="445" t="n"/>
-      <c r="M53" s="445" t="n"/>
-      <c r="N53" s="445" t="n"/>
-      <c r="O53" s="445" t="n"/>
-      <c r="P53" s="445" t="n"/>
-      <c r="Q53" s="445" t="n"/>
-      <c r="R53" s="445" t="n"/>
-      <c r="S53" s="445" t="n"/>
-      <c r="T53" s="445" t="n"/>
+      <c r="F53" s="459" t="n"/>
+      <c r="G53" s="499" t="n"/>
+      <c r="H53" s="499" t="n"/>
+      <c r="I53" s="499" t="n"/>
+      <c r="J53" s="499" t="n"/>
+      <c r="K53" s="499" t="n"/>
+      <c r="L53" s="499" t="n"/>
+      <c r="M53" s="499" t="n"/>
+      <c r="N53" s="499" t="n"/>
+      <c r="O53" s="499" t="n"/>
+      <c r="P53" s="499" t="n"/>
+      <c r="Q53" s="499" t="n"/>
+      <c r="R53" s="499" t="n"/>
+      <c r="S53" s="499" t="n"/>
+      <c r="T53" s="499" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1">
       <c r="A54" s="369" t="n"/>
@@ -7353,21 +7709,21 @@
           <t>from list, e.g. auction type, by default, lottery, etc.</t>
         </is>
       </c>
-      <c r="F54" s="444" t="n"/>
-      <c r="G54" s="445" t="n"/>
-      <c r="H54" s="445" t="n"/>
-      <c r="I54" s="445" t="n"/>
-      <c r="J54" s="445" t="n"/>
-      <c r="K54" s="445" t="n"/>
-      <c r="L54" s="445" t="n"/>
-      <c r="M54" s="445" t="n"/>
-      <c r="N54" s="445" t="n"/>
-      <c r="O54" s="445" t="n"/>
-      <c r="P54" s="445" t="n"/>
-      <c r="Q54" s="445" t="n"/>
-      <c r="R54" s="445" t="n"/>
-      <c r="S54" s="445" t="n"/>
-      <c r="T54" s="445" t="n"/>
+      <c r="F54" s="459" t="n"/>
+      <c r="G54" s="499" t="n"/>
+      <c r="H54" s="499" t="n"/>
+      <c r="I54" s="499" t="n"/>
+      <c r="J54" s="499" t="n"/>
+      <c r="K54" s="499" t="n"/>
+      <c r="L54" s="499" t="n"/>
+      <c r="M54" s="499" t="n"/>
+      <c r="N54" s="499" t="n"/>
+      <c r="O54" s="499" t="n"/>
+      <c r="P54" s="499" t="n"/>
+      <c r="Q54" s="499" t="n"/>
+      <c r="R54" s="499" t="n"/>
+      <c r="S54" s="499" t="n"/>
+      <c r="T54" s="499" t="n"/>
     </row>
     <row r="55" ht="15" customHeight="1">
       <c r="A55" s="369" t="n"/>
@@ -7391,21 +7747,21 @@
           <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
         </is>
       </c>
-      <c r="F55" s="444" t="n"/>
-      <c r="G55" s="445" t="n"/>
-      <c r="H55" s="445" t="n"/>
-      <c r="I55" s="445" t="n"/>
-      <c r="J55" s="445" t="n"/>
-      <c r="K55" s="445" t="n"/>
-      <c r="L55" s="445" t="n"/>
-      <c r="M55" s="445" t="n"/>
-      <c r="N55" s="445" t="n"/>
-      <c r="O55" s="445" t="n"/>
-      <c r="P55" s="445" t="n"/>
-      <c r="Q55" s="445" t="n"/>
-      <c r="R55" s="445" t="n"/>
-      <c r="S55" s="445" t="n"/>
-      <c r="T55" s="445" t="n"/>
+      <c r="F55" s="459" t="n"/>
+      <c r="G55" s="499" t="n"/>
+      <c r="H55" s="499" t="n"/>
+      <c r="I55" s="499" t="n"/>
+      <c r="J55" s="499" t="n"/>
+      <c r="K55" s="499" t="n"/>
+      <c r="L55" s="499" t="n"/>
+      <c r="M55" s="499" t="n"/>
+      <c r="N55" s="499" t="n"/>
+      <c r="O55" s="499" t="n"/>
+      <c r="P55" s="499" t="n"/>
+      <c r="Q55" s="499" t="n"/>
+      <c r="R55" s="499" t="n"/>
+      <c r="S55" s="499" t="n"/>
+      <c r="T55" s="499" t="n"/>
     </row>
     <row r="56" ht="15" customHeight="1">
       <c r="A56" s="369" t="n"/>
@@ -7429,21 +7785,21 @@
           <t>Value in domestic currency</t>
         </is>
       </c>
-      <c r="F56" s="444" t="n"/>
-      <c r="G56" s="445" t="n"/>
-      <c r="H56" s="445" t="n"/>
-      <c r="I56" s="445" t="n"/>
-      <c r="J56" s="445" t="n"/>
-      <c r="K56" s="445" t="n"/>
-      <c r="L56" s="445" t="n"/>
-      <c r="M56" s="445" t="n"/>
-      <c r="N56" s="445" t="n"/>
-      <c r="O56" s="445" t="n"/>
-      <c r="P56" s="445" t="n"/>
-      <c r="Q56" s="445" t="n"/>
-      <c r="R56" s="445" t="n"/>
-      <c r="S56" s="445" t="n"/>
-      <c r="T56" s="445" t="n"/>
+      <c r="F56" s="459" t="n"/>
+      <c r="G56" s="499" t="n"/>
+      <c r="H56" s="499" t="n"/>
+      <c r="I56" s="499" t="n"/>
+      <c r="J56" s="499" t="n"/>
+      <c r="K56" s="499" t="n"/>
+      <c r="L56" s="499" t="n"/>
+      <c r="M56" s="499" t="n"/>
+      <c r="N56" s="499" t="n"/>
+      <c r="O56" s="499" t="n"/>
+      <c r="P56" s="499" t="n"/>
+      <c r="Q56" s="499" t="n"/>
+      <c r="R56" s="499" t="n"/>
+      <c r="S56" s="499" t="n"/>
+      <c r="T56" s="499" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
       <c r="A57" s="369" t="n"/>
@@ -7467,21 +7823,21 @@
           <t>Expressed in years, or months</t>
         </is>
       </c>
-      <c r="F57" s="444" t="n"/>
-      <c r="G57" s="445" t="n"/>
-      <c r="H57" s="445" t="n"/>
-      <c r="I57" s="445" t="n"/>
-      <c r="J57" s="445" t="n"/>
-      <c r="K57" s="445" t="n"/>
-      <c r="L57" s="445" t="n"/>
-      <c r="M57" s="445" t="n"/>
-      <c r="N57" s="445" t="n"/>
-      <c r="O57" s="445" t="n"/>
-      <c r="P57" s="445" t="n"/>
-      <c r="Q57" s="445" t="n"/>
-      <c r="R57" s="445" t="n"/>
-      <c r="S57" s="445" t="n"/>
-      <c r="T57" s="445" t="n"/>
+      <c r="F57" s="459" t="n"/>
+      <c r="G57" s="499" t="n"/>
+      <c r="H57" s="499" t="n"/>
+      <c r="I57" s="499" t="n"/>
+      <c r="J57" s="499" t="n"/>
+      <c r="K57" s="499" t="n"/>
+      <c r="L57" s="499" t="n"/>
+      <c r="M57" s="499" t="n"/>
+      <c r="N57" s="499" t="n"/>
+      <c r="O57" s="499" t="n"/>
+      <c r="P57" s="499" t="n"/>
+      <c r="Q57" s="499" t="n"/>
+      <c r="R57" s="499" t="n"/>
+      <c r="S57" s="499" t="n"/>
+      <c r="T57" s="499" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
       <c r="A58" s="361" t="n"/>
@@ -7501,21 +7857,21 @@
         </is>
       </c>
       <c r="E58" s="449" t="n"/>
-      <c r="F58" s="444" t="n"/>
-      <c r="G58" s="445" t="n"/>
-      <c r="H58" s="445" t="n"/>
-      <c r="I58" s="445" t="n"/>
-      <c r="J58" s="445" t="n"/>
-      <c r="K58" s="445" t="n"/>
-      <c r="L58" s="445" t="n"/>
-      <c r="M58" s="445" t="n"/>
-      <c r="N58" s="445" t="n"/>
-      <c r="O58" s="445" t="n"/>
-      <c r="P58" s="445" t="n"/>
-      <c r="Q58" s="445" t="n"/>
-      <c r="R58" s="445" t="n"/>
-      <c r="S58" s="445" t="n"/>
-      <c r="T58" s="445" t="n"/>
+      <c r="F58" s="459" t="n"/>
+      <c r="G58" s="499" t="n"/>
+      <c r="H58" s="499" t="n"/>
+      <c r="I58" s="499" t="n"/>
+      <c r="J58" s="499" t="n"/>
+      <c r="K58" s="499" t="n"/>
+      <c r="L58" s="499" t="n"/>
+      <c r="M58" s="499" t="n"/>
+      <c r="N58" s="499" t="n"/>
+      <c r="O58" s="499" t="n"/>
+      <c r="P58" s="499" t="n"/>
+      <c r="Q58" s="499" t="n"/>
+      <c r="R58" s="499" t="n"/>
+      <c r="S58" s="499" t="n"/>
+      <c r="T58" s="499" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
       <c r="A59" s="452" t="inlineStr">
@@ -7543,21 +7899,21 @@
           <t>from list, e.g. permits, credits, etc</t>
         </is>
       </c>
-      <c r="F59" s="444" t="n"/>
-      <c r="G59" s="445" t="n"/>
-      <c r="H59" s="445" t="n"/>
-      <c r="I59" s="445" t="n"/>
-      <c r="J59" s="445" t="n"/>
-      <c r="K59" s="445" t="n"/>
-      <c r="L59" s="445" t="n"/>
-      <c r="M59" s="445" t="n"/>
-      <c r="N59" s="445" t="n"/>
-      <c r="O59" s="445" t="n"/>
-      <c r="P59" s="445" t="n"/>
-      <c r="Q59" s="445" t="n"/>
-      <c r="R59" s="445" t="n"/>
-      <c r="S59" s="445" t="n"/>
-      <c r="T59" s="445" t="n"/>
+      <c r="F59" s="459" t="n"/>
+      <c r="G59" s="499" t="n"/>
+      <c r="H59" s="499" t="n"/>
+      <c r="I59" s="499" t="n"/>
+      <c r="J59" s="499" t="n"/>
+      <c r="K59" s="499" t="n"/>
+      <c r="L59" s="499" t="n"/>
+      <c r="M59" s="499" t="n"/>
+      <c r="N59" s="499" t="n"/>
+      <c r="O59" s="499" t="n"/>
+      <c r="P59" s="499" t="n"/>
+      <c r="Q59" s="499" t="n"/>
+      <c r="R59" s="499" t="n"/>
+      <c r="S59" s="499" t="n"/>
+      <c r="T59" s="499" t="n"/>
     </row>
     <row r="60" ht="15" customHeight="1">
       <c r="A60" s="369" t="n"/>
@@ -7581,21 +7937,21 @@
           <t>CO2eq for ETS, but could be others if ever we cover other trading systems (nitrogen trading in agriculture)</t>
         </is>
       </c>
-      <c r="F60" s="444" t="n"/>
-      <c r="G60" s="445" t="n"/>
-      <c r="H60" s="445" t="n"/>
-      <c r="I60" s="445" t="n"/>
-      <c r="J60" s="445" t="n"/>
-      <c r="K60" s="445" t="n"/>
-      <c r="L60" s="445" t="n"/>
-      <c r="M60" s="445" t="n"/>
-      <c r="N60" s="445" t="n"/>
-      <c r="O60" s="445" t="n"/>
-      <c r="P60" s="445" t="n"/>
-      <c r="Q60" s="445" t="n"/>
-      <c r="R60" s="445" t="n"/>
-      <c r="S60" s="445" t="n"/>
-      <c r="T60" s="445" t="n"/>
+      <c r="F60" s="459" t="n"/>
+      <c r="G60" s="499" t="n"/>
+      <c r="H60" s="499" t="n"/>
+      <c r="I60" s="499" t="n"/>
+      <c r="J60" s="499" t="n"/>
+      <c r="K60" s="499" t="n"/>
+      <c r="L60" s="499" t="n"/>
+      <c r="M60" s="499" t="n"/>
+      <c r="N60" s="499" t="n"/>
+      <c r="O60" s="499" t="n"/>
+      <c r="P60" s="499" t="n"/>
+      <c r="Q60" s="499" t="n"/>
+      <c r="R60" s="499" t="n"/>
+      <c r="S60" s="499" t="n"/>
+      <c r="T60" s="499" t="n"/>
     </row>
     <row r="61" ht="15" customHeight="1">
       <c r="A61" s="369" t="n"/>
@@ -7619,21 +7975,21 @@
           <t>free allowance; auctioning; mixture of the two</t>
         </is>
       </c>
-      <c r="F61" s="444" t="n"/>
-      <c r="G61" s="445" t="n"/>
-      <c r="H61" s="445" t="n"/>
-      <c r="I61" s="445" t="n"/>
-      <c r="J61" s="445" t="n"/>
-      <c r="K61" s="445" t="n"/>
-      <c r="L61" s="445" t="n"/>
-      <c r="M61" s="445" t="n"/>
-      <c r="N61" s="445" t="n"/>
-      <c r="O61" s="445" t="n"/>
-      <c r="P61" s="445" t="n"/>
-      <c r="Q61" s="445" t="n"/>
-      <c r="R61" s="445" t="n"/>
-      <c r="S61" s="445" t="n"/>
-      <c r="T61" s="445" t="n"/>
+      <c r="F61" s="459" t="n"/>
+      <c r="G61" s="499" t="n"/>
+      <c r="H61" s="499" t="n"/>
+      <c r="I61" s="499" t="n"/>
+      <c r="J61" s="499" t="n"/>
+      <c r="K61" s="499" t="n"/>
+      <c r="L61" s="499" t="n"/>
+      <c r="M61" s="499" t="n"/>
+      <c r="N61" s="499" t="n"/>
+      <c r="O61" s="499" t="n"/>
+      <c r="P61" s="499" t="n"/>
+      <c r="Q61" s="499" t="n"/>
+      <c r="R61" s="499" t="n"/>
+      <c r="S61" s="499" t="n"/>
+      <c r="T61" s="499" t="n"/>
     </row>
     <row r="62" ht="15" customHeight="1">
       <c r="A62" s="369" t="n"/>
@@ -7657,21 +8013,21 @@
           <t>In percentages</t>
         </is>
       </c>
-      <c r="F62" s="444" t="n"/>
-      <c r="G62" s="445" t="n"/>
-      <c r="H62" s="445" t="n"/>
-      <c r="I62" s="445" t="n"/>
-      <c r="J62" s="445" t="n"/>
-      <c r="K62" s="445" t="n"/>
-      <c r="L62" s="445" t="n"/>
-      <c r="M62" s="445" t="n"/>
-      <c r="N62" s="445" t="n"/>
-      <c r="O62" s="445" t="n"/>
-      <c r="P62" s="445" t="n"/>
-      <c r="Q62" s="445" t="n"/>
-      <c r="R62" s="445" t="n"/>
-      <c r="S62" s="445" t="n"/>
-      <c r="T62" s="445" t="n"/>
+      <c r="F62" s="459" t="n"/>
+      <c r="G62" s="499" t="n"/>
+      <c r="H62" s="499" t="n"/>
+      <c r="I62" s="499" t="n"/>
+      <c r="J62" s="499" t="n"/>
+      <c r="K62" s="499" t="n"/>
+      <c r="L62" s="499" t="n"/>
+      <c r="M62" s="499" t="n"/>
+      <c r="N62" s="499" t="n"/>
+      <c r="O62" s="499" t="n"/>
+      <c r="P62" s="499" t="n"/>
+      <c r="Q62" s="499" t="n"/>
+      <c r="R62" s="499" t="n"/>
+      <c r="S62" s="499" t="n"/>
+      <c r="T62" s="499" t="n"/>
     </row>
     <row r="63" ht="15" customHeight="1">
       <c r="A63" s="369" t="n"/>
@@ -7695,21 +8051,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F63" s="444" t="n"/>
-      <c r="G63" s="445" t="n"/>
-      <c r="H63" s="445" t="n"/>
-      <c r="I63" s="445" t="n"/>
-      <c r="J63" s="445" t="n"/>
-      <c r="K63" s="445" t="n"/>
-      <c r="L63" s="445" t="n"/>
-      <c r="M63" s="445" t="n"/>
-      <c r="N63" s="445" t="n"/>
-      <c r="O63" s="445" t="n"/>
-      <c r="P63" s="445" t="n"/>
-      <c r="Q63" s="445" t="n"/>
-      <c r="R63" s="445" t="n"/>
-      <c r="S63" s="445" t="n"/>
-      <c r="T63" s="445" t="n"/>
+      <c r="F63" s="459" t="n"/>
+      <c r="G63" s="499" t="n"/>
+      <c r="H63" s="499" t="n"/>
+      <c r="I63" s="499" t="n"/>
+      <c r="J63" s="499" t="n"/>
+      <c r="K63" s="499" t="n"/>
+      <c r="L63" s="499" t="n"/>
+      <c r="M63" s="499" t="n"/>
+      <c r="N63" s="499" t="n"/>
+      <c r="O63" s="499" t="n"/>
+      <c r="P63" s="499" t="n"/>
+      <c r="Q63" s="499" t="n"/>
+      <c r="R63" s="499" t="n"/>
+      <c r="S63" s="499" t="n"/>
+      <c r="T63" s="499" t="n"/>
     </row>
     <row r="64" ht="15" customHeight="1">
       <c r="A64" s="369" t="n"/>
@@ -7733,21 +8089,21 @@
           <t>Enter the instrument IDs of relevant instruments (N/A if no link)</t>
         </is>
       </c>
-      <c r="F64" s="444" t="n"/>
-      <c r="G64" s="445" t="n"/>
-      <c r="H64" s="445" t="n"/>
-      <c r="I64" s="445" t="n"/>
-      <c r="J64" s="445" t="n"/>
-      <c r="K64" s="445" t="n"/>
-      <c r="L64" s="445" t="n"/>
-      <c r="M64" s="445" t="n"/>
-      <c r="N64" s="445" t="n"/>
-      <c r="O64" s="445" t="n"/>
-      <c r="P64" s="445" t="n"/>
-      <c r="Q64" s="445" t="n"/>
-      <c r="R64" s="445" t="n"/>
-      <c r="S64" s="445" t="n"/>
-      <c r="T64" s="445" t="n"/>
+      <c r="F64" s="459" t="n"/>
+      <c r="G64" s="499" t="n"/>
+      <c r="H64" s="499" t="n"/>
+      <c r="I64" s="499" t="n"/>
+      <c r="J64" s="499" t="n"/>
+      <c r="K64" s="499" t="n"/>
+      <c r="L64" s="499" t="n"/>
+      <c r="M64" s="499" t="n"/>
+      <c r="N64" s="499" t="n"/>
+      <c r="O64" s="499" t="n"/>
+      <c r="P64" s="499" t="n"/>
+      <c r="Q64" s="499" t="n"/>
+      <c r="R64" s="499" t="n"/>
+      <c r="S64" s="499" t="n"/>
+      <c r="T64" s="499" t="n"/>
     </row>
     <row r="65" ht="15" customHeight="1">
       <c r="A65" s="369" t="n"/>
@@ -7771,21 +8127,21 @@
           <t>yes/no</t>
         </is>
       </c>
-      <c r="F65" s="444" t="n"/>
-      <c r="G65" s="445" t="n"/>
-      <c r="H65" s="445" t="n"/>
-      <c r="I65" s="445" t="n"/>
-      <c r="J65" s="445" t="n"/>
-      <c r="K65" s="445" t="n"/>
-      <c r="L65" s="445" t="n"/>
-      <c r="M65" s="445" t="n"/>
-      <c r="N65" s="445" t="n"/>
-      <c r="O65" s="445" t="n"/>
-      <c r="P65" s="445" t="n"/>
-      <c r="Q65" s="445" t="n"/>
-      <c r="R65" s="445" t="n"/>
-      <c r="S65" s="445" t="n"/>
-      <c r="T65" s="445" t="n"/>
+      <c r="F65" s="459" t="n"/>
+      <c r="G65" s="499" t="n"/>
+      <c r="H65" s="499" t="n"/>
+      <c r="I65" s="499" t="n"/>
+      <c r="J65" s="499" t="n"/>
+      <c r="K65" s="499" t="n"/>
+      <c r="L65" s="499" t="n"/>
+      <c r="M65" s="499" t="n"/>
+      <c r="N65" s="499" t="n"/>
+      <c r="O65" s="499" t="n"/>
+      <c r="P65" s="499" t="n"/>
+      <c r="Q65" s="499" t="n"/>
+      <c r="R65" s="499" t="n"/>
+      <c r="S65" s="499" t="n"/>
+      <c r="T65" s="499" t="n"/>
     </row>
     <row r="66" ht="15" customHeight="1">
       <c r="A66" s="369" t="n"/>
@@ -7809,21 +8165,21 @@
           <t>In domestic currency (collection year -1)</t>
         </is>
       </c>
-      <c r="F66" s="444" t="n"/>
-      <c r="G66" s="445" t="n"/>
-      <c r="H66" s="445" t="n"/>
-      <c r="I66" s="445" t="n"/>
-      <c r="J66" s="445" t="n"/>
-      <c r="K66" s="445" t="n"/>
-      <c r="L66" s="445" t="n"/>
-      <c r="M66" s="445" t="n"/>
-      <c r="N66" s="445" t="n"/>
-      <c r="O66" s="445" t="n"/>
-      <c r="P66" s="445" t="n"/>
-      <c r="Q66" s="445" t="n"/>
-      <c r="R66" s="445" t="n"/>
-      <c r="S66" s="445" t="n"/>
-      <c r="T66" s="445" t="n"/>
+      <c r="F66" s="459" t="n"/>
+      <c r="G66" s="499" t="n"/>
+      <c r="H66" s="499" t="n"/>
+      <c r="I66" s="499" t="n"/>
+      <c r="J66" s="499" t="n"/>
+      <c r="K66" s="499" t="n"/>
+      <c r="L66" s="499" t="n"/>
+      <c r="M66" s="499" t="n"/>
+      <c r="N66" s="499" t="n"/>
+      <c r="O66" s="499" t="n"/>
+      <c r="P66" s="499" t="n"/>
+      <c r="Q66" s="499" t="n"/>
+      <c r="R66" s="499" t="n"/>
+      <c r="S66" s="499" t="n"/>
+      <c r="T66" s="499" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
       <c r="A67" s="369" t="n"/>
@@ -7847,21 +8203,21 @@
           <t>No if none; otherwise description of the applicable rules</t>
         </is>
       </c>
-      <c r="F67" s="444" t="n"/>
-      <c r="G67" s="445" t="n"/>
-      <c r="H67" s="445" t="n"/>
-      <c r="I67" s="445" t="n"/>
-      <c r="J67" s="445" t="n"/>
-      <c r="K67" s="445" t="n"/>
-      <c r="L67" s="445" t="n"/>
-      <c r="M67" s="445" t="n"/>
-      <c r="N67" s="445" t="n"/>
-      <c r="O67" s="445" t="n"/>
-      <c r="P67" s="445" t="n"/>
-      <c r="Q67" s="445" t="n"/>
-      <c r="R67" s="445" t="n"/>
-      <c r="S67" s="445" t="n"/>
-      <c r="T67" s="445" t="n"/>
+      <c r="F67" s="459" t="n"/>
+      <c r="G67" s="499" t="n"/>
+      <c r="H67" s="499" t="n"/>
+      <c r="I67" s="499" t="n"/>
+      <c r="J67" s="499" t="n"/>
+      <c r="K67" s="499" t="n"/>
+      <c r="L67" s="499" t="n"/>
+      <c r="M67" s="499" t="n"/>
+      <c r="N67" s="499" t="n"/>
+      <c r="O67" s="499" t="n"/>
+      <c r="P67" s="499" t="n"/>
+      <c r="Q67" s="499" t="n"/>
+      <c r="R67" s="499" t="n"/>
+      <c r="S67" s="499" t="n"/>
+      <c r="T67" s="499" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1">
       <c r="A68" s="361" t="n"/>
@@ -7885,21 +8241,21 @@
           <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
         </is>
       </c>
-      <c r="F68" s="444" t="n"/>
-      <c r="G68" s="445" t="n"/>
-      <c r="H68" s="445" t="n"/>
-      <c r="I68" s="445" t="n"/>
-      <c r="J68" s="445" t="n"/>
-      <c r="K68" s="445" t="n"/>
-      <c r="L68" s="445" t="n"/>
-      <c r="M68" s="445" t="n"/>
-      <c r="N68" s="445" t="n"/>
-      <c r="O68" s="445" t="n"/>
-      <c r="P68" s="445" t="n"/>
-      <c r="Q68" s="445" t="n"/>
-      <c r="R68" s="445" t="n"/>
-      <c r="S68" s="445" t="n"/>
-      <c r="T68" s="445" t="n"/>
+      <c r="F68" s="459" t="n"/>
+      <c r="G68" s="499" t="n"/>
+      <c r="H68" s="499" t="n"/>
+      <c r="I68" s="499" t="n"/>
+      <c r="J68" s="499" t="n"/>
+      <c r="K68" s="499" t="n"/>
+      <c r="L68" s="499" t="n"/>
+      <c r="M68" s="499" t="n"/>
+      <c r="N68" s="499" t="n"/>
+      <c r="O68" s="499" t="n"/>
+      <c r="P68" s="499" t="n"/>
+      <c r="Q68" s="499" t="n"/>
+      <c r="R68" s="499" t="n"/>
+      <c r="S68" s="499" t="n"/>
+      <c r="T68" s="499" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
       <c r="A69" s="452" t="inlineStr">
@@ -7927,21 +8283,21 @@
           <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
         </is>
       </c>
-      <c r="F69" s="444" t="n"/>
-      <c r="G69" s="445" t="n"/>
-      <c r="H69" s="445" t="n"/>
-      <c r="I69" s="445" t="n"/>
-      <c r="J69" s="445" t="n"/>
-      <c r="K69" s="445" t="n"/>
-      <c r="L69" s="445" t="n"/>
-      <c r="M69" s="445" t="n"/>
-      <c r="N69" s="445" t="n"/>
-      <c r="O69" s="445" t="n"/>
-      <c r="P69" s="445" t="n"/>
-      <c r="Q69" s="445" t="n"/>
-      <c r="R69" s="445" t="n"/>
-      <c r="S69" s="445" t="n"/>
-      <c r="T69" s="445" t="n"/>
+      <c r="F69" s="459" t="n"/>
+      <c r="G69" s="499" t="n"/>
+      <c r="H69" s="499" t="n"/>
+      <c r="I69" s="499" t="n"/>
+      <c r="J69" s="499" t="n"/>
+      <c r="K69" s="499" t="n"/>
+      <c r="L69" s="499" t="n"/>
+      <c r="M69" s="499" t="n"/>
+      <c r="N69" s="499" t="n"/>
+      <c r="O69" s="499" t="n"/>
+      <c r="P69" s="499" t="n"/>
+      <c r="Q69" s="499" t="n"/>
+      <c r="R69" s="499" t="n"/>
+      <c r="S69" s="499" t="n"/>
+      <c r="T69" s="499" t="n"/>
     </row>
     <row r="70" ht="15" customHeight="1">
       <c r="A70" s="369" t="n"/>
@@ -7965,21 +8321,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F70" s="444" t="n"/>
-      <c r="G70" s="445" t="n"/>
-      <c r="H70" s="445" t="n"/>
-      <c r="I70" s="445" t="n"/>
-      <c r="J70" s="445" t="n"/>
-      <c r="K70" s="445" t="n"/>
-      <c r="L70" s="445" t="n"/>
-      <c r="M70" s="445" t="n"/>
-      <c r="N70" s="445" t="n"/>
-      <c r="O70" s="445" t="n"/>
-      <c r="P70" s="445" t="n"/>
-      <c r="Q70" s="445" t="n"/>
-      <c r="R70" s="445" t="n"/>
-      <c r="S70" s="445" t="n"/>
-      <c r="T70" s="445" t="n"/>
+      <c r="F70" s="459" t="n"/>
+      <c r="G70" s="499" t="n"/>
+      <c r="H70" s="499" t="n"/>
+      <c r="I70" s="499" t="n"/>
+      <c r="J70" s="499" t="n"/>
+      <c r="K70" s="499" t="n"/>
+      <c r="L70" s="499" t="n"/>
+      <c r="M70" s="499" t="n"/>
+      <c r="N70" s="499" t="n"/>
+      <c r="O70" s="499" t="n"/>
+      <c r="P70" s="499" t="n"/>
+      <c r="Q70" s="499" t="n"/>
+      <c r="R70" s="499" t="n"/>
+      <c r="S70" s="499" t="n"/>
+      <c r="T70" s="499" t="n"/>
     </row>
     <row r="71" ht="15" customHeight="1">
       <c r="A71" s="369" t="n"/>
@@ -8003,21 +8359,21 @@
           <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
         </is>
       </c>
-      <c r="F71" s="444" t="n"/>
-      <c r="G71" s="445" t="n"/>
-      <c r="H71" s="445" t="n"/>
-      <c r="I71" s="445" t="n"/>
-      <c r="J71" s="445" t="n"/>
-      <c r="K71" s="445" t="n"/>
-      <c r="L71" s="445" t="n"/>
-      <c r="M71" s="445" t="n"/>
-      <c r="N71" s="445" t="n"/>
-      <c r="O71" s="445" t="n"/>
-      <c r="P71" s="445" t="n"/>
-      <c r="Q71" s="445" t="n"/>
-      <c r="R71" s="445" t="n"/>
-      <c r="S71" s="445" t="n"/>
-      <c r="T71" s="445" t="n"/>
+      <c r="F71" s="459" t="n"/>
+      <c r="G71" s="499" t="n"/>
+      <c r="H71" s="499" t="n"/>
+      <c r="I71" s="499" t="n"/>
+      <c r="J71" s="499" t="n"/>
+      <c r="K71" s="499" t="n"/>
+      <c r="L71" s="499" t="n"/>
+      <c r="M71" s="499" t="n"/>
+      <c r="N71" s="499" t="n"/>
+      <c r="O71" s="499" t="n"/>
+      <c r="P71" s="499" t="n"/>
+      <c r="Q71" s="499" t="n"/>
+      <c r="R71" s="499" t="n"/>
+      <c r="S71" s="499" t="n"/>
+      <c r="T71" s="499" t="n"/>
     </row>
     <row r="72" ht="15" customHeight="1">
       <c r="A72" s="369" t="n"/>
@@ -8041,21 +8397,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F72" s="444" t="n"/>
-      <c r="G72" s="445" t="n"/>
-      <c r="H72" s="445" t="n"/>
-      <c r="I72" s="445" t="n"/>
-      <c r="J72" s="445" t="n"/>
-      <c r="K72" s="445" t="n"/>
-      <c r="L72" s="445" t="n"/>
-      <c r="M72" s="445" t="n"/>
-      <c r="N72" s="445" t="n"/>
-      <c r="O72" s="445" t="n"/>
-      <c r="P72" s="445" t="n"/>
-      <c r="Q72" s="445" t="n"/>
-      <c r="R72" s="445" t="n"/>
-      <c r="S72" s="445" t="n"/>
-      <c r="T72" s="445" t="n"/>
+      <c r="F72" s="459" t="n"/>
+      <c r="G72" s="499" t="n"/>
+      <c r="H72" s="499" t="n"/>
+      <c r="I72" s="499" t="n"/>
+      <c r="J72" s="499" t="n"/>
+      <c r="K72" s="499" t="n"/>
+      <c r="L72" s="499" t="n"/>
+      <c r="M72" s="499" t="n"/>
+      <c r="N72" s="499" t="n"/>
+      <c r="O72" s="499" t="n"/>
+      <c r="P72" s="499" t="n"/>
+      <c r="Q72" s="499" t="n"/>
+      <c r="R72" s="499" t="n"/>
+      <c r="S72" s="499" t="n"/>
+      <c r="T72" s="499" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
       <c r="A73" s="369" t="n"/>
@@ -8079,21 +8435,21 @@
           <t>No compliance promotion; Regulatory incentives (e.g. weights, banking, pooling, trading); Information and direct assistance; Financial support; Other incentives or support</t>
         </is>
       </c>
-      <c r="F73" s="444" t="n"/>
-      <c r="G73" s="445" t="n"/>
-      <c r="H73" s="445" t="n"/>
-      <c r="I73" s="445" t="n"/>
-      <c r="J73" s="445" t="n"/>
-      <c r="K73" s="445" t="n"/>
-      <c r="L73" s="445" t="n"/>
-      <c r="M73" s="445" t="n"/>
-      <c r="N73" s="445" t="n"/>
-      <c r="O73" s="445" t="n"/>
-      <c r="P73" s="445" t="n"/>
-      <c r="Q73" s="445" t="n"/>
-      <c r="R73" s="445" t="n"/>
-      <c r="S73" s="445" t="n"/>
-      <c r="T73" s="445" t="n"/>
+      <c r="F73" s="459" t="n"/>
+      <c r="G73" s="499" t="n"/>
+      <c r="H73" s="499" t="n"/>
+      <c r="I73" s="499" t="n"/>
+      <c r="J73" s="499" t="n"/>
+      <c r="K73" s="499" t="n"/>
+      <c r="L73" s="499" t="n"/>
+      <c r="M73" s="499" t="n"/>
+      <c r="N73" s="499" t="n"/>
+      <c r="O73" s="499" t="n"/>
+      <c r="P73" s="499" t="n"/>
+      <c r="Q73" s="499" t="n"/>
+      <c r="R73" s="499" t="n"/>
+      <c r="S73" s="499" t="n"/>
+      <c r="T73" s="499" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
       <c r="A74" s="361" t="n"/>
@@ -8117,21 +8473,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F74" s="444" t="n"/>
-      <c r="G74" s="445" t="n"/>
-      <c r="H74" s="445" t="n"/>
-      <c r="I74" s="445" t="n"/>
-      <c r="J74" s="445" t="n"/>
-      <c r="K74" s="445" t="n"/>
-      <c r="L74" s="445" t="n"/>
-      <c r="M74" s="445" t="n"/>
-      <c r="N74" s="445" t="n"/>
-      <c r="O74" s="445" t="n"/>
-      <c r="P74" s="445" t="n"/>
-      <c r="Q74" s="445" t="n"/>
-      <c r="R74" s="445" t="n"/>
-      <c r="S74" s="445" t="n"/>
-      <c r="T74" s="445" t="n"/>
+      <c r="F74" s="459" t="n"/>
+      <c r="G74" s="499" t="n"/>
+      <c r="H74" s="499" t="n"/>
+      <c r="I74" s="499" t="n"/>
+      <c r="J74" s="499" t="n"/>
+      <c r="K74" s="499" t="n"/>
+      <c r="L74" s="499" t="n"/>
+      <c r="M74" s="499" t="n"/>
+      <c r="N74" s="499" t="n"/>
+      <c r="O74" s="499" t="n"/>
+      <c r="P74" s="499" t="n"/>
+      <c r="Q74" s="499" t="n"/>
+      <c r="R74" s="499" t="n"/>
+      <c r="S74" s="499" t="n"/>
+      <c r="T74" s="499" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
       <c r="A75" s="452" t="inlineStr">
@@ -8159,21 +8515,21 @@
           <t>Yes; No</t>
         </is>
       </c>
-      <c r="F75" s="444" t="n"/>
-      <c r="G75" s="445" t="n"/>
-      <c r="H75" s="445" t="n"/>
-      <c r="I75" s="445" t="n"/>
-      <c r="J75" s="445" t="n"/>
-      <c r="K75" s="445" t="n"/>
-      <c r="L75" s="445" t="n"/>
-      <c r="M75" s="445" t="n"/>
-      <c r="N75" s="445" t="n"/>
-      <c r="O75" s="445" t="n"/>
-      <c r="P75" s="445" t="n"/>
-      <c r="Q75" s="445" t="n"/>
-      <c r="R75" s="445" t="n"/>
-      <c r="S75" s="445" t="n"/>
-      <c r="T75" s="445" t="n"/>
+      <c r="F75" s="459" t="n"/>
+      <c r="G75" s="499" t="n"/>
+      <c r="H75" s="499" t="n"/>
+      <c r="I75" s="499" t="n"/>
+      <c r="J75" s="499" t="n"/>
+      <c r="K75" s="499" t="n"/>
+      <c r="L75" s="499" t="n"/>
+      <c r="M75" s="499" t="n"/>
+      <c r="N75" s="499" t="n"/>
+      <c r="O75" s="499" t="n"/>
+      <c r="P75" s="499" t="n"/>
+      <c r="Q75" s="499" t="n"/>
+      <c r="R75" s="499" t="n"/>
+      <c r="S75" s="499" t="n"/>
+      <c r="T75" s="499" t="n"/>
     </row>
     <row r="76" ht="15" customHeight="1">
       <c r="A76" s="369" t="n"/>
@@ -8198,21 +8554,21 @@
           <t>Yes, No</t>
         </is>
       </c>
-      <c r="F76" s="444" t="n"/>
-      <c r="G76" s="445" t="n"/>
-      <c r="H76" s="445" t="n"/>
-      <c r="I76" s="445" t="n"/>
-      <c r="J76" s="445" t="n"/>
-      <c r="K76" s="445" t="n"/>
-      <c r="L76" s="445" t="n"/>
-      <c r="M76" s="445" t="n"/>
-      <c r="N76" s="445" t="n"/>
-      <c r="O76" s="445" t="n"/>
-      <c r="P76" s="445" t="n"/>
-      <c r="Q76" s="445" t="n"/>
-      <c r="R76" s="445" t="n"/>
-      <c r="S76" s="445" t="n"/>
-      <c r="T76" s="445" t="n"/>
+      <c r="F76" s="459" t="n"/>
+      <c r="G76" s="499" t="n"/>
+      <c r="H76" s="499" t="n"/>
+      <c r="I76" s="499" t="n"/>
+      <c r="J76" s="499" t="n"/>
+      <c r="K76" s="499" t="n"/>
+      <c r="L76" s="499" t="n"/>
+      <c r="M76" s="499" t="n"/>
+      <c r="N76" s="499" t="n"/>
+      <c r="O76" s="499" t="n"/>
+      <c r="P76" s="499" t="n"/>
+      <c r="Q76" s="499" t="n"/>
+      <c r="R76" s="499" t="n"/>
+      <c r="S76" s="499" t="n"/>
+      <c r="T76" s="499" t="n"/>
     </row>
     <row r="77" ht="15" customHeight="1">
       <c r="A77" s="369" t="n"/>
@@ -8237,21 +8593,21 @@
           <t>Open tender; Direct purchase; Negotiated purchase; Accelerated public tender</t>
         </is>
       </c>
-      <c r="F77" s="444" t="n"/>
-      <c r="G77" s="445" t="n"/>
-      <c r="H77" s="445" t="n"/>
-      <c r="I77" s="445" t="n"/>
-      <c r="J77" s="445" t="n"/>
-      <c r="K77" s="445" t="n"/>
-      <c r="L77" s="445" t="n"/>
-      <c r="M77" s="445" t="n"/>
-      <c r="N77" s="445" t="n"/>
-      <c r="O77" s="445" t="n"/>
-      <c r="P77" s="445" t="n"/>
-      <c r="Q77" s="445" t="n"/>
-      <c r="R77" s="445" t="n"/>
-      <c r="S77" s="445" t="n"/>
-      <c r="T77" s="445" t="n"/>
+      <c r="F77" s="459" t="n"/>
+      <c r="G77" s="499" t="n"/>
+      <c r="H77" s="499" t="n"/>
+      <c r="I77" s="499" t="n"/>
+      <c r="J77" s="499" t="n"/>
+      <c r="K77" s="499" t="n"/>
+      <c r="L77" s="499" t="n"/>
+      <c r="M77" s="499" t="n"/>
+      <c r="N77" s="499" t="n"/>
+      <c r="O77" s="499" t="n"/>
+      <c r="P77" s="499" t="n"/>
+      <c r="Q77" s="499" t="n"/>
+      <c r="R77" s="499" t="n"/>
+      <c r="S77" s="499" t="n"/>
+      <c r="T77" s="499" t="n"/>
     </row>
     <row r="78" ht="15" customHeight="1">
       <c r="A78" s="369" t="n"/>
@@ -8275,21 +8631,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F78" s="444" t="n"/>
-      <c r="G78" s="445" t="n"/>
-      <c r="H78" s="445" t="n"/>
-      <c r="I78" s="445" t="n"/>
-      <c r="J78" s="445" t="n"/>
-      <c r="K78" s="445" t="n"/>
-      <c r="L78" s="445" t="n"/>
-      <c r="M78" s="445" t="n"/>
-      <c r="N78" s="445" t="n"/>
-      <c r="O78" s="445" t="n"/>
-      <c r="P78" s="445" t="n"/>
-      <c r="Q78" s="445" t="n"/>
-      <c r="R78" s="445" t="n"/>
-      <c r="S78" s="445" t="n"/>
-      <c r="T78" s="445" t="n"/>
+      <c r="F78" s="459" t="n"/>
+      <c r="G78" s="499" t="n"/>
+      <c r="H78" s="499" t="n"/>
+      <c r="I78" s="499" t="n"/>
+      <c r="J78" s="499" t="n"/>
+      <c r="K78" s="499" t="n"/>
+      <c r="L78" s="499" t="n"/>
+      <c r="M78" s="499" t="n"/>
+      <c r="N78" s="499" t="n"/>
+      <c r="O78" s="499" t="n"/>
+      <c r="P78" s="499" t="n"/>
+      <c r="Q78" s="499" t="n"/>
+      <c r="R78" s="499" t="n"/>
+      <c r="S78" s="499" t="n"/>
+      <c r="T78" s="499" t="n"/>
     </row>
     <row r="79" ht="15" customHeight="1">
       <c r="A79" s="369" t="n"/>
@@ -8314,21 +8670,21 @@
           <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
         </is>
       </c>
-      <c r="F79" s="444" t="n"/>
-      <c r="G79" s="445" t="n"/>
-      <c r="H79" s="445" t="n"/>
-      <c r="I79" s="445" t="n"/>
-      <c r="J79" s="445" t="n"/>
-      <c r="K79" s="445" t="n"/>
-      <c r="L79" s="445" t="n"/>
-      <c r="M79" s="445" t="n"/>
-      <c r="N79" s="445" t="n"/>
-      <c r="O79" s="445" t="n"/>
-      <c r="P79" s="445" t="n"/>
-      <c r="Q79" s="445" t="n"/>
-      <c r="R79" s="445" t="n"/>
-      <c r="S79" s="445" t="n"/>
-      <c r="T79" s="445" t="n"/>
+      <c r="F79" s="459" t="n"/>
+      <c r="G79" s="499" t="n"/>
+      <c r="H79" s="499" t="n"/>
+      <c r="I79" s="499" t="n"/>
+      <c r="J79" s="499" t="n"/>
+      <c r="K79" s="499" t="n"/>
+      <c r="L79" s="499" t="n"/>
+      <c r="M79" s="499" t="n"/>
+      <c r="N79" s="499" t="n"/>
+      <c r="O79" s="499" t="n"/>
+      <c r="P79" s="499" t="n"/>
+      <c r="Q79" s="499" t="n"/>
+      <c r="R79" s="499" t="n"/>
+      <c r="S79" s="499" t="n"/>
+      <c r="T79" s="499" t="n"/>
     </row>
     <row r="80" ht="15" customHeight="1">
       <c r="A80" s="369" t="n"/>
@@ -8353,21 +8709,21 @@
           <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
         </is>
       </c>
-      <c r="F80" s="444" t="n"/>
-      <c r="G80" s="445" t="n"/>
-      <c r="H80" s="445" t="n"/>
-      <c r="I80" s="445" t="n"/>
-      <c r="J80" s="445" t="n"/>
-      <c r="K80" s="445" t="n"/>
-      <c r="L80" s="445" t="n"/>
-      <c r="M80" s="445" t="n"/>
-      <c r="N80" s="445" t="n"/>
-      <c r="O80" s="445" t="n"/>
-      <c r="P80" s="445" t="n"/>
-      <c r="Q80" s="445" t="n"/>
-      <c r="R80" s="445" t="n"/>
-      <c r="S80" s="445" t="n"/>
-      <c r="T80" s="445" t="n"/>
+      <c r="F80" s="459" t="n"/>
+      <c r="G80" s="499" t="n"/>
+      <c r="H80" s="499" t="n"/>
+      <c r="I80" s="499" t="n"/>
+      <c r="J80" s="499" t="n"/>
+      <c r="K80" s="499" t="n"/>
+      <c r="L80" s="499" t="n"/>
+      <c r="M80" s="499" t="n"/>
+      <c r="N80" s="499" t="n"/>
+      <c r="O80" s="499" t="n"/>
+      <c r="P80" s="499" t="n"/>
+      <c r="Q80" s="499" t="n"/>
+      <c r="R80" s="499" t="n"/>
+      <c r="S80" s="499" t="n"/>
+      <c r="T80" s="499" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
       <c r="A81" s="369" t="n"/>
@@ -8391,21 +8747,21 @@
           <t>Yes; No</t>
         </is>
       </c>
-      <c r="F81" s="444" t="n"/>
-      <c r="G81" s="445" t="n"/>
-      <c r="H81" s="445" t="n"/>
-      <c r="I81" s="445" t="n"/>
-      <c r="J81" s="445" t="n"/>
-      <c r="K81" s="445" t="n"/>
-      <c r="L81" s="445" t="n"/>
-      <c r="M81" s="445" t="n"/>
-      <c r="N81" s="445" t="n"/>
-      <c r="O81" s="445" t="n"/>
-      <c r="P81" s="445" t="n"/>
-      <c r="Q81" s="445" t="n"/>
-      <c r="R81" s="445" t="n"/>
-      <c r="S81" s="445" t="n"/>
-      <c r="T81" s="445" t="n"/>
+      <c r="F81" s="459" t="n"/>
+      <c r="G81" s="499" t="n"/>
+      <c r="H81" s="499" t="n"/>
+      <c r="I81" s="499" t="n"/>
+      <c r="J81" s="499" t="n"/>
+      <c r="K81" s="499" t="n"/>
+      <c r="L81" s="499" t="n"/>
+      <c r="M81" s="499" t="n"/>
+      <c r="N81" s="499" t="n"/>
+      <c r="O81" s="499" t="n"/>
+      <c r="P81" s="499" t="n"/>
+      <c r="Q81" s="499" t="n"/>
+      <c r="R81" s="499" t="n"/>
+      <c r="S81" s="499" t="n"/>
+      <c r="T81" s="499" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
       <c r="A82" s="361" t="n"/>
@@ -8429,21 +8785,21 @@
           <t>in millions of domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
-      <c r="F82" s="444" t="n"/>
-      <c r="G82" s="445" t="n"/>
-      <c r="H82" s="445" t="n"/>
-      <c r="I82" s="445" t="n"/>
-      <c r="J82" s="445" t="n"/>
-      <c r="K82" s="445" t="n"/>
-      <c r="L82" s="445" t="n"/>
-      <c r="M82" s="445" t="n"/>
-      <c r="N82" s="445" t="n"/>
-      <c r="O82" s="445" t="n"/>
-      <c r="P82" s="445" t="n"/>
-      <c r="Q82" s="445" t="n"/>
-      <c r="R82" s="445" t="n"/>
-      <c r="S82" s="445" t="n"/>
-      <c r="T82" s="445" t="n"/>
+      <c r="F82" s="459" t="n"/>
+      <c r="G82" s="499" t="n"/>
+      <c r="H82" s="499" t="n"/>
+      <c r="I82" s="499" t="n"/>
+      <c r="J82" s="499" t="n"/>
+      <c r="K82" s="499" t="n"/>
+      <c r="L82" s="499" t="n"/>
+      <c r="M82" s="499" t="n"/>
+      <c r="N82" s="499" t="n"/>
+      <c r="O82" s="499" t="n"/>
+      <c r="P82" s="499" t="n"/>
+      <c r="Q82" s="499" t="n"/>
+      <c r="R82" s="499" t="n"/>
+      <c r="S82" s="499" t="n"/>
+      <c r="T82" s="499" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1">
       <c r="A83" s="452" t="inlineStr">
@@ -8471,21 +8827,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F83" s="444" t="n"/>
-      <c r="G83" s="445" t="n"/>
-      <c r="H83" s="445" t="n"/>
-      <c r="I83" s="445" t="n"/>
-      <c r="J83" s="445" t="n"/>
-      <c r="K83" s="445" t="n"/>
-      <c r="L83" s="445" t="n"/>
-      <c r="M83" s="445" t="n"/>
-      <c r="N83" s="445" t="n"/>
-      <c r="O83" s="445" t="n"/>
-      <c r="P83" s="445" t="n"/>
-      <c r="Q83" s="445" t="n"/>
-      <c r="R83" s="445" t="n"/>
-      <c r="S83" s="445" t="n"/>
-      <c r="T83" s="445" t="n"/>
+      <c r="F83" s="459" t="n"/>
+      <c r="G83" s="499" t="n"/>
+      <c r="H83" s="499" t="n"/>
+      <c r="I83" s="499" t="n"/>
+      <c r="J83" s="499" t="n"/>
+      <c r="K83" s="499" t="n"/>
+      <c r="L83" s="499" t="n"/>
+      <c r="M83" s="499" t="n"/>
+      <c r="N83" s="499" t="n"/>
+      <c r="O83" s="499" t="n"/>
+      <c r="P83" s="499" t="n"/>
+      <c r="Q83" s="499" t="n"/>
+      <c r="R83" s="499" t="n"/>
+      <c r="S83" s="499" t="n"/>
+      <c r="T83" s="499" t="n"/>
     </row>
     <row r="84" ht="15" customHeight="1">
       <c r="A84" s="369" t="n"/>
@@ -8509,21 +8865,21 @@
           <t>Government authorities (inspections or audits); Third parties (inspections or audits); The regulated agents (self-reporting)</t>
         </is>
       </c>
-      <c r="F84" s="444" t="n"/>
-      <c r="G84" s="445" t="n"/>
-      <c r="H84" s="445" t="n"/>
-      <c r="I84" s="445" t="n"/>
-      <c r="J84" s="445" t="n"/>
-      <c r="K84" s="445" t="n"/>
-      <c r="L84" s="445" t="n"/>
-      <c r="M84" s="445" t="n"/>
-      <c r="N84" s="445" t="n"/>
-      <c r="O84" s="445" t="n"/>
-      <c r="P84" s="445" t="n"/>
-      <c r="Q84" s="445" t="n"/>
-      <c r="R84" s="445" t="n"/>
-      <c r="S84" s="445" t="n"/>
-      <c r="T84" s="445" t="n"/>
+      <c r="F84" s="459" t="n"/>
+      <c r="G84" s="499" t="n"/>
+      <c r="H84" s="499" t="n"/>
+      <c r="I84" s="499" t="n"/>
+      <c r="J84" s="499" t="n"/>
+      <c r="K84" s="499" t="n"/>
+      <c r="L84" s="499" t="n"/>
+      <c r="M84" s="499" t="n"/>
+      <c r="N84" s="499" t="n"/>
+      <c r="O84" s="499" t="n"/>
+      <c r="P84" s="499" t="n"/>
+      <c r="Q84" s="499" t="n"/>
+      <c r="R84" s="499" t="n"/>
+      <c r="S84" s="499" t="n"/>
+      <c r="T84" s="499" t="n"/>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c r="A85" s="369" t="n"/>
@@ -8547,21 +8903,21 @@
           <t>N/A</t>
         </is>
       </c>
-      <c r="F85" s="444" t="n"/>
-      <c r="G85" s="445" t="n"/>
-      <c r="H85" s="445" t="n"/>
-      <c r="I85" s="445" t="n"/>
-      <c r="J85" s="445" t="n"/>
-      <c r="K85" s="445" t="n"/>
-      <c r="L85" s="445" t="n"/>
-      <c r="M85" s="445" t="n"/>
-      <c r="N85" s="445" t="n"/>
-      <c r="O85" s="445" t="n"/>
-      <c r="P85" s="445" t="n"/>
-      <c r="Q85" s="445" t="n"/>
-      <c r="R85" s="445" t="n"/>
-      <c r="S85" s="445" t="n"/>
-      <c r="T85" s="445" t="n"/>
+      <c r="F85" s="459" t="n"/>
+      <c r="G85" s="499" t="n"/>
+      <c r="H85" s="499" t="n"/>
+      <c r="I85" s="499" t="n"/>
+      <c r="J85" s="499" t="n"/>
+      <c r="K85" s="499" t="n"/>
+      <c r="L85" s="499" t="n"/>
+      <c r="M85" s="499" t="n"/>
+      <c r="N85" s="499" t="n"/>
+      <c r="O85" s="499" t="n"/>
+      <c r="P85" s="499" t="n"/>
+      <c r="Q85" s="499" t="n"/>
+      <c r="R85" s="499" t="n"/>
+      <c r="S85" s="499" t="n"/>
+      <c r="T85" s="499" t="n"/>
     </row>
     <row r="86" ht="15" customHeight="1">
       <c r="A86" s="369" t="n"/>
@@ -8586,20 +8942,20 @@
         </is>
       </c>
       <c r="F86" s="459" t="n"/>
-      <c r="G86" s="445" t="n"/>
-      <c r="H86" s="445" t="n"/>
-      <c r="I86" s="445" t="n"/>
-      <c r="J86" s="445" t="n"/>
-      <c r="K86" s="445" t="n"/>
-      <c r="L86" s="445" t="n"/>
-      <c r="M86" s="445" t="n"/>
-      <c r="N86" s="445" t="n"/>
-      <c r="O86" s="445" t="n"/>
-      <c r="P86" s="445" t="n"/>
-      <c r="Q86" s="445" t="n"/>
-      <c r="R86" s="445" t="n"/>
-      <c r="S86" s="445" t="n"/>
-      <c r="T86" s="445" t="n"/>
+      <c r="G86" s="499" t="n"/>
+      <c r="H86" s="499" t="n"/>
+      <c r="I86" s="499" t="n"/>
+      <c r="J86" s="499" t="n"/>
+      <c r="K86" s="499" t="n"/>
+      <c r="L86" s="499" t="n"/>
+      <c r="M86" s="499" t="n"/>
+      <c r="N86" s="499" t="n"/>
+      <c r="O86" s="499" t="n"/>
+      <c r="P86" s="499" t="n"/>
+      <c r="Q86" s="499" t="n"/>
+      <c r="R86" s="499" t="n"/>
+      <c r="S86" s="499" t="n"/>
+      <c r="T86" s="499" t="n"/>
     </row>
     <row r="87" ht="15" customHeight="1">
       <c r="A87" s="369" t="n"/>
@@ -8624,20 +8980,20 @@
         </is>
       </c>
       <c r="F87" s="459" t="n"/>
-      <c r="G87" s="445" t="n"/>
-      <c r="H87" s="445" t="n"/>
-      <c r="I87" s="445" t="n"/>
-      <c r="J87" s="445" t="n"/>
-      <c r="K87" s="445" t="n"/>
-      <c r="L87" s="445" t="n"/>
-      <c r="M87" s="445" t="n"/>
-      <c r="N87" s="445" t="n"/>
-      <c r="O87" s="445" t="n"/>
-      <c r="P87" s="445" t="n"/>
-      <c r="Q87" s="445" t="n"/>
-      <c r="R87" s="445" t="n"/>
-      <c r="S87" s="445" t="n"/>
-      <c r="T87" s="445" t="n"/>
+      <c r="G87" s="499" t="n"/>
+      <c r="H87" s="499" t="n"/>
+      <c r="I87" s="499" t="n"/>
+      <c r="J87" s="499" t="n"/>
+      <c r="K87" s="499" t="n"/>
+      <c r="L87" s="499" t="n"/>
+      <c r="M87" s="499" t="n"/>
+      <c r="N87" s="499" t="n"/>
+      <c r="O87" s="499" t="n"/>
+      <c r="P87" s="499" t="n"/>
+      <c r="Q87" s="499" t="n"/>
+      <c r="R87" s="499" t="n"/>
+      <c r="S87" s="499" t="n"/>
+      <c r="T87" s="499" t="n"/>
     </row>
     <row r="88" ht="15" customHeight="1">
       <c r="A88" s="369" t="n"/>
@@ -8662,20 +9018,20 @@
         </is>
       </c>
       <c r="F88" s="459" t="n"/>
-      <c r="G88" s="445" t="n"/>
-      <c r="H88" s="445" t="n"/>
-      <c r="I88" s="445" t="n"/>
-      <c r="J88" s="445" t="n"/>
-      <c r="K88" s="445" t="n"/>
-      <c r="L88" s="445" t="n"/>
-      <c r="M88" s="445" t="n"/>
-      <c r="N88" s="445" t="n"/>
-      <c r="O88" s="445" t="n"/>
-      <c r="P88" s="445" t="n"/>
-      <c r="Q88" s="445" t="n"/>
-      <c r="R88" s="445" t="n"/>
-      <c r="S88" s="445" t="n"/>
-      <c r="T88" s="445" t="n"/>
+      <c r="G88" s="499" t="n"/>
+      <c r="H88" s="499" t="n"/>
+      <c r="I88" s="499" t="n"/>
+      <c r="J88" s="499" t="n"/>
+      <c r="K88" s="499" t="n"/>
+      <c r="L88" s="499" t="n"/>
+      <c r="M88" s="499" t="n"/>
+      <c r="N88" s="499" t="n"/>
+      <c r="O88" s="499" t="n"/>
+      <c r="P88" s="499" t="n"/>
+      <c r="Q88" s="499" t="n"/>
+      <c r="R88" s="499" t="n"/>
+      <c r="S88" s="499" t="n"/>
+      <c r="T88" s="499" t="n"/>
     </row>
     <row r="89" ht="15" customHeight="1">
       <c r="A89" s="369" t="n"/>
@@ -8700,20 +9056,20 @@
         </is>
       </c>
       <c r="F89" s="459" t="n"/>
-      <c r="G89" s="445" t="n"/>
-      <c r="H89" s="445" t="n"/>
-      <c r="I89" s="445" t="n"/>
-      <c r="J89" s="445" t="n"/>
-      <c r="K89" s="445" t="n"/>
-      <c r="L89" s="445" t="n"/>
-      <c r="M89" s="445" t="n"/>
-      <c r="N89" s="445" t="n"/>
-      <c r="O89" s="445" t="n"/>
-      <c r="P89" s="445" t="n"/>
-      <c r="Q89" s="445" t="n"/>
-      <c r="R89" s="445" t="n"/>
-      <c r="S89" s="445" t="n"/>
-      <c r="T89" s="445" t="n"/>
+      <c r="G89" s="499" t="n"/>
+      <c r="H89" s="499" t="n"/>
+      <c r="I89" s="499" t="n"/>
+      <c r="J89" s="499" t="n"/>
+      <c r="K89" s="499" t="n"/>
+      <c r="L89" s="499" t="n"/>
+      <c r="M89" s="499" t="n"/>
+      <c r="N89" s="499" t="n"/>
+      <c r="O89" s="499" t="n"/>
+      <c r="P89" s="499" t="n"/>
+      <c r="Q89" s="499" t="n"/>
+      <c r="R89" s="499" t="n"/>
+      <c r="S89" s="499" t="n"/>
+      <c r="T89" s="499" t="n"/>
     </row>
     <row r="90" ht="15" customHeight="1">
       <c r="A90" s="369" t="n"/>
@@ -8738,20 +9094,20 @@
         </is>
       </c>
       <c r="F90" s="459" t="n"/>
-      <c r="G90" s="445" t="n"/>
-      <c r="H90" s="445" t="n"/>
-      <c r="I90" s="445" t="n"/>
-      <c r="J90" s="445" t="n"/>
-      <c r="K90" s="445" t="n"/>
-      <c r="L90" s="445" t="n"/>
-      <c r="M90" s="445" t="n"/>
-      <c r="N90" s="445" t="n"/>
-      <c r="O90" s="445" t="n"/>
-      <c r="P90" s="445" t="n"/>
-      <c r="Q90" s="445" t="n"/>
-      <c r="R90" s="445" t="n"/>
-      <c r="S90" s="445" t="n"/>
-      <c r="T90" s="445" t="n"/>
+      <c r="G90" s="499" t="n"/>
+      <c r="H90" s="499" t="n"/>
+      <c r="I90" s="499" t="n"/>
+      <c r="J90" s="499" t="n"/>
+      <c r="K90" s="499" t="n"/>
+      <c r="L90" s="499" t="n"/>
+      <c r="M90" s="499" t="n"/>
+      <c r="N90" s="499" t="n"/>
+      <c r="O90" s="499" t="n"/>
+      <c r="P90" s="499" t="n"/>
+      <c r="Q90" s="499" t="n"/>
+      <c r="R90" s="499" t="n"/>
+      <c r="S90" s="499" t="n"/>
+      <c r="T90" s="499" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
       <c r="A91" s="369" t="n"/>
@@ -8776,20 +9132,20 @@
         </is>
       </c>
       <c r="F91" s="459" t="n"/>
-      <c r="G91" s="445" t="n"/>
-      <c r="H91" s="445" t="n"/>
-      <c r="I91" s="445" t="n"/>
-      <c r="J91" s="445" t="n"/>
-      <c r="K91" s="445" t="n"/>
-      <c r="L91" s="445" t="n"/>
-      <c r="M91" s="445" t="n"/>
-      <c r="N91" s="445" t="n"/>
-      <c r="O91" s="445" t="n"/>
-      <c r="P91" s="445" t="n"/>
-      <c r="Q91" s="445" t="n"/>
-      <c r="R91" s="445" t="n"/>
-      <c r="S91" s="445" t="n"/>
-      <c r="T91" s="445" t="n"/>
+      <c r="G91" s="499" t="n"/>
+      <c r="H91" s="499" t="n"/>
+      <c r="I91" s="499" t="n"/>
+      <c r="J91" s="499" t="n"/>
+      <c r="K91" s="499" t="n"/>
+      <c r="L91" s="499" t="n"/>
+      <c r="M91" s="499" t="n"/>
+      <c r="N91" s="499" t="n"/>
+      <c r="O91" s="499" t="n"/>
+      <c r="P91" s="499" t="n"/>
+      <c r="Q91" s="499" t="n"/>
+      <c r="R91" s="499" t="n"/>
+      <c r="S91" s="499" t="n"/>
+      <c r="T91" s="499" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1">
       <c r="A92" s="361" t="n"/>
@@ -8814,20 +9170,20 @@
         </is>
       </c>
       <c r="F92" s="459" t="n"/>
-      <c r="G92" s="445" t="n"/>
-      <c r="H92" s="445" t="n"/>
-      <c r="I92" s="445" t="n"/>
-      <c r="J92" s="445" t="n"/>
-      <c r="K92" s="445" t="n"/>
-      <c r="L92" s="445" t="n"/>
-      <c r="M92" s="445" t="n"/>
-      <c r="N92" s="445" t="n"/>
-      <c r="O92" s="445" t="n"/>
-      <c r="P92" s="445" t="n"/>
-      <c r="Q92" s="445" t="n"/>
-      <c r="R92" s="445" t="n"/>
-      <c r="S92" s="445" t="n"/>
-      <c r="T92" s="445" t="n"/>
+      <c r="G92" s="499" t="n"/>
+      <c r="H92" s="499" t="n"/>
+      <c r="I92" s="499" t="n"/>
+      <c r="J92" s="499" t="n"/>
+      <c r="K92" s="499" t="n"/>
+      <c r="L92" s="499" t="n"/>
+      <c r="M92" s="499" t="n"/>
+      <c r="N92" s="499" t="n"/>
+      <c r="O92" s="499" t="n"/>
+      <c r="P92" s="499" t="n"/>
+      <c r="Q92" s="499" t="n"/>
+      <c r="R92" s="499" t="n"/>
+      <c r="S92" s="499" t="n"/>
+      <c r="T92" s="499" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
       <c r="A93" s="452" t="inlineStr">
@@ -8855,21 +9211,21 @@
           <t>Financial; Regulatory; Reputational; None</t>
         </is>
       </c>
-      <c r="F93" s="444" t="n"/>
-      <c r="G93" s="445" t="n"/>
-      <c r="H93" s="445" t="n"/>
-      <c r="I93" s="445" t="n"/>
-      <c r="J93" s="445" t="n"/>
-      <c r="K93" s="445" t="n"/>
-      <c r="L93" s="445" t="n"/>
-      <c r="M93" s="445" t="n"/>
-      <c r="N93" s="445" t="n"/>
-      <c r="O93" s="445" t="n"/>
-      <c r="P93" s="445" t="n"/>
-      <c r="Q93" s="445" t="n"/>
-      <c r="R93" s="445" t="n"/>
-      <c r="S93" s="445" t="n"/>
-      <c r="T93" s="445" t="n"/>
+      <c r="F93" s="459" t="n"/>
+      <c r="G93" s="499" t="n"/>
+      <c r="H93" s="499" t="n"/>
+      <c r="I93" s="499" t="n"/>
+      <c r="J93" s="499" t="n"/>
+      <c r="K93" s="499" t="n"/>
+      <c r="L93" s="499" t="n"/>
+      <c r="M93" s="499" t="n"/>
+      <c r="N93" s="499" t="n"/>
+      <c r="O93" s="499" t="n"/>
+      <c r="P93" s="499" t="n"/>
+      <c r="Q93" s="499" t="n"/>
+      <c r="R93" s="499" t="n"/>
+      <c r="S93" s="499" t="n"/>
+      <c r="T93" s="499" t="n"/>
     </row>
     <row r="94" ht="15" customHeight="1">
       <c r="A94" s="369" t="n"/>
@@ -8893,21 +9249,21 @@
           <t>Yes/no, free for detail</t>
         </is>
       </c>
-      <c r="F94" s="444" t="n"/>
-      <c r="G94" s="445" t="n"/>
-      <c r="H94" s="445" t="n"/>
-      <c r="I94" s="445" t="n"/>
-      <c r="J94" s="445" t="n"/>
-      <c r="K94" s="445" t="n"/>
-      <c r="L94" s="445" t="n"/>
-      <c r="M94" s="445" t="n"/>
-      <c r="N94" s="445" t="n"/>
-      <c r="O94" s="445" t="n"/>
-      <c r="P94" s="445" t="n"/>
-      <c r="Q94" s="445" t="n"/>
-      <c r="R94" s="445" t="n"/>
-      <c r="S94" s="445" t="n"/>
-      <c r="T94" s="445" t="n"/>
+      <c r="F94" s="459" t="n"/>
+      <c r="G94" s="499" t="n"/>
+      <c r="H94" s="499" t="n"/>
+      <c r="I94" s="499" t="n"/>
+      <c r="J94" s="499" t="n"/>
+      <c r="K94" s="499" t="n"/>
+      <c r="L94" s="499" t="n"/>
+      <c r="M94" s="499" t="n"/>
+      <c r="N94" s="499" t="n"/>
+      <c r="O94" s="499" t="n"/>
+      <c r="P94" s="499" t="n"/>
+      <c r="Q94" s="499" t="n"/>
+      <c r="R94" s="499" t="n"/>
+      <c r="S94" s="499" t="n"/>
+      <c r="T94" s="499" t="n"/>
     </row>
     <row r="95" ht="15" customHeight="1">
       <c r="A95" s="361" t="n"/>
@@ -8931,21 +9287,21 @@
           <t>Yes/no, free for detail</t>
         </is>
       </c>
-      <c r="F95" s="444" t="n"/>
-      <c r="G95" s="445" t="n"/>
-      <c r="H95" s="445" t="n"/>
-      <c r="I95" s="445" t="n"/>
-      <c r="J95" s="445" t="n"/>
-      <c r="K95" s="445" t="n"/>
-      <c r="L95" s="445" t="n"/>
-      <c r="M95" s="445" t="n"/>
-      <c r="N95" s="445" t="n"/>
-      <c r="O95" s="445" t="n"/>
-      <c r="P95" s="445" t="n"/>
-      <c r="Q95" s="445" t="n"/>
-      <c r="R95" s="445" t="n"/>
-      <c r="S95" s="445" t="n"/>
-      <c r="T95" s="445" t="n"/>
+      <c r="F95" s="459" t="n"/>
+      <c r="G95" s="499" t="n"/>
+      <c r="H95" s="499" t="n"/>
+      <c r="I95" s="499" t="n"/>
+      <c r="J95" s="499" t="n"/>
+      <c r="K95" s="499" t="n"/>
+      <c r="L95" s="499" t="n"/>
+      <c r="M95" s="499" t="n"/>
+      <c r="N95" s="499" t="n"/>
+      <c r="O95" s="499" t="n"/>
+      <c r="P95" s="499" t="n"/>
+      <c r="Q95" s="499" t="n"/>
+      <c r="R95" s="499" t="n"/>
+      <c r="S95" s="499" t="n"/>
+      <c r="T95" s="499" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -9047,660 +9403,660 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="301" t="inlineStr">
+      <c r="A2" s="505" t="inlineStr">
         <is>
           <t>Electric vehicle purchase subsidy</t>
         </is>
       </c>
-      <c r="B2" s="301" t="inlineStr">
+      <c r="B2" s="505" t="inlineStr">
         <is>
           <t>新能源汽车推广应用补贴</t>
         </is>
       </c>
-      <c r="C2" s="301" t="inlineStr">
+      <c r="C2" s="505" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D2" s="301" t="n">
+      <c r="D2" s="505" t="n">
         <v>2009</v>
       </c>
-      <c r="E2" s="301" t="n">
+      <c r="E2" s="505" t="n">
         <v>2022</v>
       </c>
-      <c r="F2" s="301" t="inlineStr">
+      <c r="F2" s="505" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G2" s="301" t="inlineStr">
+      <c r="G2" s="505" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="H2" s="301" t="inlineStr">
+      <c r="H2" s="505" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I2" s="301" t="inlineStr">
+      <c r="I2" s="505" t="inlineStr">
         <is>
           <t>Vehicle</t>
         </is>
       </c>
-      <c r="J2" s="280" t="inlineStr">
+      <c r="J2" s="261" t="inlineStr">
         <is>
           <t>http://www.mof.gov.cn/gkml/caizhengwengao/2009niancaizhengbuwengao/caizhengwengao2009dierqi/200904/t20090413_132178.htm</t>
         </is>
       </c>
-      <c r="K2" s="280" t="inlineStr">
+      <c r="K2" s="261" t="inlineStr">
         <is>
           <t>https://www.gov.cn/zhengce/zhengceku/2021-12/31/content_5665857.htm</t>
         </is>
       </c>
-      <c r="L2" s="280" t="n"/>
-      <c r="M2" s="280" t="n"/>
-      <c r="N2" s="280" t="n"/>
-      <c r="O2" s="280" t="n"/>
-      <c r="P2" s="280" t="n"/>
-      <c r="Q2" s="280" t="n"/>
-      <c r="R2" s="280" t="n"/>
+      <c r="L2" s="261" t="n"/>
+      <c r="M2" s="261" t="n"/>
+      <c r="N2" s="261" t="n"/>
+      <c r="O2" s="261" t="n"/>
+      <c r="P2" s="261" t="n"/>
+      <c r="Q2" s="261" t="n"/>
+      <c r="R2" s="261" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="301" t="inlineStr">
+      <c r="A3" s="505" t="inlineStr">
         <is>
           <t>Subsidy for the Construction of Electric Vehicle Charging Infrastructure</t>
         </is>
       </c>
-      <c r="B3" s="301" t="inlineStr">
+      <c r="B3" s="505" t="inlineStr">
         <is>
           <t>电动汽车充电基础设施建设奖补</t>
         </is>
       </c>
-      <c r="C3" s="301" t="inlineStr">
+      <c r="C3" s="505" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D3" s="301" t="n">
+      <c r="D3" s="505" t="n">
         <v>2015</v>
       </c>
-      <c r="E3" s="301" t="n">
+      <c r="E3" s="505" t="n">
         <v>2020</v>
       </c>
-      <c r="F3" s="301" t="inlineStr">
+      <c r="F3" s="505" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G3" s="301" t="inlineStr">
+      <c r="G3" s="505" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="H3" s="301" t="inlineStr">
+      <c r="H3" s="505" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I3" s="301" t="inlineStr">
+      <c r="I3" s="505" t="inlineStr">
         <is>
           <t>Vehicle</t>
         </is>
       </c>
-      <c r="J3" s="280" t="inlineStr">
+      <c r="J3" s="261" t="inlineStr">
         <is>
           <t>http://www.mof.gov.cn/gp/xxgkml/jjjss/201601/t20160120_2512185.htm</t>
         </is>
       </c>
-      <c r="K3" s="280" t="inlineStr">
+      <c r="K3" s="261" t="inlineStr">
         <is>
           <t>https://www.gov.cn/zhengce/content/2015-10/09/content_10214.htm</t>
         </is>
       </c>
-      <c r="L3" s="280" t="n"/>
-      <c r="M3" s="280" t="n"/>
-      <c r="N3" s="280" t="n"/>
-      <c r="O3" s="280" t="n"/>
-      <c r="P3" s="280" t="n"/>
-      <c r="Q3" s="280" t="n"/>
-      <c r="R3" s="280" t="n"/>
+      <c r="L3" s="261" t="n"/>
+      <c r="M3" s="261" t="n"/>
+      <c r="N3" s="261" t="n"/>
+      <c r="O3" s="261" t="n"/>
+      <c r="P3" s="261" t="n"/>
+      <c r="Q3" s="261" t="n"/>
+      <c r="R3" s="261" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="280" t="inlineStr">
+      <c r="A4" s="261" t="inlineStr">
         <is>
           <t>Renewable electricity feed-in tariff</t>
         </is>
       </c>
-      <c r="B4" s="280" t="inlineStr">
+      <c r="B4" s="261" t="inlineStr">
         <is>
           <t>可再生能源上网电价补贴</t>
         </is>
       </c>
-      <c r="C4" s="280" t="inlineStr">
+      <c r="C4" s="261" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D4" s="301" t="n">
+      <c r="D4" s="505" t="n">
         <v>2006</v>
       </c>
-      <c r="E4" s="302" t="inlineStr">
+      <c r="E4" s="506" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="F4" s="301" t="inlineStr">
+      <c r="F4" s="505" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G4" s="301" t="inlineStr">
+      <c r="G4" s="505" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="H4" s="301" t="inlineStr">
+      <c r="H4" s="505" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I4" s="280" t="inlineStr">
+      <c r="I4" s="261" t="inlineStr">
         <is>
           <t>Solar power; wind power</t>
         </is>
       </c>
-      <c r="J4" s="293" t="inlineStr">
+      <c r="J4" s="261" t="inlineStr">
         <is>
           <t>https://www.ndrc.gov.cn/xxgk/zcfb/tz/200601/t20060120_965897.html</t>
         </is>
       </c>
-      <c r="K4" s="293" t="inlineStr">
+      <c r="K4" s="261" t="inlineStr">
         <is>
           <t>https://zfxxgk.ndrc.gov.cn/web/iteminfo.jsp?id=19761</t>
         </is>
       </c>
-      <c r="L4" s="293" t="n"/>
-      <c r="M4" s="293" t="n"/>
-      <c r="N4" s="293" t="n"/>
-      <c r="O4" s="293" t="n"/>
-      <c r="P4" s="293" t="n"/>
-      <c r="Q4" s="293" t="n"/>
-      <c r="R4" s="293" t="n"/>
+      <c r="L4" s="261" t="n"/>
+      <c r="M4" s="261" t="n"/>
+      <c r="N4" s="261" t="n"/>
+      <c r="O4" s="261" t="n"/>
+      <c r="P4" s="261" t="n"/>
+      <c r="Q4" s="261" t="n"/>
+      <c r="R4" s="261" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="303" t="inlineStr">
+      <c r="A5" s="507" t="inlineStr">
         <is>
           <t>Value-added tax incentive</t>
         </is>
       </c>
-      <c r="B5" s="303" t="inlineStr">
+      <c r="B5" s="507" t="inlineStr">
         <is>
           <t>风力发电增值税优惠</t>
         </is>
       </c>
-      <c r="C5" s="280" t="inlineStr">
+      <c r="C5" s="261" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D5" s="304" t="inlineStr">
+      <c r="D5" s="508" t="inlineStr">
         <is>
           <t>2015</t>
         </is>
       </c>
-      <c r="E5" s="305" t="inlineStr">
+      <c r="E5" s="509" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F5" s="301" t="inlineStr">
+      <c r="F5" s="505" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G5" s="301" t="inlineStr">
+      <c r="G5" s="505" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="H5" s="301" t="inlineStr">
+      <c r="H5" s="505" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I5" s="280" t="inlineStr">
+      <c r="I5" s="261" t="inlineStr">
         <is>
           <t>Wind power</t>
         </is>
       </c>
-      <c r="J5" s="293" t="inlineStr">
+      <c r="J5" s="261" t="inlineStr">
         <is>
           <t>http://www.mof.gov.cn/gkml/caizhengwengao/wg2015/wg201508/201601/t20160107_1645704.htm</t>
         </is>
       </c>
-      <c r="K5" s="293" t="inlineStr">
+      <c r="K5" s="261" t="inlineStr">
         <is>
           <t>https://shanghai.chinatax.gov.cn/zcfw/zcfgk/zzs/201507/t417892.html</t>
         </is>
       </c>
-      <c r="L5" s="293" t="n"/>
-      <c r="M5" s="293" t="n"/>
-      <c r="N5" s="293" t="n"/>
-      <c r="O5" s="293" t="n"/>
-      <c r="P5" s="293" t="n"/>
-      <c r="Q5" s="293" t="n"/>
-      <c r="R5" s="293" t="n"/>
+      <c r="L5" s="261" t="n"/>
+      <c r="M5" s="261" t="n"/>
+      <c r="N5" s="261" t="n"/>
+      <c r="O5" s="261" t="n"/>
+      <c r="P5" s="261" t="n"/>
+      <c r="Q5" s="261" t="n"/>
+      <c r="R5" s="261" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="303" t="inlineStr">
+      <c r="A6" s="507" t="inlineStr">
         <is>
           <t>Value-added tax incentive</t>
         </is>
       </c>
-      <c r="B6" s="303" t="inlineStr">
+      <c r="B6" s="507" t="inlineStr">
         <is>
           <t>核电增值税优惠</t>
         </is>
       </c>
-      <c r="C6" s="280" t="inlineStr">
+      <c r="C6" s="261" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D6" s="304" t="inlineStr">
+      <c r="D6" s="508" t="inlineStr">
         <is>
           <t>2008</t>
         </is>
       </c>
-      <c r="E6" s="305" t="inlineStr">
+      <c r="E6" s="509" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F6" s="301" t="inlineStr">
+      <c r="F6" s="505" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G6" s="301" t="inlineStr">
+      <c r="G6" s="505" t="inlineStr">
         <is>
           <t>Tax</t>
         </is>
       </c>
-      <c r="H6" s="301" t="inlineStr">
+      <c r="H6" s="505" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I6" s="280" t="inlineStr">
+      <c r="I6" s="261" t="inlineStr">
         <is>
           <t>Nuclear power</t>
         </is>
       </c>
-      <c r="J6" s="293" t="inlineStr">
+      <c r="J6" s="261" t="inlineStr">
         <is>
           <t>http://www.mof.gov.cn/zhengwuxinxi/caizhengxinwen/200805/t20080519_29110.htm</t>
         </is>
       </c>
-      <c r="K6" s="293" t="inlineStr">
+      <c r="K6" s="261" t="inlineStr">
         <is>
           <t>https://guizhou.chinatax.gov.cn/wjjb/zcfgk/szfl/ygsf/202203/t20220310_72917823.html</t>
         </is>
       </c>
-      <c r="L6" s="293" t="n"/>
-      <c r="M6" s="293" t="n"/>
-      <c r="N6" s="293" t="n"/>
-      <c r="O6" s="293" t="n"/>
-      <c r="P6" s="293" t="n"/>
-      <c r="Q6" s="293" t="n"/>
-      <c r="R6" s="293" t="n"/>
+      <c r="L6" s="261" t="n"/>
+      <c r="M6" s="261" t="n"/>
+      <c r="N6" s="261" t="n"/>
+      <c r="O6" s="261" t="n"/>
+      <c r="P6" s="261" t="n"/>
+      <c r="Q6" s="261" t="n"/>
+      <c r="R6" s="261" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="280" t="inlineStr">
+      <c r="A7" s="261" t="inlineStr">
         <is>
           <t>Vehicle purchase subsidy (fuel cell vehicle)</t>
         </is>
       </c>
-      <c r="B7" s="280" t="inlineStr">
+      <c r="B7" s="261" t="inlineStr">
         <is>
           <t>燃料电池汽车示范应用奖补</t>
         </is>
       </c>
-      <c r="C7" s="306" t="inlineStr">
+      <c r="C7" s="510" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D7" s="301" t="n">
+      <c r="D7" s="505" t="n">
         <v>2021</v>
       </c>
-      <c r="E7" s="302" t="inlineStr">
+      <c r="E7" s="506" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F7" s="287" t="inlineStr">
+      <c r="F7" s="511" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G7" s="280" t="inlineStr">
+      <c r="G7" s="261" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="H7" s="280" t="inlineStr">
+      <c r="H7" s="261" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="I7" s="280" t="inlineStr">
+      <c r="I7" s="261" t="inlineStr">
         <is>
           <t>Vehicle</t>
         </is>
       </c>
-      <c r="J7" s="293" t="inlineStr">
+      <c r="J7" s="261" t="inlineStr">
         <is>
           <t>https://www.gov.cn/zhengce/zhengceku/2020-09/21/content_5545221.htm</t>
         </is>
       </c>
-      <c r="K7" s="293" t="inlineStr">
+      <c r="K7" s="261" t="inlineStr">
         <is>
           <t>http://jjs.mof.gov.cn/zhengcefagui/202009/t20200918_3591168.htm</t>
         </is>
       </c>
-      <c r="L7" s="293" t="n"/>
-      <c r="M7" s="293" t="n"/>
-      <c r="N7" s="293" t="n"/>
-      <c r="O7" s="293" t="n"/>
-      <c r="P7" s="293" t="n"/>
-      <c r="Q7" s="293" t="n"/>
-      <c r="R7" s="293" t="n"/>
+      <c r="L7" s="261" t="n"/>
+      <c r="M7" s="261" t="n"/>
+      <c r="N7" s="261" t="n"/>
+      <c r="O7" s="261" t="n"/>
+      <c r="P7" s="261" t="n"/>
+      <c r="Q7" s="261" t="n"/>
+      <c r="R7" s="261" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="280" t="inlineStr">
+      <c r="A8" s="261" t="inlineStr">
         <is>
           <t>Central bank targeted relending for the clean and efficient use of coal</t>
         </is>
       </c>
-      <c r="B8" s="280" t="inlineStr">
+      <c r="B8" s="261" t="inlineStr">
         <is>
           <t>支持煤炭清洁高效利用专项再贷款</t>
         </is>
       </c>
-      <c r="C8" s="306" t="inlineStr">
+      <c r="C8" s="510" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
-      <c r="D8" s="304" t="inlineStr">
+      <c r="D8" s="508" t="inlineStr">
         <is>
           <t>2021</t>
         </is>
       </c>
-      <c r="E8" s="307" t="inlineStr">
+      <c r="E8" s="512" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F8" s="287" t="inlineStr">
+      <c r="F8" s="511" t="inlineStr">
         <is>
           <t>Economic</t>
         </is>
       </c>
-      <c r="G8" s="280" t="inlineStr">
+      <c r="G8" s="261" t="inlineStr">
         <is>
           <t>Subsidy</t>
         </is>
       </c>
-      <c r="H8" s="280" t="inlineStr">
+      <c r="H8" s="261" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
       </c>
-      <c r="I8" s="280" t="inlineStr">
+      <c r="I8" s="261" t="inlineStr">
         <is>
           <t>Coal</t>
         </is>
       </c>
-      <c r="J8" s="280" t="inlineStr">
+      <c r="J8" s="261" t="inlineStr">
         <is>
           <t>https://kj.jdz.gov.cn/zwzx/ztzl/kjjr/zc/t1036092.shtml</t>
         </is>
       </c>
-      <c r="K8" s="280" t="inlineStr">
+      <c r="K8" s="261" t="inlineStr">
         <is>
           <t>https://www.gov.cn/zhengce/2021-11/18/content_5651619.htm</t>
         </is>
       </c>
-      <c r="L8" s="280" t="n"/>
-      <c r="M8" s="280" t="n"/>
-      <c r="N8" s="280" t="n"/>
-      <c r="O8" s="280" t="n"/>
-      <c r="P8" s="280" t="n"/>
-      <c r="Q8" s="280" t="n"/>
-      <c r="R8" s="280" t="n"/>
+      <c r="L8" s="261" t="n"/>
+      <c r="M8" s="261" t="n"/>
+      <c r="N8" s="261" t="n"/>
+      <c r="O8" s="261" t="n"/>
+      <c r="P8" s="261" t="n"/>
+      <c r="Q8" s="261" t="n"/>
+      <c r="R8" s="261" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="280" t="n"/>
-      <c r="B9" s="280" t="n"/>
-      <c r="C9" s="280" t="n"/>
-      <c r="D9" s="280" t="n"/>
-      <c r="E9" s="280" t="n"/>
-      <c r="F9" s="280" t="n"/>
-      <c r="G9" s="280" t="n"/>
-      <c r="H9" s="280" t="n"/>
-      <c r="I9" s="280" t="n"/>
-      <c r="J9" s="280" t="n"/>
-      <c r="K9" s="280" t="n"/>
-      <c r="L9" s="280" t="n"/>
-      <c r="M9" s="280" t="n"/>
-      <c r="N9" s="280" t="n"/>
-      <c r="O9" s="280" t="n"/>
-      <c r="P9" s="280" t="n"/>
-      <c r="Q9" s="280" t="n"/>
-      <c r="R9" s="280" t="n"/>
+      <c r="A9" s="261" t="n"/>
+      <c r="B9" s="261" t="n"/>
+      <c r="C9" s="261" t="n"/>
+      <c r="D9" s="261" t="n"/>
+      <c r="E9" s="261" t="n"/>
+      <c r="F9" s="261" t="n"/>
+      <c r="G9" s="261" t="n"/>
+      <c r="H9" s="261" t="n"/>
+      <c r="I9" s="261" t="n"/>
+      <c r="J9" s="261" t="n"/>
+      <c r="K9" s="261" t="n"/>
+      <c r="L9" s="261" t="n"/>
+      <c r="M9" s="261" t="n"/>
+      <c r="N9" s="261" t="n"/>
+      <c r="O9" s="261" t="n"/>
+      <c r="P9" s="261" t="n"/>
+      <c r="Q9" s="261" t="n"/>
+      <c r="R9" s="261" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="280" t="n"/>
-      <c r="B10" s="280" t="n"/>
-      <c r="C10" s="280" t="n"/>
-      <c r="D10" s="280" t="n"/>
-      <c r="E10" s="280" t="n"/>
-      <c r="F10" s="280" t="n"/>
-      <c r="G10" s="280" t="n"/>
-      <c r="H10" s="280" t="n"/>
-      <c r="I10" s="280" t="n"/>
-      <c r="J10" s="280" t="n"/>
-      <c r="K10" s="280" t="n"/>
-      <c r="L10" s="280" t="n"/>
-      <c r="M10" s="280" t="n"/>
-      <c r="N10" s="280" t="n"/>
-      <c r="O10" s="280" t="n"/>
-      <c r="P10" s="280" t="n"/>
-      <c r="Q10" s="280" t="n"/>
-      <c r="R10" s="280" t="n"/>
+      <c r="A10" s="261" t="n"/>
+      <c r="B10" s="261" t="n"/>
+      <c r="C10" s="261" t="n"/>
+      <c r="D10" s="261" t="n"/>
+      <c r="E10" s="261" t="n"/>
+      <c r="F10" s="261" t="n"/>
+      <c r="G10" s="261" t="n"/>
+      <c r="H10" s="261" t="n"/>
+      <c r="I10" s="261" t="n"/>
+      <c r="J10" s="261" t="n"/>
+      <c r="K10" s="261" t="n"/>
+      <c r="L10" s="261" t="n"/>
+      <c r="M10" s="261" t="n"/>
+      <c r="N10" s="261" t="n"/>
+      <c r="O10" s="261" t="n"/>
+      <c r="P10" s="261" t="n"/>
+      <c r="Q10" s="261" t="n"/>
+      <c r="R10" s="261" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="280" t="n"/>
-      <c r="B11" s="280" t="n"/>
-      <c r="C11" s="280" t="n"/>
-      <c r="D11" s="280" t="n"/>
-      <c r="E11" s="280" t="n"/>
-      <c r="F11" s="280" t="n"/>
-      <c r="G11" s="280" t="n"/>
-      <c r="H11" s="280" t="n"/>
-      <c r="I11" s="280" t="n"/>
-      <c r="J11" s="280" t="n"/>
-      <c r="K11" s="280" t="n"/>
-      <c r="L11" s="280" t="n"/>
-      <c r="M11" s="280" t="n"/>
-      <c r="N11" s="280" t="n"/>
-      <c r="O11" s="280" t="n"/>
-      <c r="P11" s="280" t="n"/>
-      <c r="Q11" s="280" t="n"/>
-      <c r="R11" s="280" t="n"/>
+      <c r="A11" s="261" t="n"/>
+      <c r="B11" s="261" t="n"/>
+      <c r="C11" s="261" t="n"/>
+      <c r="D11" s="261" t="n"/>
+      <c r="E11" s="261" t="n"/>
+      <c r="F11" s="261" t="n"/>
+      <c r="G11" s="261" t="n"/>
+      <c r="H11" s="261" t="n"/>
+      <c r="I11" s="261" t="n"/>
+      <c r="J11" s="261" t="n"/>
+      <c r="K11" s="261" t="n"/>
+      <c r="L11" s="261" t="n"/>
+      <c r="M11" s="261" t="n"/>
+      <c r="N11" s="261" t="n"/>
+      <c r="O11" s="261" t="n"/>
+      <c r="P11" s="261" t="n"/>
+      <c r="Q11" s="261" t="n"/>
+      <c r="R11" s="261" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="280" t="n"/>
-      <c r="B12" s="280" t="n"/>
-      <c r="C12" s="280" t="n"/>
-      <c r="D12" s="280" t="n"/>
-      <c r="E12" s="280" t="n"/>
-      <c r="F12" s="280" t="n"/>
-      <c r="G12" s="280" t="n"/>
-      <c r="H12" s="280" t="n"/>
-      <c r="I12" s="280" t="n"/>
-      <c r="J12" s="280" t="n"/>
-      <c r="K12" s="280" t="n"/>
-      <c r="L12" s="280" t="n"/>
-      <c r="M12" s="280" t="n"/>
-      <c r="N12" s="280" t="n"/>
-      <c r="O12" s="280" t="n"/>
-      <c r="P12" s="280" t="n"/>
-      <c r="Q12" s="280" t="n"/>
-      <c r="R12" s="280" t="n"/>
+      <c r="A12" s="261" t="n"/>
+      <c r="B12" s="261" t="n"/>
+      <c r="C12" s="261" t="n"/>
+      <c r="D12" s="261" t="n"/>
+      <c r="E12" s="261" t="n"/>
+      <c r="F12" s="261" t="n"/>
+      <c r="G12" s="261" t="n"/>
+      <c r="H12" s="261" t="n"/>
+      <c r="I12" s="261" t="n"/>
+      <c r="J12" s="261" t="n"/>
+      <c r="K12" s="261" t="n"/>
+      <c r="L12" s="261" t="n"/>
+      <c r="M12" s="261" t="n"/>
+      <c r="N12" s="261" t="n"/>
+      <c r="O12" s="261" t="n"/>
+      <c r="P12" s="261" t="n"/>
+      <c r="Q12" s="261" t="n"/>
+      <c r="R12" s="261" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="280" t="n"/>
-      <c r="B13" s="280" t="n"/>
-      <c r="C13" s="280" t="n"/>
-      <c r="D13" s="280" t="n"/>
-      <c r="E13" s="280" t="n"/>
-      <c r="F13" s="280" t="n"/>
-      <c r="G13" s="280" t="n"/>
-      <c r="H13" s="280" t="n"/>
-      <c r="I13" s="280" t="n"/>
-      <c r="J13" s="280" t="n"/>
-      <c r="K13" s="280" t="n"/>
-      <c r="L13" s="280" t="n"/>
-      <c r="M13" s="280" t="n"/>
-      <c r="N13" s="280" t="n"/>
-      <c r="O13" s="280" t="n"/>
-      <c r="P13" s="280" t="n"/>
-      <c r="Q13" s="280" t="n"/>
-      <c r="R13" s="280" t="n"/>
+      <c r="A13" s="261" t="n"/>
+      <c r="B13" s="261" t="n"/>
+      <c r="C13" s="261" t="n"/>
+      <c r="D13" s="261" t="n"/>
+      <c r="E13" s="261" t="n"/>
+      <c r="F13" s="261" t="n"/>
+      <c r="G13" s="261" t="n"/>
+      <c r="H13" s="261" t="n"/>
+      <c r="I13" s="261" t="n"/>
+      <c r="J13" s="261" t="n"/>
+      <c r="K13" s="261" t="n"/>
+      <c r="L13" s="261" t="n"/>
+      <c r="M13" s="261" t="n"/>
+      <c r="N13" s="261" t="n"/>
+      <c r="O13" s="261" t="n"/>
+      <c r="P13" s="261" t="n"/>
+      <c r="Q13" s="261" t="n"/>
+      <c r="R13" s="261" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="280" t="n"/>
-      <c r="B14" s="280" t="n"/>
-      <c r="C14" s="280" t="n"/>
-      <c r="D14" s="280" t="n"/>
-      <c r="E14" s="280" t="n"/>
-      <c r="F14" s="280" t="n"/>
-      <c r="G14" s="280" t="n"/>
-      <c r="H14" s="280" t="n"/>
-      <c r="I14" s="280" t="n"/>
-      <c r="J14" s="280" t="n"/>
-      <c r="K14" s="280" t="n"/>
-      <c r="L14" s="280" t="n"/>
-      <c r="M14" s="280" t="n"/>
-      <c r="N14" s="280" t="n"/>
-      <c r="O14" s="280" t="n"/>
-      <c r="P14" s="280" t="n"/>
-      <c r="Q14" s="280" t="n"/>
-      <c r="R14" s="280" t="n"/>
+      <c r="A14" s="261" t="n"/>
+      <c r="B14" s="261" t="n"/>
+      <c r="C14" s="261" t="n"/>
+      <c r="D14" s="261" t="n"/>
+      <c r="E14" s="261" t="n"/>
+      <c r="F14" s="261" t="n"/>
+      <c r="G14" s="261" t="n"/>
+      <c r="H14" s="261" t="n"/>
+      <c r="I14" s="261" t="n"/>
+      <c r="J14" s="261" t="n"/>
+      <c r="K14" s="261" t="n"/>
+      <c r="L14" s="261" t="n"/>
+      <c r="M14" s="261" t="n"/>
+      <c r="N14" s="261" t="n"/>
+      <c r="O14" s="261" t="n"/>
+      <c r="P14" s="261" t="n"/>
+      <c r="Q14" s="261" t="n"/>
+      <c r="R14" s="261" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="280" t="n"/>
-      <c r="B15" s="280" t="n"/>
-      <c r="C15" s="280" t="n"/>
-      <c r="D15" s="280" t="n"/>
-      <c r="E15" s="280" t="n"/>
-      <c r="F15" s="280" t="n"/>
-      <c r="G15" s="280" t="n"/>
-      <c r="H15" s="280" t="n"/>
-      <c r="I15" s="280" t="n"/>
-      <c r="J15" s="280" t="n"/>
-      <c r="K15" s="280" t="n"/>
-      <c r="L15" s="280" t="n"/>
-      <c r="M15" s="280" t="n"/>
-      <c r="N15" s="280" t="n"/>
-      <c r="O15" s="280" t="n"/>
-      <c r="P15" s="280" t="n"/>
-      <c r="Q15" s="280" t="n"/>
-      <c r="R15" s="280" t="n"/>
+      <c r="A15" s="261" t="n"/>
+      <c r="B15" s="261" t="n"/>
+      <c r="C15" s="261" t="n"/>
+      <c r="D15" s="261" t="n"/>
+      <c r="E15" s="261" t="n"/>
+      <c r="F15" s="261" t="n"/>
+      <c r="G15" s="261" t="n"/>
+      <c r="H15" s="261" t="n"/>
+      <c r="I15" s="261" t="n"/>
+      <c r="J15" s="261" t="n"/>
+      <c r="K15" s="261" t="n"/>
+      <c r="L15" s="261" t="n"/>
+      <c r="M15" s="261" t="n"/>
+      <c r="N15" s="261" t="n"/>
+      <c r="O15" s="261" t="n"/>
+      <c r="P15" s="261" t="n"/>
+      <c r="Q15" s="261" t="n"/>
+      <c r="R15" s="261" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="280" t="n"/>
-      <c r="B16" s="280" t="n"/>
-      <c r="C16" s="280" t="n"/>
-      <c r="D16" s="280" t="n"/>
-      <c r="E16" s="280" t="n"/>
-      <c r="F16" s="280" t="n"/>
-      <c r="G16" s="280" t="n"/>
-      <c r="H16" s="280" t="n"/>
-      <c r="I16" s="280" t="n"/>
-      <c r="J16" s="280" t="n"/>
-      <c r="K16" s="280" t="n"/>
-      <c r="L16" s="280" t="n"/>
-      <c r="M16" s="280" t="n"/>
-      <c r="N16" s="280" t="n"/>
-      <c r="O16" s="280" t="n"/>
-      <c r="P16" s="280" t="n"/>
-      <c r="Q16" s="280" t="n"/>
-      <c r="R16" s="280" t="n"/>
+      <c r="A16" s="261" t="n"/>
+      <c r="B16" s="261" t="n"/>
+      <c r="C16" s="261" t="n"/>
+      <c r="D16" s="261" t="n"/>
+      <c r="E16" s="261" t="n"/>
+      <c r="F16" s="261" t="n"/>
+      <c r="G16" s="261" t="n"/>
+      <c r="H16" s="261" t="n"/>
+      <c r="I16" s="261" t="n"/>
+      <c r="J16" s="261" t="n"/>
+      <c r="K16" s="261" t="n"/>
+      <c r="L16" s="261" t="n"/>
+      <c r="M16" s="261" t="n"/>
+      <c r="N16" s="261" t="n"/>
+      <c r="O16" s="261" t="n"/>
+      <c r="P16" s="261" t="n"/>
+      <c r="Q16" s="261" t="n"/>
+      <c r="R16" s="261" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="280" t="n"/>
-      <c r="B17" s="280" t="n"/>
-      <c r="C17" s="280" t="n"/>
-      <c r="D17" s="280" t="n"/>
-      <c r="E17" s="280" t="n"/>
-      <c r="F17" s="280" t="n"/>
-      <c r="G17" s="280" t="n"/>
-      <c r="H17" s="280" t="n"/>
-      <c r="I17" s="280" t="n"/>
-      <c r="J17" s="280" t="n"/>
-      <c r="K17" s="280" t="n"/>
-      <c r="L17" s="280" t="n"/>
-      <c r="M17" s="280" t="n"/>
-      <c r="N17" s="280" t="n"/>
-      <c r="O17" s="280" t="n"/>
-      <c r="P17" s="280" t="n"/>
-      <c r="Q17" s="280" t="n"/>
-      <c r="R17" s="280" t="n"/>
+      <c r="A17" s="261" t="n"/>
+      <c r="B17" s="261" t="n"/>
+      <c r="C17" s="261" t="n"/>
+      <c r="D17" s="261" t="n"/>
+      <c r="E17" s="261" t="n"/>
+      <c r="F17" s="261" t="n"/>
+      <c r="G17" s="261" t="n"/>
+      <c r="H17" s="261" t="n"/>
+      <c r="I17" s="261" t="n"/>
+      <c r="J17" s="261" t="n"/>
+      <c r="K17" s="261" t="n"/>
+      <c r="L17" s="261" t="n"/>
+      <c r="M17" s="261" t="n"/>
+      <c r="N17" s="261" t="n"/>
+      <c r="O17" s="261" t="n"/>
+      <c r="P17" s="261" t="n"/>
+      <c r="Q17" s="261" t="n"/>
+      <c r="R17" s="261" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="280" t="n"/>
-      <c r="B18" s="280" t="n"/>
-      <c r="C18" s="280" t="n"/>
-      <c r="D18" s="280" t="n"/>
-      <c r="E18" s="280" t="n"/>
-      <c r="F18" s="280" t="n"/>
-      <c r="G18" s="280" t="n"/>
-      <c r="H18" s="280" t="n"/>
-      <c r="I18" s="280" t="n"/>
-      <c r="J18" s="280" t="n"/>
-      <c r="K18" s="280" t="n"/>
-      <c r="L18" s="280" t="n"/>
-      <c r="M18" s="280" t="n"/>
-      <c r="N18" s="280" t="n"/>
-      <c r="O18" s="280" t="n"/>
-      <c r="P18" s="280" t="n"/>
-      <c r="Q18" s="280" t="n"/>
-      <c r="R18" s="280" t="n"/>
+      <c r="A18" s="261" t="n"/>
+      <c r="B18" s="261" t="n"/>
+      <c r="C18" s="261" t="n"/>
+      <c r="D18" s="261" t="n"/>
+      <c r="E18" s="261" t="n"/>
+      <c r="F18" s="261" t="n"/>
+      <c r="G18" s="261" t="n"/>
+      <c r="H18" s="261" t="n"/>
+      <c r="I18" s="261" t="n"/>
+      <c r="J18" s="261" t="n"/>
+      <c r="K18" s="261" t="n"/>
+      <c r="L18" s="261" t="n"/>
+      <c r="M18" s="261" t="n"/>
+      <c r="N18" s="261" t="n"/>
+      <c r="O18" s="261" t="n"/>
+      <c r="P18" s="261" t="n"/>
+      <c r="Q18" s="261" t="n"/>
+      <c r="R18" s="261" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="280" t="n"/>
-      <c r="B19" s="280" t="n"/>
-      <c r="C19" s="280" t="n"/>
-      <c r="D19" s="280" t="n"/>
-      <c r="E19" s="280" t="n"/>
-      <c r="F19" s="280" t="n"/>
-      <c r="G19" s="280" t="n"/>
-      <c r="H19" s="280" t="n"/>
-      <c r="I19" s="280" t="n"/>
-      <c r="J19" s="280" t="n"/>
-      <c r="K19" s="280" t="n"/>
-      <c r="L19" s="280" t="n"/>
-      <c r="M19" s="280" t="n"/>
-      <c r="N19" s="280" t="n"/>
-      <c r="O19" s="280" t="n"/>
-      <c r="P19" s="280" t="n"/>
-      <c r="Q19" s="280" t="n"/>
-      <c r="R19" s="280" t="n"/>
+      <c r="A19" s="261" t="n"/>
+      <c r="B19" s="261" t="n"/>
+      <c r="C19" s="261" t="n"/>
+      <c r="D19" s="261" t="n"/>
+      <c r="E19" s="261" t="n"/>
+      <c r="F19" s="261" t="n"/>
+      <c r="G19" s="261" t="n"/>
+      <c r="H19" s="261" t="n"/>
+      <c r="I19" s="261" t="n"/>
+      <c r="J19" s="261" t="n"/>
+      <c r="K19" s="261" t="n"/>
+      <c r="L19" s="261" t="n"/>
+      <c r="M19" s="261" t="n"/>
+      <c r="N19" s="261" t="n"/>
+      <c r="O19" s="261" t="n"/>
+      <c r="P19" s="261" t="n"/>
+      <c r="Q19" s="261" t="n"/>
+      <c r="R19" s="261" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10250,7 +10606,7 @@
           <t>Sub-sector</t>
         </is>
       </c>
-      <c r="M1" s="407" t="n"/>
+      <c r="M1" s="469" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11797,14 +12153,14 @@
   <dimension ref="A1:S33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="12.6640625" customWidth="1" min="1" max="1"/>
-    <col width="15.19921875" customWidth="1" min="3" max="3"/>
-    <col width="17.46484375" customWidth="1" min="8" max="8"/>
-    <col width="16.1328125" customWidth="1" min="15" max="15"/>
+    <col width="12.6875" customWidth="1" min="1" max="1"/>
+    <col width="15.1875" customWidth="1" min="3" max="3"/>
+    <col width="17.4375" customWidth="1" min="8" max="8"/>
+    <col width="16.125" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1">
-      <c r="A1" s="315" t="inlineStr">
+      <c r="A1" s="519" t="inlineStr">
         <is>
           <t>China Climate Policy Instrument Database (CCPID)</t>
         </is>
@@ -11816,137 +12172,137 @@
       <c r="F1" s="109" t="n"/>
       <c r="G1" s="109" t="n"/>
       <c r="H1" s="110" t="n"/>
-      <c r="I1" s="231" t="n"/>
-      <c r="J1" s="231" t="n"/>
-      <c r="K1" s="316" t="n"/>
-      <c r="L1" s="231" t="n"/>
-      <c r="M1" s="231" t="n"/>
-      <c r="N1" s="231" t="n"/>
-      <c r="O1" s="231" t="n"/>
-      <c r="P1" s="233" t="n"/>
-      <c r="Q1" s="233" t="n"/>
-      <c r="R1" s="233" t="n"/>
-      <c r="S1" s="233" t="n"/>
+      <c r="I1" s="522" t="n"/>
+      <c r="J1" s="522" t="n"/>
+      <c r="K1" s="523" t="n"/>
+      <c r="L1" s="522" t="n"/>
+      <c r="M1" s="522" t="n"/>
+      <c r="N1" s="522" t="n"/>
+      <c r="O1" s="522" t="n"/>
+      <c r="P1" s="524" t="n"/>
+      <c r="Q1" s="524" t="n"/>
+      <c r="R1" s="524" t="n"/>
+      <c r="S1" s="524" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="231" t="n"/>
-      <c r="B2" s="231" t="n"/>
-      <c r="C2" s="231" t="n"/>
-      <c r="D2" s="231" t="n"/>
-      <c r="E2" s="231" t="n"/>
-      <c r="F2" s="231" t="n"/>
-      <c r="G2" s="231" t="n"/>
-      <c r="H2" s="231" t="n"/>
-      <c r="I2" s="231" t="n"/>
-      <c r="J2" s="231" t="n"/>
-      <c r="K2" s="231" t="n"/>
-      <c r="L2" s="231" t="n"/>
-      <c r="M2" s="231" t="n"/>
-      <c r="N2" s="231" t="n"/>
-      <c r="O2" s="231" t="n"/>
-      <c r="P2" s="233" t="n"/>
-      <c r="Q2" s="233" t="n"/>
-      <c r="R2" s="233" t="n"/>
-      <c r="S2" s="233" t="n"/>
+      <c r="A2" s="471" t="n"/>
+      <c r="B2" s="471" t="n"/>
+      <c r="C2" s="471" t="n"/>
+      <c r="D2" s="471" t="n"/>
+      <c r="E2" s="471" t="n"/>
+      <c r="F2" s="471" t="n"/>
+      <c r="G2" s="471" t="n"/>
+      <c r="H2" s="471" t="n"/>
+      <c r="I2" s="471" t="n"/>
+      <c r="J2" s="471" t="n"/>
+      <c r="K2" s="471" t="n"/>
+      <c r="L2" s="471" t="n"/>
+      <c r="M2" s="471" t="n"/>
+      <c r="N2" s="471" t="n"/>
+      <c r="O2" s="471" t="n"/>
+      <c r="P2" s="473" t="n"/>
+      <c r="Q2" s="473" t="n"/>
+      <c r="R2" s="473" t="n"/>
+      <c r="S2" s="473" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="234" t="inlineStr">
+      <c r="A3" s="474" t="inlineStr">
         <is>
           <t>developed by MGF Lab, National School of Development, Peking University</t>
         </is>
       </c>
       <c r="B3" s="109" t="n"/>
       <c r="C3" s="110" t="n"/>
-      <c r="D3" s="231" t="n"/>
-      <c r="E3" s="231" t="n"/>
-      <c r="F3" s="231" t="n"/>
-      <c r="G3" s="231" t="n"/>
-      <c r="H3" s="231" t="n"/>
-      <c r="I3" s="231" t="n"/>
-      <c r="J3" s="231" t="n"/>
-      <c r="K3" s="231" t="n"/>
-      <c r="L3" s="231" t="n"/>
-      <c r="M3" s="231" t="n"/>
-      <c r="N3" s="231" t="n"/>
-      <c r="O3" s="231" t="n"/>
-      <c r="P3" s="233" t="n"/>
-      <c r="Q3" s="233" t="n"/>
-      <c r="R3" s="233" t="n"/>
-      <c r="S3" s="233" t="n"/>
+      <c r="D3" s="471" t="n"/>
+      <c r="E3" s="471" t="n"/>
+      <c r="F3" s="471" t="n"/>
+      <c r="G3" s="471" t="n"/>
+      <c r="H3" s="471" t="n"/>
+      <c r="I3" s="471" t="n"/>
+      <c r="J3" s="471" t="n"/>
+      <c r="K3" s="471" t="n"/>
+      <c r="L3" s="471" t="n"/>
+      <c r="M3" s="471" t="n"/>
+      <c r="N3" s="471" t="n"/>
+      <c r="O3" s="471" t="n"/>
+      <c r="P3" s="473" t="n"/>
+      <c r="Q3" s="473" t="n"/>
+      <c r="R3" s="473" t="n"/>
+      <c r="S3" s="473" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="234" t="inlineStr">
+      <c r="A4" s="474" t="inlineStr">
         <is>
           <t>as of August 2026</t>
         </is>
       </c>
       <c r="B4" s="110" t="n"/>
-      <c r="C4" s="231" t="n"/>
-      <c r="D4" s="231" t="n"/>
-      <c r="E4" s="231" t="n"/>
-      <c r="F4" s="231" t="n"/>
-      <c r="G4" s="231" t="n"/>
-      <c r="H4" s="231" t="n"/>
-      <c r="I4" s="231" t="n"/>
-      <c r="J4" s="231" t="n"/>
-      <c r="K4" s="231" t="n"/>
-      <c r="L4" s="231" t="n"/>
-      <c r="M4" s="231" t="n"/>
-      <c r="N4" s="231" t="n"/>
-      <c r="O4" s="231" t="n"/>
-      <c r="P4" s="233" t="n"/>
-      <c r="Q4" s="233" t="n"/>
-      <c r="R4" s="233" t="n"/>
-      <c r="S4" s="233" t="n"/>
+      <c r="C4" s="471" t="n"/>
+      <c r="D4" s="471" t="n"/>
+      <c r="E4" s="471" t="n"/>
+      <c r="F4" s="471" t="n"/>
+      <c r="G4" s="471" t="n"/>
+      <c r="H4" s="471" t="n"/>
+      <c r="I4" s="471" t="n"/>
+      <c r="J4" s="471" t="n"/>
+      <c r="K4" s="471" t="n"/>
+      <c r="L4" s="471" t="n"/>
+      <c r="M4" s="471" t="n"/>
+      <c r="N4" s="471" t="n"/>
+      <c r="O4" s="471" t="n"/>
+      <c r="P4" s="473" t="n"/>
+      <c r="Q4" s="473" t="n"/>
+      <c r="R4" s="473" t="n"/>
+      <c r="S4" s="473" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="231" t="n"/>
-      <c r="B5" s="231" t="n"/>
-      <c r="C5" s="231" t="n"/>
-      <c r="D5" s="231" t="n"/>
-      <c r="E5" s="231" t="n"/>
-      <c r="F5" s="231" t="n"/>
-      <c r="G5" s="231" t="n"/>
-      <c r="H5" s="231" t="n"/>
-      <c r="I5" s="231" t="n"/>
-      <c r="J5" s="231" t="n"/>
-      <c r="K5" s="231" t="n"/>
-      <c r="L5" s="231" t="n"/>
-      <c r="M5" s="231" t="n"/>
-      <c r="N5" s="231" t="n"/>
-      <c r="O5" s="231" t="n"/>
-      <c r="P5" s="233" t="n"/>
-      <c r="Q5" s="233" t="n"/>
-      <c r="R5" s="233" t="n"/>
-      <c r="S5" s="233" t="n"/>
+      <c r="A5" s="471" t="n"/>
+      <c r="B5" s="471" t="n"/>
+      <c r="C5" s="471" t="n"/>
+      <c r="D5" s="471" t="n"/>
+      <c r="E5" s="471" t="n"/>
+      <c r="F5" s="471" t="n"/>
+      <c r="G5" s="471" t="n"/>
+      <c r="H5" s="471" t="n"/>
+      <c r="I5" s="471" t="n"/>
+      <c r="J5" s="471" t="n"/>
+      <c r="K5" s="471" t="n"/>
+      <c r="L5" s="471" t="n"/>
+      <c r="M5" s="471" t="n"/>
+      <c r="N5" s="471" t="n"/>
+      <c r="O5" s="471" t="n"/>
+      <c r="P5" s="473" t="n"/>
+      <c r="Q5" s="473" t="n"/>
+      <c r="R5" s="473" t="n"/>
+      <c r="S5" s="473" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="330" t="inlineStr">
+      <c r="A6" s="475" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="B6" s="331" t="n"/>
-      <c r="C6" s="331" t="n"/>
-      <c r="D6" s="331" t="n"/>
-      <c r="E6" s="331" t="n"/>
-      <c r="F6" s="331" t="n"/>
-      <c r="G6" s="331" t="n"/>
-      <c r="H6" s="331" t="n"/>
-      <c r="I6" s="331" t="n"/>
-      <c r="J6" s="331" t="n"/>
-      <c r="K6" s="331" t="n"/>
-      <c r="L6" s="331" t="n"/>
-      <c r="M6" s="331" t="n"/>
-      <c r="N6" s="231" t="n"/>
-      <c r="O6" s="231" t="n"/>
-      <c r="P6" s="233" t="n"/>
-      <c r="Q6" s="233" t="n"/>
-      <c r="R6" s="233" t="n"/>
-      <c r="S6" s="233" t="n"/>
-    </row>
-    <row r="7" ht="191.65" customHeight="1">
-      <c r="A7" s="332" t="inlineStr">
+      <c r="B6" s="476" t="n"/>
+      <c r="C6" s="476" t="n"/>
+      <c r="D6" s="476" t="n"/>
+      <c r="E6" s="476" t="n"/>
+      <c r="F6" s="476" t="n"/>
+      <c r="G6" s="476" t="n"/>
+      <c r="H6" s="476" t="n"/>
+      <c r="I6" s="476" t="n"/>
+      <c r="J6" s="476" t="n"/>
+      <c r="K6" s="476" t="n"/>
+      <c r="L6" s="476" t="n"/>
+      <c r="M6" s="476" t="n"/>
+      <c r="N6" s="476" t="n"/>
+      <c r="O6" s="476" t="n"/>
+      <c r="P6" s="473" t="n"/>
+      <c r="Q6" s="473" t="n"/>
+      <c r="R6" s="473" t="n"/>
+      <c r="S6" s="473" t="n"/>
+    </row>
+    <row r="7" ht="223.15" customHeight="1">
+      <c r="A7" s="528" t="inlineStr">
         <is>
           <t>This database provides a comprehensive overview of China's national-level climate change mitigation and mitigation-relevant policy instruments currently in force. It is structured to align with the typology and data framework of the OECD's IFCMA Climate Policy Database, incorportating necessary adjustments to reflect the characteristics of China's policy instruments and to faciliate further analysis.
 Adjustments to the typology of the IFCMA Climate Policy Database
@@ -11969,90 +12325,90 @@
       <c r="J7" s="333" t="n"/>
       <c r="K7" s="333" t="n"/>
       <c r="L7" s="333" t="n"/>
-      <c r="M7" s="334" t="n"/>
-      <c r="N7" s="335" t="n"/>
-      <c r="O7" s="231" t="n"/>
-      <c r="P7" s="233" t="n"/>
-      <c r="Q7" s="233" t="n"/>
-      <c r="R7" s="233" t="n"/>
-      <c r="S7" s="233" t="n"/>
+      <c r="M7" s="333" t="n"/>
+      <c r="N7" s="333" t="n"/>
+      <c r="O7" s="529" t="n"/>
+      <c r="P7" s="481" t="n"/>
+      <c r="Q7" s="473" t="n"/>
+      <c r="R7" s="473" t="n"/>
+      <c r="S7" s="473" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="336" t="n"/>
-      <c r="B8" s="336" t="n"/>
-      <c r="C8" s="336" t="n"/>
-      <c r="D8" s="336" t="n"/>
-      <c r="E8" s="336" t="n"/>
-      <c r="F8" s="336" t="n"/>
-      <c r="G8" s="336" t="n"/>
-      <c r="H8" s="336" t="n"/>
-      <c r="I8" s="336" t="n"/>
-      <c r="J8" s="336" t="n"/>
-      <c r="K8" s="336" t="n"/>
-      <c r="L8" s="336" t="n"/>
-      <c r="M8" s="336" t="n"/>
-      <c r="N8" s="231" t="n"/>
-      <c r="O8" s="231" t="n"/>
-      <c r="P8" s="233" t="n"/>
-      <c r="Q8" s="233" t="n"/>
-      <c r="R8" s="233" t="n"/>
-      <c r="S8" s="233" t="n"/>
+      <c r="A8" s="479" t="n"/>
+      <c r="B8" s="479" t="n"/>
+      <c r="C8" s="479" t="n"/>
+      <c r="D8" s="479" t="n"/>
+      <c r="E8" s="479" t="n"/>
+      <c r="F8" s="479" t="n"/>
+      <c r="G8" s="479" t="n"/>
+      <c r="H8" s="479" t="n"/>
+      <c r="I8" s="479" t="n"/>
+      <c r="J8" s="479" t="n"/>
+      <c r="K8" s="479" t="n"/>
+      <c r="L8" s="479" t="n"/>
+      <c r="M8" s="479" t="n"/>
+      <c r="N8" s="479" t="n"/>
+      <c r="O8" s="479" t="n"/>
+      <c r="P8" s="473" t="n"/>
+      <c r="Q8" s="473" t="n"/>
+      <c r="R8" s="473" t="n"/>
+      <c r="S8" s="473" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="231" t="n"/>
-      <c r="B9" s="231" t="n"/>
-      <c r="C9" s="231" t="n"/>
-      <c r="D9" s="231" t="n"/>
-      <c r="E9" s="231" t="n"/>
-      <c r="F9" s="231" t="n"/>
-      <c r="G9" s="231" t="n"/>
-      <c r="H9" s="231" t="n"/>
-      <c r="I9" s="231" t="n"/>
-      <c r="J9" s="231" t="n"/>
-      <c r="K9" s="231" t="n"/>
-      <c r="L9" s="231" t="n"/>
-      <c r="M9" s="231" t="n"/>
-      <c r="N9" s="231" t="n"/>
-      <c r="O9" s="231" t="n"/>
-      <c r="P9" s="233" t="n"/>
-      <c r="Q9" s="233" t="n"/>
-      <c r="R9" s="233" t="n"/>
-      <c r="S9" s="233" t="n"/>
+      <c r="A9" s="471" t="n"/>
+      <c r="B9" s="471" t="n"/>
+      <c r="C9" s="471" t="n"/>
+      <c r="D9" s="471" t="n"/>
+      <c r="E9" s="471" t="n"/>
+      <c r="F9" s="471" t="n"/>
+      <c r="G9" s="471" t="n"/>
+      <c r="H9" s="471" t="n"/>
+      <c r="I9" s="471" t="n"/>
+      <c r="J9" s="471" t="n"/>
+      <c r="K9" s="471" t="n"/>
+      <c r="L9" s="471" t="n"/>
+      <c r="M9" s="471" t="n"/>
+      <c r="N9" s="471" t="n"/>
+      <c r="O9" s="471" t="n"/>
+      <c r="P9" s="473" t="n"/>
+      <c r="Q9" s="473" t="n"/>
+      <c r="R9" s="473" t="n"/>
+      <c r="S9" s="473" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="330" t="inlineStr">
+      <c r="A10" s="475" t="inlineStr">
         <is>
           <t>Content of this file</t>
         </is>
       </c>
       <c r="B10" s="337" t="n"/>
-      <c r="C10" s="331" t="n"/>
-      <c r="D10" s="331" t="n"/>
-      <c r="E10" s="331" t="n"/>
-      <c r="F10" s="331" t="n"/>
-      <c r="G10" s="331" t="n"/>
-      <c r="H10" s="331" t="n"/>
-      <c r="I10" s="331" t="n"/>
-      <c r="J10" s="331" t="n"/>
-      <c r="K10" s="331" t="n"/>
-      <c r="L10" s="331" t="n"/>
-      <c r="M10" s="331" t="n"/>
-      <c r="N10" s="331" t="n"/>
-      <c r="O10" s="331" t="n"/>
-      <c r="P10" s="233" t="n"/>
-      <c r="Q10" s="233" t="n"/>
-      <c r="R10" s="233" t="n"/>
-      <c r="S10" s="233" t="n"/>
+      <c r="C10" s="476" t="n"/>
+      <c r="D10" s="476" t="n"/>
+      <c r="E10" s="476" t="n"/>
+      <c r="F10" s="476" t="n"/>
+      <c r="G10" s="476" t="n"/>
+      <c r="H10" s="476" t="n"/>
+      <c r="I10" s="476" t="n"/>
+      <c r="J10" s="476" t="n"/>
+      <c r="K10" s="476" t="n"/>
+      <c r="L10" s="476" t="n"/>
+      <c r="M10" s="476" t="n"/>
+      <c r="N10" s="476" t="n"/>
+      <c r="O10" s="476" t="n"/>
+      <c r="P10" s="473" t="n"/>
+      <c r="Q10" s="473" t="n"/>
+      <c r="R10" s="473" t="n"/>
+      <c r="S10" s="473" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="338" t="inlineStr">
+      <c r="A11" s="480" t="inlineStr">
         <is>
           <t>Spreadsheet</t>
         </is>
       </c>
       <c r="B11" s="339" t="n"/>
       <c r="C11" s="340" t="n"/>
-      <c r="D11" s="338" t="inlineStr">
+      <c r="D11" s="480" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -12068,20 +12424,20 @@
       <c r="M11" s="339" t="n"/>
       <c r="N11" s="339" t="n"/>
       <c r="O11" s="340" t="n"/>
-      <c r="P11" s="341" t="n"/>
-      <c r="Q11" s="233" t="n"/>
-      <c r="R11" s="233" t="n"/>
-      <c r="S11" s="233" t="n"/>
+      <c r="P11" s="481" t="n"/>
+      <c r="Q11" s="473" t="n"/>
+      <c r="R11" s="473" t="n"/>
+      <c r="S11" s="473" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="342" t="inlineStr">
+      <c r="A12" s="482" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
       </c>
       <c r="B12" s="339" t="n"/>
       <c r="C12" s="340" t="n"/>
-      <c r="D12" s="343" t="inlineStr">
+      <c r="D12" s="483" t="inlineStr">
         <is>
           <t>Introduces this document, presents its overall function and lists MGF Lab contact points</t>
         </is>
@@ -12097,20 +12453,20 @@
       <c r="M12" s="339" t="n"/>
       <c r="N12" s="339" t="n"/>
       <c r="O12" s="340" t="n"/>
-      <c r="P12" s="341" t="n"/>
-      <c r="Q12" s="233" t="n"/>
-      <c r="R12" s="233" t="n"/>
-      <c r="S12" s="233" t="n"/>
+      <c r="P12" s="481" t="n"/>
+      <c r="Q12" s="473" t="n"/>
+      <c r="R12" s="473" t="n"/>
+      <c r="S12" s="473" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="344" t="inlineStr">
+      <c r="A13" s="484" t="inlineStr">
         <is>
           <t>Classification framework</t>
         </is>
       </c>
       <c r="B13" s="339" t="n"/>
       <c r="C13" s="340" t="n"/>
-      <c r="D13" s="343" t="inlineStr">
+      <c r="D13" s="483" t="inlineStr">
         <is>
           <t>Explains the four-level classification framework of this dataset</t>
         </is>
@@ -12126,20 +12482,20 @@
       <c r="M13" s="339" t="n"/>
       <c r="N13" s="339" t="n"/>
       <c r="O13" s="340" t="n"/>
-      <c r="P13" s="341" t="n"/>
-      <c r="Q13" s="233" t="n"/>
-      <c r="R13" s="233" t="n"/>
-      <c r="S13" s="233" t="n"/>
+      <c r="P13" s="481" t="n"/>
+      <c r="Q13" s="473" t="n"/>
+      <c r="R13" s="473" t="n"/>
+      <c r="S13" s="473" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="342" t="inlineStr">
+      <c r="A14" s="482" t="inlineStr">
         <is>
           <t>Categories and groups</t>
         </is>
       </c>
       <c r="B14" s="339" t="n"/>
       <c r="C14" s="340" t="n"/>
-      <c r="D14" s="343" t="inlineStr">
+      <c r="D14" s="483" t="inlineStr">
         <is>
           <t>Demonstrates instrument categories and instrument groups within each category</t>
         </is>
@@ -12155,20 +12511,20 @@
       <c r="M14" s="339" t="n"/>
       <c r="N14" s="339" t="n"/>
       <c r="O14" s="340" t="n"/>
-      <c r="P14" s="341" t="n"/>
-      <c r="Q14" s="233" t="n"/>
-      <c r="R14" s="233" t="n"/>
-      <c r="S14" s="233" t="n"/>
+      <c r="P14" s="481" t="n"/>
+      <c r="Q14" s="473" t="n"/>
+      <c r="R14" s="473" t="n"/>
+      <c r="S14" s="473" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="345" t="inlineStr">
+      <c r="A15" s="485" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
       <c r="B15" s="339" t="n"/>
       <c r="C15" s="340" t="n"/>
-      <c r="D15" s="343" t="inlineStr">
+      <c r="D15" s="483" t="inlineStr">
         <is>
           <t>Provides information on the number of policy instruments collected to date, by instrument category, group, approach, and sector covered</t>
         </is>
@@ -12184,20 +12540,20 @@
       <c r="M15" s="339" t="n"/>
       <c r="N15" s="339" t="n"/>
       <c r="O15" s="340" t="n"/>
-      <c r="P15" s="341" t="n"/>
-      <c r="Q15" s="233" t="n"/>
-      <c r="R15" s="233" t="n"/>
-      <c r="S15" s="233" t="n"/>
+      <c r="P15" s="481" t="n"/>
+      <c r="Q15" s="473" t="n"/>
+      <c r="R15" s="473" t="n"/>
+      <c r="S15" s="473" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="342" t="inlineStr">
+      <c r="A16" s="482" t="inlineStr">
         <is>
           <t>Approaches</t>
         </is>
       </c>
       <c r="B16" s="339" t="n"/>
       <c r="C16" s="340" t="n"/>
-      <c r="D16" s="343" t="inlineStr">
+      <c r="D16" s="483" t="inlineStr">
         <is>
           <t>Demonstrates instrument approaches within each group, and provides definition for each of them</t>
         </is>
@@ -12213,20 +12569,20 @@
       <c r="M16" s="339" t="n"/>
       <c r="N16" s="339" t="n"/>
       <c r="O16" s="340" t="n"/>
-      <c r="P16" s="341" t="n"/>
-      <c r="Q16" s="233" t="n"/>
-      <c r="R16" s="233" t="n"/>
-      <c r="S16" s="233" t="n"/>
+      <c r="P16" s="481" t="n"/>
+      <c r="Q16" s="473" t="n"/>
+      <c r="R16" s="473" t="n"/>
+      <c r="S16" s="473" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="342" t="inlineStr">
+      <c r="A17" s="482" t="inlineStr">
         <is>
           <t>Instruments overview</t>
         </is>
       </c>
       <c r="B17" s="339" t="n"/>
       <c r="C17" s="340" t="n"/>
-      <c r="D17" s="343" t="inlineStr">
+      <c r="D17" s="483" t="inlineStr">
         <is>
           <t>Provides a simplified summary table of all policy instruments collected to date</t>
         </is>
@@ -12242,20 +12598,20 @@
       <c r="M17" s="339" t="n"/>
       <c r="N17" s="339" t="n"/>
       <c r="O17" s="340" t="n"/>
-      <c r="P17" s="341" t="n"/>
-      <c r="Q17" s="233" t="n"/>
-      <c r="R17" s="233" t="n"/>
-      <c r="S17" s="233" t="n"/>
+      <c r="P17" s="481" t="n"/>
+      <c r="Q17" s="473" t="n"/>
+      <c r="R17" s="473" t="n"/>
+      <c r="S17" s="473" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="346" t="inlineStr">
+      <c r="A18" s="486" t="inlineStr">
         <is>
           <t>Economic instruments</t>
         </is>
       </c>
       <c r="B18" s="339" t="n"/>
       <c r="C18" s="340" t="n"/>
-      <c r="D18" s="343" t="inlineStr">
+      <c r="D18" s="483" t="inlineStr">
         <is>
           <t>Displays information for the Economic Instruments</t>
         </is>
@@ -12271,20 +12627,20 @@
       <c r="M18" s="339" t="n"/>
       <c r="N18" s="339" t="n"/>
       <c r="O18" s="340" t="n"/>
-      <c r="P18" s="341" t="n"/>
-      <c r="Q18" s="233" t="n"/>
-      <c r="R18" s="233" t="n"/>
-      <c r="S18" s="233" t="n"/>
+      <c r="P18" s="481" t="n"/>
+      <c r="Q18" s="473" t="n"/>
+      <c r="R18" s="473" t="n"/>
+      <c r="S18" s="473" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="347" t="inlineStr">
+      <c r="A19" s="487" t="inlineStr">
         <is>
           <t>Regulatory instruments</t>
         </is>
       </c>
       <c r="B19" s="339" t="n"/>
       <c r="C19" s="340" t="n"/>
-      <c r="D19" s="343" t="inlineStr">
+      <c r="D19" s="483" t="inlineStr">
         <is>
           <t>Displays information for the Regulatory Instruments</t>
         </is>
@@ -12300,20 +12656,20 @@
       <c r="M19" s="339" t="n"/>
       <c r="N19" s="339" t="n"/>
       <c r="O19" s="340" t="n"/>
-      <c r="P19" s="341" t="n"/>
-      <c r="Q19" s="233" t="n"/>
-      <c r="R19" s="233" t="n"/>
-      <c r="S19" s="233" t="n"/>
+      <c r="P19" s="481" t="n"/>
+      <c r="Q19" s="473" t="n"/>
+      <c r="R19" s="473" t="n"/>
+      <c r="S19" s="473" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="348" t="inlineStr">
+      <c r="A20" s="488" t="inlineStr">
         <is>
           <t>Government I&amp;C</t>
         </is>
       </c>
       <c r="B20" s="339" t="n"/>
       <c r="C20" s="340" t="n"/>
-      <c r="D20" s="343" t="inlineStr">
+      <c r="D20" s="483" t="inlineStr">
         <is>
           <t>Displays information for the Government Investment &amp; Consumption Instruments</t>
         </is>
@@ -12329,20 +12685,20 @@
       <c r="M20" s="339" t="n"/>
       <c r="N20" s="339" t="n"/>
       <c r="O20" s="340" t="n"/>
-      <c r="P20" s="341" t="n"/>
-      <c r="Q20" s="233" t="n"/>
-      <c r="R20" s="233" t="n"/>
-      <c r="S20" s="233" t="n"/>
+      <c r="P20" s="481" t="n"/>
+      <c r="Q20" s="473" t="n"/>
+      <c r="R20" s="473" t="n"/>
+      <c r="S20" s="473" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="349" t="inlineStr">
+      <c r="A21" s="489" t="inlineStr">
         <is>
           <t>Information instruments</t>
         </is>
       </c>
       <c r="B21" s="339" t="n"/>
       <c r="C21" s="340" t="n"/>
-      <c r="D21" s="343" t="inlineStr">
+      <c r="D21" s="483" t="inlineStr">
         <is>
           <t>Displays information for the Information Instruments</t>
         </is>
@@ -12358,20 +12714,20 @@
       <c r="M21" s="339" t="n"/>
       <c r="N21" s="339" t="n"/>
       <c r="O21" s="340" t="n"/>
-      <c r="P21" s="341" t="n"/>
-      <c r="Q21" s="233" t="n"/>
-      <c r="R21" s="233" t="n"/>
-      <c r="S21" s="233" t="n"/>
+      <c r="P21" s="481" t="n"/>
+      <c r="Q21" s="473" t="n"/>
+      <c r="R21" s="473" t="n"/>
+      <c r="S21" s="473" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="350" t="inlineStr">
+      <c r="A22" s="490" t="inlineStr">
         <is>
           <t>Voluntary approaches</t>
         </is>
       </c>
       <c r="B22" s="339" t="n"/>
       <c r="C22" s="340" t="n"/>
-      <c r="D22" s="343" t="inlineStr">
+      <c r="D22" s="483" t="inlineStr">
         <is>
           <t>Displays information for the Voluntary Approaches</t>
         </is>
@@ -12387,20 +12743,20 @@
       <c r="M22" s="339" t="n"/>
       <c r="N22" s="339" t="n"/>
       <c r="O22" s="340" t="n"/>
-      <c r="P22" s="341" t="n"/>
-      <c r="Q22" s="233" t="n"/>
-      <c r="R22" s="233" t="n"/>
-      <c r="S22" s="233" t="n"/>
+      <c r="P22" s="481" t="n"/>
+      <c r="Q22" s="473" t="n"/>
+      <c r="R22" s="473" t="n"/>
+      <c r="S22" s="473" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="342" t="inlineStr">
+      <c r="A23" s="482" t="inlineStr">
         <is>
           <t>Attributes definitions</t>
         </is>
       </c>
       <c r="B23" s="339" t="n"/>
       <c r="C23" s="340" t="n"/>
-      <c r="D23" s="343" t="inlineStr">
+      <c r="D23" s="483" t="inlineStr">
         <is>
           <t>Definitions of policy instrument attributes</t>
         </is>
@@ -12416,20 +12772,20 @@
       <c r="M23" s="339" t="n"/>
       <c r="N23" s="339" t="n"/>
       <c r="O23" s="340" t="n"/>
-      <c r="P23" s="341" t="n"/>
-      <c r="Q23" s="233" t="n"/>
-      <c r="R23" s="233" t="n"/>
-      <c r="S23" s="233" t="n"/>
+      <c r="P23" s="481" t="n"/>
+      <c r="Q23" s="473" t="n"/>
+      <c r="R23" s="473" t="n"/>
+      <c r="S23" s="473" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="386" t="inlineStr">
+      <c r="A24" s="491" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
       <c r="B24" s="339" t="n"/>
       <c r="C24" s="340" t="n"/>
-      <c r="D24" s="343" t="inlineStr">
+      <c r="D24" s="483" t="inlineStr">
         <is>
           <t>Displays information for policy instruments that were once included in this database but have since expired or been terminated</t>
         </is>
@@ -12445,66 +12801,66 @@
       <c r="M24" s="339" t="n"/>
       <c r="N24" s="339" t="n"/>
       <c r="O24" s="340" t="n"/>
-      <c r="P24" s="341" t="n"/>
-      <c r="Q24" s="233" t="n"/>
-      <c r="R24" s="233" t="n"/>
-      <c r="S24" s="233" t="n"/>
+      <c r="P24" s="481" t="n"/>
+      <c r="Q24" s="473" t="n"/>
+      <c r="R24" s="473" t="n"/>
+      <c r="S24" s="473" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="336" t="n"/>
-      <c r="B25" s="336" t="n"/>
-      <c r="C25" s="336" t="n"/>
-      <c r="D25" s="336" t="n"/>
-      <c r="E25" s="336" t="n"/>
-      <c r="F25" s="336" t="n"/>
-      <c r="G25" s="336" t="n"/>
-      <c r="H25" s="336" t="n"/>
-      <c r="I25" s="336" t="n"/>
-      <c r="J25" s="336" t="n"/>
-      <c r="K25" s="336" t="n"/>
-      <c r="L25" s="336" t="n"/>
-      <c r="M25" s="336" t="n"/>
-      <c r="N25" s="336" t="n"/>
-      <c r="O25" s="336" t="n"/>
-      <c r="P25" s="233" t="n"/>
-      <c r="Q25" s="233" t="n"/>
-      <c r="R25" s="233" t="n"/>
-      <c r="S25" s="233" t="n"/>
+      <c r="A25" s="479" t="n"/>
+      <c r="B25" s="479" t="n"/>
+      <c r="C25" s="479" t="n"/>
+      <c r="D25" s="479" t="n"/>
+      <c r="E25" s="479" t="n"/>
+      <c r="F25" s="479" t="n"/>
+      <c r="G25" s="479" t="n"/>
+      <c r="H25" s="479" t="n"/>
+      <c r="I25" s="479" t="n"/>
+      <c r="J25" s="479" t="n"/>
+      <c r="K25" s="479" t="n"/>
+      <c r="L25" s="479" t="n"/>
+      <c r="M25" s="479" t="n"/>
+      <c r="N25" s="479" t="n"/>
+      <c r="O25" s="479" t="n"/>
+      <c r="P25" s="473" t="n"/>
+      <c r="Q25" s="473" t="n"/>
+      <c r="R25" s="473" t="n"/>
+      <c r="S25" s="473" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="330" t="inlineStr">
+      <c r="A26" s="475" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B26" s="331" t="n"/>
-      <c r="C26" s="331" t="n"/>
-      <c r="D26" s="331" t="n"/>
-      <c r="E26" s="331" t="n"/>
-      <c r="F26" s="331" t="n"/>
-      <c r="G26" s="331" t="n"/>
-      <c r="H26" s="331" t="n"/>
-      <c r="I26" s="331" t="n"/>
-      <c r="J26" s="331" t="n"/>
-      <c r="K26" s="331" t="n"/>
-      <c r="L26" s="331" t="n"/>
-      <c r="M26" s="331" t="n"/>
-      <c r="N26" s="331" t="n"/>
-      <c r="O26" s="331" t="n"/>
-      <c r="P26" s="233" t="n"/>
-      <c r="Q26" s="233" t="n"/>
-      <c r="R26" s="233" t="n"/>
-      <c r="S26" s="233" t="n"/>
+      <c r="B26" s="476" t="n"/>
+      <c r="C26" s="476" t="n"/>
+      <c r="D26" s="476" t="n"/>
+      <c r="E26" s="476" t="n"/>
+      <c r="F26" s="476" t="n"/>
+      <c r="G26" s="476" t="n"/>
+      <c r="H26" s="476" t="n"/>
+      <c r="I26" s="476" t="n"/>
+      <c r="J26" s="476" t="n"/>
+      <c r="K26" s="476" t="n"/>
+      <c r="L26" s="476" t="n"/>
+      <c r="M26" s="476" t="n"/>
+      <c r="N26" s="476" t="n"/>
+      <c r="O26" s="476" t="n"/>
+      <c r="P26" s="473" t="n"/>
+      <c r="Q26" s="473" t="n"/>
+      <c r="R26" s="473" t="n"/>
+      <c r="S26" s="473" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="351" t="inlineStr">
+      <c r="A27" s="492" t="inlineStr">
         <is>
           <t>Bold text</t>
         </is>
       </c>
       <c r="B27" s="339" t="n"/>
       <c r="C27" s="340" t="n"/>
-      <c r="D27" s="352" t="inlineStr">
+      <c r="D27" s="493" t="inlineStr">
         <is>
           <t>Policy instrument</t>
         </is>
@@ -12520,20 +12876,20 @@
       <c r="M27" s="339" t="n"/>
       <c r="N27" s="339" t="n"/>
       <c r="O27" s="340" t="n"/>
-      <c r="P27" s="341" t="n"/>
-      <c r="Q27" s="233" t="n"/>
-      <c r="R27" s="233" t="n"/>
-      <c r="S27" s="233" t="n"/>
+      <c r="P27" s="481" t="n"/>
+      <c r="Q27" s="473" t="n"/>
+      <c r="R27" s="473" t="n"/>
+      <c r="S27" s="473" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="353" t="inlineStr">
+      <c r="A28" s="494" t="inlineStr">
         <is>
           <t>Unbolded text</t>
         </is>
       </c>
       <c r="B28" s="339" t="n"/>
       <c r="C28" s="340" t="n"/>
-      <c r="D28" s="343" t="inlineStr">
+      <c r="D28" s="483" t="inlineStr">
         <is>
           <t>Sub-schemes of the policy instrument</t>
         </is>
@@ -12549,138 +12905,139 @@
       <c r="M28" s="339" t="n"/>
       <c r="N28" s="339" t="n"/>
       <c r="O28" s="340" t="n"/>
-      <c r="P28" s="341" t="n"/>
-      <c r="Q28" s="233" t="n"/>
-      <c r="R28" s="233" t="n"/>
-      <c r="S28" s="233" t="n"/>
+      <c r="P28" s="481" t="n"/>
+      <c r="Q28" s="473" t="n"/>
+      <c r="R28" s="473" t="n"/>
+      <c r="S28" s="473" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="336" t="n"/>
-      <c r="B29" s="336" t="n"/>
-      <c r="C29" s="336" t="n"/>
-      <c r="D29" s="336" t="n"/>
-      <c r="E29" s="336" t="n"/>
-      <c r="F29" s="336" t="n"/>
-      <c r="G29" s="336" t="n"/>
-      <c r="H29" s="336" t="n"/>
-      <c r="I29" s="336" t="n"/>
-      <c r="J29" s="336" t="n"/>
-      <c r="K29" s="336" t="n"/>
-      <c r="L29" s="336" t="n"/>
-      <c r="M29" s="336" t="n"/>
-      <c r="N29" s="336" t="n"/>
-      <c r="O29" s="336" t="n"/>
-      <c r="P29" s="233" t="n"/>
-      <c r="Q29" s="233" t="n"/>
-      <c r="R29" s="233" t="n"/>
-      <c r="S29" s="233" t="n"/>
+      <c r="A29" s="479" t="n"/>
+      <c r="B29" s="479" t="n"/>
+      <c r="C29" s="479" t="n"/>
+      <c r="D29" s="479" t="n"/>
+      <c r="E29" s="479" t="n"/>
+      <c r="F29" s="479" t="n"/>
+      <c r="G29" s="479" t="n"/>
+      <c r="H29" s="479" t="n"/>
+      <c r="I29" s="479" t="n"/>
+      <c r="J29" s="479" t="n"/>
+      <c r="K29" s="479" t="n"/>
+      <c r="L29" s="479" t="n"/>
+      <c r="M29" s="479" t="n"/>
+      <c r="N29" s="479" t="n"/>
+      <c r="O29" s="479" t="n"/>
+      <c r="P29" s="473" t="n"/>
+      <c r="Q29" s="473" t="n"/>
+      <c r="R29" s="473" t="n"/>
+      <c r="S29" s="473" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="231" t="n"/>
-      <c r="B30" s="231" t="n"/>
-      <c r="C30" s="231" t="n"/>
-      <c r="D30" s="231" t="n"/>
-      <c r="E30" s="231" t="n"/>
-      <c r="F30" s="231" t="n"/>
-      <c r="G30" s="231" t="n"/>
-      <c r="H30" s="231" t="n"/>
-      <c r="I30" s="231" t="n"/>
-      <c r="J30" s="231" t="n"/>
-      <c r="K30" s="231" t="n"/>
-      <c r="L30" s="231" t="n"/>
-      <c r="M30" s="231" t="n"/>
-      <c r="N30" s="231" t="n"/>
-      <c r="O30" s="231" t="n"/>
-      <c r="P30" s="233" t="n"/>
-      <c r="Q30" s="233" t="n"/>
-      <c r="R30" s="233" t="n"/>
-      <c r="S30" s="233" t="n"/>
+      <c r="A30" s="471" t="n"/>
+      <c r="B30" s="471" t="n"/>
+      <c r="C30" s="471" t="n"/>
+      <c r="D30" s="471" t="n"/>
+      <c r="E30" s="471" t="n"/>
+      <c r="F30" s="471" t="n"/>
+      <c r="G30" s="471" t="n"/>
+      <c r="H30" s="471" t="n"/>
+      <c r="I30" s="471" t="n"/>
+      <c r="J30" s="471" t="n"/>
+      <c r="K30" s="471" t="n"/>
+      <c r="L30" s="471" t="n"/>
+      <c r="M30" s="471" t="n"/>
+      <c r="N30" s="471" t="n"/>
+      <c r="O30" s="471" t="n"/>
+      <c r="P30" s="473" t="n"/>
+      <c r="Q30" s="473" t="n"/>
+      <c r="R30" s="473" t="n"/>
+      <c r="S30" s="473" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="235" t="inlineStr">
+      <c r="A31" s="495" t="inlineStr">
         <is>
           <t>MGF Lab contact</t>
         </is>
       </c>
       <c r="B31" s="110" t="n"/>
-      <c r="C31" s="231" t="n"/>
-      <c r="D31" s="231" t="n"/>
-      <c r="E31" s="231" t="n"/>
-      <c r="F31" s="231" t="n"/>
-      <c r="G31" s="231" t="n"/>
-      <c r="H31" s="231" t="n"/>
-      <c r="I31" s="231" t="n"/>
-      <c r="J31" s="231" t="n"/>
-      <c r="K31" s="231" t="n"/>
-      <c r="L31" s="231" t="n"/>
-      <c r="M31" s="231" t="n"/>
-      <c r="N31" s="231" t="n"/>
-      <c r="O31" s="231" t="n"/>
-      <c r="P31" s="233" t="n"/>
-      <c r="Q31" s="233" t="n"/>
-      <c r="R31" s="233" t="n"/>
-      <c r="S31" s="233" t="n"/>
+      <c r="C31" s="471" t="n"/>
+      <c r="D31" s="471" t="n"/>
+      <c r="E31" s="471" t="n"/>
+      <c r="F31" s="471" t="n"/>
+      <c r="G31" s="471" t="n"/>
+      <c r="H31" s="471" t="n"/>
+      <c r="I31" s="471" t="n"/>
+      <c r="J31" s="471" t="n"/>
+      <c r="K31" s="471" t="n"/>
+      <c r="L31" s="471" t="n"/>
+      <c r="M31" s="471" t="n"/>
+      <c r="N31" s="471" t="n"/>
+      <c r="O31" s="471" t="n"/>
+      <c r="P31" s="473" t="n"/>
+      <c r="Q31" s="473" t="n"/>
+      <c r="R31" s="473" t="n"/>
+      <c r="S31" s="473" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="251" t="inlineStr">
+      <c r="A32" s="496" t="inlineStr">
         <is>
           <t>Danqing Shao</t>
         </is>
       </c>
-      <c r="B32" s="252" t="inlineStr">
+      <c r="B32" s="497" t="inlineStr">
         <is>
           <t>dqshao@nsd.pku.edu.cn</t>
         </is>
       </c>
       <c r="C32" s="110" t="n"/>
-      <c r="D32" s="231" t="n"/>
-      <c r="E32" s="231" t="n"/>
-      <c r="F32" s="231" t="n"/>
-      <c r="G32" s="231" t="n"/>
-      <c r="H32" s="231" t="n"/>
-      <c r="I32" s="231" t="n"/>
-      <c r="J32" s="231" t="n"/>
-      <c r="K32" s="231" t="n"/>
-      <c r="L32" s="231" t="n"/>
-      <c r="M32" s="231" t="n"/>
-      <c r="N32" s="231" t="n"/>
-      <c r="O32" s="231" t="n"/>
-      <c r="P32" s="233" t="n"/>
-      <c r="Q32" s="233" t="n"/>
-      <c r="R32" s="233" t="n"/>
-      <c r="S32" s="233" t="n"/>
+      <c r="D32" s="471" t="n"/>
+      <c r="E32" s="471" t="n"/>
+      <c r="F32" s="471" t="n"/>
+      <c r="G32" s="471" t="n"/>
+      <c r="H32" s="471" t="n"/>
+      <c r="I32" s="471" t="n"/>
+      <c r="J32" s="471" t="n"/>
+      <c r="K32" s="471" t="n"/>
+      <c r="L32" s="471" t="n"/>
+      <c r="M32" s="471" t="n"/>
+      <c r="N32" s="471" t="n"/>
+      <c r="O32" s="471" t="n"/>
+      <c r="P32" s="473" t="n"/>
+      <c r="Q32" s="473" t="n"/>
+      <c r="R32" s="473" t="n"/>
+      <c r="S32" s="473" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="251" t="inlineStr">
+      <c r="A33" s="496" t="inlineStr">
         <is>
           <t>Xiaobei He</t>
         </is>
       </c>
-      <c r="B33" s="252" t="inlineStr">
+      <c r="B33" s="497" t="inlineStr">
         <is>
           <t>xbhe@nsd.pku.edu.cn</t>
         </is>
       </c>
       <c r="C33" s="110" t="n"/>
-      <c r="D33" s="231" t="n"/>
-      <c r="E33" s="231" t="n"/>
-      <c r="F33" s="231" t="n"/>
-      <c r="G33" s="231" t="n"/>
-      <c r="H33" s="231" t="n"/>
-      <c r="I33" s="231" t="n"/>
-      <c r="J33" s="231" t="n"/>
-      <c r="K33" s="231" t="n"/>
-      <c r="L33" s="231" t="n"/>
-      <c r="M33" s="231" t="n"/>
-      <c r="N33" s="231" t="n"/>
-      <c r="O33" s="231" t="n"/>
-      <c r="P33" s="233" t="n"/>
-      <c r="Q33" s="233" t="n"/>
-      <c r="R33" s="233" t="n"/>
-      <c r="S33" s="233" t="n"/>
+      <c r="D33" s="471" t="n"/>
+      <c r="E33" s="471" t="n"/>
+      <c r="F33" s="471" t="n"/>
+      <c r="G33" s="471" t="n"/>
+      <c r="H33" s="471" t="n"/>
+      <c r="I33" s="471" t="n"/>
+      <c r="J33" s="471" t="n"/>
+      <c r="K33" s="471" t="n"/>
+      <c r="L33" s="471" t="n"/>
+      <c r="M33" s="471" t="n"/>
+      <c r="N33" s="471" t="n"/>
+      <c r="O33" s="471" t="n"/>
+      <c r="P33" s="473" t="n"/>
+      <c r="Q33" s="473" t="n"/>
+      <c r="R33" s="473" t="n"/>
+      <c r="S33" s="473" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="A7:O7"/>
     <mergeCell ref="D13:O13"/>
     <mergeCell ref="D11:O11"/>
     <mergeCell ref="D27:O27"/>
@@ -12708,7 +13065,6 @@
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="D23:O23"/>
     <mergeCell ref="D14:O14"/>
-    <mergeCell ref="A7:M7"/>
     <mergeCell ref="A15:C15"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D20:O20"/>

--- a/inputs/template_en.xlsx
+++ b/inputs/template_en.xlsx
@@ -6102,7 +6102,7 @@
       </c>
       <c r="E12" s="449" t="inlineStr">
         <is>
-          <t>Air pollution; Waste reduction/ circular economy; Climate change mitigation; Climate change adaptation; Economic growth; Energy efficiency; Energy security; Social security/poverty reduction; Other; Not specified</t>
+          <t>Climate change mitigation; Non-fossil energy; Energy efficiency; Green economy; Technological innovation; Energy security; Pollution control; Ecological protection; Circular economy; Adaptation; Green finance; Electrification; Industrial development; Green consumption; Information disclosure; Public awareness; Ozone layer protection</t>
         </is>
       </c>
       <c r="F12" s="459" t="n"/>

--- a/inputs/template_en.xlsx
+++ b/inputs/template_en.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Regulatory instruments" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Government I&amp;C" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Information instruments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voluntary approaches" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Voluntary approaches" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Classification framework" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Categories and groups" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Attributes definitions" sheetId="11" state="visible" r:id="rId11"/>
@@ -27,7 +27,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="89">
+  <fonts count="94">
     <font>
       <name val="等线"/>
       <family val="2"/>
@@ -619,6 +619,36 @@
       <color theme="1"/>
       <sz val="16"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF0E5C46"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color rgb="FF000000"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="16"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <color theme="10"/>
+      <sz val="12"/>
+      <u val="single"/>
     </font>
   </fonts>
   <fills count="46">
@@ -1949,7 +1979,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="530">
+  <cellXfs count="558">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="9" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -3374,6 +3404,70 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="88" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="89" fillId="19" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="91" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="53" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="65" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="65" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="59" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="28" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="67" fillId="29" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="30" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="31" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="32" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="33" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="34" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="38" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="69" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="69" fillId="0" borderId="69" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="58" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="93" fillId="0" borderId="53" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5652,7 +5746,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T95"/>
+  <dimension ref="A1:T94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col width="34.46484375" customWidth="1" min="1" max="1"/>
@@ -6163,12 +6257,12 @@
       <c r="A14" s="369" t="n"/>
       <c r="B14" s="448" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Jurisdiction level</t>
         </is>
       </c>
       <c r="C14" s="448" t="inlineStr">
         <is>
-          <t>Country where the policy instrument is applied</t>
+          <t>Jurisdiction level where the instrument is applied</t>
         </is>
       </c>
       <c r="D14" s="449" t="inlineStr">
@@ -6178,7 +6272,7 @@
       </c>
       <c r="E14" s="449" t="inlineStr">
         <is>
-          <t>IFCMA member country list</t>
+          <t>National; Sub-national; Supra-national; Special economic zone</t>
         </is>
       </c>
       <c r="F14" s="459" t="n"/>
@@ -6201,22 +6295,22 @@
       <c r="A15" s="369" t="n"/>
       <c r="B15" s="448" t="inlineStr">
         <is>
-          <t>Jurisdiction level</t>
+          <t>Jurisdiction name</t>
         </is>
       </c>
       <c r="C15" s="448" t="inlineStr">
         <is>
-          <t>Jurisdiction level where the instrument is applied</t>
+          <t>Name of jurisdiction if it is applied at supra- / international or subnational level in english language</t>
         </is>
       </c>
       <c r="D15" s="449" t="inlineStr">
         <is>
-          <t>Categorial (single choice)</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E15" s="449" t="inlineStr">
         <is>
-          <t>National; Sub-national; Supra-national; Special economic zone</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F15" s="459" t="n"/>
@@ -6239,22 +6333,22 @@
       <c r="A16" s="369" t="n"/>
       <c r="B16" s="448" t="inlineStr">
         <is>
-          <t>Jurisdiction name</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="C16" s="448" t="inlineStr">
         <is>
-          <t>Name of jurisdiction if it is applied at supra- / international or subnational level in english language</t>
+          <t>Defines if the instrument is active or inactive, and whether it is in force</t>
         </is>
       </c>
       <c r="D16" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (single choice)</t>
         </is>
       </c>
       <c r="E16" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In force; Scheduled; Ended; Non-existent</t>
         </is>
       </c>
       <c r="F16" s="459" t="n"/>
@@ -6277,22 +6371,22 @@
       <c r="A17" s="369" t="n"/>
       <c r="B17" s="448" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Adoption date</t>
         </is>
       </c>
       <c r="C17" s="448" t="inlineStr">
         <is>
-          <t>Defines if the instrument is active or inactive, and whether it is in force</t>
+          <t>Date when the instrument is approved</t>
         </is>
       </c>
       <c r="D17" s="449" t="inlineStr">
         <is>
-          <t>Categorial (single choice)</t>
+          <t>DMY protocol</t>
         </is>
       </c>
       <c r="E17" s="449" t="inlineStr">
         <is>
-          <t>In force; Scheduled; Ended; Non-existent</t>
+          <t>Fixed structure [mm/yyyy] or [yyyy]</t>
         </is>
       </c>
       <c r="F17" s="459" t="n"/>
@@ -6315,12 +6409,12 @@
       <c r="A18" s="369" t="n"/>
       <c r="B18" s="448" t="inlineStr">
         <is>
-          <t>Adoption date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="C18" s="448" t="inlineStr">
         <is>
-          <t>Date when the instrument is approved</t>
+          <t>Date of entry into force/ when the instrument became or will become legally binding</t>
         </is>
       </c>
       <c r="D18" s="449" t="inlineStr">
@@ -6353,12 +6447,12 @@
       <c r="A19" s="369" t="n"/>
       <c r="B19" s="448" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="C19" s="448" t="inlineStr">
         <is>
-          <t>Date of entry into force/ when the instrument became or will become legally binding</t>
+          <t>Date when the final requirement of the legal mandate takes effect, if relevant</t>
         </is>
       </c>
       <c r="D19" s="449" t="inlineStr">
@@ -6391,12 +6485,12 @@
       <c r="A20" s="369" t="n"/>
       <c r="B20" s="448" t="inlineStr">
         <is>
-          <t>End date</t>
+          <t>Last revision</t>
         </is>
       </c>
       <c r="C20" s="448" t="inlineStr">
         <is>
-          <t>Date when the final requirement of the legal mandate takes effect, if relevant</t>
+          <t>Date of the last update/revision to the policy instrument</t>
         </is>
       </c>
       <c r="D20" s="449" t="inlineStr">
@@ -6429,24 +6523,20 @@
       <c r="A21" s="369" t="n"/>
       <c r="B21" s="448" t="inlineStr">
         <is>
-          <t>Last revision</t>
+          <t>Last revision details</t>
         </is>
       </c>
       <c r="C21" s="448" t="inlineStr">
         <is>
-          <t>Date of the last update/revision to the policy instrument</t>
+          <t>Informs on the nature of the last revision if applicable, what has been modified [broader scope, different intensity, new earmarking, etc) and/or previous relevant revisions</t>
         </is>
       </c>
       <c r="D21" s="449" t="inlineStr">
         <is>
-          <t>DMY protocol</t>
-        </is>
-      </c>
-      <c r="E21" s="449" t="inlineStr">
-        <is>
-          <t>Fixed structure [mm/yyyy] or [yyyy]</t>
-        </is>
-      </c>
+          <t>Free text</t>
+        </is>
+      </c>
+      <c r="E21" s="449" t="n"/>
       <c r="F21" s="459" t="n"/>
       <c r="G21" s="499" t="n"/>
       <c r="H21" s="499" t="n"/>
@@ -6464,23 +6554,27 @@
       <c r="T21" s="499" t="n"/>
     </row>
     <row r="22" ht="15" customHeight="1">
-      <c r="A22" s="369" t="n"/>
+      <c r="A22" s="361" t="n"/>
       <c r="B22" s="448" t="inlineStr">
         <is>
-          <t>Last revision details</t>
+          <t>Aministrating authority</t>
         </is>
       </c>
       <c r="C22" s="448" t="inlineStr">
         <is>
-          <t>Informs on the nature of the last revision if applicable, what has been modified [broader scope, different intensity, new earmarking, etc) and/or previous relevant revisions</t>
+          <t>The institution(s) that implement and manage the instrument. This involves setting rates and/or defining the policy base</t>
         </is>
       </c>
       <c r="D22" s="449" t="inlineStr">
         <is>
-          <t>Free text</t>
-        </is>
-      </c>
-      <c r="E22" s="449" t="n"/>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E22" s="449" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
       <c r="F22" s="459" t="n"/>
       <c r="G22" s="499" t="n"/>
       <c r="H22" s="499" t="n"/>
@@ -6498,25 +6592,29 @@
       <c r="T22" s="499" t="n"/>
     </row>
     <row r="23" ht="15" customHeight="1">
-      <c r="A23" s="361" t="n"/>
+      <c r="A23" s="452" t="inlineStr">
+        <is>
+          <t>Policy regulatory base and intensity</t>
+        </is>
+      </c>
       <c r="B23" s="448" t="inlineStr">
         <is>
-          <t>Aministrating authority</t>
+          <t>Regulated asset</t>
         </is>
       </c>
       <c r="C23" s="448" t="inlineStr">
         <is>
-          <t>The institution(s) that implement and manage the instrument. This involves setting rates and/or defining the policy base</t>
+          <t>The object that is regulated; this can be a structure (e.g. boilers and turbines), a fuel (e.g. coal or gas), emissions, more generic objects such as products and inputs, as well as intangible assets</t>
         </is>
       </c>
       <c r="D23" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E23" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Non-exhaustive list</t>
         </is>
       </c>
       <c r="F23" s="459" t="n"/>
@@ -6536,29 +6634,25 @@
       <c r="T23" s="499" t="n"/>
     </row>
     <row r="24" ht="15" customHeight="1">
-      <c r="A24" s="452" t="inlineStr">
-        <is>
-          <t>Policy regulatory base and intensity</t>
-        </is>
-      </c>
+      <c r="A24" s="369" t="n"/>
       <c r="B24" s="448" t="inlineStr">
         <is>
-          <t>Regulated asset</t>
+          <t>Regulated asset (Status)</t>
         </is>
       </c>
       <c r="C24" s="448" t="inlineStr">
         <is>
-          <t>The object that is regulated; this can be a structure (e.g. boilers and turbines), a fuel (e.g. coal or gas), emissions, more generic objects such as products and inputs, as well as intangible assets</t>
+          <t>Asset status, i.e. whether an asset is newly sold or build, already existing (building stock or vehicle fleet) or is sold used</t>
         </is>
       </c>
       <c r="D24" s="449" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Categorial</t>
         </is>
       </c>
       <c r="E24" s="449" t="inlineStr">
         <is>
-          <t>Non-exhaustive list</t>
+          <t>New; existing</t>
         </is>
       </c>
       <c r="F24" s="459" t="n"/>
@@ -6581,12 +6675,12 @@
       <c r="A25" s="369" t="n"/>
       <c r="B25" s="448" t="inlineStr">
         <is>
-          <t>Regulated asset (Status)</t>
+          <t>Regulated asset (Details)</t>
         </is>
       </c>
       <c r="C25" s="448" t="inlineStr">
         <is>
-          <t>Asset status, i.e. whether an asset is newly sold or build, already existing (building stock or vehicle fleet) or is sold used</t>
+          <t>Asset type, which can take various forms depending on asset. Could include enginge types, or other technological specifications</t>
         </is>
       </c>
       <c r="D25" s="449" t="inlineStr">
@@ -6596,7 +6690,7 @@
       </c>
       <c r="E25" s="449" t="inlineStr">
         <is>
-          <t>New; existing</t>
+          <t>Non-exhaustive list</t>
         </is>
       </c>
       <c r="F25" s="459" t="n"/>
@@ -6619,22 +6713,22 @@
       <c r="A26" s="369" t="n"/>
       <c r="B26" s="448" t="inlineStr">
         <is>
-          <t>Regulated asset (Details)</t>
+          <t>Regulated asset (Other)</t>
         </is>
       </c>
       <c r="C26" s="448" t="inlineStr">
         <is>
-          <t>Asset type, which can take various forms depending on asset. Could include enginge types, or other technological specifications</t>
+          <t>Other details relevant to define the regulated assets</t>
         </is>
       </c>
       <c r="D26" s="449" t="inlineStr">
         <is>
-          <t>Categorial</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E26" s="449" t="inlineStr">
         <is>
-          <t>Non-exhaustive list</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F26" s="459" t="n"/>
@@ -6657,22 +6751,22 @@
       <c r="A27" s="369" t="n"/>
       <c r="B27" s="448" t="inlineStr">
         <is>
-          <t>Regulated asset (Other)</t>
+          <t>Regulated asset (Cut-off range)</t>
         </is>
       </c>
       <c r="C27" s="448" t="inlineStr">
         <is>
-          <t>Other details relevant to define the regulated assets</t>
+          <t>Refers to the specific details outlining the range or category of the regulatory base that is subject to the regulation by the instrument. The brackets delineate the boundaries within which regulatory stipulations are applied by the instrument. It could be income brackets, asset classes (e.g. based on size).</t>
         </is>
       </c>
       <c r="D27" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Open structure</t>
         </is>
       </c>
       <c r="E27" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>[XXXX ; YYYY] + unit</t>
         </is>
       </c>
       <c r="F27" s="459" t="n"/>
@@ -6695,22 +6789,22 @@
       <c r="A28" s="369" t="n"/>
       <c r="B28" s="448" t="inlineStr">
         <is>
-          <t>Regulated asset (Cut-off range)</t>
+          <t>Regulated agent</t>
         </is>
       </c>
       <c r="C28" s="448" t="inlineStr">
         <is>
-          <t>Refers to the specific details outlining the range or category of the regulatory base that is subject to the regulation by the instrument. The brackets delineate the boundaries within which regulatory stipulations are applied by the instrument. It could be income brackets, asset classes (e.g. based on size).</t>
+          <t>Entity that must legally comply with the policy instrument, or that receive the established benefit or information</t>
         </is>
       </c>
       <c r="D28" s="449" t="inlineStr">
         <is>
-          <t>Open structure</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E28" s="449" t="inlineStr">
         <is>
-          <t>[XXXX ; YYYY] + unit</t>
+          <t>Households; Firms; Governments; Non-governmental organisations</t>
         </is>
       </c>
       <c r="F28" s="459" t="n"/>
@@ -6733,22 +6827,22 @@
       <c r="A29" s="369" t="n"/>
       <c r="B29" s="448" t="inlineStr">
         <is>
-          <t>Regulated agent</t>
+          <t>Regulated agent (Detail)</t>
         </is>
       </c>
       <c r="C29" s="448" t="inlineStr">
         <is>
-          <t>Entity that must legally comply with the policy instrument, or that receive the established benefit or information</t>
+          <t>Details relevant to define the regulated agents (e.g., vehicles older than 10 years, housholds/firms above a certain revenue treshhold, etc.)</t>
         </is>
       </c>
       <c r="D29" s="449" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E29" s="449" t="inlineStr">
         <is>
-          <t>Households; Firms; Governments; Non-governmental organisations</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F29" s="459" t="n"/>
@@ -6771,22 +6865,22 @@
       <c r="A30" s="369" t="n"/>
       <c r="B30" s="448" t="inlineStr">
         <is>
-          <t>Regulated agent (Detail)</t>
+          <t>Regulated activity</t>
         </is>
       </c>
       <c r="C30" s="448" t="inlineStr">
         <is>
-          <t>Details relevant to define the regulated agents (e.g., vehicles older than 10 years, housholds/firms above a certain revenue treshhold, etc.)</t>
+          <t>The point of incidence when the policy instrument intervenes</t>
         </is>
       </c>
       <c r="D30" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E30" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Non-exhaustive list</t>
         </is>
       </c>
       <c r="F30" s="459" t="n"/>
@@ -6809,22 +6903,22 @@
       <c r="A31" s="369" t="n"/>
       <c r="B31" s="448" t="inlineStr">
         <is>
-          <t>Regulated activity</t>
+          <t>Regulated activity (Details)</t>
         </is>
       </c>
       <c r="C31" s="448" t="inlineStr">
         <is>
-          <t>The point of incidence when the policy instrument intervenes</t>
+          <t>Other details relevant to define the regulated activity</t>
         </is>
       </c>
       <c r="D31" s="449" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E31" s="449" t="inlineStr">
         <is>
-          <t>Non-exhaustive list</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F31" s="459" t="n"/>
@@ -6847,12 +6941,12 @@
       <c r="A32" s="369" t="n"/>
       <c r="B32" s="448" t="inlineStr">
         <is>
-          <t>Regulated activity (Details)</t>
+          <t>Intensity (Value)</t>
         </is>
       </c>
       <c r="C32" s="448" t="inlineStr">
         <is>
-          <t>Other details relevant to define the regulated activity</t>
+          <t>The numerical value used in the legislation (level, rate, target, etc)</t>
         </is>
       </c>
       <c r="D32" s="449" t="inlineStr">
@@ -6885,12 +6979,12 @@
       <c r="A33" s="369" t="n"/>
       <c r="B33" s="448" t="inlineStr">
         <is>
-          <t>Intensity (Value)</t>
+          <t>Intensity (Unit)</t>
         </is>
       </c>
       <c r="C33" s="448" t="inlineStr">
         <is>
-          <t>The numerical value used in the legislation (level, rate, target, etc)</t>
+          <t>The unit of the intensity value, e.g. EUR, km, %, level, etc.</t>
         </is>
       </c>
       <c r="D33" s="449" t="inlineStr">
@@ -6900,7 +6994,7 @@
       </c>
       <c r="E33" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>[unit as stated in the regulation]</t>
         </is>
       </c>
       <c r="F33" s="459" t="n"/>
@@ -6923,12 +7017,12 @@
       <c r="A34" s="369" t="n"/>
       <c r="B34" s="448" t="inlineStr">
         <is>
-          <t>Intensity (Unit)</t>
+          <t>Intensity (Details)</t>
         </is>
       </c>
       <c r="C34" s="448" t="inlineStr">
         <is>
-          <t>The unit of the intensity value, e.g. EUR, km, %, level, etc.</t>
+          <t>Further details about the intensity, if necessary, e.g. if the intensity is calculated on a formula, the formula and an average intensity value can be provided</t>
         </is>
       </c>
       <c r="D34" s="449" t="inlineStr">
@@ -6938,7 +7032,7 @@
       </c>
       <c r="E34" s="449" t="inlineStr">
         <is>
-          <t>[unit as stated in the regulation]</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F34" s="459" t="n"/>
@@ -6961,12 +7055,12 @@
       <c r="A35" s="369" t="n"/>
       <c r="B35" s="448" t="inlineStr">
         <is>
-          <t>Intensity (Details)</t>
+          <t>Requirement specification</t>
         </is>
       </c>
       <c r="C35" s="448" t="inlineStr">
         <is>
-          <t>Further details about the intensity, if necessary, e.g. if the intensity is calculated on a formula, the formula and an average intensity value can be provided</t>
+          <t>If an intensity changes based on a requirement not yet captured in the asset, activity or agent attributes but is relevant to understand and describe a policy instrument, this requirement is entered here.</t>
         </is>
       </c>
       <c r="D35" s="449" t="inlineStr">
@@ -6999,12 +7093,12 @@
       <c r="A36" s="369" t="n"/>
       <c r="B36" s="448" t="inlineStr">
         <is>
-          <t>Requirement specification</t>
+          <t>Compliance calculation methodology I</t>
         </is>
       </c>
       <c r="C36" s="448" t="inlineStr">
         <is>
-          <t>If an intensity changes based on a requirement not yet captured in the asset, activity or agent attributes but is relevant to understand and describe a policy instrument, this requirement is entered here.</t>
+          <t>Indicates whether the instrument applies to individual regulated assets or an aggregate of assets (e.g., their total production, operation, or sales).</t>
         </is>
       </c>
       <c r="D36" s="449" t="inlineStr">
@@ -7034,15 +7128,15 @@
       <c r="T36" s="499" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1">
-      <c r="A37" s="369" t="n"/>
+      <c r="A37" s="361" t="n"/>
       <c r="B37" s="448" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology I</t>
+          <t>Compliance calculation methodology II</t>
         </is>
       </c>
       <c r="C37" s="448" t="inlineStr">
         <is>
-          <t>Indicates whether the instrument applies to individual regulated assets or an aggregate of assets (e.g., their total production, operation, or sales).</t>
+          <t>Describes the methodology or rules used to evaluate compliance with the instrument’s requirements.</t>
         </is>
       </c>
       <c r="D37" s="449" t="inlineStr">
@@ -7072,15 +7166,19 @@
       <c r="T37" s="499" t="n"/>
     </row>
     <row r="38" ht="15" customHeight="1">
-      <c r="A38" s="361" t="n"/>
+      <c r="A38" s="452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">References to legislation   </t>
+        </is>
+      </c>
       <c r="B38" s="448" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology II</t>
+          <t>Legal statute</t>
         </is>
       </c>
       <c r="C38" s="448" t="inlineStr">
         <is>
-          <t>Describes the methodology or rules used to evaluate compliance with the instrument’s requirements.</t>
+          <t>Name of relevant legal document(s) and chapter(s) and/or article(s) that established or modified the instrument (if revised)</t>
         </is>
       </c>
       <c r="D38" s="449" t="inlineStr">
@@ -7110,19 +7208,15 @@
       <c r="T38" s="499" t="n"/>
     </row>
     <row r="39" ht="15" customHeight="1">
-      <c r="A39" s="452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">References to legislation   </t>
-        </is>
-      </c>
+      <c r="A39" s="369" t="n"/>
       <c r="B39" s="448" t="inlineStr">
         <is>
-          <t>Legal statute</t>
+          <t>Legal document</t>
         </is>
       </c>
       <c r="C39" s="448" t="inlineStr">
         <is>
-          <t>Name of relevant legal document(s) and chapter(s) and/or article(s) that established or modified the instrument (if revised)</t>
+          <t>Weblink to the relevant legal document that established or modified the instrument (if revised)</t>
         </is>
       </c>
       <c r="D39" s="449" t="inlineStr">
@@ -7152,15 +7246,15 @@
       <c r="T39" s="499" t="n"/>
     </row>
     <row r="40" ht="15" customHeight="1">
-      <c r="A40" s="369" t="n"/>
+      <c r="A40" s="361" t="n"/>
       <c r="B40" s="448" t="inlineStr">
         <is>
-          <t>Legal document</t>
+          <t>Other relevant websites</t>
         </is>
       </c>
       <c r="C40" s="448" t="inlineStr">
         <is>
-          <t>Weblink to the relevant legal document that established or modified the instrument (if revised)</t>
+          <t>Weblinks to other relevant websites</t>
         </is>
       </c>
       <c r="D40" s="449" t="inlineStr">
@@ -7190,31 +7284,35 @@
       <c r="T40" s="499" t="n"/>
     </row>
     <row r="41" ht="15" customHeight="1">
-      <c r="A41" s="361" t="n"/>
+      <c r="A41" s="452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">GHG emission base  </t>
+        </is>
+      </c>
       <c r="B41" s="448" t="inlineStr">
         <is>
-          <t>Other relevant websites</t>
+          <t>GHG emission coverage (absolute)</t>
         </is>
       </c>
       <c r="C41" s="448" t="inlineStr">
         <is>
-          <t>Weblinks to other relevant websites</t>
+          <t>Quantification of the instrument's emission base, in absolute terms</t>
         </is>
       </c>
       <c r="D41" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Numerical</t>
         </is>
       </c>
       <c r="E41" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="F41" s="459" t="n"/>
-      <c r="G41" s="499" t="n"/>
-      <c r="H41" s="499" t="n"/>
-      <c r="I41" s="499" t="n"/>
+          <t>in KtCO2eq</t>
+        </is>
+      </c>
+      <c r="F41" s="500" t="n"/>
+      <c r="G41" s="501" t="n"/>
+      <c r="H41" s="501" t="n"/>
+      <c r="I41" s="502" t="n"/>
       <c r="J41" s="499" t="n"/>
       <c r="K41" s="499" t="n"/>
       <c r="L41" s="499" t="n"/>
@@ -7228,19 +7326,15 @@
       <c r="T41" s="499" t="n"/>
     </row>
     <row r="42" ht="15" customHeight="1">
-      <c r="A42" s="452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">GHG emission base  </t>
-        </is>
-      </c>
+      <c r="A42" s="361" t="n"/>
       <c r="B42" s="448" t="inlineStr">
         <is>
-          <t>GHG emission coverage (absolute)</t>
+          <t>GHG emission base (% domestic emissions)</t>
         </is>
       </c>
       <c r="C42" s="448" t="inlineStr">
         <is>
-          <t>Quantification of the instrument's emission base, in absolute terms</t>
+          <t>Quantification of the instrument's emission base, relative to total domestic emissions</t>
         </is>
       </c>
       <c r="D42" s="449" t="inlineStr">
@@ -7250,7 +7344,7 @@
       </c>
       <c r="E42" s="449" t="inlineStr">
         <is>
-          <t>in KtCO2eq</t>
+          <t>in % [over domestic emissions]</t>
         </is>
       </c>
       <c r="F42" s="500" t="n"/>
@@ -7270,31 +7364,35 @@
       <c r="T42" s="499" t="n"/>
     </row>
     <row r="43" ht="15" customHeight="1">
-      <c r="A43" s="361" t="n"/>
+      <c r="A43" s="452" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Classifications &amp; Indicators  </t>
+        </is>
+      </c>
       <c r="B43" s="448" t="inlineStr">
         <is>
-          <t>GHG emission base (% domestic emissions)</t>
+          <t>Economic sector</t>
         </is>
       </c>
       <c r="C43" s="448" t="inlineStr">
         <is>
-          <t>Quantification of the instrument's emission base, relative to total domestic emissions</t>
+          <t>Classification based on the regulated agent. If the regulated agent is a firm, the sector will be allocated according to the International Standard Industrial Classification of All Economic Activities (ISIC)</t>
         </is>
       </c>
       <c r="D43" s="449" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorial</t>
         </is>
       </c>
       <c r="E43" s="449" t="inlineStr">
         <is>
-          <t>in % [over domestic emissions]</t>
-        </is>
-      </c>
-      <c r="F43" s="500" t="n"/>
-      <c r="G43" s="501" t="n"/>
-      <c r="H43" s="501" t="n"/>
-      <c r="I43" s="502" t="n"/>
+          <t>2-digit ISIC classification</t>
+        </is>
+      </c>
+      <c r="F43" s="459" t="n"/>
+      <c r="G43" s="499" t="n"/>
+      <c r="H43" s="499" t="n"/>
+      <c r="I43" s="499" t="n"/>
       <c r="J43" s="499" t="n"/>
       <c r="K43" s="499" t="n"/>
       <c r="L43" s="499" t="n"/>
@@ -7308,19 +7406,15 @@
       <c r="T43" s="499" t="n"/>
     </row>
     <row r="44" ht="15" customHeight="1">
-      <c r="A44" s="452" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Classifications &amp; Indicators  </t>
-        </is>
-      </c>
+      <c r="A44" s="369" t="n"/>
       <c r="B44" s="448" t="inlineStr">
         <is>
-          <t>Economic sector</t>
+          <t>GHGs affected</t>
         </is>
       </c>
       <c r="C44" s="448" t="inlineStr">
         <is>
-          <t>Classification based on the regulated agent. If the regulated agent is a firm, the sector will be allocated according to the International Standard Industrial Classification of All Economic Activities (ISIC)</t>
+          <t>GHGs that are regulated (where directly regulated); otherwise GHG that are likely to be affected by the instrument.</t>
         </is>
       </c>
       <c r="D44" s="449" t="inlineStr">
@@ -7330,7 +7424,7 @@
       </c>
       <c r="E44" s="449" t="inlineStr">
         <is>
-          <t>2-digit ISIC classification</t>
+          <t>CO2; CH4; N2O; SF6; HFCs; PFCs; NF3</t>
         </is>
       </c>
       <c r="F44" s="459" t="n"/>
@@ -7353,12 +7447,12 @@
       <c r="A45" s="369" t="n"/>
       <c r="B45" s="448" t="inlineStr">
         <is>
-          <t>GHGs affected</t>
+          <t>Mitigation effect</t>
         </is>
       </c>
       <c r="C45" s="448" t="inlineStr">
         <is>
-          <t>GHGs that are regulated (where directly regulated); otherwise GHG that are likely to be affected by the instrument.</t>
+          <t>Describes whether effect on GHG emissions/sinks is likely to be positive, negative, or unknown</t>
         </is>
       </c>
       <c r="D45" s="449" t="inlineStr">
@@ -7368,7 +7462,7 @@
       </c>
       <c r="E45" s="449" t="inlineStr">
         <is>
-          <t>CO2; CH4; N2O; SF6; HFCs; PFCs; NF3</t>
+          <t>positive, negative, neutral, unknown</t>
         </is>
       </c>
       <c r="F45" s="459" t="n"/>
@@ -7388,15 +7482,15 @@
       <c r="T45" s="499" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1">
-      <c r="A46" s="369" t="n"/>
+      <c r="A46" s="361" t="n"/>
       <c r="B46" s="448" t="inlineStr">
         <is>
-          <t>Mitigation effect</t>
+          <t>Mitigation co-benefits</t>
         </is>
       </c>
       <c r="C46" s="448" t="inlineStr">
         <is>
-          <t>Describes whether effect on GHG emissions/sinks is likely to be positive, negative, or unknown</t>
+          <t>Additional, non-mitigation positive outcomes or advantages that result from the implementation of climate change mitigating measures, identified by the IFCMA Secretariat.</t>
         </is>
       </c>
       <c r="D46" s="449" t="inlineStr">
@@ -7406,7 +7500,7 @@
       </c>
       <c r="E46" s="449" t="inlineStr">
         <is>
-          <t>positive, negative, neutral, unknown</t>
+          <t>Adaptation; Air pollution; Energy supply security; Technological innovation; Poverty reduction; Employment; Industrial development; Other (non-exhaustive list, current options here based on IPCC)</t>
         </is>
       </c>
       <c r="F46" s="459" t="n"/>
@@ -7426,27 +7520,15 @@
       <c r="T46" s="499" t="n"/>
     </row>
     <row r="47" ht="15" customHeight="1">
-      <c r="A47" s="361" t="n"/>
-      <c r="B47" s="448" t="inlineStr">
-        <is>
-          <t>Mitigation co-benefits</t>
-        </is>
-      </c>
-      <c r="C47" s="448" t="inlineStr">
-        <is>
-          <t>Additional, non-mitigation positive outcomes or advantages that result from the implementation of climate change mitigating measures, identified by the IFCMA Secretariat.</t>
-        </is>
-      </c>
-      <c r="D47" s="449" t="inlineStr">
-        <is>
-          <t>Categorial</t>
-        </is>
-      </c>
-      <c r="E47" s="449" t="inlineStr">
-        <is>
-          <t>Adaptation; Air pollution; Energy supply security; Technological innovation; Poverty reduction; Employment; Industrial development; Other (non-exhaustive list, current options here based on IPCC)</t>
-        </is>
-      </c>
+      <c r="A47" s="446" t="inlineStr">
+        <is>
+          <t>Instrument type-specific attributes</t>
+        </is>
+      </c>
+      <c r="B47" s="339" t="n"/>
+      <c r="C47" s="339" t="n"/>
+      <c r="D47" s="339" t="n"/>
+      <c r="E47" s="340" t="n"/>
       <c r="F47" s="459" t="n"/>
       <c r="G47" s="499" t="n"/>
       <c r="H47" s="499" t="n"/>
@@ -7464,93 +7546,105 @@
       <c r="T47" s="499" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="446" t="inlineStr">
-        <is>
-          <t>Instrument type-specific attributes</t>
-        </is>
-      </c>
-      <c r="B48" s="339" t="n"/>
-      <c r="C48" s="339" t="n"/>
-      <c r="D48" s="339" t="n"/>
-      <c r="E48" s="340" t="n"/>
-      <c r="F48" s="459" t="n"/>
-      <c r="G48" s="499" t="n"/>
-      <c r="H48" s="499" t="n"/>
-      <c r="I48" s="499" t="n"/>
-      <c r="J48" s="499" t="n"/>
-      <c r="K48" s="499" t="n"/>
-      <c r="L48" s="499" t="n"/>
-      <c r="M48" s="499" t="n"/>
-      <c r="N48" s="499" t="n"/>
-      <c r="O48" s="499" t="n"/>
-      <c r="P48" s="499" t="n"/>
-      <c r="Q48" s="499" t="n"/>
-      <c r="R48" s="499" t="n"/>
-      <c r="S48" s="499" t="n"/>
-      <c r="T48" s="499" t="n"/>
+      <c r="A48" s="452" t="inlineStr">
+        <is>
+          <t>Taxes</t>
+        </is>
+      </c>
+      <c r="B48" s="456" t="inlineStr">
+        <is>
+          <t>Annual revenue</t>
+        </is>
+      </c>
+      <c r="C48" s="456" t="inlineStr">
+        <is>
+          <t>Tax revenue of the recorded tax</t>
+        </is>
+      </c>
+      <c r="D48" s="456" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+      <c r="E48" s="456" t="inlineStr">
+        <is>
+          <t>in millions of domestic currency, USD or otherwise applicable unit</t>
+        </is>
+      </c>
+      <c r="F48" s="503" t="n"/>
+      <c r="G48" s="504" t="n"/>
+      <c r="H48" s="504" t="n"/>
+      <c r="I48" s="504" t="n"/>
+      <c r="J48" s="504" t="n"/>
+      <c r="K48" s="504" t="n"/>
+      <c r="L48" s="504" t="n"/>
+      <c r="M48" s="504" t="n"/>
+      <c r="N48" s="504" t="n"/>
+      <c r="O48" s="504" t="n"/>
+      <c r="P48" s="504" t="n"/>
+      <c r="Q48" s="504" t="n"/>
+      <c r="R48" s="504" t="n"/>
+      <c r="S48" s="504" t="n"/>
+      <c r="T48" s="504" t="n"/>
     </row>
     <row r="49" ht="15" customHeight="1">
-      <c r="A49" s="452" t="inlineStr">
-        <is>
-          <t>Taxes</t>
-        </is>
-      </c>
-      <c r="B49" s="456" t="inlineStr">
-        <is>
-          <t>Annual revenue</t>
-        </is>
-      </c>
-      <c r="C49" s="456" t="inlineStr">
-        <is>
-          <t>Tax revenue of the recorded tax</t>
-        </is>
-      </c>
-      <c r="D49" s="456" t="inlineStr">
+      <c r="A49" s="369" t="n"/>
+      <c r="B49" s="449" t="inlineStr">
+        <is>
+          <t>Earmarked revenue*</t>
+        </is>
+      </c>
+      <c r="C49" s="449" t="inlineStr">
+        <is>
+          <t>The policy financed by the revenue of the recorded tax (recorded even if not otherwise part of this database)</t>
+        </is>
+      </c>
+      <c r="D49" s="449" t="inlineStr">
+        <is>
+          <t>Free or binary</t>
+        </is>
+      </c>
+      <c r="E49" s="449" t="inlineStr">
+        <is>
+          <t>ID of the financed policy instrument or “Earmarked” if financed policy is not included in the database</t>
+        </is>
+      </c>
+      <c r="F49" s="459" t="n"/>
+      <c r="G49" s="499" t="n"/>
+      <c r="H49" s="499" t="n"/>
+      <c r="I49" s="499" t="n"/>
+      <c r="J49" s="499" t="n"/>
+      <c r="K49" s="499" t="n"/>
+      <c r="L49" s="499" t="n"/>
+      <c r="M49" s="499" t="n"/>
+      <c r="N49" s="499" t="n"/>
+      <c r="O49" s="499" t="n"/>
+      <c r="P49" s="499" t="n"/>
+      <c r="Q49" s="499" t="n"/>
+      <c r="R49" s="499" t="n"/>
+      <c r="S49" s="499" t="n"/>
+      <c r="T49" s="499" t="n"/>
+    </row>
+    <row r="50" ht="15" customHeight="1">
+      <c r="A50" s="361" t="n"/>
+      <c r="B50" s="449" t="inlineStr">
+        <is>
+          <t>Annual revenue forgone</t>
+        </is>
+      </c>
+      <c r="C50" s="449" t="inlineStr">
+        <is>
+          <t>If tax incentive, estimated loss in tax revenue due to the recorded tax incentive (recorded for the year the instrument is recorded)</t>
+        </is>
+      </c>
+      <c r="D50" s="449" t="inlineStr">
         <is>
           <t>Numerical</t>
         </is>
       </c>
-      <c r="E49" s="456" t="inlineStr">
+      <c r="E50" s="449" t="inlineStr">
         <is>
           <t>in millions of domestic currency, USD or otherwise applicable unit</t>
-        </is>
-      </c>
-      <c r="F49" s="503" t="n"/>
-      <c r="G49" s="504" t="n"/>
-      <c r="H49" s="504" t="n"/>
-      <c r="I49" s="504" t="n"/>
-      <c r="J49" s="504" t="n"/>
-      <c r="K49" s="504" t="n"/>
-      <c r="L49" s="504" t="n"/>
-      <c r="M49" s="504" t="n"/>
-      <c r="N49" s="504" t="n"/>
-      <c r="O49" s="504" t="n"/>
-      <c r="P49" s="504" t="n"/>
-      <c r="Q49" s="504" t="n"/>
-      <c r="R49" s="504" t="n"/>
-      <c r="S49" s="504" t="n"/>
-      <c r="T49" s="504" t="n"/>
-    </row>
-    <row r="50" ht="15" customHeight="1">
-      <c r="A50" s="369" t="n"/>
-      <c r="B50" s="449" t="inlineStr">
-        <is>
-          <t>Earmarked revenue*</t>
-        </is>
-      </c>
-      <c r="C50" s="449" t="inlineStr">
-        <is>
-          <t>The policy financed by the revenue of the recorded tax (recorded even if not otherwise part of this database)</t>
-        </is>
-      </c>
-      <c r="D50" s="449" t="inlineStr">
-        <is>
-          <t>Free or binary</t>
-        </is>
-      </c>
-      <c r="E50" s="449" t="inlineStr">
-        <is>
-          <t>ID of the financed policy instrument or “Earmarked” if financed policy is not included in the database</t>
         </is>
       </c>
       <c r="F50" s="459" t="n"/>
@@ -7570,15 +7664,19 @@
       <c r="T50" s="499" t="n"/>
     </row>
     <row r="51" ht="15" customHeight="1">
-      <c r="A51" s="361" t="n"/>
+      <c r="A51" s="447" t="inlineStr">
+        <is>
+          <t>Subsidies</t>
+        </is>
+      </c>
       <c r="B51" s="449" t="inlineStr">
         <is>
-          <t>Annual revenue forgone</t>
+          <t>Annual expenditure</t>
         </is>
       </c>
       <c r="C51" s="449" t="inlineStr">
         <is>
-          <t>If tax incentive, estimated loss in tax revenue due to the recorded tax incentive (recorded for the year the instrument is recorded)</t>
+          <t>The financial allocation or budget earmarked in the year preceding the data collecting</t>
         </is>
       </c>
       <c r="D51" s="449" t="inlineStr">
@@ -7608,19 +7706,15 @@
       <c r="T51" s="499" t="n"/>
     </row>
     <row r="52" ht="15" customHeight="1">
-      <c r="A52" s="447" t="inlineStr">
-        <is>
-          <t>Subsidies</t>
-        </is>
-      </c>
+      <c r="A52" s="369" t="n"/>
       <c r="B52" s="449" t="inlineStr">
         <is>
-          <t>Annual expenditure</t>
+          <t>Limit</t>
         </is>
       </c>
       <c r="C52" s="449" t="inlineStr">
         <is>
-          <t>The financial allocation or budget earmarked in the year preceding the data collecting</t>
+          <t>The overall financial allocation, budget earmarked over the entire duration of the instrument, the amount of assets subsidised (capacity limit), the time horizon of the subsidyor other limits on totals for the subsidy</t>
         </is>
       </c>
       <c r="D52" s="449" t="inlineStr">
@@ -7630,7 +7724,7 @@
       </c>
       <c r="E52" s="449" t="inlineStr">
         <is>
-          <t>in millions of domestic currency, USD or otherwise applicable unit</t>
+          <t>in domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
       <c r="F52" s="459" t="n"/>
@@ -7653,22 +7747,22 @@
       <c r="A53" s="369" t="n"/>
       <c r="B53" s="449" t="inlineStr">
         <is>
-          <t>Limit</t>
+          <t>Distribution mechanism</t>
         </is>
       </c>
       <c r="C53" s="449" t="inlineStr">
         <is>
-          <t>The overall financial allocation, budget earmarked over the entire duration of the instrument, the amount of assets subsidised (capacity limit), the time horizon of the subsidyor other limits on totals for the subsidy</t>
+          <t>The mechanism by which the subsidy is awarded</t>
         </is>
       </c>
       <c r="D53" s="449" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Categorial</t>
         </is>
       </c>
       <c r="E53" s="449" t="inlineStr">
         <is>
-          <t>in domestic currency, USD or otherwise applicable unit</t>
+          <t>from list, e.g. auction type, by default, lottery, etc.</t>
         </is>
       </c>
       <c r="F53" s="459" t="n"/>
@@ -7691,22 +7785,22 @@
       <c r="A54" s="369" t="n"/>
       <c r="B54" s="449" t="inlineStr">
         <is>
-          <t>Distribution mechanism</t>
+          <t>Enforcement mechanism</t>
         </is>
       </c>
       <c r="C54" s="449" t="inlineStr">
         <is>
-          <t>The mechanism by which the subsidy is awarded</t>
+          <t>If a performance is expected, how is non-compliance punished</t>
         </is>
       </c>
       <c r="D54" s="449" t="inlineStr">
         <is>
-          <t>Categorial</t>
+          <t>Categorial, free for details</t>
         </is>
       </c>
       <c r="E54" s="449" t="inlineStr">
         <is>
-          <t>from list, e.g. auction type, by default, lottery, etc.</t>
+          <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
         </is>
       </c>
       <c r="F54" s="459" t="n"/>
@@ -7729,22 +7823,22 @@
       <c r="A55" s="369" t="n"/>
       <c r="B55" s="449" t="inlineStr">
         <is>
-          <t>Enforcement mechanism</t>
+          <t>Subsidy floor or ceiling</t>
         </is>
       </c>
       <c r="C55" s="449" t="inlineStr">
         <is>
-          <t>If a performance is expected, how is non-compliance punished</t>
+          <t>The minimum or maximum limits set for subsidies per year (for the year the instrument is recorded), indicating the lower and upper bounds within which subsidy amounts must fall.</t>
         </is>
       </c>
       <c r="D55" s="449" t="inlineStr">
         <is>
-          <t>Categorial, free for details</t>
+          <t>Numerical</t>
         </is>
       </c>
       <c r="E55" s="449" t="inlineStr">
         <is>
-          <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
+          <t>Value in domestic currency</t>
         </is>
       </c>
       <c r="F55" s="459" t="n"/>
@@ -7767,22 +7861,22 @@
       <c r="A56" s="369" t="n"/>
       <c r="B56" s="449" t="inlineStr">
         <is>
-          <t>Subsidy floor or ceiling</t>
+          <t>Support Duration</t>
         </is>
       </c>
       <c r="C56" s="449" t="inlineStr">
         <is>
-          <t>The minimum or maximum limits set for subsidies per year (for the year the instrument is recorded), indicating the lower and upper bounds within which subsidy amounts must fall.</t>
+          <t>The time range during which the support is provided (contract length, annual payments, etc)</t>
         </is>
       </c>
       <c r="D56" s="449" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E56" s="449" t="inlineStr">
         <is>
-          <t>Value in domestic currency</t>
+          <t>Expressed in years, or months</t>
         </is>
       </c>
       <c r="F56" s="459" t="n"/>
@@ -7802,27 +7896,23 @@
       <c r="T56" s="499" t="n"/>
     </row>
     <row r="57" ht="15" customHeight="1">
-      <c r="A57" s="369" t="n"/>
+      <c r="A57" s="361" t="n"/>
       <c r="B57" s="449" t="inlineStr">
         <is>
-          <t>Support Duration</t>
+          <t>Subsidies: Monitoring mechanism</t>
         </is>
       </c>
       <c r="C57" s="449" t="inlineStr">
         <is>
-          <t>The time range during which the support is provided (contract length, annual payments, etc)</t>
+          <t>Any monitoring scheme</t>
         </is>
       </c>
       <c r="D57" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="E57" s="449" t="inlineStr">
-        <is>
-          <t>Expressed in years, or months</t>
-        </is>
-      </c>
+          <t>Categorial, free for details</t>
+        </is>
+      </c>
+      <c r="E57" s="449" t="n"/>
       <c r="F57" s="459" t="n"/>
       <c r="G57" s="499" t="n"/>
       <c r="H57" s="499" t="n"/>
@@ -7840,23 +7930,31 @@
       <c r="T57" s="499" t="n"/>
     </row>
     <row r="58" ht="15" customHeight="1">
-      <c r="A58" s="361" t="n"/>
+      <c r="A58" s="452" t="inlineStr">
+        <is>
+          <t>Trading scheme</t>
+        </is>
+      </c>
       <c r="B58" s="449" t="inlineStr">
         <is>
-          <t>Subsidies: Monitoring mechanism</t>
+          <t>Type</t>
         </is>
       </c>
       <c r="C58" s="449" t="inlineStr">
         <is>
-          <t>Any monitoring scheme</t>
+          <t>The trading system in place, i.e., trading of permits or credits</t>
         </is>
       </c>
       <c r="D58" s="449" t="inlineStr">
         <is>
-          <t>Categorial, free for details</t>
-        </is>
-      </c>
-      <c r="E58" s="449" t="n"/>
+          <t>Categorial</t>
+        </is>
+      </c>
+      <c r="E58" s="449" t="inlineStr">
+        <is>
+          <t>from list, e.g. permits, credits, etc</t>
+        </is>
+      </c>
       <c r="F58" s="459" t="n"/>
       <c r="G58" s="499" t="n"/>
       <c r="H58" s="499" t="n"/>
@@ -7874,29 +7972,25 @@
       <c r="T58" s="499" t="n"/>
     </row>
     <row r="59" ht="15" customHeight="1">
-      <c r="A59" s="452" t="inlineStr">
-        <is>
-          <t>Trading scheme</t>
-        </is>
-      </c>
+      <c r="A59" s="369" t="n"/>
       <c r="B59" s="449" t="inlineStr">
         <is>
-          <t>Type</t>
+          <t>Cap</t>
         </is>
       </c>
       <c r="C59" s="449" t="inlineStr">
         <is>
-          <t>The trading system in place, i.e., trading of permits or credits</t>
+          <t>The upper limit or cap imposed on the total greenhouse gas emissions allowed within a specific period under a GHG cap-and-trade or emissions trading system; if this cell is filled, it is a permit, otherwise a credit (relevant for UNFCCC reporting)</t>
         </is>
       </c>
       <c r="D59" s="449" t="inlineStr">
         <is>
-          <t>Categorial</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E59" s="449" t="inlineStr">
         <is>
-          <t>from list, e.g. permits, credits, etc</t>
+          <t>CO2eq for ETS, but could be others if ever we cover other trading systems (nitrogen trading in agriculture)</t>
         </is>
       </c>
       <c r="F59" s="459" t="n"/>
@@ -7919,12 +8013,12 @@
       <c r="A60" s="369" t="n"/>
       <c r="B60" s="449" t="inlineStr">
         <is>
-          <t>Cap</t>
+          <t>Allowance mechanism</t>
         </is>
       </c>
       <c r="C60" s="449" t="inlineStr">
         <is>
-          <t>The upper limit or cap imposed on the total greenhouse gas emissions allowed within a specific period under a GHG cap-and-trade or emissions trading system; if this cell is filled, it is a permit, otherwise a credit (relevant for UNFCCC reporting)</t>
+          <t>The system or method used to distribute or allocate emission allowances within the trading system, specifying how entities receive their allowances, as well as the allowance size and potentially other aspects</t>
         </is>
       </c>
       <c r="D60" s="449" t="inlineStr">
@@ -7934,7 +8028,7 @@
       </c>
       <c r="E60" s="449" t="inlineStr">
         <is>
-          <t>CO2eq for ETS, but could be others if ever we cover other trading systems (nitrogen trading in agriculture)</t>
+          <t>free allowance; auctioning; mixture of the two</t>
         </is>
       </c>
       <c r="F60" s="459" t="n"/>
@@ -7957,22 +8051,22 @@
       <c r="A61" s="369" t="n"/>
       <c r="B61" s="449" t="inlineStr">
         <is>
-          <t>Allowance mechanism</t>
+          <t>Free allowance</t>
         </is>
       </c>
       <c r="C61" s="449" t="inlineStr">
         <is>
-          <t>The system or method used to distribute or allocate emission allowances within the trading system, specifying how entities receive their allowances, as well as the allowance size and potentially other aspects</t>
+          <t>Share of free allowance</t>
         </is>
       </c>
       <c r="D61" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Numerial</t>
         </is>
       </c>
       <c r="E61" s="449" t="inlineStr">
         <is>
-          <t>free allowance; auctioning; mixture of the two</t>
+          <t>In percentages</t>
         </is>
       </c>
       <c r="F61" s="459" t="n"/>
@@ -7995,22 +8089,22 @@
       <c r="A62" s="369" t="n"/>
       <c r="B62" s="449" t="inlineStr">
         <is>
-          <t>Free allowance</t>
+          <t>Volume</t>
         </is>
       </c>
       <c r="C62" s="449" t="inlineStr">
         <is>
-          <t>Share of free allowance</t>
+          <t>Traded volume in collection year-1</t>
         </is>
       </c>
       <c r="D62" s="449" t="inlineStr">
         <is>
-          <t>Numerial</t>
+          <t>Numerical</t>
         </is>
       </c>
       <c r="E62" s="449" t="inlineStr">
         <is>
-          <t>In percentages</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F62" s="459" t="n"/>
@@ -8033,22 +8127,22 @@
       <c r="A63" s="369" t="n"/>
       <c r="B63" s="449" t="inlineStr">
         <is>
-          <t>Volume</t>
+          <t>Linkages</t>
         </is>
       </c>
       <c r="C63" s="449" t="inlineStr">
         <is>
-          <t>Traded volume in collection year-1</t>
+          <t>Linkages with other ETS</t>
         </is>
       </c>
       <c r="D63" s="449" t="inlineStr">
         <is>
-          <t>Numerical</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E63" s="449" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Enter the instrument IDs of relevant instruments (N/A if no link)</t>
         </is>
       </c>
       <c r="F63" s="459" t="n"/>
@@ -8071,22 +8165,22 @@
       <c r="A64" s="369" t="n"/>
       <c r="B64" s="449" t="inlineStr">
         <is>
-          <t>Linkages</t>
+          <t>Market stabilisation mechanism</t>
         </is>
       </c>
       <c r="C64" s="449" t="inlineStr">
         <is>
-          <t>Linkages with other ETS</t>
+          <t>The existence of any mechanism or provision within the trading system designed to stabilize the market, prevent extreme price fluctuations, or address imbalances in supply and demand. E.g., secondary markets/ offsets and credits</t>
         </is>
       </c>
       <c r="D64" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Dichotomous, free for details</t>
         </is>
       </c>
       <c r="E64" s="449" t="inlineStr">
         <is>
-          <t>Enter the instrument IDs of relevant instruments (N/A if no link)</t>
+          <t>yes/no</t>
         </is>
       </c>
       <c r="F64" s="459" t="n"/>
@@ -8109,22 +8203,22 @@
       <c r="A65" s="369" t="n"/>
       <c r="B65" s="449" t="inlineStr">
         <is>
-          <t>Market stabilisation mechanism</t>
+          <t>Revenue (annual)</t>
         </is>
       </c>
       <c r="C65" s="449" t="inlineStr">
         <is>
-          <t>The existence of any mechanism or provision within the trading system designed to stabilize the market, prevent extreme price fluctuations, or address imbalances in supply and demand. E.g., secondary markets/ offsets and credits</t>
+          <t>The yearly revenue generated from the trading system, including any fees, fines, or other financial flows associated with emissions trading. (for the system, rather than for the government)</t>
         </is>
       </c>
       <c r="D65" s="449" t="inlineStr">
         <is>
-          <t>Dichotomous, free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E65" s="449" t="inlineStr">
         <is>
-          <t>yes/no</t>
+          <t>In domestic currency (collection year -1)</t>
         </is>
       </c>
       <c r="F65" s="459" t="n"/>
@@ -8147,12 +8241,12 @@
       <c r="A66" s="369" t="n"/>
       <c r="B66" s="449" t="inlineStr">
         <is>
-          <t>Revenue (annual)</t>
+          <t>Offset use allowed</t>
         </is>
       </c>
       <c r="C66" s="449" t="inlineStr">
         <is>
-          <t>The yearly revenue generated from the trading system, including any fees, fines, or other financial flows associated with emissions trading. (for the system, rather than for the government)</t>
+          <t>Rules of which offsets are allowed or reference to such rules; "No" if no offsets allowed</t>
         </is>
       </c>
       <c r="D66" s="449" t="inlineStr">
@@ -8162,7 +8256,7 @@
       </c>
       <c r="E66" s="449" t="inlineStr">
         <is>
-          <t>In domestic currency (collection year -1)</t>
+          <t>No if none; otherwise description of the applicable rules</t>
         </is>
       </c>
       <c r="F66" s="459" t="n"/>
@@ -8182,25 +8276,25 @@
       <c r="T66" s="499" t="n"/>
     </row>
     <row r="67" ht="15" customHeight="1">
-      <c r="A67" s="369" t="n"/>
+      <c r="A67" s="361" t="n"/>
       <c r="B67" s="449" t="inlineStr">
         <is>
-          <t>Offset use allowed</t>
+          <t>Penalties for non-compliance per unit</t>
         </is>
       </c>
       <c r="C67" s="449" t="inlineStr">
         <is>
-          <t>Rules of which offsets are allowed or reference to such rules; "No" if no offsets allowed</t>
+          <t>The consequences or fines imposed on entities that fail to comply with the regulations and requirements of the emissions trading system</t>
         </is>
       </c>
       <c r="D67" s="449" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Catgorial, free for details</t>
         </is>
       </c>
       <c r="E67" s="449" t="inlineStr">
         <is>
-          <t>No if none; otherwise description of the applicable rules</t>
+          <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
         </is>
       </c>
       <c r="F67" s="459" t="n"/>
@@ -8220,25 +8314,29 @@
       <c r="T67" s="499" t="n"/>
     </row>
     <row r="68" ht="15" customHeight="1">
-      <c r="A68" s="361" t="n"/>
-      <c r="B68" s="449" t="inlineStr">
-        <is>
-          <t>Penalties for non-compliance per unit</t>
-        </is>
-      </c>
-      <c r="C68" s="449" t="inlineStr">
-        <is>
-          <t>The consequences or fines imposed on entities that fail to comply with the regulations and requirements of the emissions trading system</t>
-        </is>
-      </c>
-      <c r="D68" s="449" t="inlineStr">
-        <is>
-          <t>Catgorial, free for details</t>
-        </is>
-      </c>
-      <c r="E68" s="449" t="inlineStr">
-        <is>
-          <t>administrative action (e.g. warning, permit withdrawal); legal action (e.g. prosecution); monetary fines</t>
+      <c r="A68" s="452" t="inlineStr">
+        <is>
+          <t>Regulatory instruments</t>
+        </is>
+      </c>
+      <c r="B68" s="448" t="inlineStr">
+        <is>
+          <t>Compliance monitoring</t>
+        </is>
+      </c>
+      <c r="C68" s="448" t="inlineStr">
+        <is>
+          <t>Captures whether methods, processes, or systems are in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy</t>
+        </is>
+      </c>
+      <c r="D68" s="448" t="inlineStr">
+        <is>
+          <t>Categorial (single choice), free for details</t>
+        </is>
+      </c>
+      <c r="E68" s="448" t="inlineStr">
+        <is>
+          <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
         </is>
       </c>
       <c r="F68" s="459" t="n"/>
@@ -8258,29 +8356,25 @@
       <c r="T68" s="499" t="n"/>
     </row>
     <row r="69" ht="15" customHeight="1">
-      <c r="A69" s="452" t="inlineStr">
-        <is>
-          <t>Regulatory instruments</t>
-        </is>
-      </c>
+      <c r="A69" s="369" t="n"/>
       <c r="B69" s="448" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Compliance monitoring details</t>
         </is>
       </c>
       <c r="C69" s="448" t="inlineStr">
         <is>
-          <t>Captures whether methods, processes, or systems are in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy</t>
+          <t>Captures details on the compliance method (i.e. details on Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other)</t>
         </is>
       </c>
       <c r="D69" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E69" s="448" t="inlineStr">
         <is>
-          <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F69" s="459" t="n"/>
@@ -8303,22 +8397,22 @@
       <c r="A70" s="369" t="n"/>
       <c r="B70" s="448" t="inlineStr">
         <is>
-          <t>Compliance monitoring details</t>
+          <t>Compliance enforcement</t>
         </is>
       </c>
       <c r="C70" s="448" t="inlineStr">
         <is>
-          <t>Captures details on the compliance method (i.e. details on Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other)</t>
+          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy</t>
         </is>
       </c>
       <c r="D70" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E70" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
         </is>
       </c>
       <c r="F70" s="459" t="n"/>
@@ -8341,22 +8435,22 @@
       <c r="A71" s="369" t="n"/>
       <c r="B71" s="448" t="inlineStr">
         <is>
-          <t>Compliance enforcement</t>
+          <t>Compliance enforcement details</t>
         </is>
       </c>
       <c r="C71" s="448" t="inlineStr">
         <is>
-          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy</t>
+          <t>Captures details on the enforcement method and process (i.e. detao;s on Monetary penalties; Prohibitions; Compliance order; Other)</t>
         </is>
       </c>
       <c r="D71" s="448" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E71" s="448" t="inlineStr">
         <is>
-          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F71" s="459" t="n"/>
@@ -8379,22 +8473,22 @@
       <c r="A72" s="369" t="n"/>
       <c r="B72" s="448" t="inlineStr">
         <is>
-          <t>Compliance enforcement details</t>
+          <t>Compliance promotion</t>
         </is>
       </c>
       <c r="C72" s="448" t="inlineStr">
         <is>
-          <t>Captures details on the enforcement method and process (i.e. detao;s on Monetary penalties; Prohibitions; Compliance order; Other)</t>
+          <t>Initiatives or activities aimed at encouraging and facilitating compliance with the regulatory measures of the climate change mitigation policy</t>
         </is>
       </c>
       <c r="D72" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E72" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No compliance promotion; Regulatory incentives (e.g. weights, banking, pooling, trading); Information and direct assistance; Financial support; Other incentives or support</t>
         </is>
       </c>
       <c r="F72" s="459" t="n"/>
@@ -8414,25 +8508,25 @@
       <c r="T72" s="499" t="n"/>
     </row>
     <row r="73" ht="15" customHeight="1">
-      <c r="A73" s="369" t="n"/>
+      <c r="A73" s="361" t="n"/>
       <c r="B73" s="448" t="inlineStr">
         <is>
-          <t>Compliance promotion</t>
+          <t>Compliance promotion details</t>
         </is>
       </c>
       <c r="C73" s="448" t="inlineStr">
         <is>
-          <t>Initiatives or activities aimed at encouraging and facilitating compliance with the regulatory measures of the climate change mitigation policy</t>
+          <t>Captures details on compliance promotion methods and processes (e.g. details on regulatory incentives such as weights, banking, pooling, trading, or other; information/direct assistance; financial support; other compliance promotion processes)</t>
         </is>
       </c>
       <c r="D73" s="448" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E73" s="448" t="inlineStr">
         <is>
-          <t>No compliance promotion; Regulatory incentives (e.g. weights, banking, pooling, trading); Information and direct assistance; Financial support; Other incentives or support</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F73" s="459" t="n"/>
@@ -8452,25 +8546,29 @@
       <c r="T73" s="499" t="n"/>
     </row>
     <row r="74" ht="15" customHeight="1">
-      <c r="A74" s="361" t="n"/>
+      <c r="A74" s="452" t="inlineStr">
+        <is>
+          <t>Government investment and consumption</t>
+        </is>
+      </c>
       <c r="B74" s="448" t="inlineStr">
         <is>
-          <t>Compliance promotion details</t>
+          <t>Public investment: Co-financing</t>
         </is>
       </c>
       <c r="C74" s="448" t="inlineStr">
         <is>
-          <t>Captures details on compliance promotion methods and processes (e.g. details on regulatory incentives such as weights, banking, pooling, trading, or other; information/direct assistance; financial support; other compliance promotion processes)</t>
+          <t>Indicates whether the government is financing the project/technology completely or is co-financing it</t>
         </is>
       </c>
       <c r="D74" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (single choice)</t>
         </is>
       </c>
       <c r="E74" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Yes; No</t>
         </is>
       </c>
       <c r="F74" s="459" t="n"/>
@@ -8490,29 +8588,26 @@
       <c r="T74" s="499" t="n"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="452" t="inlineStr">
-        <is>
-          <t>Government investment and consumption</t>
-        </is>
-      </c>
+      <c r="A75" s="369" t="n"/>
       <c r="B75" s="448" t="inlineStr">
         <is>
-          <t>Public investment: Co-financing</t>
+          <t>Public investment: Selection process</t>
         </is>
       </c>
       <c r="C75" s="448" t="inlineStr">
         <is>
-          <t>Indicates whether the government is financing the project/technology completely or is co-financing it</t>
+          <t>Details regarding how the project or investment is chosen as an investment target. If there's a structured selection process, it indicates the criteria for selection</t>
         </is>
       </c>
       <c r="D75" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice)</t>
+          <t>Categorial (single choice), free
+for details</t>
         </is>
       </c>
       <c r="E75" s="448" t="inlineStr">
         <is>
-          <t>Yes; No</t>
+          <t>Yes, No</t>
         </is>
       </c>
       <c r="F75" s="459" t="n"/>
@@ -8535,12 +8630,12 @@
       <c r="A76" s="369" t="n"/>
       <c r="B76" s="448" t="inlineStr">
         <is>
-          <t>Public investment: Selection process</t>
+          <t>Public procurement: Tender process</t>
         </is>
       </c>
       <c r="C76" s="448" t="inlineStr">
         <is>
-          <t>Details regarding how the project or investment is chosen as an investment target. If there's a structured selection process, it indicates the criteria for selection</t>
+          <t>Indicates the type of tender/ purchase process</t>
         </is>
       </c>
       <c r="D76" s="448" t="inlineStr">
@@ -8551,7 +8646,7 @@
       </c>
       <c r="E76" s="448" t="inlineStr">
         <is>
-          <t>Yes, No</t>
+          <t>Open tender; Direct purchase; Negotiated purchase; Accelerated public tender</t>
         </is>
       </c>
       <c r="F76" s="459" t="n"/>
@@ -8574,23 +8669,22 @@
       <c r="A77" s="369" t="n"/>
       <c r="B77" s="448" t="inlineStr">
         <is>
-          <t>Public procurement: Tender process</t>
+          <t>Public procurement: Award criteria tender process</t>
         </is>
       </c>
       <c r="C77" s="448" t="inlineStr">
         <is>
-          <t>Indicates the type of tender/ purchase process</t>
+          <t>Indicates if there is a premium given to bidders that comply with specific requirements in the tender process</t>
         </is>
       </c>
       <c r="D77" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice), free
-for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E77" s="448" t="inlineStr">
         <is>
-          <t>Open tender; Direct purchase; Negotiated purchase; Accelerated public tender</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F77" s="459" t="n"/>
@@ -8613,22 +8707,23 @@
       <c r="A78" s="369" t="n"/>
       <c r="B78" s="448" t="inlineStr">
         <is>
-          <t>Public procurement: Award criteria tender process</t>
+          <t>Public procurement: Compliance monitoring</t>
         </is>
       </c>
       <c r="C78" s="448" t="inlineStr">
         <is>
-          <t>Indicates if there is a premium given to bidders that comply with specific requirements in the tender process</t>
+          <t>The methods, processes, or systems in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy</t>
         </is>
       </c>
       <c r="D78" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (single choice), free
+for details</t>
         </is>
       </c>
       <c r="E78" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
         </is>
       </c>
       <c r="F78" s="459" t="n"/>
@@ -8651,23 +8746,23 @@
       <c r="A79" s="369" t="n"/>
       <c r="B79" s="448" t="inlineStr">
         <is>
-          <t>Public procurement: Compliance monitoring</t>
+          <t>Public procurement: Compliance enforcement</t>
         </is>
       </c>
       <c r="C79" s="448" t="inlineStr">
         <is>
-          <t>The methods, processes, or systems in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy</t>
+          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy</t>
         </is>
       </c>
       <c r="D79" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice), free
+          <t>Categorial (multiple choice), free
 for details</t>
         </is>
       </c>
       <c r="E79" s="448" t="inlineStr">
         <is>
-          <t>No compliance monitoring; Self-monitoring and reporting; Inspections or audits conducted by government authorities or third parties; Other</t>
+          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
         </is>
       </c>
       <c r="F79" s="459" t="n"/>
@@ -8690,23 +8785,22 @@
       <c r="A80" s="369" t="n"/>
       <c r="B80" s="448" t="inlineStr">
         <is>
-          <t>Public procurement: Compliance enforcement</t>
+          <t>Public procurement: Life-cycle costing</t>
         </is>
       </c>
       <c r="C80" s="448" t="inlineStr">
         <is>
-          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy</t>
+          <t>Evaluating the financial proposals while considering the total costs over the life cycle of a product, service or works including (i) purchase price and all associated costs (delivery, installation, insurance, etc.); (ii) operating costs, including energy, fuel and water use, spares, and maintenance (iii) end-of-life costs, such as decommissioning or disposal; and (iv) costs imputed to environmental externalities.</t>
         </is>
       </c>
       <c r="D80" s="448" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free
-for details</t>
+          <t>Categorial (single choice)</t>
         </is>
       </c>
       <c r="E80" s="448" t="inlineStr">
         <is>
-          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
+          <t>Yes; No</t>
         </is>
       </c>
       <c r="F80" s="459" t="n"/>
@@ -8726,25 +8820,25 @@
       <c r="T80" s="499" t="n"/>
     </row>
     <row r="81" ht="15" customHeight="1">
-      <c r="A81" s="369" t="n"/>
-      <c r="B81" s="448" t="inlineStr">
-        <is>
-          <t>Public procurement: Life-cycle costing</t>
-        </is>
-      </c>
-      <c r="C81" s="448" t="inlineStr">
-        <is>
-          <t>Evaluating the financial proposals while considering the total costs over the life cycle of a product, service or works including (i) purchase price and all associated costs (delivery, installation, insurance, etc.); (ii) operating costs, including energy, fuel and water use, spares, and maintenance (iii) end-of-life costs, such as decommissioning or disposal; and (iv) costs imputed to environmental externalities.</t>
-        </is>
-      </c>
-      <c r="D81" s="448" t="inlineStr">
-        <is>
-          <t>Categorial (single choice)</t>
-        </is>
-      </c>
-      <c r="E81" s="448" t="inlineStr">
-        <is>
-          <t>Yes; No</t>
+      <c r="A81" s="361" t="n"/>
+      <c r="B81" s="449" t="inlineStr">
+        <is>
+          <t>Public investment/procurement: Annual expenditure</t>
+        </is>
+      </c>
+      <c r="C81" s="449" t="inlineStr">
+        <is>
+          <t>The financial allocation or budget earmarked in the year preceding the data collecting</t>
+        </is>
+      </c>
+      <c r="D81" s="449" t="inlineStr">
+        <is>
+          <t>Numerical</t>
+        </is>
+      </c>
+      <c r="E81" s="449" t="inlineStr">
+        <is>
+          <t>in millions of domestic currency, USD or otherwise applicable unit</t>
         </is>
       </c>
       <c r="F81" s="459" t="n"/>
@@ -8764,25 +8858,29 @@
       <c r="T81" s="499" t="n"/>
     </row>
     <row r="82" ht="15" customHeight="1">
-      <c r="A82" s="361" t="n"/>
-      <c r="B82" s="449" t="inlineStr">
-        <is>
-          <t>Public investment/procurement: Annual expenditure</t>
-        </is>
-      </c>
-      <c r="C82" s="449" t="inlineStr">
-        <is>
-          <t>The financial allocation or budget earmarked in the year preceding the data collecting</t>
-        </is>
-      </c>
-      <c r="D82" s="449" t="inlineStr">
-        <is>
-          <t>Numerical</t>
-        </is>
-      </c>
-      <c r="E82" s="449" t="inlineStr">
-        <is>
-          <t>in millions of domestic currency, USD or otherwise applicable unit</t>
+      <c r="A82" s="452" t="inlineStr">
+        <is>
+          <t>Information instruments</t>
+        </is>
+      </c>
+      <c r="B82" s="448" t="inlineStr">
+        <is>
+          <t>Instrument linkage</t>
+        </is>
+      </c>
+      <c r="C82" s="448" t="inlineStr">
+        <is>
+          <t>Captures whether the information instrument is directly linked to other instruments</t>
+        </is>
+      </c>
+      <c r="D82" s="448" t="inlineStr">
+        <is>
+          <t>Free</t>
+        </is>
+      </c>
+      <c r="E82" s="448" t="inlineStr">
+        <is>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F82" s="459" t="n"/>
@@ -8802,29 +8900,25 @@
       <c r="T82" s="499" t="n"/>
     </row>
     <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="452" t="inlineStr">
-        <is>
-          <t>Information instruments</t>
-        </is>
-      </c>
+      <c r="A83" s="369" t="n"/>
       <c r="B83" s="448" t="inlineStr">
         <is>
-          <t>Instrument linkage</t>
+          <t>Responsibility information capturing</t>
         </is>
       </c>
       <c r="C83" s="448" t="inlineStr">
         <is>
-          <t>Captures whether the information instrument is directly linked to other instruments</t>
+          <t>Details on who is responsible for capturing the required information.</t>
         </is>
       </c>
       <c r="D83" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (single choice)</t>
         </is>
       </c>
       <c r="E83" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Government authorities (inspections or audits); Third parties (inspections or audits); The regulated agents (self-reporting)</t>
         </is>
       </c>
       <c r="F83" s="459" t="n"/>
@@ -8847,22 +8941,22 @@
       <c r="A84" s="369" t="n"/>
       <c r="B84" s="448" t="inlineStr">
         <is>
-          <t>Responsibility information capturing</t>
+          <t>Information transmission</t>
         </is>
       </c>
       <c r="C84" s="448" t="inlineStr">
         <is>
-          <t>Details on who is responsible for capturing the required information.</t>
+          <t>Indicates how the information is transmitted to the government.</t>
         </is>
       </c>
       <c r="D84" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice)</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E84" s="448" t="inlineStr">
         <is>
-          <t>Government authorities (inspections or audits); Third parties (inspections or audits); The regulated agents (self-reporting)</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F84" s="459" t="n"/>
@@ -8885,22 +8979,22 @@
       <c r="A85" s="369" t="n"/>
       <c r="B85" s="448" t="inlineStr">
         <is>
-          <t>Information transmission</t>
+          <t>Frequency of information provision</t>
         </is>
       </c>
       <c r="C85" s="448" t="inlineStr">
         <is>
-          <t>Indicates how the information is transmitted to the government.</t>
+          <t>Indicates how often the information has to be provided.</t>
         </is>
       </c>
       <c r="D85" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial (single choice), free for details</t>
         </is>
       </c>
       <c r="E85" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>In real-time; Quarterly; Annually; Other, details:__</t>
         </is>
       </c>
       <c r="F85" s="459" t="n"/>
@@ -8923,22 +9017,22 @@
       <c r="A86" s="369" t="n"/>
       <c r="B86" s="448" t="inlineStr">
         <is>
-          <t>Frequency of information provision</t>
+          <t>Public availability of information</t>
         </is>
       </c>
       <c r="C86" s="448" t="inlineStr">
         <is>
-          <t>Indicates how often the information has to be provided.</t>
+          <t>Details about whether the information is publicly available and, if so, where it can be accessed.</t>
         </is>
       </c>
       <c r="D86" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E86" s="448" t="inlineStr">
         <is>
-          <t>In real-time; Quarterly; Annually; Other, details:__</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F86" s="459" t="n"/>
@@ -8961,22 +9055,22 @@
       <c r="A87" s="369" t="n"/>
       <c r="B87" s="448" t="inlineStr">
         <is>
-          <t>Public availability of information</t>
+          <t>For labels: Type</t>
         </is>
       </c>
       <c r="C87" s="448" t="inlineStr">
         <is>
-          <t>Details about whether the information is publicly available and, if so, where it can be accessed.</t>
+          <t>Indicates how labels are assigned and designed.</t>
         </is>
       </c>
       <c r="D87" s="448" t="inlineStr">
         <is>
-          <t>Free</t>
+          <t>Categorial</t>
         </is>
       </c>
       <c r="E87" s="448" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>Binary (based on a single threshold value); Categorial; Continuously</t>
         </is>
       </c>
       <c r="F87" s="459" t="n"/>
@@ -8999,22 +9093,22 @@
       <c r="A88" s="369" t="n"/>
       <c r="B88" s="448" t="inlineStr">
         <is>
-          <t>For labels: Type</t>
+          <t>Compliance monitoring</t>
         </is>
       </c>
       <c r="C88" s="448" t="inlineStr">
         <is>
-          <t>Indicates how labels are assigned and designed.</t>
+          <t>The methods, processes, or systems in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy.</t>
         </is>
       </c>
       <c r="D88" s="448" t="inlineStr">
         <is>
-          <t>Categorial</t>
+          <t>Categorial (single choice), free for details</t>
         </is>
       </c>
       <c r="E88" s="448" t="inlineStr">
         <is>
-          <t>Binary (based on a single threshold value); Categorial; Continuously</t>
+          <t>No compliance monitoring Random; Targeted, according to a criteria:__; Regular temporal intervals:__; Irregular temporal intervals; Inspections/audits with prior notice; Inspections/audits without prior notice</t>
         </is>
       </c>
       <c r="F88" s="459" t="n"/>
@@ -9037,22 +9131,22 @@
       <c r="A89" s="369" t="n"/>
       <c r="B89" s="448" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Compliance enforcement</t>
         </is>
       </c>
       <c r="C89" s="448" t="inlineStr">
         <is>
-          <t>The methods, processes, or systems in place to monitor and ensure compliance with the regulatory aspects of the climate change mitigation policy.</t>
+          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy.</t>
         </is>
       </c>
       <c r="D89" s="448" t="inlineStr">
         <is>
-          <t>Categorial (single choice), free for details</t>
+          <t>Categorial (multiple choice), free for details</t>
         </is>
       </c>
       <c r="E89" s="448" t="inlineStr">
         <is>
-          <t>No compliance monitoring Random; Targeted, according to a criteria:__; Regular temporal intervals:__; Irregular temporal intervals; Inspections/audits with prior notice; Inspections/audits without prior notice</t>
+          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
         </is>
       </c>
       <c r="F89" s="459" t="n"/>
@@ -9075,12 +9169,12 @@
       <c r="A90" s="369" t="n"/>
       <c r="B90" s="448" t="inlineStr">
         <is>
-          <t>Compliance enforcement</t>
+          <t>Compliance promotion</t>
         </is>
       </c>
       <c r="C90" s="448" t="inlineStr">
         <is>
-          <t>The consequences imposed on agents that do not adhere to the regulatory requirements of the climate change mitigation policy.</t>
+          <t>Initiatives or activities aimed at encouraging and facilitating compliance with the regulatory measures of the climate change mitigation policy.</t>
         </is>
       </c>
       <c r="D90" s="448" t="inlineStr">
@@ -9090,7 +9184,7 @@
       </c>
       <c r="E90" s="448" t="inlineStr">
         <is>
-          <t>No compliance enforcement; Monetary penalties; Prohibitions; Compliance order; Other</t>
+          <t>No compliance promotion; Information and direct assistance; Financial support; Other incentives or support</t>
         </is>
       </c>
       <c r="F90" s="459" t="n"/>
@@ -9110,25 +9204,25 @@
       <c r="T90" s="499" t="n"/>
     </row>
     <row r="91" ht="15" customHeight="1">
-      <c r="A91" s="369" t="n"/>
+      <c r="A91" s="361" t="n"/>
       <c r="B91" s="448" t="inlineStr">
         <is>
-          <t>Compliance promotion</t>
+          <t>Details on capacity building, training/education, information campaigns and award schemes</t>
         </is>
       </c>
       <c r="C91" s="448" t="inlineStr">
         <is>
-          <t>Initiatives or activities aimed at encouraging and facilitating compliance with the regulatory measures of the climate change mitigation policy.</t>
+          <t>Indicates details on the frequency, the target group and the annual budget allocated</t>
         </is>
       </c>
       <c r="D91" s="448" t="inlineStr">
         <is>
-          <t>Categorial (multiple choice), free for details</t>
+          <t>Free</t>
         </is>
       </c>
       <c r="E91" s="448" t="inlineStr">
         <is>
-          <t>No compliance promotion; Information and direct assistance; Financial support; Other incentives or support</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="F91" s="459" t="n"/>
@@ -9148,25 +9242,29 @@
       <c r="T91" s="499" t="n"/>
     </row>
     <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="361" t="n"/>
-      <c r="B92" s="448" t="inlineStr">
-        <is>
-          <t>Details on capacity building, training/education, information campaigns and award schemes</t>
-        </is>
-      </c>
-      <c r="C92" s="448" t="inlineStr">
-        <is>
-          <t>Indicates details on the frequency, the target group and the annual budget allocated</t>
-        </is>
-      </c>
-      <c r="D92" s="448" t="inlineStr">
-        <is>
-          <t>Free</t>
-        </is>
-      </c>
-      <c r="E92" s="448" t="inlineStr">
-        <is>
-          <t>N/A</t>
+      <c r="A92" s="452" t="inlineStr">
+        <is>
+          <t>Voluntary approaches</t>
+        </is>
+      </c>
+      <c r="B92" s="449" t="inlineStr">
+        <is>
+          <t>Incentives for Participation</t>
+        </is>
+      </c>
+      <c r="C92" s="449" t="inlineStr">
+        <is>
+          <t>The rewards, benefits, or positive inducements offered to encourage voluntary participation in climate change mitigation activities or programs</t>
+        </is>
+      </c>
+      <c r="D92" s="449" t="inlineStr">
+        <is>
+          <t>Categorial (single choice)</t>
+        </is>
+      </c>
+      <c r="E92" s="449" t="inlineStr">
+        <is>
+          <t>Financial; Regulatory; Reputational; None</t>
         </is>
       </c>
       <c r="F92" s="459" t="n"/>
@@ -9186,29 +9284,25 @@
       <c r="T92" s="499" t="n"/>
     </row>
     <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="452" t="inlineStr">
-        <is>
-          <t>Voluntary approaches</t>
-        </is>
-      </c>
+      <c r="A93" s="369" t="n"/>
       <c r="B93" s="449" t="inlineStr">
         <is>
-          <t>Incentives for Participation</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="C93" s="449" t="inlineStr">
         <is>
-          <t>The rewards, benefits, or positive inducements offered to encourage voluntary participation in climate change mitigation activities or programs</t>
+          <t>The processes and systems in place to track and assess voluntary actions or initiatives related to climate change mitigation.</t>
         </is>
       </c>
       <c r="D93" s="449" t="inlineStr">
         <is>
-          <t>Categorial (single choice)</t>
+          <t>Dichotomous, free for details</t>
         </is>
       </c>
       <c r="E93" s="449" t="inlineStr">
         <is>
-          <t>Financial; Regulatory; Reputational; None</t>
+          <t>Yes/no, free for detail</t>
         </is>
       </c>
       <c r="F93" s="459" t="n"/>
@@ -9227,16 +9321,16 @@
       <c r="S93" s="499" t="n"/>
       <c r="T93" s="499" t="n"/>
     </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="369" t="n"/>
+    <row r="94">
+      <c r="A94" s="361" t="n"/>
       <c r="B94" s="449" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Sanctions for non-compliance</t>
         </is>
       </c>
       <c r="C94" s="449" t="inlineStr">
         <is>
-          <t>The processes and systems in place to track and assess voluntary actions or initiatives related to climate change mitigation.</t>
+          <t>The consequences or penalties imposed on agents or individuals who fail to fulfill their voluntary commitments or obligations related to climate change mitigation.</t>
         </is>
       </c>
       <c r="D94" s="449" t="inlineStr">
@@ -9265,61 +9359,24 @@
       <c r="S94" s="499" t="n"/>
       <c r="T94" s="499" t="n"/>
     </row>
-    <row r="95" ht="15" customHeight="1">
-      <c r="A95" s="361" t="n"/>
-      <c r="B95" s="449" t="inlineStr">
-        <is>
-          <t>Sanctions for non-compliance</t>
-        </is>
-      </c>
-      <c r="C95" s="449" t="inlineStr">
-        <is>
-          <t>The consequences or penalties imposed on agents or individuals who fail to fulfill their voluntary commitments or obligations related to climate change mitigation.</t>
-        </is>
-      </c>
-      <c r="D95" s="449" t="inlineStr">
-        <is>
-          <t>Dichotomous, free for details</t>
-        </is>
-      </c>
-      <c r="E95" s="449" t="inlineStr">
-        <is>
-          <t>Yes/no, free for detail</t>
-        </is>
-      </c>
-      <c r="F95" s="459" t="n"/>
-      <c r="G95" s="499" t="n"/>
-      <c r="H95" s="499" t="n"/>
-      <c r="I95" s="499" t="n"/>
-      <c r="J95" s="499" t="n"/>
-      <c r="K95" s="499" t="n"/>
-      <c r="L95" s="499" t="n"/>
-      <c r="M95" s="499" t="n"/>
-      <c r="N95" s="499" t="n"/>
-      <c r="O95" s="499" t="n"/>
-      <c r="P95" s="499" t="n"/>
-      <c r="Q95" s="499" t="n"/>
-      <c r="R95" s="499" t="n"/>
-      <c r="S95" s="499" t="n"/>
-      <c r="T95" s="499" t="n"/>
-    </row>
+    <row r="95" ht="15" customHeight="1"/>
   </sheetData>
   <mergeCells count="15">
     <mergeCell ref="A4:A7"/>
-    <mergeCell ref="A39:A41"/>
-    <mergeCell ref="A44:A47"/>
-    <mergeCell ref="A75:A82"/>
-    <mergeCell ref="A48:E48"/>
-    <mergeCell ref="A52:A58"/>
+    <mergeCell ref="A23:A37"/>
+    <mergeCell ref="A48:A50"/>
     <mergeCell ref="A2:E2"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A69:A74"/>
-    <mergeCell ref="A8:A23"/>
-    <mergeCell ref="A83:A92"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="A24:A38"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="A74:A81"/>
+    <mergeCell ref="A43:A46"/>
+    <mergeCell ref="A51:A57"/>
+    <mergeCell ref="A92:A94"/>
+    <mergeCell ref="A82:A91"/>
+    <mergeCell ref="A47:E47"/>
+    <mergeCell ref="A41:A42"/>
+    <mergeCell ref="A38:A40"/>
+    <mergeCell ref="A68:A73"/>
+    <mergeCell ref="A8:A22"/>
+    <mergeCell ref="A58:A67"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10069,7 +10126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN2"/>
+  <dimension ref="A1:BM2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -10110,12 +10167,12 @@
       <c r="S1" s="95" t="n"/>
       <c r="T1" s="95" t="n"/>
       <c r="U1" s="95" t="n"/>
-      <c r="V1" s="95" t="n"/>
-      <c r="W1" s="391" t="inlineStr">
+      <c r="V1" s="391" t="inlineStr">
         <is>
           <t>Policy regulatory base and intensity</t>
         </is>
       </c>
+      <c r="W1" s="392" t="n"/>
       <c r="X1" s="392" t="n"/>
       <c r="Y1" s="392" t="n"/>
       <c r="Z1" s="392" t="n"/>
@@ -10129,12 +10186,12 @@
       <c r="AH1" s="392" t="n"/>
       <c r="AI1" s="392" t="n"/>
       <c r="AJ1" s="392" t="n"/>
-      <c r="AK1" s="392" t="n"/>
-      <c r="AL1" s="393" t="inlineStr">
+      <c r="AK1" s="393" t="inlineStr">
         <is>
           <t>Instrument-specific attributes</t>
         </is>
       </c>
+      <c r="AL1" s="100" t="n"/>
       <c r="AM1" s="100" t="n"/>
       <c r="AN1" s="100" t="n"/>
       <c r="AO1" s="100" t="n"/>
@@ -10152,29 +10209,28 @@
       <c r="BA1" s="100" t="n"/>
       <c r="BB1" s="100" t="n"/>
       <c r="BC1" s="100" t="n"/>
-      <c r="BD1" s="100" t="n"/>
-      <c r="BE1" s="394" t="inlineStr">
+      <c r="BD1" s="394" t="inlineStr">
         <is>
           <t>GHG emission base</t>
         </is>
       </c>
-      <c r="BF1" s="101" t="n"/>
-      <c r="BG1" s="395" t="inlineStr">
+      <c r="BE1" s="101" t="n"/>
+      <c r="BF1" s="395" t="inlineStr">
         <is>
           <t>Classification &amp; Indicators</t>
         </is>
       </c>
+      <c r="BG1" s="100" t="n"/>
       <c r="BH1" s="100" t="n"/>
       <c r="BI1" s="100" t="n"/>
-      <c r="BJ1" s="100" t="n"/>
-      <c r="BK1" s="396" t="inlineStr">
+      <c r="BJ1" s="396" t="inlineStr">
         <is>
           <t>References to legislation</t>
         </is>
       </c>
+      <c r="BK1" s="392" t="n"/>
       <c r="BL1" s="392" t="n"/>
-      <c r="BM1" s="392" t="n"/>
-      <c r="BN1" s="397" t="n"/>
+      <c r="BM1" s="397" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="398" t="inlineStr">
@@ -10239,282 +10295,277 @@
       </c>
       <c r="M2" s="401" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Jurisdiction level</t>
         </is>
       </c>
       <c r="N2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction level</t>
+          <t>Jurisdiction name</t>
         </is>
       </c>
       <c r="O2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction name</t>
+          <t>Adoption date</t>
         </is>
       </c>
       <c r="P2" s="401" t="inlineStr">
         <is>
-          <t>Adoption date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="Q2" s="401" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="R2" s="401" t="inlineStr">
         <is>
-          <t>End date</t>
+          <t>Last revisions</t>
         </is>
       </c>
       <c r="S2" s="401" t="inlineStr">
         <is>
-          <t>Last revisions</t>
+          <t>Last revisions (Details)</t>
         </is>
       </c>
       <c r="T2" s="401" t="inlineStr">
         <is>
-          <t>Last revisions (Details)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="U2" s="401" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="V2" s="401" t="inlineStr">
-        <is>
           <t>Administrating authorities</t>
         </is>
       </c>
+      <c r="V2" s="402" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
       <c r="W2" s="402" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Asset (Status)</t>
         </is>
       </c>
       <c r="X2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Status)</t>
+          <t>Asset (Details)</t>
         </is>
       </c>
       <c r="Y2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Details)</t>
+          <t>Asset (Other)</t>
         </is>
       </c>
       <c r="Z2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Other)</t>
+          <t>Asset (Cut-off range)</t>
         </is>
       </c>
       <c r="AA2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Cut-off range)</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="AB2" s="402" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Agent (Detail)</t>
         </is>
       </c>
       <c r="AC2" s="402" t="inlineStr">
         <is>
-          <t>Agent (Detail)</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="AD2" s="402" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Activity (Details)</t>
         </is>
       </c>
       <c r="AE2" s="402" t="inlineStr">
         <is>
-          <t>Activity (Details)</t>
+          <t>Intensity (Value)</t>
         </is>
       </c>
       <c r="AF2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Value)</t>
+          <t>Intensity (Unit)</t>
         </is>
       </c>
       <c r="AG2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Unit)</t>
+          <t>Intensity (Details)</t>
         </is>
       </c>
       <c r="AH2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Details)</t>
+          <t>Requirement specification</t>
         </is>
       </c>
       <c r="AI2" s="402" t="inlineStr">
         <is>
-          <t>Requirement specification</t>
+          <t>Compliance calculation methodology I</t>
         </is>
       </c>
       <c r="AJ2" s="402" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology I</t>
-        </is>
-      </c>
-      <c r="AK2" s="402" t="inlineStr">
-        <is>
           <t>Compliance calculation methodology II</t>
         </is>
       </c>
+      <c r="AK2" s="403" t="inlineStr">
+        <is>
+          <t>Tax and Tax Incentive: annual revenue</t>
+        </is>
+      </c>
       <c r="AL2" s="403" t="inlineStr">
         <is>
-          <t>Tax and Tax Incentive: annual revenue</t>
+          <t>Tax and Tax Incentive: earmarked revenue</t>
         </is>
       </c>
       <c r="AM2" s="403" t="inlineStr">
         <is>
-          <t>Tax and Tax Incentive: earmarked revenue</t>
+          <t>Tax and Tax Incentive: annual revenue forgone</t>
         </is>
       </c>
       <c r="AN2" s="403" t="inlineStr">
         <is>
-          <t>Tax and Tax Incentive: annual revenue forgone</t>
+          <t>Subsidy: annual budget/ expenditure</t>
         </is>
       </c>
       <c r="AO2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: annual budget/ expenditure</t>
+          <t>Subsidy: Limit</t>
         </is>
       </c>
       <c r="AP2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: Limit</t>
+          <t>Subsidy: Floor or ceiling</t>
         </is>
       </c>
       <c r="AQ2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: Floor or ceiling</t>
+          <t>Subsidy: distribution mechanism</t>
         </is>
       </c>
       <c r="AR2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: distribution mechanism</t>
+          <t>Subsidy: Support duration</t>
         </is>
       </c>
       <c r="AS2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: Support duration</t>
+          <t>Subsidy: Enforcement Mechanism</t>
         </is>
       </c>
       <c r="AT2" s="403" t="inlineStr">
         <is>
-          <t>Subsidy: Enforcement Mechanism</t>
+          <t>Trading System: Type</t>
         </is>
       </c>
       <c r="AU2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: Type</t>
+          <t>Trading System: cap</t>
         </is>
       </c>
       <c r="AV2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: cap</t>
+          <t>Trading System: allowance mechanism</t>
         </is>
       </c>
       <c r="AW2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: allowance mechanism</t>
+          <t>Trading System: Free Allowance</t>
         </is>
       </c>
       <c r="AX2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: Free Allowance</t>
+          <t>Trading System: Offset use allowed</t>
         </is>
       </c>
       <c r="AY2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: Offset use allowed</t>
+          <t>Trading System: Linkages</t>
         </is>
       </c>
       <c r="AZ2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: Linkages</t>
+          <t>Trading System: market stabilisation mechanism</t>
         </is>
       </c>
       <c r="BA2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: market stabilisation mechanism</t>
+          <t>Trading System: revenue (annual)</t>
         </is>
       </c>
       <c r="BB2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: revenue (annual)</t>
+          <t>Trading System: Volume</t>
         </is>
       </c>
       <c r="BC2" s="403" t="inlineStr">
         <is>
-          <t>Trading System: Volume</t>
-        </is>
-      </c>
-      <c r="BD2" s="403" t="inlineStr">
-        <is>
           <t>Trading System: penalties for non-compliance</t>
         </is>
       </c>
+      <c r="BD2" s="404" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (absolute)</t>
+        </is>
+      </c>
       <c r="BE2" s="404" t="inlineStr">
         <is>
-          <t>GHG emission coverage (absolute)</t>
-        </is>
-      </c>
-      <c r="BF2" s="404" t="inlineStr">
-        <is>
           <t>GHG emission coverage (% domestic emissions)</t>
         </is>
       </c>
+      <c r="BF2" s="399" t="inlineStr">
+        <is>
+          <t>Economic sector</t>
+        </is>
+      </c>
       <c r="BG2" s="399" t="inlineStr">
         <is>
-          <t>Economic sector</t>
+          <t>GHGs affected</t>
         </is>
       </c>
       <c r="BH2" s="399" t="inlineStr">
         <is>
-          <t>GHGs affected</t>
-        </is>
-      </c>
-      <c r="BI2" s="399" t="inlineStr">
-        <is>
           <t>Mitigation effects</t>
         </is>
       </c>
-      <c r="BJ2" s="405" t="inlineStr">
+      <c r="BI2" s="405" t="inlineStr">
         <is>
           <t>Mitigation co-benefits</t>
         </is>
       </c>
+      <c r="BJ2" s="401" t="inlineStr">
+        <is>
+          <t>Legal statute</t>
+        </is>
+      </c>
       <c r="BK2" s="401" t="inlineStr">
         <is>
-          <t>Legal statute</t>
+          <t>Legal document</t>
         </is>
       </c>
       <c r="BL2" s="401" t="inlineStr">
         <is>
-          <t>Legal document</t>
-        </is>
-      </c>
-      <c r="BM2" s="401" t="inlineStr">
-        <is>
           <t>Other weblinks</t>
         </is>
       </c>
-      <c r="BN2" s="406" t="n"/>
+      <c r="BM2" s="406" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="BK1:BM1"/>
-    <mergeCell ref="AL1:BD1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="BE1:BF1"/>
-    <mergeCell ref="W1:AK1"/>
+    <mergeCell ref="AK1:BC1"/>
+    <mergeCell ref="BJ1:BL1"/>
+    <mergeCell ref="V1:AJ1"/>
+    <mergeCell ref="BF1:BI1"/>
+    <mergeCell ref="BD1:BE1"/>
+    <mergeCell ref="M1:U1"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="BG1:BJ1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9"/>
@@ -10619,7 +10670,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -10660,12 +10711,12 @@
       <c r="S1" s="228" t="n"/>
       <c r="T1" s="228" t="n"/>
       <c r="U1" s="228" t="n"/>
-      <c r="V1" s="228" t="n"/>
-      <c r="W1" s="411" t="inlineStr">
+      <c r="V1" s="411" t="inlineStr">
         <is>
           <t>Policy regulatory base and intensity</t>
         </is>
       </c>
+      <c r="W1" s="228" t="n"/>
       <c r="X1" s="228" t="n"/>
       <c r="Y1" s="228" t="n"/>
       <c r="Z1" s="228" t="n"/>
@@ -10679,39 +10730,38 @@
       <c r="AH1" s="228" t="n"/>
       <c r="AI1" s="228" t="n"/>
       <c r="AJ1" s="228" t="n"/>
-      <c r="AK1" s="228" t="n"/>
-      <c r="AL1" s="412" t="inlineStr">
+      <c r="AK1" s="412" t="inlineStr">
         <is>
           <t>Instrument-specific attributes</t>
         </is>
       </c>
+      <c r="AL1" s="228" t="n"/>
       <c r="AM1" s="228" t="n"/>
       <c r="AN1" s="228" t="n"/>
       <c r="AO1" s="228" t="n"/>
       <c r="AP1" s="228" t="n"/>
-      <c r="AQ1" s="228" t="n"/>
-      <c r="AR1" s="413" t="inlineStr">
+      <c r="AQ1" s="413" t="inlineStr">
         <is>
           <t>GHG emission base</t>
         </is>
       </c>
-      <c r="AS1" s="229" t="n"/>
-      <c r="AT1" s="414" t="inlineStr">
+      <c r="AR1" s="229" t="n"/>
+      <c r="AS1" s="414" t="inlineStr">
         <is>
           <t>Classification &amp; Indicators</t>
         </is>
       </c>
+      <c r="AT1" s="228" t="n"/>
       <c r="AU1" s="228" t="n"/>
       <c r="AV1" s="228" t="n"/>
-      <c r="AW1" s="228" t="n"/>
-      <c r="AX1" s="415" t="inlineStr">
+      <c r="AW1" s="415" t="inlineStr">
         <is>
           <t>References to legislation</t>
         </is>
       </c>
+      <c r="AX1" s="228" t="n"/>
       <c r="AY1" s="228" t="n"/>
-      <c r="AZ1" s="228" t="n"/>
-      <c r="BA1" s="416" t="n"/>
+      <c r="AZ1" s="416" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="398" t="inlineStr">
@@ -10776,217 +10826,212 @@
       </c>
       <c r="M2" s="419" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Jurisdiction level</t>
         </is>
       </c>
       <c r="N2" s="419" t="inlineStr">
         <is>
-          <t>Jurisdiction level</t>
+          <t>Jurisdiction name</t>
         </is>
       </c>
       <c r="O2" s="419" t="inlineStr">
         <is>
-          <t>Jurisdiction name</t>
+          <t>Adoption date</t>
         </is>
       </c>
       <c r="P2" s="419" t="inlineStr">
         <is>
-          <t>Adoption date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="Q2" s="419" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="R2" s="419" t="inlineStr">
         <is>
-          <t>End date</t>
+          <t>Last revisions</t>
         </is>
       </c>
       <c r="S2" s="419" t="inlineStr">
         <is>
-          <t>Last revisions</t>
+          <t>Last revisions (Details)</t>
         </is>
       </c>
       <c r="T2" s="419" t="inlineStr">
         <is>
-          <t>Last revisions (Details)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="U2" s="419" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="V2" s="419" t="inlineStr">
-        <is>
           <t>Administrating authorities</t>
         </is>
       </c>
+      <c r="V2" s="420" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
       <c r="W2" s="420" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Asset (Status)</t>
         </is>
       </c>
       <c r="X2" s="420" t="inlineStr">
         <is>
-          <t>Asset (Status)</t>
+          <t>Asset (Details)</t>
         </is>
       </c>
       <c r="Y2" s="420" t="inlineStr">
         <is>
-          <t>Asset (Details)</t>
+          <t>Asset (Other)</t>
         </is>
       </c>
       <c r="Z2" s="420" t="inlineStr">
         <is>
-          <t>Asset (Other)</t>
+          <t>Asset (Cut-off range)</t>
         </is>
       </c>
       <c r="AA2" s="420" t="inlineStr">
         <is>
-          <t>Asset (Cut-off range)</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="AB2" s="420" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Agent (Detail)</t>
         </is>
       </c>
       <c r="AC2" s="420" t="inlineStr">
         <is>
-          <t>Agent (Detail)</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="AD2" s="420" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Activity (Details)</t>
         </is>
       </c>
       <c r="AE2" s="420" t="inlineStr">
         <is>
-          <t>Activity (Details)</t>
+          <t>Intensity (Value)</t>
         </is>
       </c>
       <c r="AF2" s="420" t="inlineStr">
         <is>
-          <t>Intensity (Value)</t>
+          <t>Intensity (Unit)</t>
         </is>
       </c>
       <c r="AG2" s="420" t="inlineStr">
         <is>
-          <t>Intensity (Unit)</t>
+          <t>Intensity (Details)</t>
         </is>
       </c>
       <c r="AH2" s="420" t="inlineStr">
         <is>
-          <t>Intensity (Details)</t>
+          <t>Requirement specification</t>
         </is>
       </c>
       <c r="AI2" s="420" t="inlineStr">
         <is>
-          <t>Requirement specification</t>
+          <t>Compliance calculation methodology I</t>
         </is>
       </c>
       <c r="AJ2" s="420" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology I</t>
-        </is>
-      </c>
-      <c r="AK2" s="420" t="inlineStr">
-        <is>
           <t>Compliance calculation methodology II</t>
         </is>
       </c>
+      <c r="AK2" s="418" t="inlineStr">
+        <is>
+          <t>Compliance monitoring</t>
+        </is>
+      </c>
       <c r="AL2" s="418" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
+          <t>Compliance monitoring details</t>
         </is>
       </c>
       <c r="AM2" s="418" t="inlineStr">
         <is>
-          <t>Compliance monitoring details</t>
+          <t>Compliance enforcement</t>
         </is>
       </c>
       <c r="AN2" s="418" t="inlineStr">
         <is>
-          <t>Compliance enforcement</t>
+          <t>Compliance enforcement details</t>
         </is>
       </c>
       <c r="AO2" s="418" t="inlineStr">
         <is>
-          <t>Compliance enforcement details</t>
+          <t>Compliance promotion</t>
         </is>
       </c>
       <c r="AP2" s="418" t="inlineStr">
         <is>
-          <t>Compliance promotion</t>
-        </is>
-      </c>
-      <c r="AQ2" s="418" t="inlineStr">
-        <is>
           <t>Compliance promotion detail</t>
         </is>
       </c>
+      <c r="AQ2" s="421" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (absolute)</t>
+        </is>
+      </c>
       <c r="AR2" s="421" t="inlineStr">
         <is>
-          <t>GHG emission coverage (absolute)</t>
-        </is>
-      </c>
-      <c r="AS2" s="421" t="inlineStr">
-        <is>
           <t>GHG emission coverage (% domestic emissions)</t>
         </is>
       </c>
+      <c r="AS2" s="422" t="inlineStr">
+        <is>
+          <t>Economic sector</t>
+        </is>
+      </c>
       <c r="AT2" s="422" t="inlineStr">
         <is>
-          <t>Economic sector</t>
+          <t>GHGs affected</t>
         </is>
       </c>
       <c r="AU2" s="422" t="inlineStr">
         <is>
-          <t>GHGs affected</t>
+          <t>Mitigation effects</t>
         </is>
       </c>
       <c r="AV2" s="422" t="inlineStr">
         <is>
-          <t>Mitigation effects</t>
-        </is>
-      </c>
-      <c r="AW2" s="422" t="inlineStr">
-        <is>
           <t>Mitigation co-benefits</t>
         </is>
       </c>
+      <c r="AW2" s="423" t="inlineStr">
+        <is>
+          <t>Legal statute</t>
+        </is>
+      </c>
       <c r="AX2" s="423" t="inlineStr">
         <is>
-          <t>Legal statute</t>
+          <t>Legal document</t>
         </is>
       </c>
       <c r="AY2" s="423" t="inlineStr">
         <is>
-          <t>Legal document</t>
-        </is>
-      </c>
-      <c r="AZ2" s="423" t="inlineStr">
-        <is>
           <t>Other weblinks</t>
         </is>
       </c>
-      <c r="BA2" s="406" t="n"/>
+      <c r="AZ2" s="406" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="AX1:AZ1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="AL1:AQ1"/>
-    <mergeCell ref="W1:AK1"/>
-    <mergeCell ref="AR1:AS1"/>
+    <mergeCell ref="V1:AJ1"/>
+    <mergeCell ref="AK1:AP1"/>
+    <mergeCell ref="AW1:AY1"/>
+    <mergeCell ref="M1:U1"/>
     <mergeCell ref="C1:F1"/>
+    <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="AT1:AW1"/>
+    <mergeCell ref="AS1:AV1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -10998,7 +11043,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BC2"/>
+  <dimension ref="A1:BB2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
@@ -11039,12 +11084,12 @@
       <c r="S1" s="100" t="n"/>
       <c r="T1" s="100" t="n"/>
       <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="427" t="inlineStr">
+      <c r="V1" s="427" t="inlineStr">
         <is>
           <t>Policy regulatory base and intensity</t>
         </is>
       </c>
+      <c r="W1" s="100" t="n"/>
       <c r="X1" s="100" t="n"/>
       <c r="Y1" s="100" t="n"/>
       <c r="Z1" s="100" t="n"/>
@@ -11058,41 +11103,40 @@
       <c r="AH1" s="100" t="n"/>
       <c r="AI1" s="100" t="n"/>
       <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="393" t="inlineStr">
+      <c r="AK1" s="393" t="inlineStr">
         <is>
           <t>Instrument-specific attributes</t>
         </is>
       </c>
+      <c r="AL1" s="100" t="n"/>
       <c r="AM1" s="100" t="n"/>
       <c r="AN1" s="100" t="n"/>
       <c r="AO1" s="100" t="n"/>
       <c r="AP1" s="100" t="n"/>
       <c r="AQ1" s="100" t="n"/>
       <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="428" t="inlineStr">
+      <c r="AS1" s="428" t="inlineStr">
         <is>
           <t>GHG emission base</t>
         </is>
       </c>
-      <c r="AU1" s="101" t="n"/>
-      <c r="AV1" s="395" t="inlineStr">
+      <c r="AT1" s="101" t="n"/>
+      <c r="AU1" s="395" t="inlineStr">
         <is>
           <t>Classifications &amp; Indicators</t>
         </is>
       </c>
+      <c r="AV1" s="100" t="n"/>
       <c r="AW1" s="100" t="n"/>
       <c r="AX1" s="100" t="n"/>
-      <c r="AY1" s="100" t="n"/>
-      <c r="AZ1" s="426" t="inlineStr">
+      <c r="AY1" s="426" t="inlineStr">
         <is>
           <t>References to legislation</t>
         </is>
       </c>
+      <c r="AZ1" s="100" t="n"/>
       <c r="BA1" s="100" t="n"/>
-      <c r="BB1" s="100" t="n"/>
-      <c r="BC1" s="429" t="n"/>
+      <c r="BB1" s="429" t="n"/>
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="398" t="inlineStr">
@@ -11157,227 +11201,222 @@
       </c>
       <c r="M2" s="401" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Jurisdiction level</t>
         </is>
       </c>
       <c r="N2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction level</t>
+          <t>Jurisdiction name</t>
         </is>
       </c>
       <c r="O2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction name</t>
+          <t>Adoption date</t>
         </is>
       </c>
       <c r="P2" s="401" t="inlineStr">
         <is>
-          <t>Adoption date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="Q2" s="401" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="R2" s="401" t="inlineStr">
         <is>
-          <t>End date</t>
+          <t>Last revisions</t>
         </is>
       </c>
       <c r="S2" s="401" t="inlineStr">
         <is>
-          <t>Last revisions</t>
+          <t>Last revisions (Details)</t>
         </is>
       </c>
       <c r="T2" s="401" t="inlineStr">
         <is>
-          <t>Last revisions (Details)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="U2" s="401" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="V2" s="401" t="inlineStr">
-        <is>
           <t>Administrating authorities</t>
         </is>
       </c>
+      <c r="V2" s="402" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
       <c r="W2" s="402" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Asset (Status)</t>
         </is>
       </c>
       <c r="X2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Status)</t>
+          <t>Asset (Details)</t>
         </is>
       </c>
       <c r="Y2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Details)</t>
+          <t>Asset (Other)</t>
         </is>
       </c>
       <c r="Z2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Other)</t>
+          <t>Asset (Cut-off range)</t>
         </is>
       </c>
       <c r="AA2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Cut-off range)</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="AB2" s="402" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Agent (Detail)</t>
         </is>
       </c>
       <c r="AC2" s="402" t="inlineStr">
         <is>
-          <t>Agent (Detail)</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="AD2" s="402" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Activity (Details)</t>
         </is>
       </c>
       <c r="AE2" s="402" t="inlineStr">
         <is>
-          <t>Activity (Details)</t>
+          <t>Intensity (Value)</t>
         </is>
       </c>
       <c r="AF2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Value)</t>
+          <t>Intensity (Unit)</t>
         </is>
       </c>
       <c r="AG2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Unit)</t>
+          <t>Intensity (Details)</t>
         </is>
       </c>
       <c r="AH2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Details)</t>
+          <t>Requirement specification</t>
         </is>
       </c>
       <c r="AI2" s="402" t="inlineStr">
         <is>
-          <t>Requirement specification</t>
+          <t>Compliance calculation methodology I</t>
         </is>
       </c>
       <c r="AJ2" s="402" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology I</t>
-        </is>
-      </c>
-      <c r="AK2" s="402" t="inlineStr">
-        <is>
           <t>Compliance calculation methodology II</t>
         </is>
       </c>
+      <c r="AK2" s="403" t="inlineStr">
+        <is>
+          <t>Public investment: Co-financing</t>
+        </is>
+      </c>
       <c r="AL2" s="403" t="inlineStr">
         <is>
-          <t>Public investment: Co-financing</t>
+          <t>Public investment: Selection process</t>
         </is>
       </c>
       <c r="AM2" s="403" t="inlineStr">
         <is>
-          <t>Public investment: Selection process</t>
+          <t>Public procurement: Tender process</t>
         </is>
       </c>
       <c r="AN2" s="403" t="inlineStr">
         <is>
-          <t>Public procurement: Tender process</t>
+          <t>Public procurement: Award criteria tender process</t>
         </is>
       </c>
       <c r="AO2" s="403" t="inlineStr">
         <is>
-          <t>Public procurement: Award criteria tender process</t>
+          <t>Public procurement: Compliance monitoring</t>
         </is>
       </c>
       <c r="AP2" s="403" t="inlineStr">
         <is>
-          <t>Public procurement: Compliance monitoring</t>
+          <t>Public procurement: Compliance enforcement</t>
         </is>
       </c>
       <c r="AQ2" s="403" t="inlineStr">
         <is>
-          <t>Public procurement: Compliance enforcement</t>
+          <t>Public procurement: Life-cycle costing</t>
         </is>
       </c>
       <c r="AR2" s="403" t="inlineStr">
         <is>
-          <t>Public procurement: Life-cycle costing</t>
-        </is>
-      </c>
-      <c r="AS2" s="403" t="inlineStr">
-        <is>
           <t>Public investment/procurement: Annual expenditure</t>
         </is>
       </c>
+      <c r="AS2" s="404" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (absolute)</t>
+        </is>
+      </c>
       <c r="AT2" s="404" t="inlineStr">
         <is>
-          <t>GHG emission coverage (absolute)</t>
-        </is>
-      </c>
-      <c r="AU2" s="404" t="inlineStr">
-        <is>
           <t>GHG emission coverage (% domestic emissions)</t>
         </is>
       </c>
+      <c r="AU2" s="430" t="inlineStr">
+        <is>
+          <t>Economic sector</t>
+        </is>
+      </c>
       <c r="AV2" s="430" t="inlineStr">
         <is>
-          <t>Economic sector</t>
+          <t>GHGs affected</t>
         </is>
       </c>
       <c r="AW2" s="430" t="inlineStr">
         <is>
-          <t>GHGs affected</t>
+          <t>Mitigation effect</t>
         </is>
       </c>
       <c r="AX2" s="430" t="inlineStr">
         <is>
-          <t>Mitigation effect</t>
-        </is>
-      </c>
-      <c r="AY2" s="430" t="inlineStr">
-        <is>
           <t>Mitigation co-benefits</t>
         </is>
       </c>
+      <c r="AY2" s="401" t="inlineStr">
+        <is>
+          <t>Legal statute</t>
+        </is>
+      </c>
       <c r="AZ2" s="401" t="inlineStr">
         <is>
-          <t>Legal statute</t>
+          <t>Legal document</t>
         </is>
       </c>
       <c r="BA2" s="401" t="inlineStr">
         <is>
-          <t>Legal document</t>
-        </is>
-      </c>
-      <c r="BB2" s="401" t="inlineStr">
-        <is>
           <t>Other weblinks</t>
         </is>
       </c>
-      <c r="BC2" s="406" t="n"/>
+      <c r="BB2" s="406" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="AZ1:BB1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="W1:AK1"/>
-    <mergeCell ref="AV1:AY1"/>
+    <mergeCell ref="AU1:AX1"/>
+    <mergeCell ref="V1:AJ1"/>
+    <mergeCell ref="AY1:BA1"/>
+    <mergeCell ref="M1:U1"/>
     <mergeCell ref="C1:F1"/>
-    <mergeCell ref="AT1:AU1"/>
+    <mergeCell ref="AS1:AT1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="AL1:AS1"/>
+    <mergeCell ref="AK1:AR1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11389,7 +11428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD2"/>
+  <dimension ref="A1:BC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
   <cols>
     <col width="20" customWidth="1" min="46" max="46"/>
@@ -11434,12 +11473,12 @@
       <c r="S1" s="100" t="n"/>
       <c r="T1" s="100" t="n"/>
       <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="432" t="inlineStr">
+      <c r="V1" s="432" t="inlineStr">
         <is>
           <t>Policy regulatory base and intensity</t>
         </is>
       </c>
+      <c r="W1" s="100" t="n"/>
       <c r="X1" s="100" t="n"/>
       <c r="Y1" s="100" t="n"/>
       <c r="Z1" s="100" t="n"/>
@@ -11453,12 +11492,12 @@
       <c r="AH1" s="100" t="n"/>
       <c r="AI1" s="100" t="n"/>
       <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="433" t="inlineStr">
+      <c r="AK1" s="433" t="inlineStr">
         <is>
           <t>Instrument-specific attributes</t>
         </is>
       </c>
+      <c r="AL1" s="392" t="n"/>
       <c r="AM1" s="392" t="n"/>
       <c r="AN1" s="392" t="n"/>
       <c r="AO1" s="392" t="n"/>
@@ -11467,19 +11506,18 @@
       <c r="AR1" s="392" t="n"/>
       <c r="AS1" s="392" t="n"/>
       <c r="AT1" s="392" t="n"/>
-      <c r="AU1" s="392" t="n"/>
-      <c r="AV1" s="438" t="inlineStr">
+      <c r="AU1" s="438" t="inlineStr">
         <is>
           <t>GHG emission base</t>
         </is>
       </c>
-      <c r="AW1" s="100" t="n"/>
-      <c r="AX1" s="439" t="inlineStr">
+      <c r="AV1" s="100" t="n"/>
+      <c r="AW1" s="439" t="inlineStr">
         <is>
           <t>Classifications &amp; Indicators</t>
         </is>
       </c>
-      <c r="BB1" s="440" t="inlineStr">
+      <c r="BA1" s="440" t="inlineStr">
         <is>
           <t>References to legislation</t>
         </is>
@@ -11548,220 +11586,215 @@
       </c>
       <c r="M2" s="401" t="inlineStr">
         <is>
-          <t>Country</t>
+          <t>Jurisdiction level</t>
         </is>
       </c>
       <c r="N2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction level</t>
+          <t>Jurisdiction name</t>
         </is>
       </c>
       <c r="O2" s="401" t="inlineStr">
         <is>
-          <t>Jurisdiction name</t>
+          <t>Adoption date</t>
         </is>
       </c>
       <c r="P2" s="401" t="inlineStr">
         <is>
-          <t>Adoption date</t>
+          <t>Start date</t>
         </is>
       </c>
       <c r="Q2" s="401" t="inlineStr">
         <is>
-          <t>Start date</t>
+          <t>End date</t>
         </is>
       </c>
       <c r="R2" s="401" t="inlineStr">
         <is>
-          <t>End date</t>
+          <t>Last revision</t>
         </is>
       </c>
       <c r="S2" s="401" t="inlineStr">
         <is>
-          <t>Last revision</t>
+          <t>Last revision (Details)</t>
         </is>
       </c>
       <c r="T2" s="401" t="inlineStr">
         <is>
-          <t>Last revision (Details)</t>
+          <t>Status</t>
         </is>
       </c>
       <c r="U2" s="401" t="inlineStr">
         <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="V2" s="401" t="inlineStr">
-        <is>
           <t>Administrating authorities</t>
         </is>
       </c>
+      <c r="V2" s="402" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
       <c r="W2" s="402" t="inlineStr">
         <is>
-          <t>Asset</t>
+          <t>Asset (Status)</t>
         </is>
       </c>
       <c r="X2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Status)</t>
+          <t>Asset (Details)</t>
         </is>
       </c>
       <c r="Y2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Details)</t>
+          <t>Asset (Other)</t>
         </is>
       </c>
       <c r="Z2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Other)</t>
+          <t>Asset (Cut-off range)</t>
         </is>
       </c>
       <c r="AA2" s="402" t="inlineStr">
         <is>
-          <t>Asset (Cut-off range)</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="AB2" s="402" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>Agent (Detail)</t>
         </is>
       </c>
       <c r="AC2" s="402" t="inlineStr">
         <is>
-          <t>Agent (Detail)</t>
+          <t>Activity</t>
         </is>
       </c>
       <c r="AD2" s="402" t="inlineStr">
         <is>
-          <t>Activity</t>
+          <t>Activity (Details)</t>
         </is>
       </c>
       <c r="AE2" s="402" t="inlineStr">
         <is>
-          <t>Activity (Details)</t>
+          <t>Intensity (Value)</t>
         </is>
       </c>
       <c r="AF2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Value)</t>
+          <t>Intensity (Unit)</t>
         </is>
       </c>
       <c r="AG2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Unit)</t>
+          <t>Intensity (Details)</t>
         </is>
       </c>
       <c r="AH2" s="402" t="inlineStr">
         <is>
-          <t>Intensity (Details)</t>
+          <t>Requirement specification</t>
         </is>
       </c>
       <c r="AI2" s="402" t="inlineStr">
         <is>
-          <t>Requirement specification</t>
+          <t>Compliance calculation methodology I</t>
         </is>
       </c>
       <c r="AJ2" s="402" t="inlineStr">
         <is>
-          <t>Compliance calculation methodology I</t>
-        </is>
-      </c>
-      <c r="AK2" s="402" t="inlineStr">
-        <is>
           <t>Compliance calculation methodology II</t>
         </is>
       </c>
+      <c r="AK2" s="403" t="inlineStr">
+        <is>
+          <t>Instrument linkage</t>
+        </is>
+      </c>
       <c r="AL2" s="403" t="inlineStr">
         <is>
-          <t>Instrument linkage</t>
+          <t>Responsibility information capturing</t>
         </is>
       </c>
       <c r="AM2" s="403" t="inlineStr">
         <is>
-          <t>Responsibility information capturing</t>
+          <t>Information transmission</t>
         </is>
       </c>
       <c r="AN2" s="403" t="inlineStr">
         <is>
-          <t>Information transmission</t>
+          <t>Frequency of information provision</t>
         </is>
       </c>
       <c r="AO2" s="403" t="inlineStr">
         <is>
-          <t>Frequency of information provision</t>
+          <t>Public availability of information</t>
         </is>
       </c>
       <c r="AP2" s="403" t="inlineStr">
         <is>
-          <t>Public availability of information</t>
+          <t>For labels: Type</t>
         </is>
       </c>
       <c r="AQ2" s="403" t="inlineStr">
         <is>
-          <t>For labels: Type</t>
+          <t>Compliance monitoring</t>
         </is>
       </c>
       <c r="AR2" s="403" t="inlineStr">
         <is>
-          <t>Compliance monitoring</t>
-        </is>
-      </c>
-      <c r="AS2" s="403" t="inlineStr">
-        <is>
           <t>Compliance enforcement</t>
         </is>
       </c>
-      <c r="AT2" s="436" t="inlineStr">
+      <c r="AS2" s="436" t="inlineStr">
         <is>
           <t>Compliance promotion</t>
         </is>
       </c>
-      <c r="AU2" s="403" t="inlineStr">
+      <c r="AT2" s="403" t="inlineStr">
         <is>
           <t>Details on capacity building, training/education, information campaigns and award schemes</t>
         </is>
       </c>
+      <c r="AU2" s="437" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (absolute)</t>
+        </is>
+      </c>
       <c r="AV2" s="437" t="inlineStr">
         <is>
-          <t>GHG emission coverage (absolute)</t>
-        </is>
-      </c>
-      <c r="AW2" s="437" t="inlineStr">
-        <is>
           <t>GHG emission coverage (% domestic emissions)</t>
         </is>
       </c>
+      <c r="AW2" s="399" t="inlineStr">
+        <is>
+          <t>Economic sector</t>
+        </is>
+      </c>
       <c r="AX2" s="399" t="inlineStr">
         <is>
-          <t>Economic sector</t>
+          <t>GHGs affected</t>
         </is>
       </c>
       <c r="AY2" s="399" t="inlineStr">
         <is>
-          <t>GHGs affected</t>
+          <t>Mitigation effect</t>
         </is>
       </c>
       <c r="AZ2" s="399" t="inlineStr">
         <is>
-          <t>Mitigation effect</t>
-        </is>
-      </c>
-      <c r="BA2" s="399" t="inlineStr">
-        <is>
           <t>Mitigation co-benefits</t>
         </is>
       </c>
+      <c r="BA2" s="401" t="inlineStr">
+        <is>
+          <t>Legal statute</t>
+        </is>
+      </c>
       <c r="BB2" s="401" t="inlineStr">
         <is>
-          <t>Legal statute</t>
+          <t>Legal document</t>
         </is>
       </c>
       <c r="BC2" s="401" t="inlineStr">
-        <is>
-          <t>Legal document</t>
-        </is>
-      </c>
-      <c r="BD2" s="401" t="inlineStr">
         <is>
           <t>Other weblinks</t>
         </is>
@@ -11769,382 +11802,21 @@
     </row>
   </sheetData>
   <mergeCells count="9">
+    <mergeCell ref="AK1:AT1"/>
     <mergeCell ref="G1:L1"/>
-    <mergeCell ref="AL1:AU1"/>
-    <mergeCell ref="BB1:BD1"/>
-    <mergeCell ref="AV1:AW1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="W1:AK1"/>
+    <mergeCell ref="AW1:AZ1"/>
+    <mergeCell ref="BA1:BC1"/>
+    <mergeCell ref="V1:AJ1"/>
+    <mergeCell ref="M1:U1"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="A1:B1"/>
-    <mergeCell ref="AX1:BA1"/>
+    <mergeCell ref="AU1:AV1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AX2"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
-  <sheetData>
-    <row r="1" ht="15.75" customHeight="1">
-      <c r="A1" s="387" t="inlineStr">
-        <is>
-          <t>Identification</t>
-        </is>
-      </c>
-      <c r="B1" s="93" t="n"/>
-      <c r="C1" s="424" t="inlineStr">
-        <is>
-          <t>Instrument typology</t>
-        </is>
-      </c>
-      <c r="D1" s="100" t="n"/>
-      <c r="E1" s="100" t="n"/>
-      <c r="F1" s="101" t="n"/>
-      <c r="G1" s="425" t="inlineStr">
-        <is>
-          <t>Policy Description</t>
-        </is>
-      </c>
-      <c r="H1" s="100" t="n"/>
-      <c r="I1" s="100" t="n"/>
-      <c r="J1" s="100" t="n"/>
-      <c r="K1" s="100" t="n"/>
-      <c r="L1" s="100" t="n"/>
-      <c r="M1" s="426" t="inlineStr">
-        <is>
-          <t>Administrative information</t>
-        </is>
-      </c>
-      <c r="N1" s="100" t="n"/>
-      <c r="O1" s="100" t="n"/>
-      <c r="P1" s="100" t="n"/>
-      <c r="Q1" s="100" t="n"/>
-      <c r="R1" s="100" t="n"/>
-      <c r="S1" s="100" t="n"/>
-      <c r="T1" s="100" t="n"/>
-      <c r="U1" s="100" t="n"/>
-      <c r="V1" s="100" t="n"/>
-      <c r="W1" s="427" t="inlineStr">
-        <is>
-          <t>Policy regulatory base and intensity</t>
-        </is>
-      </c>
-      <c r="X1" s="100" t="n"/>
-      <c r="Y1" s="100" t="n"/>
-      <c r="Z1" s="100" t="n"/>
-      <c r="AA1" s="100" t="n"/>
-      <c r="AB1" s="100" t="n"/>
-      <c r="AC1" s="100" t="n"/>
-      <c r="AD1" s="100" t="n"/>
-      <c r="AE1" s="100" t="n"/>
-      <c r="AF1" s="100" t="n"/>
-      <c r="AG1" s="100" t="n"/>
-      <c r="AH1" s="100" t="n"/>
-      <c r="AI1" s="100" t="n"/>
-      <c r="AJ1" s="100" t="n"/>
-      <c r="AK1" s="100" t="n"/>
-      <c r="AL1" s="393" t="inlineStr">
-        <is>
-          <t>Instrument-specific attributes</t>
-        </is>
-      </c>
-      <c r="AM1" s="100" t="n"/>
-      <c r="AN1" s="100" t="n"/>
-      <c r="AO1" s="428" t="inlineStr">
-        <is>
-          <t>GHG emission base</t>
-        </is>
-      </c>
-      <c r="AP1" s="101" t="n"/>
-      <c r="AQ1" s="395" t="inlineStr">
-        <is>
-          <t>Classifications &amp; Indicators</t>
-        </is>
-      </c>
-      <c r="AR1" s="100" t="n"/>
-      <c r="AS1" s="100" t="n"/>
-      <c r="AT1" s="100" t="n"/>
-      <c r="AU1" s="426" t="inlineStr">
-        <is>
-          <t>References to legislation</t>
-        </is>
-      </c>
-      <c r="AV1" s="100" t="n"/>
-      <c r="AW1" s="100" t="n"/>
-      <c r="AX1" s="429" t="n"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="398" t="inlineStr">
-        <is>
-          <t>Policy Instrument ID</t>
-        </is>
-      </c>
-      <c r="B2" s="398" t="inlineStr">
-        <is>
-          <t>Instrument / subscheme</t>
-        </is>
-      </c>
-      <c r="C2" s="399" t="inlineStr">
-        <is>
-          <t>Group</t>
-        </is>
-      </c>
-      <c r="D2" s="399" t="inlineStr">
-        <is>
-          <t>Approach</t>
-        </is>
-      </c>
-      <c r="E2" s="399" t="inlineStr">
-        <is>
-          <t>Emission sector</t>
-        </is>
-      </c>
-      <c r="F2" s="399" t="inlineStr">
-        <is>
-          <t>Sub-sector</t>
-        </is>
-      </c>
-      <c r="G2" s="400" t="inlineStr">
-        <is>
-          <t>Domestic instrument name</t>
-        </is>
-      </c>
-      <c r="H2" s="400" t="inlineStr">
-        <is>
-          <t>English instrument name</t>
-        </is>
-      </c>
-      <c r="I2" s="400" t="inlineStr">
-        <is>
-          <t>Policy Package</t>
-        </is>
-      </c>
-      <c r="J2" s="400" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="K2" s="400" t="inlineStr">
-        <is>
-          <t>Objective</t>
-        </is>
-      </c>
-      <c r="L2" s="400" t="inlineStr">
-        <is>
-          <t>Mitigation relevance</t>
-        </is>
-      </c>
-      <c r="M2" s="401" t="inlineStr">
-        <is>
-          <t>Country</t>
-        </is>
-      </c>
-      <c r="N2" s="401" t="inlineStr">
-        <is>
-          <t>Jurisdiction level</t>
-        </is>
-      </c>
-      <c r="O2" s="401" t="inlineStr">
-        <is>
-          <t>Jurisdiction name</t>
-        </is>
-      </c>
-      <c r="P2" s="401" t="inlineStr">
-        <is>
-          <t>Adoption date</t>
-        </is>
-      </c>
-      <c r="Q2" s="401" t="inlineStr">
-        <is>
-          <t>Start date</t>
-        </is>
-      </c>
-      <c r="R2" s="401" t="inlineStr">
-        <is>
-          <t>End date</t>
-        </is>
-      </c>
-      <c r="S2" s="401" t="inlineStr">
-        <is>
-          <t>Last revisions</t>
-        </is>
-      </c>
-      <c r="T2" s="401" t="inlineStr">
-        <is>
-          <t>Last revisions (Details)</t>
-        </is>
-      </c>
-      <c r="U2" s="401" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="V2" s="401" t="inlineStr">
-        <is>
-          <t>Administrating authorities</t>
-        </is>
-      </c>
-      <c r="W2" s="402" t="inlineStr">
-        <is>
-          <t>Asset</t>
-        </is>
-      </c>
-      <c r="X2" s="402" t="inlineStr">
-        <is>
-          <t>Asset (Status)</t>
-        </is>
-      </c>
-      <c r="Y2" s="402" t="inlineStr">
-        <is>
-          <t>Asset (Details)</t>
-        </is>
-      </c>
-      <c r="Z2" s="402" t="inlineStr">
-        <is>
-          <t>Asset (Other)</t>
-        </is>
-      </c>
-      <c r="AA2" s="402" t="inlineStr">
-        <is>
-          <t>Asset (Cut-off range)</t>
-        </is>
-      </c>
-      <c r="AB2" s="402" t="inlineStr">
-        <is>
-          <t>Agent</t>
-        </is>
-      </c>
-      <c r="AC2" s="402" t="inlineStr">
-        <is>
-          <t>Agent (Detail)</t>
-        </is>
-      </c>
-      <c r="AD2" s="402" t="inlineStr">
-        <is>
-          <t>Activity</t>
-        </is>
-      </c>
-      <c r="AE2" s="402" t="inlineStr">
-        <is>
-          <t>Activity (Details)</t>
-        </is>
-      </c>
-      <c r="AF2" s="402" t="inlineStr">
-        <is>
-          <t>Intensity (Value)</t>
-        </is>
-      </c>
-      <c r="AG2" s="402" t="inlineStr">
-        <is>
-          <t>Intensity (Unit)</t>
-        </is>
-      </c>
-      <c r="AH2" s="402" t="inlineStr">
-        <is>
-          <t>Intensity (Details)</t>
-        </is>
-      </c>
-      <c r="AI2" s="402" t="inlineStr">
-        <is>
-          <t>Requirement specification</t>
-        </is>
-      </c>
-      <c r="AJ2" s="402" t="inlineStr">
-        <is>
-          <t>Compliance calculation methodology I</t>
-        </is>
-      </c>
-      <c r="AK2" s="402" t="inlineStr">
-        <is>
-          <t>Compliance calculation methodology II</t>
-        </is>
-      </c>
-      <c r="AL2" s="400" t="inlineStr">
-        <is>
-          <t>Incentives for Participation</t>
-        </is>
-      </c>
-      <c r="AM2" s="400" t="inlineStr">
-        <is>
-          <t>Monitoring</t>
-        </is>
-      </c>
-      <c r="AN2" s="400" t="inlineStr">
-        <is>
-          <t>Sanctions for non-compliance</t>
-        </is>
-      </c>
-      <c r="AO2" s="404" t="inlineStr">
-        <is>
-          <t>GHG emission coverage (absolute)</t>
-        </is>
-      </c>
-      <c r="AP2" s="404" t="inlineStr">
-        <is>
-          <t>GHG emission coverage (% domestic emissions)</t>
-        </is>
-      </c>
-      <c r="AQ2" s="399" t="inlineStr">
-        <is>
-          <t>Economic sector</t>
-        </is>
-      </c>
-      <c r="AR2" s="399" t="inlineStr">
-        <is>
-          <t>GHGs affected</t>
-        </is>
-      </c>
-      <c r="AS2" s="399" t="inlineStr">
-        <is>
-          <t>Mitigation effect</t>
-        </is>
-      </c>
-      <c r="AT2" s="399" t="inlineStr">
-        <is>
-          <t>Mitigation co-benefits</t>
-        </is>
-      </c>
-      <c r="AU2" s="401" t="inlineStr">
-        <is>
-          <t>Legal statute</t>
-        </is>
-      </c>
-      <c r="AV2" s="401" t="inlineStr">
-        <is>
-          <t>Legal document</t>
-        </is>
-      </c>
-      <c r="AW2" s="401" t="inlineStr">
-        <is>
-          <t>Other weblinks</t>
-        </is>
-      </c>
-      <c r="AX2" s="406" t="n"/>
-    </row>
-  </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="AQ1:AT1"/>
-    <mergeCell ref="G1:L1"/>
-    <mergeCell ref="AL1:AN1"/>
-    <mergeCell ref="M1:V1"/>
-    <mergeCell ref="AU1:AW1"/>
-    <mergeCell ref="W1:AK1"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12160,7 +11832,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="26.25" customHeight="1">
-      <c r="A1" s="519" t="inlineStr">
+      <c r="A1" s="530" t="inlineStr">
         <is>
           <t>China Climate Policy Instrument Database (CCPID)</t>
         </is>
@@ -12172,137 +11844,137 @@
       <c r="F1" s="109" t="n"/>
       <c r="G1" s="109" t="n"/>
       <c r="H1" s="110" t="n"/>
-      <c r="I1" s="522" t="n"/>
-      <c r="J1" s="522" t="n"/>
-      <c r="K1" s="523" t="n"/>
-      <c r="L1" s="522" t="n"/>
-      <c r="M1" s="522" t="n"/>
-      <c r="N1" s="522" t="n"/>
-      <c r="O1" s="522" t="n"/>
-      <c r="P1" s="524" t="n"/>
-      <c r="Q1" s="524" t="n"/>
-      <c r="R1" s="524" t="n"/>
-      <c r="S1" s="524" t="n"/>
+      <c r="I1" s="531" t="n"/>
+      <c r="J1" s="531" t="n"/>
+      <c r="K1" s="532" t="n"/>
+      <c r="L1" s="531" t="n"/>
+      <c r="M1" s="531" t="n"/>
+      <c r="N1" s="531" t="n"/>
+      <c r="O1" s="531" t="n"/>
+      <c r="P1" s="533" t="n"/>
+      <c r="Q1" s="533" t="n"/>
+      <c r="R1" s="533" t="n"/>
+      <c r="S1" s="533" t="n"/>
     </row>
     <row r="2">
-      <c r="A2" s="471" t="n"/>
-      <c r="B2" s="471" t="n"/>
-      <c r="C2" s="471" t="n"/>
-      <c r="D2" s="471" t="n"/>
-      <c r="E2" s="471" t="n"/>
-      <c r="F2" s="471" t="n"/>
-      <c r="G2" s="471" t="n"/>
-      <c r="H2" s="471" t="n"/>
-      <c r="I2" s="471" t="n"/>
-      <c r="J2" s="471" t="n"/>
-      <c r="K2" s="471" t="n"/>
-      <c r="L2" s="471" t="n"/>
-      <c r="M2" s="471" t="n"/>
-      <c r="N2" s="471" t="n"/>
-      <c r="O2" s="471" t="n"/>
-      <c r="P2" s="473" t="n"/>
-      <c r="Q2" s="473" t="n"/>
-      <c r="R2" s="473" t="n"/>
-      <c r="S2" s="473" t="n"/>
+      <c r="A2" s="534" t="n"/>
+      <c r="B2" s="534" t="n"/>
+      <c r="C2" s="534" t="n"/>
+      <c r="D2" s="534" t="n"/>
+      <c r="E2" s="534" t="n"/>
+      <c r="F2" s="534" t="n"/>
+      <c r="G2" s="534" t="n"/>
+      <c r="H2" s="534" t="n"/>
+      <c r="I2" s="534" t="n"/>
+      <c r="J2" s="534" t="n"/>
+      <c r="K2" s="534" t="n"/>
+      <c r="L2" s="534" t="n"/>
+      <c r="M2" s="534" t="n"/>
+      <c r="N2" s="534" t="n"/>
+      <c r="O2" s="534" t="n"/>
+      <c r="P2" s="499" t="n"/>
+      <c r="Q2" s="499" t="n"/>
+      <c r="R2" s="499" t="n"/>
+      <c r="S2" s="499" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="474" t="inlineStr">
+      <c r="A3" s="535" t="inlineStr">
         <is>
           <t>developed by MGF Lab, National School of Development, Peking University</t>
         </is>
       </c>
-      <c r="B3" s="109" t="n"/>
-      <c r="C3" s="110" t="n"/>
-      <c r="D3" s="471" t="n"/>
-      <c r="E3" s="471" t="n"/>
-      <c r="F3" s="471" t="n"/>
-      <c r="G3" s="471" t="n"/>
-      <c r="H3" s="471" t="n"/>
-      <c r="I3" s="471" t="n"/>
-      <c r="J3" s="471" t="n"/>
-      <c r="K3" s="471" t="n"/>
-      <c r="L3" s="471" t="n"/>
-      <c r="M3" s="471" t="n"/>
-      <c r="N3" s="471" t="n"/>
-      <c r="O3" s="471" t="n"/>
-      <c r="P3" s="473" t="n"/>
-      <c r="Q3" s="473" t="n"/>
-      <c r="R3" s="473" t="n"/>
-      <c r="S3" s="473" t="n"/>
+      <c r="B3" s="536" t="n"/>
+      <c r="C3" s="536" t="n"/>
+      <c r="D3" s="536" t="n"/>
+      <c r="E3" s="536" t="n"/>
+      <c r="F3" s="536" t="n"/>
+      <c r="G3" s="537" t="n"/>
+      <c r="H3" s="534" t="n"/>
+      <c r="I3" s="534" t="n"/>
+      <c r="J3" s="534" t="n"/>
+      <c r="K3" s="534" t="n"/>
+      <c r="L3" s="534" t="n"/>
+      <c r="M3" s="534" t="n"/>
+      <c r="N3" s="534" t="n"/>
+      <c r="O3" s="534" t="n"/>
+      <c r="P3" s="499" t="n"/>
+      <c r="Q3" s="499" t="n"/>
+      <c r="R3" s="499" t="n"/>
+      <c r="S3" s="499" t="n"/>
     </row>
     <row r="4">
-      <c r="A4" s="474" t="inlineStr">
-        <is>
-          <t>as of August 2026</t>
+      <c r="A4" s="538" t="inlineStr">
+        <is>
+          <t>as of September 2026</t>
         </is>
       </c>
       <c r="B4" s="110" t="n"/>
-      <c r="C4" s="471" t="n"/>
-      <c r="D4" s="471" t="n"/>
-      <c r="E4" s="471" t="n"/>
-      <c r="F4" s="471" t="n"/>
-      <c r="G4" s="471" t="n"/>
-      <c r="H4" s="471" t="n"/>
-      <c r="I4" s="471" t="n"/>
-      <c r="J4" s="471" t="n"/>
-      <c r="K4" s="471" t="n"/>
-      <c r="L4" s="471" t="n"/>
-      <c r="M4" s="471" t="n"/>
-      <c r="N4" s="471" t="n"/>
-      <c r="O4" s="471" t="n"/>
-      <c r="P4" s="473" t="n"/>
-      <c r="Q4" s="473" t="n"/>
-      <c r="R4" s="473" t="n"/>
-      <c r="S4" s="473" t="n"/>
+      <c r="C4" s="534" t="n"/>
+      <c r="D4" s="534" t="n"/>
+      <c r="E4" s="534" t="n"/>
+      <c r="F4" s="534" t="n"/>
+      <c r="G4" s="534" t="n"/>
+      <c r="H4" s="534" t="n"/>
+      <c r="I4" s="534" t="n"/>
+      <c r="J4" s="534" t="n"/>
+      <c r="K4" s="534" t="n"/>
+      <c r="L4" s="534" t="n"/>
+      <c r="M4" s="534" t="n"/>
+      <c r="N4" s="534" t="n"/>
+      <c r="O4" s="534" t="n"/>
+      <c r="P4" s="499" t="n"/>
+      <c r="Q4" s="499" t="n"/>
+      <c r="R4" s="499" t="n"/>
+      <c r="S4" s="499" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="471" t="n"/>
-      <c r="B5" s="471" t="n"/>
-      <c r="C5" s="471" t="n"/>
-      <c r="D5" s="471" t="n"/>
-      <c r="E5" s="471" t="n"/>
-      <c r="F5" s="471" t="n"/>
-      <c r="G5" s="471" t="n"/>
-      <c r="H5" s="471" t="n"/>
-      <c r="I5" s="471" t="n"/>
-      <c r="J5" s="471" t="n"/>
-      <c r="K5" s="471" t="n"/>
-      <c r="L5" s="471" t="n"/>
-      <c r="M5" s="471" t="n"/>
-      <c r="N5" s="471" t="n"/>
-      <c r="O5" s="471" t="n"/>
-      <c r="P5" s="473" t="n"/>
-      <c r="Q5" s="473" t="n"/>
-      <c r="R5" s="473" t="n"/>
-      <c r="S5" s="473" t="n"/>
+      <c r="A5" s="534" t="n"/>
+      <c r="B5" s="534" t="n"/>
+      <c r="C5" s="534" t="n"/>
+      <c r="D5" s="534" t="n"/>
+      <c r="E5" s="534" t="n"/>
+      <c r="F5" s="534" t="n"/>
+      <c r="G5" s="534" t="n"/>
+      <c r="H5" s="534" t="n"/>
+      <c r="I5" s="534" t="n"/>
+      <c r="J5" s="534" t="n"/>
+      <c r="K5" s="534" t="n"/>
+      <c r="L5" s="534" t="n"/>
+      <c r="M5" s="534" t="n"/>
+      <c r="N5" s="534" t="n"/>
+      <c r="O5" s="534" t="n"/>
+      <c r="P5" s="499" t="n"/>
+      <c r="Q5" s="499" t="n"/>
+      <c r="R5" s="499" t="n"/>
+      <c r="S5" s="499" t="n"/>
     </row>
     <row r="6" ht="16.5" customHeight="1">
-      <c r="A6" s="475" t="inlineStr">
+      <c r="A6" s="539" t="inlineStr">
         <is>
           <t>Overview</t>
         </is>
       </c>
-      <c r="B6" s="476" t="n"/>
-      <c r="C6" s="476" t="n"/>
-      <c r="D6" s="476" t="n"/>
-      <c r="E6" s="476" t="n"/>
-      <c r="F6" s="476" t="n"/>
-      <c r="G6" s="476" t="n"/>
-      <c r="H6" s="476" t="n"/>
-      <c r="I6" s="476" t="n"/>
-      <c r="J6" s="476" t="n"/>
-      <c r="K6" s="476" t="n"/>
-      <c r="L6" s="476" t="n"/>
-      <c r="M6" s="476" t="n"/>
-      <c r="N6" s="476" t="n"/>
-      <c r="O6" s="476" t="n"/>
-      <c r="P6" s="473" t="n"/>
-      <c r="Q6" s="473" t="n"/>
-      <c r="R6" s="473" t="n"/>
-      <c r="S6" s="473" t="n"/>
+      <c r="B6" s="540" t="n"/>
+      <c r="C6" s="540" t="n"/>
+      <c r="D6" s="540" t="n"/>
+      <c r="E6" s="540" t="n"/>
+      <c r="F6" s="540" t="n"/>
+      <c r="G6" s="540" t="n"/>
+      <c r="H6" s="540" t="n"/>
+      <c r="I6" s="540" t="n"/>
+      <c r="J6" s="540" t="n"/>
+      <c r="K6" s="540" t="n"/>
+      <c r="L6" s="540" t="n"/>
+      <c r="M6" s="540" t="n"/>
+      <c r="N6" s="540" t="n"/>
+      <c r="O6" s="540" t="n"/>
+      <c r="P6" s="499" t="n"/>
+      <c r="Q6" s="499" t="n"/>
+      <c r="R6" s="499" t="n"/>
+      <c r="S6" s="499" t="n"/>
     </row>
     <row r="7" ht="223.15" customHeight="1">
-      <c r="A7" s="528" t="inlineStr">
+      <c r="A7" s="541" t="inlineStr">
         <is>
           <t>This database provides a comprehensive overview of China's national-level climate change mitigation and mitigation-relevant policy instruments currently in force. It is structured to align with the typology and data framework of the OECD's IFCMA Climate Policy Database, incorportating necessary adjustments to reflect the characteristics of China's policy instruments and to faciliate further analysis.
 Adjustments to the typology of the IFCMA Climate Policy Database
@@ -12314,101 +11986,101 @@
 - "Mitigation relevance" added in the "Policy description" block.</t>
         </is>
       </c>
-      <c r="B7" s="333" t="n"/>
-      <c r="C7" s="333" t="n"/>
-      <c r="D7" s="333" t="n"/>
-      <c r="E7" s="333" t="n"/>
-      <c r="F7" s="333" t="n"/>
-      <c r="G7" s="333" t="n"/>
-      <c r="H7" s="333" t="n"/>
-      <c r="I7" s="333" t="n"/>
-      <c r="J7" s="333" t="n"/>
-      <c r="K7" s="333" t="n"/>
-      <c r="L7" s="333" t="n"/>
-      <c r="M7" s="333" t="n"/>
-      <c r="N7" s="333" t="n"/>
-      <c r="O7" s="529" t="n"/>
-      <c r="P7" s="481" t="n"/>
-      <c r="Q7" s="473" t="n"/>
-      <c r="R7" s="473" t="n"/>
-      <c r="S7" s="473" t="n"/>
+      <c r="B7" s="339" t="n"/>
+      <c r="C7" s="339" t="n"/>
+      <c r="D7" s="339" t="n"/>
+      <c r="E7" s="339" t="n"/>
+      <c r="F7" s="339" t="n"/>
+      <c r="G7" s="339" t="n"/>
+      <c r="H7" s="339" t="n"/>
+      <c r="I7" s="339" t="n"/>
+      <c r="J7" s="339" t="n"/>
+      <c r="K7" s="339" t="n"/>
+      <c r="L7" s="339" t="n"/>
+      <c r="M7" s="339" t="n"/>
+      <c r="N7" s="339" t="n"/>
+      <c r="O7" s="340" t="n"/>
+      <c r="P7" s="459" t="n"/>
+      <c r="Q7" s="499" t="n"/>
+      <c r="R7" s="499" t="n"/>
+      <c r="S7" s="499" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="479" t="n"/>
-      <c r="B8" s="479" t="n"/>
-      <c r="C8" s="479" t="n"/>
-      <c r="D8" s="479" t="n"/>
-      <c r="E8" s="479" t="n"/>
-      <c r="F8" s="479" t="n"/>
-      <c r="G8" s="479" t="n"/>
-      <c r="H8" s="479" t="n"/>
-      <c r="I8" s="479" t="n"/>
-      <c r="J8" s="479" t="n"/>
-      <c r="K8" s="479" t="n"/>
-      <c r="L8" s="479" t="n"/>
-      <c r="M8" s="479" t="n"/>
-      <c r="N8" s="479" t="n"/>
-      <c r="O8" s="479" t="n"/>
-      <c r="P8" s="473" t="n"/>
-      <c r="Q8" s="473" t="n"/>
-      <c r="R8" s="473" t="n"/>
-      <c r="S8" s="473" t="n"/>
+      <c r="A8" s="542" t="n"/>
+      <c r="B8" s="542" t="n"/>
+      <c r="C8" s="542" t="n"/>
+      <c r="D8" s="542" t="n"/>
+      <c r="E8" s="542" t="n"/>
+      <c r="F8" s="542" t="n"/>
+      <c r="G8" s="542" t="n"/>
+      <c r="H8" s="542" t="n"/>
+      <c r="I8" s="542" t="n"/>
+      <c r="J8" s="542" t="n"/>
+      <c r="K8" s="542" t="n"/>
+      <c r="L8" s="542" t="n"/>
+      <c r="M8" s="542" t="n"/>
+      <c r="N8" s="542" t="n"/>
+      <c r="O8" s="542" t="n"/>
+      <c r="P8" s="499" t="n"/>
+      <c r="Q8" s="499" t="n"/>
+      <c r="R8" s="499" t="n"/>
+      <c r="S8" s="499" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="471" t="n"/>
-      <c r="B9" s="471" t="n"/>
-      <c r="C9" s="471" t="n"/>
-      <c r="D9" s="471" t="n"/>
-      <c r="E9" s="471" t="n"/>
-      <c r="F9" s="471" t="n"/>
-      <c r="G9" s="471" t="n"/>
-      <c r="H9" s="471" t="n"/>
-      <c r="I9" s="471" t="n"/>
-      <c r="J9" s="471" t="n"/>
-      <c r="K9" s="471" t="n"/>
-      <c r="L9" s="471" t="n"/>
-      <c r="M9" s="471" t="n"/>
-      <c r="N9" s="471" t="n"/>
-      <c r="O9" s="471" t="n"/>
-      <c r="P9" s="473" t="n"/>
-      <c r="Q9" s="473" t="n"/>
-      <c r="R9" s="473" t="n"/>
-      <c r="S9" s="473" t="n"/>
+      <c r="A9" s="534" t="n"/>
+      <c r="B9" s="534" t="n"/>
+      <c r="C9" s="534" t="n"/>
+      <c r="D9" s="534" t="n"/>
+      <c r="E9" s="534" t="n"/>
+      <c r="F9" s="534" t="n"/>
+      <c r="G9" s="534" t="n"/>
+      <c r="H9" s="534" t="n"/>
+      <c r="I9" s="534" t="n"/>
+      <c r="J9" s="534" t="n"/>
+      <c r="K9" s="534" t="n"/>
+      <c r="L9" s="534" t="n"/>
+      <c r="M9" s="534" t="n"/>
+      <c r="N9" s="534" t="n"/>
+      <c r="O9" s="534" t="n"/>
+      <c r="P9" s="499" t="n"/>
+      <c r="Q9" s="499" t="n"/>
+      <c r="R9" s="499" t="n"/>
+      <c r="S9" s="499" t="n"/>
     </row>
     <row r="10" ht="16.5" customHeight="1">
-      <c r="A10" s="475" t="inlineStr">
+      <c r="A10" s="539" t="inlineStr">
         <is>
           <t>Content of this file</t>
         </is>
       </c>
       <c r="B10" s="337" t="n"/>
-      <c r="C10" s="476" t="n"/>
-      <c r="D10" s="476" t="n"/>
-      <c r="E10" s="476" t="n"/>
-      <c r="F10" s="476" t="n"/>
-      <c r="G10" s="476" t="n"/>
-      <c r="H10" s="476" t="n"/>
-      <c r="I10" s="476" t="n"/>
-      <c r="J10" s="476" t="n"/>
-      <c r="K10" s="476" t="n"/>
-      <c r="L10" s="476" t="n"/>
-      <c r="M10" s="476" t="n"/>
-      <c r="N10" s="476" t="n"/>
-      <c r="O10" s="476" t="n"/>
-      <c r="P10" s="473" t="n"/>
-      <c r="Q10" s="473" t="n"/>
-      <c r="R10" s="473" t="n"/>
-      <c r="S10" s="473" t="n"/>
+      <c r="C10" s="540" t="n"/>
+      <c r="D10" s="540" t="n"/>
+      <c r="E10" s="540" t="n"/>
+      <c r="F10" s="540" t="n"/>
+      <c r="G10" s="540" t="n"/>
+      <c r="H10" s="540" t="n"/>
+      <c r="I10" s="540" t="n"/>
+      <c r="J10" s="540" t="n"/>
+      <c r="K10" s="540" t="n"/>
+      <c r="L10" s="540" t="n"/>
+      <c r="M10" s="540" t="n"/>
+      <c r="N10" s="540" t="n"/>
+      <c r="O10" s="540" t="n"/>
+      <c r="P10" s="499" t="n"/>
+      <c r="Q10" s="499" t="n"/>
+      <c r="R10" s="499" t="n"/>
+      <c r="S10" s="499" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="480" t="inlineStr">
+      <c r="A11" s="543" t="inlineStr">
         <is>
           <t>Spreadsheet</t>
         </is>
       </c>
       <c r="B11" s="339" t="n"/>
       <c r="C11" s="340" t="n"/>
-      <c r="D11" s="480" t="inlineStr">
+      <c r="D11" s="543" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
@@ -12424,20 +12096,20 @@
       <c r="M11" s="339" t="n"/>
       <c r="N11" s="339" t="n"/>
       <c r="O11" s="340" t="n"/>
-      <c r="P11" s="481" t="n"/>
-      <c r="Q11" s="473" t="n"/>
-      <c r="R11" s="473" t="n"/>
-      <c r="S11" s="473" t="n"/>
+      <c r="P11" s="459" t="n"/>
+      <c r="Q11" s="499" t="n"/>
+      <c r="R11" s="499" t="n"/>
+      <c r="S11" s="499" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="482" t="inlineStr">
+      <c r="A12" s="544" t="inlineStr">
         <is>
           <t>Cover</t>
         </is>
       </c>
       <c r="B12" s="339" t="n"/>
       <c r="C12" s="340" t="n"/>
-      <c r="D12" s="483" t="inlineStr">
+      <c r="D12" s="545" t="inlineStr">
         <is>
           <t>Introduces this document, presents its overall function and lists MGF Lab contact points</t>
         </is>
@@ -12453,20 +12125,20 @@
       <c r="M12" s="339" t="n"/>
       <c r="N12" s="339" t="n"/>
       <c r="O12" s="340" t="n"/>
-      <c r="P12" s="481" t="n"/>
-      <c r="Q12" s="473" t="n"/>
-      <c r="R12" s="473" t="n"/>
-      <c r="S12" s="473" t="n"/>
+      <c r="P12" s="459" t="n"/>
+      <c r="Q12" s="499" t="n"/>
+      <c r="R12" s="499" t="n"/>
+      <c r="S12" s="499" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="484" t="inlineStr">
+      <c r="A13" s="544" t="inlineStr">
         <is>
           <t>Classification framework</t>
         </is>
       </c>
       <c r="B13" s="339" t="n"/>
       <c r="C13" s="340" t="n"/>
-      <c r="D13" s="483" t="inlineStr">
+      <c r="D13" s="545" t="inlineStr">
         <is>
           <t>Explains the four-level classification framework of this dataset</t>
         </is>
@@ -12482,20 +12154,20 @@
       <c r="M13" s="339" t="n"/>
       <c r="N13" s="339" t="n"/>
       <c r="O13" s="340" t="n"/>
-      <c r="P13" s="481" t="n"/>
-      <c r="Q13" s="473" t="n"/>
-      <c r="R13" s="473" t="n"/>
-      <c r="S13" s="473" t="n"/>
+      <c r="P13" s="459" t="n"/>
+      <c r="Q13" s="499" t="n"/>
+      <c r="R13" s="499" t="n"/>
+      <c r="S13" s="499" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="482" t="inlineStr">
+      <c r="A14" s="544" t="inlineStr">
         <is>
           <t>Categories and groups</t>
         </is>
       </c>
       <c r="B14" s="339" t="n"/>
       <c r="C14" s="340" t="n"/>
-      <c r="D14" s="483" t="inlineStr">
+      <c r="D14" s="545" t="inlineStr">
         <is>
           <t>Demonstrates instrument categories and instrument groups within each category</t>
         </is>
@@ -12511,20 +12183,20 @@
       <c r="M14" s="339" t="n"/>
       <c r="N14" s="339" t="n"/>
       <c r="O14" s="340" t="n"/>
-      <c r="P14" s="481" t="n"/>
-      <c r="Q14" s="473" t="n"/>
-      <c r="R14" s="473" t="n"/>
-      <c r="S14" s="473" t="n"/>
+      <c r="P14" s="459" t="n"/>
+      <c r="Q14" s="499" t="n"/>
+      <c r="R14" s="499" t="n"/>
+      <c r="S14" s="499" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="485" t="inlineStr">
+      <c r="A15" s="546" t="inlineStr">
         <is>
           <t>Summary</t>
         </is>
       </c>
       <c r="B15" s="339" t="n"/>
       <c r="C15" s="340" t="n"/>
-      <c r="D15" s="483" t="inlineStr">
+      <c r="D15" s="545" t="inlineStr">
         <is>
           <t>Provides information on the number of policy instruments collected to date, by instrument category, group, approach, and sector covered</t>
         </is>
@@ -12540,20 +12212,20 @@
       <c r="M15" s="339" t="n"/>
       <c r="N15" s="339" t="n"/>
       <c r="O15" s="340" t="n"/>
-      <c r="P15" s="481" t="n"/>
-      <c r="Q15" s="473" t="n"/>
-      <c r="R15" s="473" t="n"/>
-      <c r="S15" s="473" t="n"/>
+      <c r="P15" s="459" t="n"/>
+      <c r="Q15" s="499" t="n"/>
+      <c r="R15" s="499" t="n"/>
+      <c r="S15" s="499" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="482" t="inlineStr">
+      <c r="A16" s="544" t="inlineStr">
         <is>
           <t>Approaches</t>
         </is>
       </c>
       <c r="B16" s="339" t="n"/>
       <c r="C16" s="340" t="n"/>
-      <c r="D16" s="483" t="inlineStr">
+      <c r="D16" s="545" t="inlineStr">
         <is>
           <t>Demonstrates instrument approaches within each group, and provides definition for each of them</t>
         </is>
@@ -12569,20 +12241,20 @@
       <c r="M16" s="339" t="n"/>
       <c r="N16" s="339" t="n"/>
       <c r="O16" s="340" t="n"/>
-      <c r="P16" s="481" t="n"/>
-      <c r="Q16" s="473" t="n"/>
-      <c r="R16" s="473" t="n"/>
-      <c r="S16" s="473" t="n"/>
+      <c r="P16" s="459" t="n"/>
+      <c r="Q16" s="499" t="n"/>
+      <c r="R16" s="499" t="n"/>
+      <c r="S16" s="499" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="482" t="inlineStr">
+      <c r="A17" s="544" t="inlineStr">
         <is>
           <t>Instruments overview</t>
         </is>
       </c>
       <c r="B17" s="339" t="n"/>
       <c r="C17" s="340" t="n"/>
-      <c r="D17" s="483" t="inlineStr">
+      <c r="D17" s="545" t="inlineStr">
         <is>
           <t>Provides a simplified summary table of all policy instruments collected to date</t>
         </is>
@@ -12598,20 +12270,20 @@
       <c r="M17" s="339" t="n"/>
       <c r="N17" s="339" t="n"/>
       <c r="O17" s="340" t="n"/>
-      <c r="P17" s="481" t="n"/>
-      <c r="Q17" s="473" t="n"/>
-      <c r="R17" s="473" t="n"/>
-      <c r="S17" s="473" t="n"/>
+      <c r="P17" s="459" t="n"/>
+      <c r="Q17" s="499" t="n"/>
+      <c r="R17" s="499" t="n"/>
+      <c r="S17" s="499" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="486" t="inlineStr">
+      <c r="A18" s="547" t="inlineStr">
         <is>
           <t>Economic instruments</t>
         </is>
       </c>
       <c r="B18" s="339" t="n"/>
       <c r="C18" s="340" t="n"/>
-      <c r="D18" s="483" t="inlineStr">
+      <c r="D18" s="545" t="inlineStr">
         <is>
           <t>Displays information for the Economic Instruments</t>
         </is>
@@ -12627,20 +12299,20 @@
       <c r="M18" s="339" t="n"/>
       <c r="N18" s="339" t="n"/>
       <c r="O18" s="340" t="n"/>
-      <c r="P18" s="481" t="n"/>
-      <c r="Q18" s="473" t="n"/>
-      <c r="R18" s="473" t="n"/>
-      <c r="S18" s="473" t="n"/>
+      <c r="P18" s="459" t="n"/>
+      <c r="Q18" s="499" t="n"/>
+      <c r="R18" s="499" t="n"/>
+      <c r="S18" s="499" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="487" t="inlineStr">
+      <c r="A19" s="548" t="inlineStr">
         <is>
           <t>Regulatory instruments</t>
         </is>
       </c>
       <c r="B19" s="339" t="n"/>
       <c r="C19" s="340" t="n"/>
-      <c r="D19" s="483" t="inlineStr">
+      <c r="D19" s="545" t="inlineStr">
         <is>
           <t>Displays information for the Regulatory Instruments</t>
         </is>
@@ -12656,20 +12328,20 @@
       <c r="M19" s="339" t="n"/>
       <c r="N19" s="339" t="n"/>
       <c r="O19" s="340" t="n"/>
-      <c r="P19" s="481" t="n"/>
-      <c r="Q19" s="473" t="n"/>
-      <c r="R19" s="473" t="n"/>
-      <c r="S19" s="473" t="n"/>
+      <c r="P19" s="459" t="n"/>
+      <c r="Q19" s="499" t="n"/>
+      <c r="R19" s="499" t="n"/>
+      <c r="S19" s="499" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="488" t="inlineStr">
+      <c r="A20" s="549" t="inlineStr">
         <is>
           <t>Government I&amp;C</t>
         </is>
       </c>
       <c r="B20" s="339" t="n"/>
       <c r="C20" s="340" t="n"/>
-      <c r="D20" s="483" t="inlineStr">
+      <c r="D20" s="545" t="inlineStr">
         <is>
           <t>Displays information for the Government Investment &amp; Consumption Instruments</t>
         </is>
@@ -12685,20 +12357,20 @@
       <c r="M20" s="339" t="n"/>
       <c r="N20" s="339" t="n"/>
       <c r="O20" s="340" t="n"/>
-      <c r="P20" s="481" t="n"/>
-      <c r="Q20" s="473" t="n"/>
-      <c r="R20" s="473" t="n"/>
-      <c r="S20" s="473" t="n"/>
+      <c r="P20" s="459" t="n"/>
+      <c r="Q20" s="499" t="n"/>
+      <c r="R20" s="499" t="n"/>
+      <c r="S20" s="499" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="489" t="inlineStr">
+      <c r="A21" s="550" t="inlineStr">
         <is>
           <t>Information instruments</t>
         </is>
       </c>
       <c r="B21" s="339" t="n"/>
       <c r="C21" s="340" t="n"/>
-      <c r="D21" s="483" t="inlineStr">
+      <c r="D21" s="545" t="inlineStr">
         <is>
           <t>Displays information for the Information Instruments</t>
         </is>
@@ -12714,20 +12386,20 @@
       <c r="M21" s="339" t="n"/>
       <c r="N21" s="339" t="n"/>
       <c r="O21" s="340" t="n"/>
-      <c r="P21" s="481" t="n"/>
-      <c r="Q21" s="473" t="n"/>
-      <c r="R21" s="473" t="n"/>
-      <c r="S21" s="473" t="n"/>
+      <c r="P21" s="459" t="n"/>
+      <c r="Q21" s="499" t="n"/>
+      <c r="R21" s="499" t="n"/>
+      <c r="S21" s="499" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="490" t="inlineStr">
+      <c r="A22" s="551" t="inlineStr">
         <is>
           <t>Voluntary approaches</t>
         </is>
       </c>
       <c r="B22" s="339" t="n"/>
       <c r="C22" s="340" t="n"/>
-      <c r="D22" s="483" t="inlineStr">
+      <c r="D22" s="545" t="inlineStr">
         <is>
           <t>Displays information for the Voluntary Approaches</t>
         </is>
@@ -12743,20 +12415,20 @@
       <c r="M22" s="339" t="n"/>
       <c r="N22" s="339" t="n"/>
       <c r="O22" s="340" t="n"/>
-      <c r="P22" s="481" t="n"/>
-      <c r="Q22" s="473" t="n"/>
-      <c r="R22" s="473" t="n"/>
-      <c r="S22" s="473" t="n"/>
+      <c r="P22" s="459" t="n"/>
+      <c r="Q22" s="499" t="n"/>
+      <c r="R22" s="499" t="n"/>
+      <c r="S22" s="499" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="482" t="inlineStr">
+      <c r="A23" s="544" t="inlineStr">
         <is>
           <t>Attributes definitions</t>
         </is>
       </c>
       <c r="B23" s="339" t="n"/>
       <c r="C23" s="340" t="n"/>
-      <c r="D23" s="483" t="inlineStr">
+      <c r="D23" s="545" t="inlineStr">
         <is>
           <t>Definitions of policy instrument attributes</t>
         </is>
@@ -12772,20 +12444,20 @@
       <c r="M23" s="339" t="n"/>
       <c r="N23" s="339" t="n"/>
       <c r="O23" s="340" t="n"/>
-      <c r="P23" s="481" t="n"/>
-      <c r="Q23" s="473" t="n"/>
-      <c r="R23" s="473" t="n"/>
-      <c r="S23" s="473" t="n"/>
+      <c r="P23" s="459" t="n"/>
+      <c r="Q23" s="499" t="n"/>
+      <c r="R23" s="499" t="n"/>
+      <c r="S23" s="499" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="491" t="inlineStr">
+      <c r="A24" s="552" t="inlineStr">
         <is>
           <t>Ended</t>
         </is>
       </c>
       <c r="B24" s="339" t="n"/>
       <c r="C24" s="340" t="n"/>
-      <c r="D24" s="483" t="inlineStr">
+      <c r="D24" s="545" t="inlineStr">
         <is>
           <t>Displays information for policy instruments that were once included in this database but have since expired or been terminated</t>
         </is>
@@ -12801,66 +12473,66 @@
       <c r="M24" s="339" t="n"/>
       <c r="N24" s="339" t="n"/>
       <c r="O24" s="340" t="n"/>
-      <c r="P24" s="481" t="n"/>
-      <c r="Q24" s="473" t="n"/>
-      <c r="R24" s="473" t="n"/>
-      <c r="S24" s="473" t="n"/>
+      <c r="P24" s="459" t="n"/>
+      <c r="Q24" s="499" t="n"/>
+      <c r="R24" s="499" t="n"/>
+      <c r="S24" s="499" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="479" t="n"/>
-      <c r="B25" s="479" t="n"/>
-      <c r="C25" s="479" t="n"/>
-      <c r="D25" s="479" t="n"/>
-      <c r="E25" s="479" t="n"/>
-      <c r="F25" s="479" t="n"/>
-      <c r="G25" s="479" t="n"/>
-      <c r="H25" s="479" t="n"/>
-      <c r="I25" s="479" t="n"/>
-      <c r="J25" s="479" t="n"/>
-      <c r="K25" s="479" t="n"/>
-      <c r="L25" s="479" t="n"/>
-      <c r="M25" s="479" t="n"/>
-      <c r="N25" s="479" t="n"/>
-      <c r="O25" s="479" t="n"/>
-      <c r="P25" s="473" t="n"/>
-      <c r="Q25" s="473" t="n"/>
-      <c r="R25" s="473" t="n"/>
-      <c r="S25" s="473" t="n"/>
+      <c r="A25" s="542" t="n"/>
+      <c r="B25" s="542" t="n"/>
+      <c r="C25" s="542" t="n"/>
+      <c r="D25" s="542" t="n"/>
+      <c r="E25" s="542" t="n"/>
+      <c r="F25" s="542" t="n"/>
+      <c r="G25" s="542" t="n"/>
+      <c r="H25" s="542" t="n"/>
+      <c r="I25" s="542" t="n"/>
+      <c r="J25" s="542" t="n"/>
+      <c r="K25" s="542" t="n"/>
+      <c r="L25" s="542" t="n"/>
+      <c r="M25" s="542" t="n"/>
+      <c r="N25" s="542" t="n"/>
+      <c r="O25" s="542" t="n"/>
+      <c r="P25" s="499" t="n"/>
+      <c r="Q25" s="499" t="n"/>
+      <c r="R25" s="499" t="n"/>
+      <c r="S25" s="499" t="n"/>
     </row>
     <row r="26" ht="16.5" customHeight="1">
-      <c r="A26" s="475" t="inlineStr">
+      <c r="A26" s="539" t="inlineStr">
         <is>
           <t>Legend</t>
         </is>
       </c>
-      <c r="B26" s="476" t="n"/>
-      <c r="C26" s="476" t="n"/>
-      <c r="D26" s="476" t="n"/>
-      <c r="E26" s="476" t="n"/>
-      <c r="F26" s="476" t="n"/>
-      <c r="G26" s="476" t="n"/>
-      <c r="H26" s="476" t="n"/>
-      <c r="I26" s="476" t="n"/>
-      <c r="J26" s="476" t="n"/>
-      <c r="K26" s="476" t="n"/>
-      <c r="L26" s="476" t="n"/>
-      <c r="M26" s="476" t="n"/>
-      <c r="N26" s="476" t="n"/>
-      <c r="O26" s="476" t="n"/>
-      <c r="P26" s="473" t="n"/>
-      <c r="Q26" s="473" t="n"/>
-      <c r="R26" s="473" t="n"/>
-      <c r="S26" s="473" t="n"/>
+      <c r="B26" s="540" t="n"/>
+      <c r="C26" s="540" t="n"/>
+      <c r="D26" s="540" t="n"/>
+      <c r="E26" s="540" t="n"/>
+      <c r="F26" s="540" t="n"/>
+      <c r="G26" s="540" t="n"/>
+      <c r="H26" s="540" t="n"/>
+      <c r="I26" s="540" t="n"/>
+      <c r="J26" s="540" t="n"/>
+      <c r="K26" s="540" t="n"/>
+      <c r="L26" s="540" t="n"/>
+      <c r="M26" s="540" t="n"/>
+      <c r="N26" s="540" t="n"/>
+      <c r="O26" s="540" t="n"/>
+      <c r="P26" s="499" t="n"/>
+      <c r="Q26" s="499" t="n"/>
+      <c r="R26" s="499" t="n"/>
+      <c r="S26" s="499" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="492" t="inlineStr">
+      <c r="A27" s="553" t="inlineStr">
         <is>
           <t>Bold text</t>
         </is>
       </c>
       <c r="B27" s="339" t="n"/>
       <c r="C27" s="340" t="n"/>
-      <c r="D27" s="493" t="inlineStr">
+      <c r="D27" s="554" t="inlineStr">
         <is>
           <t>Policy instrument</t>
         </is>
@@ -12876,20 +12548,20 @@
       <c r="M27" s="339" t="n"/>
       <c r="N27" s="339" t="n"/>
       <c r="O27" s="340" t="n"/>
-      <c r="P27" s="481" t="n"/>
-      <c r="Q27" s="473" t="n"/>
-      <c r="R27" s="473" t="n"/>
-      <c r="S27" s="473" t="n"/>
+      <c r="P27" s="459" t="n"/>
+      <c r="Q27" s="499" t="n"/>
+      <c r="R27" s="499" t="n"/>
+      <c r="S27" s="499" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="494" t="inlineStr">
+      <c r="A28" s="555" t="inlineStr">
         <is>
           <t>Unbolded text</t>
         </is>
       </c>
       <c r="B28" s="339" t="n"/>
       <c r="C28" s="340" t="n"/>
-      <c r="D28" s="483" t="inlineStr">
+      <c r="D28" s="545" t="inlineStr">
         <is>
           <t>Sub-schemes of the policy instrument</t>
         </is>
@@ -12905,145 +12577,144 @@
       <c r="M28" s="339" t="n"/>
       <c r="N28" s="339" t="n"/>
       <c r="O28" s="340" t="n"/>
-      <c r="P28" s="481" t="n"/>
-      <c r="Q28" s="473" t="n"/>
-      <c r="R28" s="473" t="n"/>
-      <c r="S28" s="473" t="n"/>
+      <c r="P28" s="459" t="n"/>
+      <c r="Q28" s="499" t="n"/>
+      <c r="R28" s="499" t="n"/>
+      <c r="S28" s="499" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="479" t="n"/>
-      <c r="B29" s="479" t="n"/>
-      <c r="C29" s="479" t="n"/>
-      <c r="D29" s="479" t="n"/>
-      <c r="E29" s="479" t="n"/>
-      <c r="F29" s="479" t="n"/>
-      <c r="G29" s="479" t="n"/>
-      <c r="H29" s="479" t="n"/>
-      <c r="I29" s="479" t="n"/>
-      <c r="J29" s="479" t="n"/>
-      <c r="K29" s="479" t="n"/>
-      <c r="L29" s="479" t="n"/>
-      <c r="M29" s="479" t="n"/>
-      <c r="N29" s="479" t="n"/>
-      <c r="O29" s="479" t="n"/>
-      <c r="P29" s="473" t="n"/>
-      <c r="Q29" s="473" t="n"/>
-      <c r="R29" s="473" t="n"/>
-      <c r="S29" s="473" t="n"/>
+      <c r="A29" s="542" t="n"/>
+      <c r="B29" s="542" t="n"/>
+      <c r="C29" s="542" t="n"/>
+      <c r="D29" s="542" t="n"/>
+      <c r="E29" s="542" t="n"/>
+      <c r="F29" s="542" t="n"/>
+      <c r="G29" s="542" t="n"/>
+      <c r="H29" s="542" t="n"/>
+      <c r="I29" s="542" t="n"/>
+      <c r="J29" s="542" t="n"/>
+      <c r="K29" s="542" t="n"/>
+      <c r="L29" s="542" t="n"/>
+      <c r="M29" s="542" t="n"/>
+      <c r="N29" s="542" t="n"/>
+      <c r="O29" s="542" t="n"/>
+      <c r="P29" s="499" t="n"/>
+      <c r="Q29" s="499" t="n"/>
+      <c r="R29" s="499" t="n"/>
+      <c r="S29" s="499" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="471" t="n"/>
-      <c r="B30" s="471" t="n"/>
-      <c r="C30" s="471" t="n"/>
-      <c r="D30" s="471" t="n"/>
-      <c r="E30" s="471" t="n"/>
-      <c r="F30" s="471" t="n"/>
-      <c r="G30" s="471" t="n"/>
-      <c r="H30" s="471" t="n"/>
-      <c r="I30" s="471" t="n"/>
-      <c r="J30" s="471" t="n"/>
-      <c r="K30" s="471" t="n"/>
-      <c r="L30" s="471" t="n"/>
-      <c r="M30" s="471" t="n"/>
-      <c r="N30" s="471" t="n"/>
-      <c r="O30" s="471" t="n"/>
-      <c r="P30" s="473" t="n"/>
-      <c r="Q30" s="473" t="n"/>
-      <c r="R30" s="473" t="n"/>
-      <c r="S30" s="473" t="n"/>
+      <c r="A30" s="534" t="n"/>
+      <c r="B30" s="534" t="n"/>
+      <c r="C30" s="534" t="n"/>
+      <c r="D30" s="534" t="n"/>
+      <c r="E30" s="534" t="n"/>
+      <c r="F30" s="534" t="n"/>
+      <c r="G30" s="534" t="n"/>
+      <c r="H30" s="534" t="n"/>
+      <c r="I30" s="534" t="n"/>
+      <c r="J30" s="534" t="n"/>
+      <c r="K30" s="534" t="n"/>
+      <c r="L30" s="534" t="n"/>
+      <c r="M30" s="534" t="n"/>
+      <c r="N30" s="534" t="n"/>
+      <c r="O30" s="534" t="n"/>
+      <c r="P30" s="499" t="n"/>
+      <c r="Q30" s="499" t="n"/>
+      <c r="R30" s="499" t="n"/>
+      <c r="S30" s="499" t="n"/>
     </row>
     <row r="31" ht="16.5" customHeight="1">
-      <c r="A31" s="495" t="inlineStr">
+      <c r="A31" s="556" t="inlineStr">
         <is>
           <t>MGF Lab contact</t>
         </is>
       </c>
       <c r="B31" s="110" t="n"/>
-      <c r="C31" s="471" t="n"/>
-      <c r="D31" s="471" t="n"/>
-      <c r="E31" s="471" t="n"/>
-      <c r="F31" s="471" t="n"/>
-      <c r="G31" s="471" t="n"/>
-      <c r="H31" s="471" t="n"/>
-      <c r="I31" s="471" t="n"/>
-      <c r="J31" s="471" t="n"/>
-      <c r="K31" s="471" t="n"/>
-      <c r="L31" s="471" t="n"/>
-      <c r="M31" s="471" t="n"/>
-      <c r="N31" s="471" t="n"/>
-      <c r="O31" s="471" t="n"/>
-      <c r="P31" s="473" t="n"/>
-      <c r="Q31" s="473" t="n"/>
-      <c r="R31" s="473" t="n"/>
-      <c r="S31" s="473" t="n"/>
+      <c r="C31" s="534" t="n"/>
+      <c r="D31" s="534" t="n"/>
+      <c r="E31" s="534" t="n"/>
+      <c r="F31" s="534" t="n"/>
+      <c r="G31" s="534" t="n"/>
+      <c r="H31" s="534" t="n"/>
+      <c r="I31" s="534" t="n"/>
+      <c r="J31" s="534" t="n"/>
+      <c r="K31" s="534" t="n"/>
+      <c r="L31" s="534" t="n"/>
+      <c r="M31" s="534" t="n"/>
+      <c r="N31" s="534" t="n"/>
+      <c r="O31" s="534" t="n"/>
+      <c r="P31" s="499" t="n"/>
+      <c r="Q31" s="499" t="n"/>
+      <c r="R31" s="499" t="n"/>
+      <c r="S31" s="499" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="496" t="inlineStr">
+      <c r="A32" s="556" t="inlineStr">
         <is>
           <t>Danqing Shao</t>
         </is>
       </c>
-      <c r="B32" s="497" t="inlineStr">
+      <c r="B32" s="557" t="inlineStr">
         <is>
           <t>dqshao@nsd.pku.edu.cn</t>
         </is>
       </c>
       <c r="C32" s="110" t="n"/>
-      <c r="D32" s="471" t="n"/>
-      <c r="E32" s="471" t="n"/>
-      <c r="F32" s="471" t="n"/>
-      <c r="G32" s="471" t="n"/>
-      <c r="H32" s="471" t="n"/>
-      <c r="I32" s="471" t="n"/>
-      <c r="J32" s="471" t="n"/>
-      <c r="K32" s="471" t="n"/>
-      <c r="L32" s="471" t="n"/>
-      <c r="M32" s="471" t="n"/>
-      <c r="N32" s="471" t="n"/>
-      <c r="O32" s="471" t="n"/>
-      <c r="P32" s="473" t="n"/>
-      <c r="Q32" s="473" t="n"/>
-      <c r="R32" s="473" t="n"/>
-      <c r="S32" s="473" t="n"/>
+      <c r="D32" s="534" t="n"/>
+      <c r="E32" s="534" t="n"/>
+      <c r="F32" s="534" t="n"/>
+      <c r="G32" s="534" t="n"/>
+      <c r="H32" s="534" t="n"/>
+      <c r="I32" s="534" t="n"/>
+      <c r="J32" s="534" t="n"/>
+      <c r="K32" s="534" t="n"/>
+      <c r="L32" s="534" t="n"/>
+      <c r="M32" s="534" t="n"/>
+      <c r="N32" s="534" t="n"/>
+      <c r="O32" s="534" t="n"/>
+      <c r="P32" s="499" t="n"/>
+      <c r="Q32" s="499" t="n"/>
+      <c r="R32" s="499" t="n"/>
+      <c r="S32" s="499" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="496" t="inlineStr">
+      <c r="A33" s="556" t="inlineStr">
         <is>
           <t>Xiaobei He</t>
         </is>
       </c>
-      <c r="B33" s="497" t="inlineStr">
+      <c r="B33" s="557" t="inlineStr">
         <is>
           <t>xbhe@nsd.pku.edu.cn</t>
         </is>
       </c>
       <c r="C33" s="110" t="n"/>
-      <c r="D33" s="471" t="n"/>
-      <c r="E33" s="471" t="n"/>
-      <c r="F33" s="471" t="n"/>
-      <c r="G33" s="471" t="n"/>
-      <c r="H33" s="471" t="n"/>
-      <c r="I33" s="471" t="n"/>
-      <c r="J33" s="471" t="n"/>
-      <c r="K33" s="471" t="n"/>
-      <c r="L33" s="471" t="n"/>
-      <c r="M33" s="471" t="n"/>
-      <c r="N33" s="471" t="n"/>
-      <c r="O33" s="471" t="n"/>
-      <c r="P33" s="473" t="n"/>
-      <c r="Q33" s="473" t="n"/>
-      <c r="R33" s="473" t="n"/>
-      <c r="S33" s="473" t="n"/>
+      <c r="D33" s="534" t="n"/>
+      <c r="E33" s="534" t="n"/>
+      <c r="F33" s="534" t="n"/>
+      <c r="G33" s="534" t="n"/>
+      <c r="H33" s="534" t="n"/>
+      <c r="I33" s="534" t="n"/>
+      <c r="J33" s="534" t="n"/>
+      <c r="K33" s="534" t="n"/>
+      <c r="L33" s="534" t="n"/>
+      <c r="M33" s="534" t="n"/>
+      <c r="N33" s="534" t="n"/>
+      <c r="O33" s="534" t="n"/>
+      <c r="P33" s="499" t="n"/>
+      <c r="Q33" s="499" t="n"/>
+      <c r="R33" s="499" t="n"/>
+      <c r="S33" s="499" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="40">
+  <mergeCells count="39">
     <mergeCell ref="A7:O7"/>
+    <mergeCell ref="D11:O11"/>
     <mergeCell ref="D13:O13"/>
-    <mergeCell ref="D11:O11"/>
     <mergeCell ref="D27:O27"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="A27:C27"/>
-    <mergeCell ref="A3:C3"/>
     <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A12:C12"/>
@@ -13058,11 +12729,10 @@
     <mergeCell ref="A20:C20"/>
     <mergeCell ref="D12:O12"/>
     <mergeCell ref="A28:C28"/>
+    <mergeCell ref="A19:C19"/>
     <mergeCell ref="D24:O24"/>
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D15:O15"/>
-    <mergeCell ref="A16:C16"/>
     <mergeCell ref="D23:O23"/>
     <mergeCell ref="D14:O14"/>
     <mergeCell ref="A15:C15"/>
@@ -13075,10 +12745,366 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="D22:O22"/>
     <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D21:O21"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="D21:O21"/>
+    <mergeCell ref="A16:C16"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AW2"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="13.9"/>
+  <sheetData>
+    <row r="1" ht="15.75" customHeight="1">
+      <c r="A1" s="387" t="inlineStr">
+        <is>
+          <t>Identification</t>
+        </is>
+      </c>
+      <c r="B1" s="93" t="n"/>
+      <c r="C1" s="424" t="inlineStr">
+        <is>
+          <t>Instrument typology</t>
+        </is>
+      </c>
+      <c r="D1" s="100" t="n"/>
+      <c r="E1" s="100" t="n"/>
+      <c r="F1" s="101" t="n"/>
+      <c r="G1" s="425" t="inlineStr">
+        <is>
+          <t>Policy Description</t>
+        </is>
+      </c>
+      <c r="H1" s="100" t="n"/>
+      <c r="I1" s="100" t="n"/>
+      <c r="J1" s="100" t="n"/>
+      <c r="K1" s="100" t="n"/>
+      <c r="L1" s="100" t="n"/>
+      <c r="M1" s="426" t="inlineStr">
+        <is>
+          <t>Administrative information</t>
+        </is>
+      </c>
+      <c r="N1" s="100" t="n"/>
+      <c r="O1" s="100" t="n"/>
+      <c r="P1" s="100" t="n"/>
+      <c r="Q1" s="100" t="n"/>
+      <c r="R1" s="100" t="n"/>
+      <c r="S1" s="100" t="n"/>
+      <c r="T1" s="100" t="n"/>
+      <c r="U1" s="100" t="n"/>
+      <c r="V1" s="427" t="inlineStr">
+        <is>
+          <t>Policy regulatory base and intensity</t>
+        </is>
+      </c>
+      <c r="W1" s="100" t="n"/>
+      <c r="X1" s="100" t="n"/>
+      <c r="Y1" s="100" t="n"/>
+      <c r="Z1" s="100" t="n"/>
+      <c r="AA1" s="100" t="n"/>
+      <c r="AB1" s="100" t="n"/>
+      <c r="AC1" s="100" t="n"/>
+      <c r="AD1" s="100" t="n"/>
+      <c r="AE1" s="100" t="n"/>
+      <c r="AF1" s="100" t="n"/>
+      <c r="AG1" s="100" t="n"/>
+      <c r="AH1" s="100" t="n"/>
+      <c r="AI1" s="100" t="n"/>
+      <c r="AJ1" s="100" t="n"/>
+      <c r="AK1" s="393" t="inlineStr">
+        <is>
+          <t>Instrument-specific attributes</t>
+        </is>
+      </c>
+      <c r="AL1" s="100" t="n"/>
+      <c r="AM1" s="100" t="n"/>
+      <c r="AN1" s="428" t="inlineStr">
+        <is>
+          <t>GHG emission base</t>
+        </is>
+      </c>
+      <c r="AO1" s="101" t="n"/>
+      <c r="AP1" s="395" t="inlineStr">
+        <is>
+          <t>Classifications &amp; Indicators</t>
+        </is>
+      </c>
+      <c r="AQ1" s="100" t="n"/>
+      <c r="AR1" s="100" t="n"/>
+      <c r="AS1" s="100" t="n"/>
+      <c r="AT1" s="426" t="inlineStr">
+        <is>
+          <t>References to legislation</t>
+        </is>
+      </c>
+      <c r="AU1" s="100" t="n"/>
+      <c r="AV1" s="100" t="n"/>
+      <c r="AW1" s="429" t="n"/>
+    </row>
+    <row r="2" ht="15.75" customHeight="1">
+      <c r="A2" s="398" t="inlineStr">
+        <is>
+          <t>Policy Instrument ID</t>
+        </is>
+      </c>
+      <c r="B2" s="398" t="inlineStr">
+        <is>
+          <t>Instrument / subscheme</t>
+        </is>
+      </c>
+      <c r="C2" s="399" t="inlineStr">
+        <is>
+          <t>Group</t>
+        </is>
+      </c>
+      <c r="D2" s="399" t="inlineStr">
+        <is>
+          <t>Approach</t>
+        </is>
+      </c>
+      <c r="E2" s="399" t="inlineStr">
+        <is>
+          <t>Emission sector</t>
+        </is>
+      </c>
+      <c r="F2" s="399" t="inlineStr">
+        <is>
+          <t>Sub-sector</t>
+        </is>
+      </c>
+      <c r="G2" s="400" t="inlineStr">
+        <is>
+          <t>Domestic instrument name</t>
+        </is>
+      </c>
+      <c r="H2" s="400" t="inlineStr">
+        <is>
+          <t>English instrument name</t>
+        </is>
+      </c>
+      <c r="I2" s="400" t="inlineStr">
+        <is>
+          <t>Policy Package</t>
+        </is>
+      </c>
+      <c r="J2" s="400" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="K2" s="400" t="inlineStr">
+        <is>
+          <t>Objective</t>
+        </is>
+      </c>
+      <c r="L2" s="400" t="inlineStr">
+        <is>
+          <t>Mitigation relevance</t>
+        </is>
+      </c>
+      <c r="M2" s="401" t="inlineStr">
+        <is>
+          <t>Jurisdiction level</t>
+        </is>
+      </c>
+      <c r="N2" s="401" t="inlineStr">
+        <is>
+          <t>Jurisdiction name</t>
+        </is>
+      </c>
+      <c r="O2" s="401" t="inlineStr">
+        <is>
+          <t>Adoption date</t>
+        </is>
+      </c>
+      <c r="P2" s="401" t="inlineStr">
+        <is>
+          <t>Start date</t>
+        </is>
+      </c>
+      <c r="Q2" s="401" t="inlineStr">
+        <is>
+          <t>End date</t>
+        </is>
+      </c>
+      <c r="R2" s="401" t="inlineStr">
+        <is>
+          <t>Last revisions</t>
+        </is>
+      </c>
+      <c r="S2" s="401" t="inlineStr">
+        <is>
+          <t>Last revisions (Details)</t>
+        </is>
+      </c>
+      <c r="T2" s="401" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="U2" s="401" t="inlineStr">
+        <is>
+          <t>Administrating authorities</t>
+        </is>
+      </c>
+      <c r="V2" s="402" t="inlineStr">
+        <is>
+          <t>Asset</t>
+        </is>
+      </c>
+      <c r="W2" s="402" t="inlineStr">
+        <is>
+          <t>Asset (Status)</t>
+        </is>
+      </c>
+      <c r="X2" s="402" t="inlineStr">
+        <is>
+          <t>Asset (Details)</t>
+        </is>
+      </c>
+      <c r="Y2" s="402" t="inlineStr">
+        <is>
+          <t>Asset (Other)</t>
+        </is>
+      </c>
+      <c r="Z2" s="402" t="inlineStr">
+        <is>
+          <t>Asset (Cut-off range)</t>
+        </is>
+      </c>
+      <c r="AA2" s="402" t="inlineStr">
+        <is>
+          <t>Agent</t>
+        </is>
+      </c>
+      <c r="AB2" s="402" t="inlineStr">
+        <is>
+          <t>Agent (Detail)</t>
+        </is>
+      </c>
+      <c r="AC2" s="402" t="inlineStr">
+        <is>
+          <t>Activity</t>
+        </is>
+      </c>
+      <c r="AD2" s="402" t="inlineStr">
+        <is>
+          <t>Activity (Details)</t>
+        </is>
+      </c>
+      <c r="AE2" s="402" t="inlineStr">
+        <is>
+          <t>Intensity (Value)</t>
+        </is>
+      </c>
+      <c r="AF2" s="402" t="inlineStr">
+        <is>
+          <t>Intensity (Unit)</t>
+        </is>
+      </c>
+      <c r="AG2" s="402" t="inlineStr">
+        <is>
+          <t>Intensity (Details)</t>
+        </is>
+      </c>
+      <c r="AH2" s="402" t="inlineStr">
+        <is>
+          <t>Requirement specification</t>
+        </is>
+      </c>
+      <c r="AI2" s="402" t="inlineStr">
+        <is>
+          <t>Compliance calculation methodology I</t>
+        </is>
+      </c>
+      <c r="AJ2" s="402" t="inlineStr">
+        <is>
+          <t>Compliance calculation methodology II</t>
+        </is>
+      </c>
+      <c r="AK2" s="400" t="inlineStr">
+        <is>
+          <t>Incentives for Participation</t>
+        </is>
+      </c>
+      <c r="AL2" s="400" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="AM2" s="400" t="inlineStr">
+        <is>
+          <t>Sanctions for non-compliance</t>
+        </is>
+      </c>
+      <c r="AN2" s="404" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (absolute)</t>
+        </is>
+      </c>
+      <c r="AO2" s="404" t="inlineStr">
+        <is>
+          <t>GHG emission coverage (% domestic emissions)</t>
+        </is>
+      </c>
+      <c r="AP2" s="399" t="inlineStr">
+        <is>
+          <t>Economic sector</t>
+        </is>
+      </c>
+      <c r="AQ2" s="399" t="inlineStr">
+        <is>
+          <t>GHGs affected</t>
+        </is>
+      </c>
+      <c r="AR2" s="399" t="inlineStr">
+        <is>
+          <t>Mitigation effect</t>
+        </is>
+      </c>
+      <c r="AS2" s="399" t="inlineStr">
+        <is>
+          <t>Mitigation co-benefits</t>
+        </is>
+      </c>
+      <c r="AT2" s="401" t="inlineStr">
+        <is>
+          <t>Legal statute</t>
+        </is>
+      </c>
+      <c r="AU2" s="401" t="inlineStr">
+        <is>
+          <t>Legal document</t>
+        </is>
+      </c>
+      <c r="AV2" s="401" t="inlineStr">
+        <is>
+          <t>Other weblinks</t>
+        </is>
+      </c>
+      <c r="AW2" s="406" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="AK1:AM1"/>
+    <mergeCell ref="V1:AJ1"/>
+    <mergeCell ref="AT1:AV1"/>
+    <mergeCell ref="AN1:AO1"/>
+    <mergeCell ref="M1:U1"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="AP1:AS1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 

--- a/inputs/template_en.xlsx
+++ b/inputs/template_en.xlsx
@@ -6196,7 +6196,7 @@
       </c>
       <c r="E12" s="449" t="inlineStr">
         <is>
-          <t>Climate change mitigation; Non-fossil energy; Energy efficiency; Green economy; Technological innovation; Energy security; Pollution control; Ecological protection; Circular economy; Adaptation; Green finance; Electrification; Industrial development; Green consumption; Information disclosure; Public awareness; Ozone layer protection</t>
+          <t>Climate change mitigation; Non-fossil energy; Energy efficiency; Green economy; Technological innovation; Energy security; Pollution control; Ecological protection; Biodiversity protection; Natural resource protection; Circular economy; Climate change adaptation; Green finance; Electrification; Industrial development; Green consumption; Information disclosure; Public awareness; Ozone layer protection</t>
         </is>
       </c>
       <c r="F12" s="459" t="n"/>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="E46" s="449" t="inlineStr">
         <is>
-          <t>Adaptation; Air pollution; Energy supply security; Technological innovation; Poverty reduction; Employment; Industrial development; Other (non-exhaustive list, current options here based on IPCC)</t>
+          <t>Energy conservation; Technological innovation; Energy security; Pollution control; Ecological protection; Resource conservation; Circular economy; Renewable energy development; Public health; Climate change adaptation; Employment and poverty reduction; Industrial development; Biodiversity conservation; Desertification control; Green consumption; Food security</t>
         </is>
       </c>
       <c r="F46" s="459" t="n"/>
